--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -440,19 +440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J359"/>
+  <dimension ref="A1:J360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="87" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-086</t>
+          <t>BT-031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18.56</v>
+        <v>14.34</v>
       </c>
       <c r="H4" t="n">
-        <v>21.34</v>
+        <v>16.49</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -639,14 +639,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -664,11 +664,15 @@
           <t>Peyton Manning Signed Jersey</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>150</v>
-      </c>
-      <c r="F5" t="n">
-        <v>350</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G5" t="n">
         <v>18.56</v>
@@ -690,7 +694,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-082</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -700,7 +704,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>books / skip</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -738,7 +742,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-083</t>
+          <t>BT-082</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -756,17 +760,21 @@
           <t>Michael Jordan Signed Hat</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>250</v>
-      </c>
-      <c r="F7" t="n">
-        <v>600</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G7" t="n">
-        <v>22.78</v>
+        <v>18.56</v>
       </c>
       <c r="H7" t="n">
-        <v>26.2</v>
+        <v>21.34</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -775,14 +783,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-025</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -792,7 +800,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,17 +808,21 @@
           <t>Dan Marino signed Photo</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" t="n">
-        <v>250</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G8" t="n">
-        <v>25.31</v>
+        <v>20.25</v>
       </c>
       <c r="H8" t="n">
-        <v>29.11</v>
+        <v>23.29</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -819,14 +831,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>low-mid $75 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-012</t>
+          <t>BT-071</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -836,7 +848,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -844,17 +856,21 @@
           <t>Rusty Wallace signed helmet</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>80</v>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>27.84</v>
+        <v>20.25</v>
       </c>
       <c r="H9" t="n">
-        <v>32.02</v>
+        <v>23.29</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -863,14 +879,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-020</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,7 +896,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -888,17 +904,21 @@
           <t>Joe DiMaggio signed hat</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" t="n">
-        <v>500</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" t="n">
-        <v>27.84</v>
+        <v>20.25</v>
       </c>
       <c r="H10" t="n">
-        <v>32.02</v>
+        <v>23.29</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -907,14 +927,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -924,7 +944,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -932,17 +952,21 @@
           <t>Joe Flacco signed jersey</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" t="n">
-        <v>150</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G11" t="n">
-        <v>27.84</v>
+        <v>20.25</v>
       </c>
       <c r="H11" t="n">
-        <v>32.02</v>
+        <v>23.29</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -951,14 +975,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT-111</t>
+          <t>BT-083</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -987,10 +1011,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27.84</v>
+        <v>22.78</v>
       </c>
       <c r="H12" t="n">
-        <v>32.02</v>
+        <v>26.2</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -999,14 +1023,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BT-113</t>
+          <t>BT-025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,7 +1040,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1024,17 +1048,21 @@
           <t>baseballs</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>75</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>27.84</v>
+        <v>25.31</v>
       </c>
       <c r="H13" t="n">
-        <v>32.02</v>
+        <v>29.11</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1043,14 +1071,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $75 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BT-032</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,7 +1088,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1068,17 +1096,21 @@
           <t>sports collectibles</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F14" t="n">
-        <v>120</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G14" t="n">
-        <v>30.38</v>
+        <v>27.84</v>
       </c>
       <c r="H14" t="n">
-        <v>34.94</v>
+        <v>32.02</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1087,14 +1119,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>low-mid $90 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BT-057</t>
+          <t>BT-032</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1138,7 +1170,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BT-118</t>
+          <t>BT-162</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1182,7 +1214,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BT-124</t>
+          <t>BT-026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1211,26 +1243,26 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30.38</v>
+        <v>37.12</v>
       </c>
       <c r="H17" t="n">
-        <v>34.94</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>42.69</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>low-mid $90 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BT-162</t>
+          <t>BT-455</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1259,26 +1291,26 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>30.38</v>
+        <v>37.12</v>
       </c>
       <c r="H18" t="n">
-        <v>34.94</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>42.69</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>low-mid $90 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BT-008</t>
+          <t>BT-066</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1303,10 +1335,10 @@
         <v>180</v>
       </c>
       <c r="G19" t="n">
-        <v>37.12</v>
+        <v>47.25</v>
       </c>
       <c r="H19" t="n">
-        <v>42.69</v>
+        <v>54.34</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -1315,14 +1347,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $140 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BT-023</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1347,10 +1379,10 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>37.12</v>
+        <v>54</v>
       </c>
       <c r="H20" t="n">
-        <v>42.69</v>
+        <v>62.1</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -1359,14 +1391,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $160 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BT-026</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1395,10 +1427,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>37.12</v>
+        <v>71.72</v>
       </c>
       <c r="H21" t="n">
-        <v>42.69</v>
+        <v>82.48</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -1407,14 +1439,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BT-455</t>
+          <t>BT-284</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1424,7 +1456,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,17 +1464,21 @@
           <t>Reggie Bush signed jersey</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>80</v>
-      </c>
-      <c r="F22" t="n">
-        <v>200</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>37.12</v>
+        <v>71.72</v>
       </c>
       <c r="H22" t="n">
-        <v>42.69</v>
+        <v>82.48</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -1451,19 +1487,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BT-007</t>
+          <t>BT-081</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1487,31 +1523,31 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>46.41</v>
+        <v>12.66</v>
       </c>
       <c r="H23" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>14.56</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>low-mid $138 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $38 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BT-073</t>
+          <t>BT-017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1531,31 +1567,31 @@
         <v>150</v>
       </c>
       <c r="G24" t="n">
-        <v>46.41</v>
+        <v>14.34</v>
       </c>
       <c r="H24" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>16.49</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>low-mid $138 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BT-075</t>
+          <t>BT-117</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1575,31 +1611,31 @@
         <v>200</v>
       </c>
       <c r="G25" t="n">
-        <v>46.41</v>
+        <v>15.19</v>
       </c>
       <c r="H25" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>17.47</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>low-mid $138 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BT-078</t>
+          <t>BT-163</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1623,31 +1659,31 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>46.41</v>
+        <v>15.19</v>
       </c>
       <c r="H26" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>17.47</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>low-mid $138 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BT-080</t>
+          <t>BT-165</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1671,36 +1707,36 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>46.41</v>
+        <v>15.19</v>
       </c>
       <c r="H27" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>17.47</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>low-mid $138 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BT-066</t>
+          <t>BT-167</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>breweriana / sports bar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1715,31 +1751,31 @@
         <v>80</v>
       </c>
       <c r="G28" t="n">
-        <v>47.25</v>
+        <v>15.19</v>
       </c>
       <c r="H28" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>17.47</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>low-mid $140 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-016</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1759,36 +1795,36 @@
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>54</v>
+        <v>16.03</v>
       </c>
       <c r="H29" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>18.43</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>low-mid $160 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BT-004</t>
+          <t>BT-030</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>breweriana</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1796,42 +1832,38 @@
           <t>beer pitchers</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" t="n">
+        <v>80</v>
       </c>
       <c r="G30" t="n">
-        <v>67.5</v>
+        <v>16.03</v>
       </c>
       <c r="H30" t="n">
-        <v>77.62</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>18.43</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>low-mid $200 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-101</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1851,31 +1883,31 @@
         <v>180</v>
       </c>
       <c r="G31" t="n">
-        <v>71.72</v>
+        <v>16.03</v>
       </c>
       <c r="H31" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>18.43</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BT-284</t>
+          <t>BT-322</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1899,31 +1931,31 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>71.72</v>
+        <v>16.03</v>
       </c>
       <c r="H32" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>18.43</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BT-010</t>
+          <t>BT-335</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1947,36 +1979,36 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>92.81</v>
+        <v>16.03</v>
       </c>
       <c r="H33" t="n">
-        <v>106.73</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>18.43</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>low-mid $275 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BT-006</t>
+          <t>BT-020</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ephemera</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1984,33 +2016,37 @@
           <t>Playboy magazines</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>40</v>
-      </c>
-      <c r="F34" t="n">
-        <v>120</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G34" t="n">
-        <v>113.91</v>
+        <v>27.84</v>
       </c>
       <c r="H34" t="n">
-        <v>131</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>32.02</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>low-mid $338 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BT-014</t>
+          <t>BT-111</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2039,26 +2075,26 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12.66</v>
+        <v>27.84</v>
       </c>
       <c r="H35" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>32.02</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>low-mid $38 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BT-081</t>
+          <t>BT-113</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2087,31 +2123,31 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>12.66</v>
+        <v>27.84</v>
       </c>
       <c r="H36" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>32.02</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>low-mid $38 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BT-331</t>
+          <t>BT-003</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2134,32 +2170,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="H37" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>low-mid $38 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BT-017</t>
+          <t>BT-004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2178,37 +2218,41 @@
       <c r="F38" t="n">
         <v>220</v>
       </c>
-      <c r="G38" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="H38" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BT-117</t>
+          <t>BT-005</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>modern office / skip</t>
+          <t>modern tech / skip</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2226,32 +2270,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H39" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BT-163</t>
+          <t>BT-006</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2274,32 +2322,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H40" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BT-165</t>
+          <t>BT-007</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2322,32 +2374,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H41" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BT-167</t>
+          <t>BT-008</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2370,37 +2426,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H42" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-010</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>modern utility / skip</t>
+          <t>modern tech / skip</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,32 +2478,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H43" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-012</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2462,32 +2526,36 @@
       <c r="F44" t="n">
         <v>100</v>
       </c>
-      <c r="G44" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H44" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BT-101</t>
+          <t>BT-013</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2510,32 +2578,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H45" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BT-322</t>
+          <t>BT-014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2554,32 +2626,36 @@
       <c r="F46" t="n">
         <v>150</v>
       </c>
-      <c r="G46" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H46" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BT-335</t>
+          <t>BT-015</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2602,32 +2678,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H47" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-018</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2650,32 +2730,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H48" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BT-015</t>
+          <t>BT-019</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2698,32 +2782,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H49" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BT-035</t>
+          <t>BT-022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2746,37 +2834,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H50" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BT-071</t>
+          <t>BT-023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2784,38 +2876,46 @@
           <t>signed sports photos</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>60</v>
-      </c>
-      <c r="F51" t="n">
-        <v>180</v>
-      </c>
-      <c r="G51" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H51" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2838,32 +2938,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H52" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-027</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2886,32 +2990,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H53" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BT-404</t>
+          <t>BT-028</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2934,27 +3042,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H54" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BT-003</t>
+          <t>BT-033</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3006,7 +3118,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BT-005</t>
+          <t>BT-034</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3058,7 +3170,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BT-013</t>
+          <t>BT-035</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3106,7 +3218,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BT-018</t>
+          <t>BT-037</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3151,14 +3263,14 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BT-019</t>
+          <t>BT-038</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3210,7 +3322,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BT-022</t>
+          <t>BT-040</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3262,7 +3374,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BT-024</t>
+          <t>BT-042</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3303,14 +3415,14 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BT-027</t>
+          <t>BT-043</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3320,7 +3432,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dinnerware / pottery</t>
+          <t>dishes / skip</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3328,11 +3440,15 @@
           <t>Poppy Trail dishes</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>100</v>
-      </c>
-      <c r="F62" t="n">
-        <v>250</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3358,7 +3474,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BT-028</t>
+          <t>BT-044</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3368,7 +3484,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dinnerware / pottery</t>
+          <t>dishes / skip</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3376,11 +3492,15 @@
           <t>Poppy Trail dishes</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>100</v>
-      </c>
-      <c r="F63" t="n">
-        <v>250</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3406,7 +3526,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BT-031</t>
+          <t>BT-045</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3416,7 +3536,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dinnerware / pottery</t>
+          <t>dishes / skip</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3424,11 +3544,15 @@
           <t>Poppy Trail dishes</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>100</v>
-      </c>
-      <c r="F64" t="n">
-        <v>250</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3454,7 +3578,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BT-033</t>
+          <t>BT-046</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3464,7 +3588,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>dinnerware / pottery</t>
+          <t>dishes / skip</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3472,11 +3596,15 @@
           <t>Poppy Trail dishes</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>100</v>
-      </c>
-      <c r="F65" t="n">
-        <v>250</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3495,14 +3623,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BT-034</t>
+          <t>BT-049</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3512,19 +3640,23 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ephemera</t>
+          <t>dishes / skip</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>matchbooks</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>25</v>
-      </c>
-      <c r="F66" t="n">
-        <v>75</v>
+          <t>Poppy Trail dishes</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3550,7 +3682,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BT-037</t>
+          <t>BT-051</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3560,19 +3692,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>ephemera</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>mini Coca-Cola bottles</t>
+          <t>matchbooks</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3598,7 +3730,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BT-038</t>
+          <t>BT-053</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3608,19 +3740,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>vintage tools</t>
+          <t>advertising</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>toolbox</t>
+          <t>mini Coca-Cola bottles</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3646,7 +3778,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BT-040</t>
+          <t>BT-054</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3661,14 +3793,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>wrenches</t>
+          <t>toolbox</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F69" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3694,7 +3826,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BT-042</t>
+          <t>BT-056</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3704,19 +3836,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage tools</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>costume jewelry</t>
+          <t>wrenches</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F70" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3735,14 +3867,14 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>fit 0.10 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BT-043</t>
+          <t>BT-057</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3752,23 +3884,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>stamp collection</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>costume jewelry</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>40</v>
+      </c>
+      <c r="F71" t="n">
+        <v>120</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3787,14 +3915,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BT-044</t>
+          <t>BT-059</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3809,7 +3937,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mlay skin care</t>
+          <t>stamp collection</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3846,7 +3974,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BT-045</t>
+          <t>BT-061</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3861,7 +3989,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rock collection</t>
+          <t>Mlay skin care</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3898,7 +4026,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BT-046</t>
+          <t>BT-062</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3913,7 +4041,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ilight skin care</t>
+          <t>rock collection</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3943,14 +4071,14 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>fit 0.10 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BT-049</t>
+          <t>BT-063</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3965,7 +4093,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pontiac care kit</t>
+          <t>Ilight skin care</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4002,7 +4130,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BT-051</t>
+          <t>BT-064</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4017,7 +4145,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>stamp album</t>
+          <t>Pontiac care kit</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4054,7 +4182,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BT-053</t>
+          <t>BT-067</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4069,7 +4197,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>foreign coin collection</t>
+          <t>stamp album</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4106,7 +4234,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BT-054</t>
+          <t>BT-068</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4121,7 +4249,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bulls collectibles</t>
+          <t>foreign coin collection</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4158,7 +4286,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BT-056</t>
+          <t>BT-070</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4173,7 +4301,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #98)</t>
+          <t>Bulls collectibles</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4210,7 +4338,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BT-059</t>
+          <t>BT-073</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4225,7 +4353,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>White Sox collectibles</t>
+          <t>Uncaptioned lot (Photo #98)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4255,14 +4383,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BT-061</t>
+          <t>BT-075</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4272,19 +4400,23 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>trading cards</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>30</v>
-      </c>
-      <c r="F81" t="n">
-        <v>100</v>
+          <t>White Sox collectibles</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4303,14 +4435,14 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BT-062</t>
+          <t>BT-076</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4320,23 +4452,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1994 World Series Ball</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>trading cards</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>30</v>
+      </c>
+      <c r="F82" t="n">
+        <v>100</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4355,14 +4483,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BT-063</t>
+          <t>BT-078</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4377,7 +4505,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Don Mattingly signed ball</t>
+          <t>1994 World Series Ball</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4407,14 +4535,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BT-064</t>
+          <t>BT-080</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4429,7 +4557,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Billy Martin signed ball</t>
+          <t>Don Mattingly signed ball</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4459,14 +4587,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BT-067</t>
+          <t>BT-088</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4481,7 +4609,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Greg Maddux</t>
+          <t>Billy Martin signed ball</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4518,7 +4646,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BT-068</t>
+          <t>BT-089</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4533,7 +4661,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bud Selig</t>
+          <t>Greg Maddux</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4570,7 +4698,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BT-070</t>
+          <t>BT-091</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4585,7 +4713,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Nintendo Game Boy games</t>
+          <t>Bud Selig</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4622,7 +4750,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BT-088</t>
+          <t>BT-092</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4632,19 +4760,23 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>baseball cards</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>50</v>
-      </c>
-      <c r="F88" t="n">
-        <v>180</v>
+          <t>Nintendo Game Boy games</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4670,7 +4802,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BT-089</t>
+          <t>BT-093</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4685,7 +4817,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>vintage baseball cards</t>
+          <t>baseball cards</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -4718,7 +4850,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BT-091</t>
+          <t>BT-094</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4728,23 +4860,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1970 proof set</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>vintage baseball cards</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" t="n">
+        <v>180</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4770,7 +4898,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BT-092</t>
+          <t>BT-095</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4780,19 +4908,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>sports bobble heads</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>30</v>
-      </c>
-      <c r="F91" t="n">
-        <v>90</v>
+          <t>1970 proof set</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4818,7 +4950,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BT-093</t>
+          <t>BT-096</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4828,19 +4960,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>collectibles</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>signed sports photos</t>
+          <t>sports bobble heads</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F92" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4866,7 +4998,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BT-094</t>
+          <t>BT-098</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4876,12 +5008,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #120)</t>
+          <t>signed sports photos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4918,7 +5050,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BT-095</t>
+          <t>BT-099</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4933,7 +5065,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #121)</t>
+          <t>Uncaptioned lot (Photo #120)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4970,7 +5102,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BT-096</t>
+          <t>BT-102</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4985,7 +5117,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #122)</t>
+          <t>Uncaptioned lot (Photo #121)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5022,7 +5154,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BT-098</t>
+          <t>BT-103</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5037,7 +5169,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #123)</t>
+          <t>Uncaptioned lot (Photo #122)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5074,7 +5206,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BT-099</t>
+          <t>BT-105</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5084,19 +5216,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>signed sports photos</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>60</v>
-      </c>
-      <c r="F97" t="n">
-        <v>180</v>
+          <t>Uncaptioned lot (Photo #123)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5122,7 +5258,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BT-102</t>
+          <t>BT-107</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5132,12 +5268,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>cracker Jack mini cards</t>
+          <t>signed sports photos</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5174,7 +5310,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BT-103</t>
+          <t>BT-108</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5189,7 +5325,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>cut autographs</t>
+          <t>cracker Jack mini cards</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5226,7 +5362,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BT-105</t>
+          <t>BT-110</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5241,7 +5377,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>roberto Clemente bat</t>
+          <t>cut autographs</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5278,7 +5414,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BT-107</t>
+          <t>BT-115</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5293,7 +5429,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Frank Thomas signed photo</t>
+          <t>roberto Clemente bat</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5330,7 +5466,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BT-108</t>
+          <t>BT-118</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5345,7 +5481,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #132)</t>
+          <t>Frank Thomas signed photo</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5375,14 +5511,14 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BT-110</t>
+          <t>BT-120</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5397,7 +5533,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #133)</t>
+          <t>Uncaptioned lot (Photo #132)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5434,7 +5570,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BT-115</t>
+          <t>BT-121</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5449,7 +5585,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #134)</t>
+          <t>Uncaptioned lot (Photo #133)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5486,7 +5622,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BT-120</t>
+          <t>BT-122</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5501,7 +5637,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>factory baseball sets</t>
+          <t>Uncaptioned lot (Photo #134)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5538,7 +5674,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BT-121</t>
+          <t>BT-123</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5553,7 +5689,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>squuish mellows</t>
+          <t>factory baseball sets</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5590,7 +5726,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BT-122</t>
+          <t>BT-124</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5605,7 +5741,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>animal trap</t>
+          <t>squuish mellows</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5635,14 +5771,14 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BT-123</t>
+          <t>BT-125</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5657,7 +5793,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>wringer</t>
+          <t>animal trap</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5694,7 +5830,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BT-125</t>
+          <t>BT-127</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5709,7 +5845,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>skittles game</t>
+          <t>wringer</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5746,7 +5882,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BT-127</t>
+          <t>BT-128</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5761,7 +5897,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>New shower head</t>
+          <t>skittles game</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5798,7 +5934,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BT-128</t>
+          <t>BT-130</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5813,7 +5949,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tarzan movie display</t>
+          <t>New shower head</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5850,7 +5986,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BT-130</t>
+          <t>BT-132</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5865,7 +6001,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Madame Alexander doll</t>
+          <t>Tarzan movie display</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5902,7 +6038,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BT-132</t>
+          <t>BT-133</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5917,7 +6053,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Fisher Price toys</t>
+          <t>Madame Alexander doll</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5954,7 +6090,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BT-133</t>
+          <t>BT-134</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5969,7 +6105,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Snack Sets</t>
+          <t>Fisher Price toys</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6006,7 +6142,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BT-134</t>
+          <t>BT-135</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6021,7 +6157,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #146)</t>
+          <t>Snack Sets</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6058,7 +6194,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BT-135</t>
+          <t>BT-136</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6073,7 +6209,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #147)</t>
+          <t>Uncaptioned lot (Photo #146)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6110,7 +6246,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BT-136</t>
+          <t>BT-137</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6125,7 +6261,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #148)</t>
+          <t>Uncaptioned lot (Photo #147)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6162,7 +6298,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BT-137</t>
+          <t>BT-138</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6177,7 +6313,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Fiesta Ware dishes</t>
+          <t>Uncaptioned lot (Photo #148)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6214,7 +6350,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BT-138</t>
+          <t>BT-139</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6229,7 +6365,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fry cutter</t>
+          <t>Fiesta Ware dishes</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6266,7 +6402,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BT-139</t>
+          <t>BT-140</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6281,7 +6417,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>coffee grinder</t>
+          <t>Fry cutter</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6318,7 +6454,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BT-140</t>
+          <t>BT-141</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6333,7 +6469,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Pyrex bowl</t>
+          <t>coffee grinder</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6370,7 +6506,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BT-141</t>
+          <t>BT-142</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6385,7 +6521,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Yashica</t>
+          <t>Pyrex bowl</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6422,7 +6558,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BT-142</t>
+          <t>BT-143</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6437,7 +6573,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>necklace</t>
+          <t>Yashica</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6474,7 +6610,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BT-143</t>
+          <t>BT-144</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6489,7 +6625,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>punch bowl mugs</t>
+          <t>necklace</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6526,7 +6662,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BT-144</t>
+          <t>BT-146</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6541,7 +6677,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Lego building blocks</t>
+          <t>punch bowl mugs</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6578,7 +6714,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BT-146</t>
+          <t>BT-147</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6593,7 +6729,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Polaroid camera</t>
+          <t>Lego building blocks</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6630,7 +6766,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BT-147</t>
+          <t>BT-148</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6640,19 +6776,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tonka crane</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>60</v>
-      </c>
-      <c r="F127" t="n">
-        <v>180</v>
+          <t>Polaroid camera</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6678,7 +6818,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BT-148</t>
+          <t>BT-149</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6688,19 +6828,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>bobble heads</t>
+          <t>Tonka crane</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F128" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6726,7 +6866,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BT-149</t>
+          <t>BT-150</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6774,7 +6914,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BT-150</t>
+          <t>BT-152</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6822,7 +6962,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BT-152</t>
+          <t>BT-154</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6832,23 +6972,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>collectibles</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Bob Ross bobble head</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>bobble heads</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>30</v>
+      </c>
+      <c r="F131" t="n">
+        <v>90</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -6874,7 +7010,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BT-154</t>
+          <t>BT-155</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6889,7 +7025,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wahl pens</t>
+          <t>Bob Ross bobble head</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6926,7 +7062,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BT-155</t>
+          <t>BT-156</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6941,7 +7077,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>antique flatware</t>
+          <t>Wahl pens</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6978,7 +7114,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BT-156</t>
+          <t>BT-158</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6993,7 +7129,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>steak knives</t>
+          <t>antique flatware</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7030,7 +7166,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BT-158</t>
+          <t>BT-159</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7045,7 +7181,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>the Beatles magazine</t>
+          <t>steak knives</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7082,7 +7218,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BT-159</t>
+          <t>BT-161</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7097,7 +7233,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>UNCLE magazine</t>
+          <t>the Beatles magazine</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7134,7 +7270,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BT-161</t>
+          <t>BT-168</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7149,7 +7285,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>vintage Pens &amp;amp; pencils</t>
+          <t>UNCLE magazine</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7186,7 +7322,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BT-168</t>
+          <t>BT-170</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7201,7 +7337,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>watches</t>
+          <t>vintage Pens &amp;amp; pencils</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7238,7 +7374,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BT-170</t>
+          <t>BT-171</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7253,7 +7389,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>vintage wrist watches</t>
+          <t>watches</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7290,7 +7426,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BT-171</t>
+          <t>BT-172</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7305,7 +7441,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>necklaces</t>
+          <t>vintage wrist watches</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7342,7 +7478,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BT-172</t>
+          <t>BT-174</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7352,19 +7488,23 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>estate costume jewelry</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>40</v>
-      </c>
-      <c r="F141" t="n">
-        <v>120</v>
+          <t>necklaces</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7390,7 +7530,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BT-174</t>
+          <t>BT-175</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7400,23 +7540,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #183)</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>estate costume jewelry</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>40</v>
+      </c>
+      <c r="F142" t="n">
+        <v>120</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7442,7 +7578,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BT-175</t>
+          <t>BT-176</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7457,7 +7593,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wonder Woman shield</t>
+          <t>Uncaptioned lot (Photo #183)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7494,7 +7630,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BT-176</t>
+          <t>BT-177</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7509,7 +7645,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>hummingbird window</t>
+          <t>Wonder Woman shield</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7546,7 +7682,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BT-177</t>
+          <t>BT-178</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7561,7 +7697,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>sports pennnats</t>
+          <t>hummingbird window</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7598,7 +7734,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BT-178</t>
+          <t>BT-179</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7613,7 +7749,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Pink Floyd concert poster</t>
+          <t>sports pennnats</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7650,7 +7786,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BT-179</t>
+          <t>BT-183</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7665,7 +7801,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Jurassic Park 3-D panels</t>
+          <t>Pink Floyd concert poster</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7702,7 +7838,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BT-183</t>
+          <t>BT-184</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7717,7 +7853,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Canada Dry trays</t>
+          <t>Jurassic Park 3-D panels</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7754,7 +7890,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BT-184</t>
+          <t>BT-185</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7769,7 +7905,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>signed Packers poster</t>
+          <t>Canada Dry trays</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7806,7 +7942,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BT-185</t>
+          <t>BT-187</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7821,7 +7957,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Safety score board</t>
+          <t>signed Packers poster</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7858,7 +7994,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BT-187</t>
+          <t>BT-189</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7873,7 +8009,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #195)</t>
+          <t>Safety score board</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7910,7 +8046,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BT-189</t>
+          <t>BT-190</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7925,7 +8061,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Packers plaques</t>
+          <t>Uncaptioned lot (Photo #195)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7962,7 +8098,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BT-190</t>
+          <t>BT-191</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7977,7 +8113,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #198)</t>
+          <t>Packers plaques</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8014,7 +8150,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BT-191</t>
+          <t>BT-192</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8029,7 +8165,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #199)</t>
+          <t>Uncaptioned lot (Photo #198)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8066,7 +8202,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BT-192</t>
+          <t>BT-193</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8081,7 +8217,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Ronnie Harper signed photo</t>
+          <t>Uncaptioned lot (Photo #199)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8118,7 +8254,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BT-193</t>
+          <t>BT-195</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8133,7 +8269,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Ryne Sandberg signed photo</t>
+          <t>Ronnie Harper signed photo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8170,7 +8306,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BT-195</t>
+          <t>BT-196</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8185,7 +8321,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Planters Peanuts display</t>
+          <t>Ryne Sandberg signed photo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8222,7 +8358,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BT-196</t>
+          <t>BT-198</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8237,7 +8373,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #205)</t>
+          <t>Planters Peanuts display</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8274,7 +8410,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BT-198</t>
+          <t>BT-199</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8289,7 +8425,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>framed beaded purse</t>
+          <t>Uncaptioned lot (Photo #205)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8326,7 +8462,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BT-199</t>
+          <t>BT-200</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8378,7 +8514,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BT-200</t>
+          <t>BT-201</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8393,7 +8529,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mattel store displays</t>
+          <t>framed beaded purse</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8430,7 +8566,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BT-201</t>
+          <t>BT-203</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8445,7 +8581,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Boyscout sign</t>
+          <t>Mattel store displays</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8482,7 +8618,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BT-203</t>
+          <t>BT-205</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8497,7 +8633,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>baseball display case</t>
+          <t>Boyscout sign</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8534,7 +8670,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BT-205</t>
+          <t>BT-206</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8549,7 +8685,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Star Wars posters</t>
+          <t>baseball display case</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8586,7 +8722,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BT-206</t>
+          <t>BT-208</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8601,7 +8737,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lion walking stick</t>
+          <t>Star Wars posters</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8638,7 +8774,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BT-208</t>
+          <t>BT-209</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8653,7 +8789,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>display case</t>
+          <t>Lion walking stick</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8690,7 +8826,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BT-209</t>
+          <t>BT-210</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8705,7 +8841,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Bob Hope record set</t>
+          <t>display case</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8742,7 +8878,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BT-210</t>
+          <t>BT-212</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8757,7 +8893,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>trench coat</t>
+          <t>Bob Hope record set</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8794,7 +8930,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BT-212</t>
+          <t>BT-213</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8809,7 +8945,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>sports books</t>
+          <t>trench coat</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8846,7 +8982,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BT-213</t>
+          <t>BT-215</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8861,7 +8997,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Simpsons poster</t>
+          <t>sports books</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8898,7 +9034,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BT-215</t>
+          <t>BT-216</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8913,7 +9049,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Firestone outboard motor</t>
+          <t>Simpsons poster</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8950,7 +9086,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BT-216</t>
+          <t>BT-217</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8965,7 +9101,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>gear chest</t>
+          <t>Firestone outboard motor</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9002,7 +9138,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BT-217</t>
+          <t>BT-218</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9017,7 +9153,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>hockey gear</t>
+          <t>gear chest</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9054,7 +9190,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BT-218</t>
+          <t>BT-220</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9069,7 +9205,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Ken Griffey Jr Nike poster</t>
+          <t>hockey gear</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9106,7 +9242,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BT-220</t>
+          <t>BT-222</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9121,7 +9257,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Angel figures</t>
+          <t>Ken Griffey Jr Nike poster</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9158,7 +9294,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BT-222</t>
+          <t>BT-223</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9173,7 +9309,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #229)</t>
+          <t>Angel figures</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9210,7 +9346,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BT-223</t>
+          <t>BT-224</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9225,7 +9361,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>art glass paper weights</t>
+          <t>Uncaptioned lot (Photo #229)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9262,7 +9398,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BT-224</t>
+          <t>BT-225</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9277,7 +9413,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>pottery</t>
+          <t>art glass paper weights</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9314,7 +9450,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BT-225</t>
+          <t>BT-226</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9329,7 +9465,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ball jars</t>
+          <t>pottery</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9366,7 +9502,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BT-226</t>
+          <t>BT-227</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9381,7 +9517,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>RC car</t>
+          <t>ball jars</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -9418,7 +9554,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BT-227</t>
+          <t>BT-229</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9433,7 +9569,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>mini nutcrackes</t>
+          <t>RC car</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9470,7 +9606,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BT-229</t>
+          <t>BT-230</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9485,7 +9621,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Century Progress bottle</t>
+          <t>mini nutcrackes</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9522,7 +9658,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BT-230</t>
+          <t>BT-231</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9537,7 +9673,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>glass bowl</t>
+          <t>Century Progress bottle</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9574,7 +9710,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BT-231</t>
+          <t>BT-232</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9589,7 +9725,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>military uniforms</t>
+          <t>glass bowl</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9626,7 +9762,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BT-232</t>
+          <t>BT-233</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9641,7 +9777,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>sports wall plaques</t>
+          <t>military uniforms</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9678,7 +9814,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BT-233</t>
+          <t>BT-234</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9693,7 +9829,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Funko Pop figs</t>
+          <t>sports wall plaques</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9730,7 +9866,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BT-234</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9745,7 +9881,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>New curved monitor</t>
+          <t>Funko Pop figs</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9782,7 +9918,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-236</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9797,7 +9933,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>glass Christmas ornaments</t>
+          <t>New curved monitor</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9834,7 +9970,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BT-236</t>
+          <t>BT-238</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9849,7 +9985,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Snoopy comic</t>
+          <t>glass Christmas ornaments</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9886,7 +10022,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BT-238</t>
+          <t>BT-239</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9901,7 +10037,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>brass horn</t>
+          <t>Snoopy comic</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9938,7 +10074,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>BT-239</t>
+          <t>BT-240</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9953,7 +10089,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Batman wallet</t>
+          <t>brass horn</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9990,7 +10126,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BT-240</t>
+          <t>BT-241</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10005,7 +10141,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Scottie dog glass set</t>
+          <t>Batman wallet</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10042,7 +10178,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BT-241</t>
+          <t>BT-242</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10057,7 +10193,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Schlitz hat</t>
+          <t>Scottie dog glass set</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10094,7 +10230,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BT-242</t>
+          <t>BT-243</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10109,7 +10245,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Circus collectibles</t>
+          <t>Schlitz hat</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -10146,7 +10282,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BT-243</t>
+          <t>BT-244</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10161,7 +10297,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #250)</t>
+          <t>Circus collectibles</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -10198,7 +10334,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BT-244</t>
+          <t>BT-245</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10213,7 +10349,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Coca-Cola collectibles</t>
+          <t>Uncaptioned lot (Photo #250)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10250,7 +10386,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BT-245</t>
+          <t>BT-246</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10265,7 +10401,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #253)</t>
+          <t>Coca-Cola collectibles</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10302,7 +10438,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BT-246</t>
+          <t>BT-247</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10317,7 +10453,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Lite Brite</t>
+          <t>Uncaptioned lot (Photo #253)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10354,7 +10490,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>BT-247</t>
+          <t>BT-248</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10369,7 +10505,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>dog figures</t>
+          <t>Lite Brite</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -10406,7 +10542,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BT-248</t>
+          <t>BT-250</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10421,7 +10557,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>new Barbie doll</t>
+          <t>dog figures</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -10458,7 +10594,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BT-250</t>
+          <t>BT-251</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10473,7 +10609,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NASCAR collectibles</t>
+          <t>new Barbie doll</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10510,7 +10646,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BT-251</t>
+          <t>BT-253</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10525,7 +10661,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>boxing headlines</t>
+          <t>NASCAR collectibles</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -10562,7 +10698,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BT-253</t>
+          <t>BT-254</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10577,7 +10713,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>sports shoes</t>
+          <t>boxing headlines</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10614,7 +10750,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BT-254</t>
+          <t>BT-255</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10629,7 +10765,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>sports apparel</t>
+          <t>sports shoes</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10666,7 +10802,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BT-255</t>
+          <t>BT-256</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10681,7 +10817,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #263)</t>
+          <t>sports apparel</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10718,7 +10854,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BT-256</t>
+          <t>BT-257</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -10733,7 +10869,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>sports ephemera</t>
+          <t>Uncaptioned lot (Photo #263)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -10770,7 +10906,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BT-257</t>
+          <t>BT-259</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -10785,7 +10921,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>circus programs</t>
+          <t>sports ephemera</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10822,7 +10958,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BT-259</t>
+          <t>BT-260</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -10837,7 +10973,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>catchers gear</t>
+          <t>circus programs</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10874,7 +11010,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BT-260</t>
+          <t>BT-261</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -10889,7 +11025,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Pope John Paul records</t>
+          <t>catchers gear</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10926,7 +11062,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BT-261</t>
+          <t>BT-263</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -10941,7 +11077,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>stamp collection</t>
+          <t>Pope John Paul records</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10978,7 +11114,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BT-263</t>
+          <t>BT-264</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -10993,7 +11129,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Brewers collectibles</t>
+          <t>stamp collection</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11030,7 +11166,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BT-264</t>
+          <t>BT-265</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11045,7 +11181,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>sports autographs</t>
+          <t>Brewers collectibles</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11082,7 +11218,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BT-265</t>
+          <t>BT-266</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11097,7 +11233,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Budweiser egg can</t>
+          <t>sports autographs</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11134,7 +11270,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BT-266</t>
+          <t>BT-268</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11149,7 +11285,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>coffee cans</t>
+          <t>Budweiser egg can</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -11186,7 +11322,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BT-268</t>
+          <t>BT-269</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11201,7 +11337,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Ernie Banks signed T-shirt</t>
+          <t>coffee cans</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11238,7 +11374,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BT-269</t>
+          <t>BT-270</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11253,7 +11389,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>smalls</t>
+          <t>Ernie Banks signed T-shirt</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11290,7 +11426,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BT-270</t>
+          <t>BT-271</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11305,7 +11441,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>stereo optic cards</t>
+          <t>smalls</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11342,7 +11478,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BT-271</t>
+          <t>BT-273</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11357,7 +11493,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Coca-Cola bank</t>
+          <t>stereo optic cards</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -11394,7 +11530,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BT-273</t>
+          <t>BT-274</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11409,7 +11545,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #282)</t>
+          <t>Coca-Cola bank</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11446,7 +11582,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BT-274</t>
+          <t>BT-275</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11461,7 +11597,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #283)</t>
+          <t>Uncaptioned lot (Photo #282)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -11498,7 +11634,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BT-275</t>
+          <t>BT-276</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11508,19 +11644,23 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>vintage topps baseball cards</t>
-        </is>
-      </c>
-      <c r="E221" t="n">
-        <v>150</v>
-      </c>
-      <c r="F221" t="n">
-        <v>400</v>
+          <t>Uncaptioned lot (Photo #283)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -11546,7 +11686,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BT-276</t>
+          <t>BT-278</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11556,23 +11696,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>vintage Topps football cards</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>vintage topps baseball cards</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>150</v>
+      </c>
+      <c r="F222" t="n">
+        <v>400</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -11598,7 +11734,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BT-278</t>
+          <t>BT-280</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11613,7 +11749,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #287)</t>
+          <t>vintage Topps football cards</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11650,7 +11786,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BT-280</t>
+          <t>BT-282</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11665,7 +11801,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #288)</t>
+          <t>Uncaptioned lot (Photo #287)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11702,7 +11838,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BT-282</t>
+          <t>BT-283</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11717,7 +11853,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #289)</t>
+          <t>Uncaptioned lot (Photo #288)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11754,7 +11890,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BT-283</t>
+          <t>BT-285</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11769,7 +11905,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #290)</t>
+          <t>Uncaptioned lot (Photo #289)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -11806,7 +11942,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BT-285</t>
+          <t>BT-287</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11821,7 +11957,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #291)</t>
+          <t>Uncaptioned lot (Photo #290)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11858,7 +11994,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BT-287</t>
+          <t>BT-288</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11873,7 +12009,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #292)</t>
+          <t>Uncaptioned lot (Photo #291)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -11910,7 +12046,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BT-288</t>
+          <t>BT-289</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11925,7 +12061,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #293)</t>
+          <t>Uncaptioned lot (Photo #292)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -11962,7 +12098,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BT-289</t>
+          <t>BT-290</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11977,7 +12113,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #294)</t>
+          <t>Uncaptioned lot (Photo #293)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -12014,7 +12150,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BT-290</t>
+          <t>BT-291</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12029,7 +12165,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #295)</t>
+          <t>Uncaptioned lot (Photo #294)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -12066,7 +12202,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BT-291</t>
+          <t>BT-292</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12081,7 +12217,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #296)</t>
+          <t>Uncaptioned lot (Photo #295)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12118,7 +12254,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>BT-292</t>
+          <t>BT-293</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12133,7 +12269,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #297)</t>
+          <t>Uncaptioned lot (Photo #296)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12170,7 +12306,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BT-293</t>
+          <t>BT-294</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12185,7 +12321,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>new German silver rings</t>
+          <t>Uncaptioned lot (Photo #297)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12222,7 +12358,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BT-294</t>
+          <t>BT-295</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12237,7 +12373,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>new necklaces</t>
+          <t>new German silver rings</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -12274,7 +12410,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>BT-295</t>
+          <t>BT-296</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12289,7 +12425,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Bears Jersey</t>
+          <t>new necklaces</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -12326,7 +12462,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BT-296</t>
+          <t>BT-297</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12341,7 +12477,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Packers / Bears program</t>
+          <t>Bears Jersey</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -12378,7 +12514,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BT-297</t>
+          <t>BT-298</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12393,7 +12529,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>display cases</t>
+          <t>Packers / Bears program</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -12430,7 +12566,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BT-298</t>
+          <t>BT-300</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12445,7 +12581,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #305)</t>
+          <t>display cases</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -12482,7 +12618,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>BT-300</t>
+          <t>BT-301</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12497,7 +12633,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Shure microphone</t>
+          <t>Uncaptioned lot (Photo #305)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -12534,7 +12670,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>BT-301</t>
+          <t>BT-302</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12549,7 +12685,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Jenkins signed jersey</t>
+          <t>Shure microphone</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12586,7 +12722,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>BT-302</t>
+          <t>BT-303</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12601,7 +12737,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>hand tools</t>
+          <t>Jenkins signed jersey</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -12638,7 +12774,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BT-303</t>
+          <t>BT-305</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12653,7 +12789,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>fruit plaques</t>
+          <t>hand tools</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12690,7 +12826,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BT-305</t>
+          <t>BT-306</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12705,7 +12841,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>sewing supplies</t>
+          <t>fruit plaques</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -12742,7 +12878,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BT-306</t>
+          <t>BT-308</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12757,7 +12893,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>children's records</t>
+          <t>sewing supplies</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12794,7 +12930,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BT-308</t>
+          <t>BT-310</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12809,7 +12945,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>movie projectors</t>
+          <t>children's records</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -12846,7 +12982,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BT-310</t>
+          <t>BT-311</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12861,7 +12997,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>linens</t>
+          <t>movie projectors</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -12898,7 +13034,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BT-311</t>
+          <t>BT-312</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12913,7 +13049,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Moon walk headline</t>
+          <t>linens</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -12950,7 +13086,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BT-312</t>
+          <t>BT-313</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12965,7 +13101,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>paintball gun</t>
+          <t>Moon walk headline</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -13002,7 +13138,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BT-313</t>
+          <t>BT-315</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13012,19 +13148,23 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>game used trading cards</t>
-        </is>
-      </c>
-      <c r="E250" t="n">
-        <v>30</v>
-      </c>
-      <c r="F250" t="n">
-        <v>100</v>
+          <t>paintball gun</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -13050,7 +13190,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>BT-315</t>
+          <t>BT-317</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13060,23 +13200,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Kodak camera</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>game used trading cards</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>30</v>
+      </c>
+      <c r="F251" t="n">
+        <v>100</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -13102,7 +13238,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BT-317</t>
+          <t>BT-318</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13117,7 +13253,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Van Briggle ashtray</t>
+          <t>Kodak camera</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -13154,7 +13290,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BT-318</t>
+          <t>BT-320</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13169,7 +13305,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NASCAR cars</t>
+          <t>Van Briggle ashtray</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -13206,7 +13342,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BT-320</t>
+          <t>BT-323</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13221,7 +13357,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>new slot car track</t>
+          <t>NASCAR cars</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -13258,7 +13394,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BT-323</t>
+          <t>BT-324</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13273,7 +13409,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>bottle toppers</t>
+          <t>new slot car track</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -13310,7 +13446,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BT-324</t>
+          <t>BT-325</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13325,7 +13461,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>vintage book set</t>
+          <t>bottle toppers</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -13362,7 +13498,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BT-325</t>
+          <t>BT-327</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13377,7 +13513,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>wooden puzzle</t>
+          <t>vintage book set</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -13414,7 +13550,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BT-327</t>
+          <t>BT-328</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13424,19 +13560,23 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>signed baseballs</t>
-        </is>
-      </c>
-      <c r="E258" t="n">
-        <v>25</v>
-      </c>
-      <c r="F258" t="n">
-        <v>75</v>
+          <t>wooden puzzle</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -13462,7 +13602,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BT-328</t>
+          <t>BT-329</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13477,7 +13617,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>dietz lantern</t>
+          <t>signed baseballs</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -13514,7 +13654,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>BT-329</t>
+          <t>BT-330</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13529,7 +13669,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Ammo</t>
+          <t>dietz lantern</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -13566,7 +13706,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BT-330</t>
+          <t>BT-331</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13576,19 +13716,23 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>sports trading cards</t>
-        </is>
-      </c>
-      <c r="E261" t="n">
-        <v>30</v>
-      </c>
-      <c r="F261" t="n">
-        <v>100</v>
+          <t>Ammo</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -13624,23 +13768,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>belt buckles</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>sports trading cards</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>30</v>
+      </c>
+      <c r="F262" t="n">
+        <v>100</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -13681,7 +13821,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>vintage lighters</t>
+          <t>belt buckles</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -13733,7 +13873,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>new wrist watch</t>
+          <t>vintage lighters</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -13785,7 +13925,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #340)</t>
+          <t>new wrist watch</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -13837,7 +13977,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Morgan dollar pocket watch</t>
+          <t>Uncaptioned lot (Photo #340)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -13889,7 +14029,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Jim Beam decanters</t>
+          <t>Morgan dollar pocket watch</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -13941,7 +14081,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Louis L'Amour books</t>
+          <t>Jim Beam decanters</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -13993,7 +14133,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Tractor diecast</t>
+          <t>Louis L'Amour books</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -14045,7 +14185,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>gas pump pocket knives</t>
+          <t>Tractor diecast</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -14097,7 +14237,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #347)</t>
+          <t>gas pump pocket knives</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -14149,7 +14289,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #348)</t>
+          <t>Uncaptioned lot (Photo #347)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -14201,7 +14341,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Budweiser belt buckles</t>
+          <t>Uncaptioned lot (Photo #348)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -14253,7 +14393,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Royal typewriter</t>
+          <t>Budweiser belt buckles</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -14305,7 +14445,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Cuckoo Clock</t>
+          <t>Royal typewriter</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -14357,7 +14497,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>comic books</t>
+          <t>Cuckoo Clock</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -14409,7 +14549,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Pong video game system</t>
+          <t>comic books</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14461,7 +14601,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Harley Davidson pocket watches</t>
+          <t>Pong video game system</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -14513,7 +14653,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>John Wayne collectibles</t>
+          <t>Harley Davidson pocket watches</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -14565,7 +14705,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Thomas Kinkade train set</t>
+          <t>John Wayne collectibles</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -14617,7 +14757,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Gone with Wind dolls</t>
+          <t>Thomas Kinkade train set</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -14669,7 +14809,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Ali signed gloves</t>
+          <t>Gone with Wind dolls</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -14721,7 +14861,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>replica Packers rings</t>
+          <t>Ali signed gloves</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -14773,7 +14913,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>vintage Babe Ruth postcards</t>
+          <t>replica Packers rings</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -14825,7 +14965,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #365)</t>
+          <t>vintage Babe Ruth postcards</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -14877,7 +15017,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Mickey Mouse Zippo lighter</t>
+          <t>Uncaptioned lot (Photo #365)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -14929,7 +15069,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #368)</t>
+          <t>Mickey Mouse Zippo lighter</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -14981,7 +15121,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #369)</t>
+          <t>Uncaptioned lot (Photo #368)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -15033,7 +15173,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #370)</t>
+          <t>Uncaptioned lot (Photo #369)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -15085,7 +15225,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Vans jacket</t>
+          <t>Uncaptioned lot (Photo #370)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15137,7 +15277,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>sports cards</t>
+          <t>Vans jacket</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15189,7 +15329,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>gaming cards</t>
+          <t>sports cards</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15241,7 +15381,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Garbage Pail Kids cards</t>
+          <t>gaming cards</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15293,7 +15433,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #378)</t>
+          <t>Garbage Pail Kids cards</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -15345,7 +15485,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>GI Joe action figures</t>
+          <t>Uncaptioned lot (Photo #378)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -15397,7 +15537,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>antique postcards</t>
+          <t>GI Joe action figures</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15449,7 +15589,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #383)</t>
+          <t>antique postcards</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -15501,7 +15641,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #384)</t>
+          <t>Uncaptioned lot (Photo #383)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -15553,7 +15693,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Hot Wheels Gear Box</t>
+          <t>Uncaptioned lot (Photo #384)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -15605,7 +15745,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Rte 66 plaque</t>
+          <t>Hot Wheels Gear Box</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -15657,7 +15797,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Daisy bb gun</t>
+          <t>Rte 66 plaque</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -15709,7 +15849,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>Daisy bb gun</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -15761,7 +15901,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Zorro toy weapons</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -15813,7 +15953,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>toys</t>
+          <t>Zorro toy weapons</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -15865,7 +16005,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Barbie dolls</t>
+          <t>toys</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -15917,7 +16057,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #397)</t>
+          <t>Barbie dolls</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -15969,7 +16109,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #398)</t>
+          <t>Uncaptioned lot (Photo #397)</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16021,7 +16161,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>cap guns</t>
+          <t>Uncaptioned lot (Photo #398)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16073,7 +16213,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Novelity gifts</t>
+          <t>cap guns</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16125,7 +16265,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #402)</t>
+          <t>Novelity gifts</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16177,7 +16317,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #403)</t>
+          <t>Uncaptioned lot (Photo #402)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16224,19 +16364,23 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>sports memorabilia</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>sports collectibles</t>
-        </is>
-      </c>
-      <c r="E312" t="n">
-        <v>40</v>
-      </c>
-      <c r="F312" t="n">
-        <v>120</v>
+          <t>Uncaptioned lot (Photo #403)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -16277,7 +16421,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>N scale train set</t>
+          <t>sports collectibles</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -16314,7 +16458,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>BT-406</t>
+          <t>BT-404</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -16329,7 +16473,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>carnival glass</t>
+          <t>N scale train set</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -16366,7 +16510,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BT-408</t>
+          <t>BT-406</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -16381,7 +16525,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>door knocker</t>
+          <t>carnival glass</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16418,7 +16562,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BT-409</t>
+          <t>BT-408</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -16433,7 +16577,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>home decor</t>
+          <t>door knocker</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16470,7 +16614,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BT-410</t>
+          <t>BT-409</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -16485,7 +16629,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>mini picnic table</t>
+          <t>home decor</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -16522,7 +16666,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>BT-411</t>
+          <t>BT-410</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -16537,7 +16681,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>purses</t>
+          <t>mini picnic table</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -16574,7 +16718,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>BT-413</t>
+          <t>BT-411</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -16589,7 +16733,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>batter bowl</t>
+          <t>purses</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -16626,7 +16770,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>BT-414</t>
+          <t>BT-413</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -16641,7 +16785,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>new M&amp;amp;Ms blanket</t>
+          <t>batter bowl</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -16678,7 +16822,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BT-415</t>
+          <t>BT-414</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -16693,7 +16837,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>book shelf speakers</t>
+          <t>new M&amp;amp;Ms blanket</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -16730,7 +16874,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BT-416</t>
+          <t>BT-415</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -16745,7 +16889,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>birthday figures</t>
+          <t>book shelf speakers</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -16782,7 +16926,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BT-417</t>
+          <t>BT-416</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -16797,7 +16941,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>vintage lighter</t>
+          <t>birthday figures</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -16834,7 +16978,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BT-418</t>
+          <t>BT-417</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -16849,7 +16993,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>new steamer</t>
+          <t>vintage lighter</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -16886,7 +17030,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BT-419</t>
+          <t>BT-418</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -16901,7 +17045,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>new juicer</t>
+          <t>new steamer</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -16938,7 +17082,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>BT-421</t>
+          <t>BT-419</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -16953,7 +17097,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>swim fins</t>
+          <t>new juicer</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -16990,7 +17134,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BT-422</t>
+          <t>BT-421</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -17005,7 +17149,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>new canister set</t>
+          <t>swim fins</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17042,7 +17186,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>BT-423</t>
+          <t>BT-422</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -17057,7 +17201,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>puzzles</t>
+          <t>new canister set</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17094,7 +17238,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>BT-424</t>
+          <t>BT-423</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -17109,7 +17253,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>cake caddy</t>
+          <t>puzzles</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17146,7 +17290,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>BT-425</t>
+          <t>BT-424</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -17161,7 +17305,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>art supplies</t>
+          <t>cake caddy</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -17198,7 +17342,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>BT-426</t>
+          <t>BT-425</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -17213,7 +17357,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #428)</t>
+          <t>art supplies</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -17250,7 +17394,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BT-428</t>
+          <t>BT-426</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -17265,7 +17409,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #429)</t>
+          <t>Uncaptioned lot (Photo #428)</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -17302,7 +17446,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BT-429</t>
+          <t>BT-428</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -17317,7 +17461,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Sealife camera</t>
+          <t>Uncaptioned lot (Photo #429)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -17354,7 +17498,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BT-430</t>
+          <t>BT-429</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -17369,7 +17513,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>mini military toys</t>
+          <t>Sealife camera</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -17406,7 +17550,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BT-431</t>
+          <t>BT-430</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -17421,7 +17565,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Pokemon collectibles</t>
+          <t>mini military toys</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -17458,7 +17602,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BT-432</t>
+          <t>BT-431</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -17473,7 +17617,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #434)</t>
+          <t>Pokemon collectibles</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -17510,7 +17654,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BT-434</t>
+          <t>BT-432</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -17525,7 +17669,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>brass table lamps</t>
+          <t>Uncaptioned lot (Photo #434)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -17562,7 +17706,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>BT-435</t>
+          <t>BT-434</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -17577,7 +17721,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Hamm's beer keg</t>
+          <t>brass table lamps</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -17614,7 +17758,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BT-436</t>
+          <t>BT-435</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -17629,7 +17773,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>35mm cameras</t>
+          <t>Hamm's beer keg</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -17666,7 +17810,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BT-437</t>
+          <t>BT-436</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -17681,7 +17825,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Fisher Price little people circus train</t>
+          <t>35mm cameras</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -17718,7 +17862,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BT-438</t>
+          <t>BT-437</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -17733,7 +17877,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Big Ben alarm clock</t>
+          <t>Fisher Price little people circus train</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -17770,7 +17914,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BT-439</t>
+          <t>BT-438</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -17785,7 +17929,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>basket</t>
+          <t>Big Ben alarm clock</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -17822,7 +17966,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BT-440</t>
+          <t>BT-439</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -17837,7 +17981,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Mid Century table lamp</t>
+          <t>basket</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -17874,7 +18018,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>BT-442</t>
+          <t>BT-440</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -17889,7 +18033,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>board games</t>
+          <t>Mid Century table lamp</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -17926,7 +18070,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BT-443</t>
+          <t>BT-442</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -17941,7 +18085,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>carving set</t>
+          <t>board games</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -17978,7 +18122,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BT-444</t>
+          <t>BT-443</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -17993,7 +18137,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>belt buckles</t>
+          <t>carving set</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -18030,7 +18174,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BT-445</t>
+          <t>BT-444</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -18045,7 +18189,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #447)</t>
+          <t>belt buckles</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -18082,7 +18226,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BT-447</t>
+          <t>BT-445</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -18097,7 +18241,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #448)</t>
+          <t>Uncaptioned lot (Photo #447)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -18134,7 +18278,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BT-448</t>
+          <t>BT-447</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -18149,7 +18293,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #449)</t>
+          <t>Uncaptioned lot (Photo #448)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -18186,7 +18330,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BT-449</t>
+          <t>BT-448</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -18201,7 +18345,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>toys</t>
+          <t>Uncaptioned lot (Photo #449)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -18238,7 +18382,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>BT-450</t>
+          <t>BT-449</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -18253,7 +18397,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>action figures</t>
+          <t>toys</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -18290,7 +18434,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BT-451</t>
+          <t>BT-450</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -18305,7 +18449,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Uncaptioned lot (Photo #453)</t>
+          <t>action figures</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -18342,7 +18486,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BT-453</t>
+          <t>BT-451</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18357,7 +18501,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>New bird bath</t>
+          <t>Uncaptioned lot (Photo #453)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -18394,7 +18538,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BT-454</t>
+          <t>BT-453</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -18404,19 +18548,23 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>glassware</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Waterford crystal bowl</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>80</v>
-      </c>
-      <c r="F354" t="n">
-        <v>200</v>
+          <t>New bird bath</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -18442,7 +18590,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>BT-456</t>
+          <t>BT-454</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -18452,23 +18600,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>glassware</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>movie camera</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Waterford crystal bowl</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>80</v>
+      </c>
+      <c r="F355" t="n">
+        <v>200</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -18494,7 +18638,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BT-458</t>
+          <t>BT-456</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -18509,7 +18653,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>beer tap handles</t>
+          <t>movie camera</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -18546,7 +18690,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>BT-460</t>
+          <t>BT-458</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -18561,7 +18705,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>antique telephone</t>
+          <t>beer tap handles</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -18598,7 +18742,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>BT-462</t>
+          <t>BT-460</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -18613,7 +18757,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>new Barbie dolls</t>
+          <t>antique telephone</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -18650,50 +18794,102 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
+          <t>BT-462</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>general estate</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>new Barbie dolls</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>fit 0.20 below threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
           <t>BT-464</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>general estate</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>general estate</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
         <is>
           <t>new Barbie dolls</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
         <is>
           <t>fit 0.20 below threshold</t>
         </is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT-029</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G2" t="n">
         <v>14.34</v>
@@ -554,7 +554,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-031</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
-        <v>14.34</v>
+        <v>18.56</v>
       </c>
       <c r="H3" t="n">
-        <v>16.49</v>
+        <v>21.34</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -591,14 +591,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-086</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>14.34</v>
+        <v>18.56</v>
       </c>
       <c r="H4" t="n">
-        <v>16.49</v>
+        <v>21.34</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -639,14 +639,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-082</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-251</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-082</t>
+          <t>BT-071</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18.56</v>
+        <v>20.25</v>
       </c>
       <c r="H7" t="n">
-        <v>21.34</v>
+        <v>23.29</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -783,14 +783,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>20.25</v>
+        <v>22.78</v>
       </c>
       <c r="H8" t="n">
-        <v>23.29</v>
+        <v>26.2</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -831,14 +831,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-071</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20.25</v>
+        <v>33.75</v>
       </c>
       <c r="H9" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>38.81</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $100 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
@@ -915,19 +915,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20.25</v>
+        <v>33.75</v>
       </c>
       <c r="H10" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>38.81</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $100 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
@@ -963,26 +963,26 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>20.25</v>
+        <v>33.75</v>
       </c>
       <c r="H11" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>38.81</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>low-mid $60 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $100 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT-083</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1011,26 +1011,26 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>22.78</v>
+        <v>38.81</v>
       </c>
       <c r="H12" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>44.63</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $115 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BT-025</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1059,26 +1059,26 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>25.31</v>
+        <v>105.47</v>
       </c>
       <c r="H13" t="n">
-        <v>29.11</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>121.29</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>low-mid $75 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $312 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-284</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1107,36 +1107,36 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>27.84</v>
+        <v>105.47</v>
       </c>
       <c r="H14" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>121.29</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>NEEDS APPROVAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $312 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BT-032</t>
+          <t>BT-066</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1148,13 +1148,13 @@
         <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>30.38</v>
+        <v>10.12</v>
       </c>
       <c r="H15" t="n">
-        <v>34.94</v>
+        <v>11.64</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1163,24 +1163,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>low-mid $90 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $30 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BT-162</t>
+          <t>BT-016</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>furniture / smalls</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1188,17 +1188,21 @@
           <t>mini hope chest</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>30</v>
-      </c>
-      <c r="F16" t="n">
-        <v>80</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G16" t="n">
-        <v>30.38</v>
+        <v>14.34</v>
       </c>
       <c r="H16" t="n">
-        <v>34.94</v>
+        <v>16.49</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1207,19 +1211,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>low-mid $90 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BT-026</t>
+          <t>BT-030</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1243,31 +1247,31 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>37.12</v>
+        <v>14.34</v>
       </c>
       <c r="H17" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>16.49</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BT-455</t>
+          <t>BT-101</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1291,36 +1295,36 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>37.12</v>
+        <v>14.34</v>
       </c>
       <c r="H18" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>16.49</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>low-mid $110 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BT-066</t>
+          <t>BT-322</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1328,38 +1332,42 @@
           <t>baseball cards</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" t="n">
-        <v>180</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G19" t="n">
-        <v>47.25</v>
+        <v>14.34</v>
       </c>
       <c r="H19" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>16.49</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>low-mid $140 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-335</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1379,31 +1387,31 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>54</v>
+        <v>14.34</v>
       </c>
       <c r="H20" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>16.49</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>low-mid $160 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-113</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1427,31 +1435,31 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>71.72</v>
+        <v>18.56</v>
       </c>
       <c r="H21" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>21.34</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $55 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BT-284</t>
+          <t>BT-032</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1475,26 +1483,26 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>71.72</v>
+        <v>22.78</v>
       </c>
       <c r="H22" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>NEEDS APPROVAL</t>
+        <v>26.2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>low-mid $212 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BT-081</t>
+          <t>BT-162</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1523,36 +1531,36 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>12.66</v>
+        <v>22.78</v>
       </c>
       <c r="H23" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>26.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>low-mid $38 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>low-mid $68 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BT-017</t>
+          <t>BT-003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>games / vintage</t>
+          <t>games / skip</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1560,43 +1568,51 @@
           <t>Mahjong</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>50</v>
-      </c>
-      <c r="F24" t="n">
-        <v>150</v>
-      </c>
-      <c r="G24" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="H24" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>low-mid $42 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BT-117</t>
+          <t>BT-004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>glassware</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1604,38 +1620,46 @@
           <t>Waterford crystal bowl</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>80</v>
-      </c>
-      <c r="F25" t="n">
-        <v>200</v>
-      </c>
-      <c r="G25" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H25" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BT-163</t>
+          <t>BT-005</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1658,32 +1682,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H26" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BT-165</t>
+          <t>BT-006</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1706,37 +1734,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H27" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BT-167</t>
+          <t>BT-007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>breweriana / sports bar</t>
+          <t>barware / skip</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1744,43 +1776,51 @@
           <t>Chicago Bears glasses</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F28" t="n">
-        <v>80</v>
-      </c>
-      <c r="G28" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="H28" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>low-mid $45 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1792,39 +1832,43 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H29" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>80</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-010</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>breweriana</t>
+          <t>barware / skip</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1832,38 +1876,46 @@
           <t>beer pitchers</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" t="n">
-        <v>80</v>
-      </c>
-      <c r="G30" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H30" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BT-101</t>
+          <t>BT-012</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1877,37 +1929,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>180</v>
-      </c>
-      <c r="G31" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H31" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+        <v>120</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BT-322</t>
+          <t>BT-013</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1930,32 +1986,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H32" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BT-335</t>
+          <t>BT-014</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1978,32 +2038,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>16.03</v>
-      </c>
-      <c r="H33" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>low-mid $48 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BT-020</t>
+          <t>BT-015</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2026,32 +2090,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="H34" t="n">
-        <v>32.02</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BT-111</t>
+          <t>BT-017</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2074,11 +2142,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32.02</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2087,19 +2159,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BT-113</t>
+          <t>BT-018</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2122,11 +2194,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="H36" t="n">
-        <v>32.02</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2135,14 +2211,14 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>low-mid $82 x 38% less 10% condition, 3 source(s), high confidence — over budget cap</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BT-003</t>
+          <t>BT-019</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2194,7 +2270,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BT-004</t>
+          <t>BT-020</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2213,10 +2289,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2235,14 +2311,14 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BT-005</t>
+          <t>BT-022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2294,7 +2370,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BT-006</t>
+          <t>BT-023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2346,7 +2422,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BT-007</t>
+          <t>BT-024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2391,14 +2467,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BT-008</t>
+          <t>BT-025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2450,7 +2526,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT-010</t>
+          <t>BT-026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2495,14 +2571,14 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BT-012</t>
+          <t>BT-027</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2512,7 +2588,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2550,7 +2626,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BT-013</t>
+          <t>BT-028</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2602,7 +2678,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BT-014</t>
+          <t>BT-029</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2621,10 +2697,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2643,14 +2719,14 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BT-015</t>
+          <t>BT-031</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2695,14 +2771,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BT-018</t>
+          <t>BT-033</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2754,7 +2830,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BT-019</t>
+          <t>BT-034</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2806,7 +2882,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BT-022</t>
+          <t>BT-035</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2858,7 +2934,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BT-023</t>
+          <t>BT-037</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2910,7 +2986,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BT-024</t>
+          <t>BT-038</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2962,7 +3038,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BT-027</t>
+          <t>BT-040</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2972,7 +3048,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>uncertified autographs / skip</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3014,7 +3090,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BT-028</t>
+          <t>BT-042</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3059,14 +3135,14 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BT-033</t>
+          <t>BT-043</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3118,7 +3194,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BT-034</t>
+          <t>BT-044</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3170,7 +3246,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BT-035</t>
+          <t>BT-045</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3180,7 +3256,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage toys / electronics</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3189,10 +3265,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="F57" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3218,7 +3294,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BT-037</t>
+          <t>BT-046</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3270,7 +3346,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BT-038</t>
+          <t>BT-049</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3322,7 +3398,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BT-040</t>
+          <t>BT-051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3374,7 +3450,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BT-042</t>
+          <t>BT-053</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3415,14 +3491,14 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BT-043</t>
+          <t>BT-054</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3474,7 +3550,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BT-044</t>
+          <t>BT-056</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3526,7 +3602,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BT-045</t>
+          <t>BT-057</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3571,14 +3647,14 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BT-046</t>
+          <t>BT-059</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3623,14 +3699,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BT-049</t>
+          <t>BT-061</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3675,14 +3751,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BT-051</t>
+          <t>BT-062</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3692,7 +3768,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ephemera</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3700,11 +3776,15 @@
           <t>matchbooks</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>25</v>
-      </c>
-      <c r="F67" t="n">
-        <v>75</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3730,7 +3810,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BT-053</t>
+          <t>BT-063</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3740,7 +3820,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>advertising</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3778,7 +3858,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BT-054</t>
+          <t>BT-064</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3788,7 +3868,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>vintage tools</t>
+          <t>tools / skip backlog</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3796,11 +3876,15 @@
           <t>toolbox</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>50</v>
-      </c>
-      <c r="F69" t="n">
-        <v>120</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3826,7 +3910,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BT-056</t>
+          <t>BT-067</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3836,7 +3920,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vintage tools</t>
+          <t>tools / skip backlog</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3844,11 +3928,15 @@
           <t>wrenches</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>30</v>
-      </c>
-      <c r="F70" t="n">
-        <v>80</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3874,7 +3962,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BT-057</t>
+          <t>BT-068</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3893,10 +3981,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F71" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3915,14 +4003,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BT-059</t>
+          <t>BT-070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3974,7 +4062,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BT-061</t>
+          <t>BT-073</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4019,14 +4107,14 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BT-062</t>
+          <t>BT-075</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4071,14 +4159,14 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BT-063</t>
+          <t>BT-076</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4123,14 +4211,14 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BT-064</t>
+          <t>BT-078</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4175,14 +4263,14 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BT-067</t>
+          <t>BT-080</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4227,14 +4315,14 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BT-068</t>
+          <t>BT-081</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4286,7 +4374,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BT-070</t>
+          <t>BT-083</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4331,14 +4419,14 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BT-073</t>
+          <t>BT-086</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4390,7 +4478,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BT-075</t>
+          <t>BT-088</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4435,14 +4523,14 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BT-076</t>
+          <t>BT-089</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4452,7 +4540,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4464,7 +4552,7 @@
         <v>30</v>
       </c>
       <c r="F82" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4483,14 +4571,14 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BT-078</t>
+          <t>BT-091</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4535,14 +4623,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BT-080</t>
+          <t>BT-092</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4587,14 +4675,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BT-088</t>
+          <t>BT-093</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4646,7 +4734,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BT-089</t>
+          <t>BT-094</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4698,7 +4786,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BT-091</t>
+          <t>BT-095</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4750,7 +4838,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BT-092</t>
+          <t>BT-096</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4802,7 +4890,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BT-093</t>
+          <t>BT-098</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4812,7 +4900,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4820,11 +4908,15 @@
           <t>baseball cards</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v>50</v>
-      </c>
-      <c r="F89" t="n">
-        <v>180</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4850,7 +4942,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BT-094</t>
+          <t>BT-099</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4860,7 +4952,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4869,10 +4961,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F90" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4898,7 +4990,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BT-095</t>
+          <t>BT-102</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4950,7 +5042,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BT-096</t>
+          <t>BT-103</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4960,7 +5052,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>collectibles / skip</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4968,11 +5060,15 @@
           <t>sports bobble heads</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v>30</v>
-      </c>
-      <c r="F92" t="n">
-        <v>90</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4998,7 +5094,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BT-098</t>
+          <t>BT-105</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5050,7 +5146,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BT-099</t>
+          <t>BT-107</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5102,7 +5198,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BT-102</t>
+          <t>BT-108</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5154,7 +5250,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BT-103</t>
+          <t>BT-110</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5206,7 +5302,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BT-105</t>
+          <t>BT-111</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5258,7 +5354,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BT-107</t>
+          <t>BT-115</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5310,7 +5406,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BT-108</t>
+          <t>BT-117</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5355,14 +5451,14 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BT-110</t>
+          <t>BT-118</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5407,14 +5503,14 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BT-115</t>
+          <t>BT-120</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5466,7 +5562,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BT-118</t>
+          <t>BT-121</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5511,14 +5607,14 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BT-120</t>
+          <t>BT-122</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5570,7 +5666,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BT-121</t>
+          <t>BT-123</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5622,7 +5718,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BT-122</t>
+          <t>BT-124</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5667,14 +5763,14 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BT-123</t>
+          <t>BT-125</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5726,7 +5822,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BT-124</t>
+          <t>BT-127</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5771,14 +5867,14 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fit 0.00 below threshold</t>
+          <t>fit 0.20 below threshold</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BT-125</t>
+          <t>BT-128</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5830,7 +5926,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BT-127</t>
+          <t>BT-130</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5882,7 +5978,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BT-128</t>
+          <t>BT-132</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5934,7 +6030,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BT-130</t>
+          <t>BT-133</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5986,7 +6082,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BT-132</t>
+          <t>BT-134</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6038,7 +6134,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BT-133</t>
+          <t>BT-135</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6090,7 +6186,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BT-134</t>
+          <t>BT-136</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6142,7 +6238,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BT-135</t>
+          <t>BT-137</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6194,7 +6290,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BT-136</t>
+          <t>BT-138</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6246,7 +6342,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BT-137</t>
+          <t>BT-139</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6298,7 +6394,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BT-138</t>
+          <t>BT-140</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6350,7 +6446,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BT-139</t>
+          <t>BT-141</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6402,7 +6498,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BT-140</t>
+          <t>BT-142</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6454,7 +6550,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BT-141</t>
+          <t>BT-143</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6506,7 +6602,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BT-142</t>
+          <t>BT-144</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6558,7 +6654,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BT-143</t>
+          <t>BT-146</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6610,7 +6706,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BT-144</t>
+          <t>BT-147</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6662,7 +6758,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BT-146</t>
+          <t>BT-148</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6714,7 +6810,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BT-147</t>
+          <t>BT-149</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6766,7 +6862,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BT-148</t>
+          <t>BT-150</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6818,7 +6914,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BT-149</t>
+          <t>BT-152</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6837,10 +6933,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6866,7 +6962,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BT-150</t>
+          <t>BT-154</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6876,7 +6972,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>collectibles / skip</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6884,11 +6980,15 @@
           <t>bobble heads</t>
         </is>
       </c>
-      <c r="E129" t="n">
-        <v>30</v>
-      </c>
-      <c r="F129" t="n">
-        <v>90</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6914,7 +7014,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BT-152</t>
+          <t>BT-155</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6924,7 +7024,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>collectibles / skip</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6932,11 +7032,15 @@
           <t>bobble heads</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v>30</v>
-      </c>
-      <c r="F130" t="n">
-        <v>90</v>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6962,7 +7066,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BT-154</t>
+          <t>BT-156</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6972,7 +7076,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>collectibles</t>
+          <t>collectibles / skip</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6980,11 +7084,15 @@
           <t>bobble heads</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>30</v>
-      </c>
-      <c r="F131" t="n">
-        <v>90</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7010,7 +7118,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BT-155</t>
+          <t>BT-158</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7062,7 +7170,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BT-156</t>
+          <t>BT-159</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7114,7 +7222,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BT-158</t>
+          <t>BT-161</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7166,7 +7274,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BT-159</t>
+          <t>BT-163</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7211,14 +7319,14 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BT-161</t>
+          <t>BT-165</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7263,14 +7371,14 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BT-168</t>
+          <t>BT-167</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7315,14 +7423,14 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BT-170</t>
+          <t>BT-168</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7374,7 +7482,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BT-171</t>
+          <t>BT-170</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7426,7 +7534,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BT-172</t>
+          <t>BT-171</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7478,7 +7586,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BT-174</t>
+          <t>BT-172</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7530,7 +7638,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BT-175</t>
+          <t>BT-174</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7549,10 +7657,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F142" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7578,7 +7686,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BT-176</t>
+          <t>BT-175</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7630,7 +7738,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BT-177</t>
+          <t>BT-176</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7682,7 +7790,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BT-178</t>
+          <t>BT-177</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7734,7 +7842,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BT-179</t>
+          <t>BT-178</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7786,7 +7894,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BT-183</t>
+          <t>BT-179</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7838,7 +7946,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BT-184</t>
+          <t>BT-183</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7890,7 +7998,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BT-185</t>
+          <t>BT-184</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7942,7 +8050,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BT-187</t>
+          <t>BT-185</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7994,7 +8102,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BT-189</t>
+          <t>BT-187</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8046,7 +8154,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BT-190</t>
+          <t>BT-189</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8098,7 +8206,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BT-191</t>
+          <t>BT-190</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8150,7 +8258,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BT-192</t>
+          <t>BT-191</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8202,7 +8310,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BT-193</t>
+          <t>BT-192</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8254,7 +8362,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BT-195</t>
+          <t>BT-193</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8306,7 +8414,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BT-196</t>
+          <t>BT-195</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8358,7 +8466,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BT-198</t>
+          <t>BT-196</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8410,7 +8518,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BT-199</t>
+          <t>BT-198</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8462,7 +8570,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BT-200</t>
+          <t>BT-199</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8514,7 +8622,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BT-201</t>
+          <t>BT-200</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8566,7 +8674,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BT-203</t>
+          <t>BT-201</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8618,7 +8726,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BT-205</t>
+          <t>BT-203</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8670,7 +8778,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BT-206</t>
+          <t>BT-205</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8722,7 +8830,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BT-208</t>
+          <t>BT-206</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8774,7 +8882,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BT-209</t>
+          <t>BT-208</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8826,7 +8934,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BT-210</t>
+          <t>BT-209</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8878,7 +8986,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BT-212</t>
+          <t>BT-210</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8930,7 +9038,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BT-213</t>
+          <t>BT-212</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8982,7 +9090,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BT-215</t>
+          <t>BT-213</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9034,7 +9142,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BT-216</t>
+          <t>BT-215</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9086,7 +9194,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>BT-217</t>
+          <t>BT-216</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9138,7 +9246,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BT-218</t>
+          <t>BT-217</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9190,7 +9298,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BT-220</t>
+          <t>BT-218</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9242,7 +9350,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BT-222</t>
+          <t>BT-220</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9294,7 +9402,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BT-223</t>
+          <t>BT-222</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9346,7 +9454,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BT-224</t>
+          <t>BT-223</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9398,7 +9506,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BT-225</t>
+          <t>BT-224</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9450,7 +9558,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BT-226</t>
+          <t>BT-225</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9502,7 +9610,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BT-227</t>
+          <t>BT-226</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9554,7 +9662,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BT-229</t>
+          <t>BT-227</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9606,7 +9714,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BT-230</t>
+          <t>BT-229</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9658,7 +9766,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BT-231</t>
+          <t>BT-230</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9668,7 +9776,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9676,15 +9784,11 @@
           <t>Century Progress bottle</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E183" t="n">
+        <v>30</v>
+      </c>
+      <c r="F183" t="n">
+        <v>80</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -9710,7 +9814,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BT-232</t>
+          <t>BT-231</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9762,7 +9866,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BT-233</t>
+          <t>BT-232</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9814,7 +9918,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BT-234</t>
+          <t>BT-233</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9866,7 +9970,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-234</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10396,7 +10500,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10404,15 +10508,11 @@
           <t>Coca-Cola collectibles</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E197" t="n">
+        <v>40</v>
+      </c>
+      <c r="F197" t="n">
+        <v>100</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -10594,7 +10694,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BT-251</t>
+          <t>BT-253</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10646,7 +10746,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BT-253</t>
+          <t>BT-254</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10698,7 +10798,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BT-254</t>
+          <t>BT-255</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10750,7 +10850,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BT-255</t>
+          <t>BT-256</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10802,7 +10902,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BT-256</t>
+          <t>BT-257</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10854,7 +10954,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BT-257</t>
+          <t>BT-259</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -10906,7 +11006,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BT-259</t>
+          <t>BT-260</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -10958,7 +11058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BT-260</t>
+          <t>BT-261</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11010,7 +11110,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BT-261</t>
+          <t>BT-263</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11062,7 +11162,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BT-263</t>
+          <t>BT-264</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11114,7 +11214,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BT-264</t>
+          <t>BT-265</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11166,7 +11266,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BT-265</t>
+          <t>BT-266</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11218,7 +11318,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BT-266</t>
+          <t>BT-268</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11270,7 +11370,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BT-268</t>
+          <t>BT-269</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11322,7 +11422,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BT-269</t>
+          <t>BT-270</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11374,7 +11474,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BT-270</t>
+          <t>BT-271</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11426,7 +11526,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BT-271</t>
+          <t>BT-273</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11478,7 +11578,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BT-273</t>
+          <t>BT-274</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11530,7 +11630,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BT-274</t>
+          <t>BT-275</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11582,7 +11682,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BT-275</t>
+          <t>BT-276</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11634,7 +11734,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BT-276</t>
+          <t>BT-278</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11686,7 +11786,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BT-278</t>
+          <t>BT-280</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11696,7 +11796,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11705,10 +11805,10 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F222" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -11734,7 +11834,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BT-280</t>
+          <t>BT-282</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11786,7 +11886,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BT-282</t>
+          <t>BT-283</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11838,7 +11938,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BT-283</t>
+          <t>BT-285</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11890,7 +11990,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BT-285</t>
+          <t>BT-287</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11942,7 +12042,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BT-287</t>
+          <t>BT-288</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11994,7 +12094,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BT-288</t>
+          <t>BT-289</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12046,7 +12146,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BT-289</t>
+          <t>BT-290</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12098,7 +12198,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BT-290</t>
+          <t>BT-291</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12150,7 +12250,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>BT-291</t>
+          <t>BT-292</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12202,7 +12302,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>BT-292</t>
+          <t>BT-293</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12254,7 +12354,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>BT-293</t>
+          <t>BT-294</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12306,7 +12406,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BT-294</t>
+          <t>BT-295</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12358,7 +12458,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BT-295</t>
+          <t>BT-296</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12410,7 +12510,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>BT-296</t>
+          <t>BT-297</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12462,7 +12562,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BT-297</t>
+          <t>BT-298</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12514,7 +12614,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BT-298</t>
+          <t>BT-300</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12566,7 +12666,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BT-300</t>
+          <t>BT-301</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12618,7 +12718,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>BT-301</t>
+          <t>BT-302</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12670,7 +12770,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>BT-302</t>
+          <t>BT-303</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12722,7 +12822,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>BT-303</t>
+          <t>BT-305</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12774,7 +12874,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>BT-305</t>
+          <t>BT-306</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12826,7 +12926,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BT-306</t>
+          <t>BT-308</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12878,7 +12978,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BT-308</t>
+          <t>BT-310</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12930,7 +13030,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BT-310</t>
+          <t>BT-311</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12982,7 +13082,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BT-311</t>
+          <t>BT-312</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13034,7 +13134,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BT-312</t>
+          <t>BT-313</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13086,7 +13186,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BT-313</t>
+          <t>BT-315</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13138,7 +13238,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BT-315</t>
+          <t>BT-317</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13190,7 +13290,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>BT-317</t>
+          <t>BT-318</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13200,7 +13300,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -13212,7 +13312,7 @@
         <v>30</v>
       </c>
       <c r="F251" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -13238,7 +13338,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BT-318</t>
+          <t>BT-320</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13290,7 +13390,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>BT-320</t>
+          <t>BT-323</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13342,7 +13442,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BT-323</t>
+          <t>BT-324</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13394,7 +13494,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BT-324</t>
+          <t>BT-325</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13446,7 +13546,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BT-325</t>
+          <t>BT-327</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13498,7 +13598,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>BT-327</t>
+          <t>BT-328</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13550,7 +13650,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>BT-328</t>
+          <t>BT-329</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13602,7 +13702,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BT-329</t>
+          <t>BT-330</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13654,7 +13754,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>BT-330</t>
+          <t>BT-331</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13706,7 +13806,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>BT-331</t>
+          <t>BT-332</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13758,7 +13858,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>BT-332</t>
+          <t>BT-334</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13768,7 +13868,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -13780,7 +13880,7 @@
         <v>30</v>
       </c>
       <c r="F262" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -13806,7 +13906,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>BT-334</t>
+          <t>BT-336</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13858,7 +13958,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>BT-336</t>
+          <t>BT-337</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13910,7 +14010,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BT-337</t>
+          <t>BT-338</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13962,7 +14062,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BT-338</t>
+          <t>BT-340</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -14014,7 +14114,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BT-340</t>
+          <t>BT-341</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -14066,7 +14166,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>BT-341</t>
+          <t>BT-342</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -14118,7 +14218,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>BT-342</t>
+          <t>BT-343</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -14170,7 +14270,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>BT-343</t>
+          <t>BT-344</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -14222,7 +14322,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BT-344</t>
+          <t>BT-345</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -14274,7 +14374,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>BT-345</t>
+          <t>BT-347</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -14326,7 +14426,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>BT-347</t>
+          <t>BT-348</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -14378,7 +14478,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>BT-348</t>
+          <t>BT-349</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -14430,7 +14530,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>BT-349</t>
+          <t>BT-350</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -14482,7 +14582,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>BT-350</t>
+          <t>BT-351</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -14534,7 +14634,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>BT-351</t>
+          <t>BT-352</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -14586,7 +14686,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>BT-352</t>
+          <t>BT-353</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -14638,7 +14738,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>BT-353</t>
+          <t>BT-354</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -14690,7 +14790,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>BT-354</t>
+          <t>BT-356</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -14742,7 +14842,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>BT-356</t>
+          <t>BT-357</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -14794,7 +14894,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>BT-357</t>
+          <t>BT-358</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -14846,7 +14946,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>BT-358</t>
+          <t>BT-360</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -14898,7 +14998,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>BT-360</t>
+          <t>BT-361</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -14950,7 +15050,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BT-361</t>
+          <t>BT-363</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -15002,7 +15102,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>BT-363</t>
+          <t>BT-365</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -15054,7 +15154,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>BT-365</t>
+          <t>BT-366</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -15106,7 +15206,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BT-366</t>
+          <t>BT-368</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -15158,7 +15258,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>BT-368</t>
+          <t>BT-369</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -15210,7 +15310,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BT-369</t>
+          <t>BT-370</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -15262,7 +15362,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>BT-370</t>
+          <t>BT-371</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -15314,7 +15414,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BT-371</t>
+          <t>BT-373</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -15366,7 +15466,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BT-373</t>
+          <t>BT-375</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -15418,7 +15518,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BT-375</t>
+          <t>BT-376</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -15470,7 +15570,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BT-376</t>
+          <t>BT-378</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -15522,7 +15622,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BT-378</t>
+          <t>BT-379</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -15574,7 +15674,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BT-379</t>
+          <t>BT-381</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -15626,7 +15726,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BT-381</t>
+          <t>BT-383</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -15678,7 +15778,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BT-383</t>
+          <t>BT-384</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -15730,7 +15830,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BT-384</t>
+          <t>BT-385</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -15782,7 +15882,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BT-385</t>
+          <t>BT-387</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -15834,7 +15934,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BT-387</t>
+          <t>BT-389</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -15886,7 +15986,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>BT-389</t>
+          <t>BT-390</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -15938,7 +16038,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>BT-390</t>
+          <t>BT-392</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -15990,7 +16090,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>BT-392</t>
+          <t>BT-394</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -16042,7 +16142,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>BT-394</t>
+          <t>BT-395</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -16094,7 +16194,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>BT-395</t>
+          <t>BT-397</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -16146,7 +16246,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>BT-397</t>
+          <t>BT-398</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -16198,7 +16298,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BT-398</t>
+          <t>BT-399</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -16250,7 +16350,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BT-399</t>
+          <t>BT-400</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -16302,7 +16402,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BT-400</t>
+          <t>BT-402</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -16354,7 +16454,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>BT-402</t>
+          <t>BT-403</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -16406,7 +16506,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>BT-403</t>
+          <t>BT-404</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -16458,7 +16558,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>BT-404</t>
+          <t>BT-406</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -16510,7 +16610,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BT-406</t>
+          <t>BT-408</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -16562,7 +16662,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BT-408</t>
+          <t>BT-409</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -16614,7 +16714,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BT-409</t>
+          <t>BT-410</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -16666,7 +16766,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>BT-410</t>
+          <t>BT-411</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -16718,7 +16818,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>BT-411</t>
+          <t>BT-413</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -16770,7 +16870,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>BT-413</t>
+          <t>BT-414</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -16822,7 +16922,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BT-414</t>
+          <t>BT-415</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -16874,7 +16974,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BT-415</t>
+          <t>BT-416</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -16926,7 +17026,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BT-416</t>
+          <t>BT-417</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -16978,7 +17078,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BT-417</t>
+          <t>BT-418</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -17030,7 +17130,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BT-418</t>
+          <t>BT-419</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -17082,7 +17182,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>BT-419</t>
+          <t>BT-421</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -17134,7 +17234,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BT-421</t>
+          <t>BT-422</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -17186,7 +17286,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>BT-422</t>
+          <t>BT-423</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -17238,7 +17338,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>BT-423</t>
+          <t>BT-424</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -17290,7 +17390,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>BT-424</t>
+          <t>BT-425</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -17342,7 +17442,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>BT-425</t>
+          <t>BT-426</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -17394,7 +17494,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BT-426</t>
+          <t>BT-428</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -17446,7 +17546,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BT-428</t>
+          <t>BT-429</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -17498,7 +17598,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BT-429</t>
+          <t>BT-430</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -17550,7 +17650,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BT-430</t>
+          <t>BT-431</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -17602,7 +17702,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BT-431</t>
+          <t>BT-432</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -17654,7 +17754,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BT-432</t>
+          <t>BT-434</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -17706,7 +17806,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>BT-434</t>
+          <t>BT-435</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -17758,7 +17858,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BT-435</t>
+          <t>BT-436</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -17810,7 +17910,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BT-436</t>
+          <t>BT-437</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -17862,7 +17962,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BT-437</t>
+          <t>BT-438</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -17914,7 +18014,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BT-438</t>
+          <t>BT-439</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -17966,7 +18066,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BT-439</t>
+          <t>BT-440</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -18018,7 +18118,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>BT-440</t>
+          <t>BT-442</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -18070,7 +18170,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BT-442</t>
+          <t>BT-443</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -18080,7 +18180,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>general estate</t>
+          <t>games / skip</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -18115,14 +18215,14 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>fit 0.20 below threshold</t>
+          <t>fit 0.00 below threshold</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BT-443</t>
+          <t>BT-444</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -18174,7 +18274,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BT-444</t>
+          <t>BT-445</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -18226,7 +18326,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BT-445</t>
+          <t>BT-447</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -18278,7 +18378,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BT-447</t>
+          <t>BT-448</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -18330,7 +18430,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BT-448</t>
+          <t>BT-449</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -18382,7 +18482,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>BT-449</t>
+          <t>BT-450</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -18434,7 +18534,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BT-450</t>
+          <t>BT-451</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -18486,7 +18586,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BT-451</t>
+          <t>BT-453</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18538,7 +18638,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BT-453</t>
+          <t>BT-454</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -18590,7 +18690,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>BT-454</t>
+          <t>BT-455</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -18600,7 +18700,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>glassware</t>
+          <t>general estate</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -18608,11 +18708,15 @@
           <t>Waterford crystal bowl</t>
         </is>
       </c>
-      <c r="E355" t="n">
-        <v>80</v>
-      </c>
-      <c r="F355" t="n">
-        <v>200</v>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="187" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -491,392 +491,392 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-066</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vintage Topps Baseball Cards (1959-69 Golden Era Stars)</t>
+          <t>Lot of six handheld electronic LCD games including Radica titles, late 1990s to 2000s.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$250-$500</t>
+          <t>$26-$32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>11.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edison rolls (11-12 canisters + bare roll)</t>
+          <t>Bulk lot of sports trading cards in a multi-row cardboard storage box, predominantly late 20th-century/1980s–2000s issues.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$100-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
-        <v>40</v>
-      </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>17.25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estate Costume Jewelry (Tray 12/14/16: 50-70 pcs)</t>
+          <t>Assorted lot of non-sport trading cards, including MAD Magazine, pop culture, automobile, and entertainment cards, c. 1970s-1990s</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>costume jewelry (Tray Lot 2)</t>
+          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>estate costume jewelry (Tray Lot 3)</t>
+          <t>Vintage Bell System / Western Electric pink Touch-Tone Princess telephone in original box, c. 1970s.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lionel building set</t>
+          <t>Vintage E.T. The Extra-Terrestrial ceramic nightlight figure, likely Universal City Studios licensed or craft mold, c. 1982</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$50-$120</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>princess phone</t>
+          <t>Assortment of vintage estate costume jewelry, including beaded necklaces, brooches, chains, pendants, and faux pearls arranged in auction trays.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$40-$100</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ET nightlight</t>
+          <t>Vintage Lionel metal construction set in fitted wooden carrying case, circa late 1930s.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$40-$100</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>advertising / bottles</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Century Progress bottle</t>
+          <t>Assorted bulk lot of vintage and modern costume jewelry in a plastic storage bin, including faux pearl strands, beaded necklaces, pins, brooches, and bagged smalls.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trading cards</t>
+          <t>Assorted estate costume jewelry lot including rhinestone brooches (such as Christmas tree pins), faux pearl and beaded necklaces, pendants, and cuff bracelet, mid to late 20th century.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>non-sport trading cards</t>
+          <t>Group of Edison phonograph cylinder records and containers, Thomas A. Edison, Inc., circa 1902–1929.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>17.25</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -887,32 +887,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BT-066</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hand held video games (5 Radica/LCD units)</t>
+          <t>Group of vintage baseball trading cards including Topps and Bowman releases featuring various Major League Baseball players</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>$25-$45</t>
+          <t>$250-$320</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>11.5</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="187" customWidth="1" min="3" max="3"/>
+    <col width="219" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lot of six handheld electronic LCD games including Radica titles, late 1990s to 2000s.</t>
+          <t>Lot of handheld LCD electronic games, including Radica and electronic handheld game titles, c. 1990s-2000s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulk lot of sports trading cards in a multi-row cardboard storage box, predominantly late 20th-century/1980s–2000s issues.</t>
+          <t>Bulk collection of loose sports trading cards (hockey, football, baseball) housed in a multi-row cardboard monster storage box.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assorted lot of non-sport trading cards, including MAD Magazine, pop culture, automobile, and entertainment cards, c. 1970s-1990s</t>
+          <t>Assorted vintage non-sport trading card collection in plastic cases and top loaders, featuring Garbage Pail Kids, MAD Magazine, classic automobiles, and entertainment sets, Topps and other publishers, c. 1980s-1990s.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle</t>
+          <t>1933 Chicago World's Fair 'A Century of Progress' embossed glass souvenir bottle</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage Bell System / Western Electric pink Touch-Tone Princess telephone in original box, c. 1970s.</t>
+          <t>Vintage Western Electric pink Princess push-button (Touch-Tone) telephone with original box, Bell System, c. 1965-1975.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vintage E.T. The Extra-Terrestrial ceramic nightlight figure, likely Universal City Studios licensed or craft mold, c. 1982</t>
+          <t>Vintage E.T. The Extra-Terrestrial ceramic figure nightlight, likely Universal City Studios licensed or ceramic craft mold, c. 1982.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assortment of vintage estate costume jewelry, including beaded necklaces, brooches, chains, pendants, and faux pearls arranged in auction trays.</t>
+          <t>Assorted vintage and contemporary estate costume jewelry including beaded necklaces, brooches, chains, pendants, and bracelets in three black jewelry trays (labeled 12, 14, 16)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction set in fitted wooden carrying case, circa late 1930s.</t>
+          <t>Vintage metal construction set in wooden case, attributed as Lionel, c. 1930s-1940s</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assorted bulk lot of vintage and modern costume jewelry in a plastic storage bin, including faux pearl strands, beaded necklaces, pins, brooches, and bagged smalls.</t>
+          <t>Bulk lot of assorted costume jewelry including faux pearls, beaded necklaces, pins, and loose components in a plastic bin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assorted estate costume jewelry lot including rhinestone brooches (such as Christmas tree pins), faux pearl and beaded necklaces, pendants, and cuff bracelet, mid to late 20th century.</t>
+          <t>Tray lot of vintage costume jewelry, including rhinestone brooches (notably holiday/Christmas tree designs), beaded multi-strand necklaces, cabochon pendant, and charm elements, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Group of Edison phonograph cylinder records and containers, Thomas A. Edison, Inc., circa 1902–1929.</t>
+          <t>Lot of vintage Edison phonograph cylinder record containers and cylinders, Thomas A. Edison, Inc., circa 1900-1920s</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Group of vintage baseball trading cards including Topps and Bowman releases featuring various Major League Baseball players</t>
+          <t>Assortment of vintage baseball trading cards including 1950s and 1960s Topps and Bowman issues in protective top loaders</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="219" customWidth="1" min="3" max="3"/>
+    <col width="173" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lot of handheld LCD electronic games, including Radica and electronic handheld game titles, c. 1990s-2000s</t>
+          <t>Collection of vintage electronic handheld LCD games including Radica titles, c. 1990s-2000s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulk collection of loose sports trading cards (hockey, football, baseball) housed in a multi-row cardboard monster storage box.</t>
+          <t>Multi-row cardboard storage box containing large collection of sports trading cards, c. 1980s-2000s</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assorted vintage non-sport trading card collection in plastic cases and top loaders, featuring Garbage Pail Kids, MAD Magazine, classic automobiles, and entertainment sets, Topps and other publishers, c. 1980s-1990s.</t>
+          <t>Assorted vintage non-sport trading card collection in protective sleeves, including MAD Magazine, automotive, and pop culture cards, c. 1970s-1990s</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1933 Chicago World's Fair 'A Century of Progress' embossed glass souvenir bottle</t>
+          <t>1933 Chicago World's Fair Century of Progress embossed clear glass souvenir bottle</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage Western Electric pink Princess push-button (Touch-Tone) telephone with original box, Bell System, c. 1965-1975.</t>
+          <t>Vintage pink push-button Princess telephone by Western Electric / Bell System in original box, circa 1970s</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vintage E.T. The Extra-Terrestrial ceramic figure nightlight, likely Universal City Studios licensed or ceramic craft mold, c. 1982.</t>
+          <t>E.T. The Extra-Terrestrial nightlight figure, molded ceramic or soft plastic, c. 1982.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assorted vintage and contemporary estate costume jewelry including beaded necklaces, brooches, chains, pendants, and bracelets in three black jewelry trays (labeled 12, 14, 16)</t>
+          <t>Assorted estate costume jewelry trays including beaded necklaces, brooches, chains, and pendants, mid to late 20th century.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vintage metal construction set in wooden case, attributed as Lionel, c. 1930s-1940s</t>
+          <t>Vintage Lionel metal construction building set in fitted wooden case</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulk lot of assorted costume jewelry including faux pearls, beaded necklaces, pins, and loose components in a plastic bin</t>
+          <t>Bulk plastic tub containing assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, pins, and fashion accessories, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tray lot of vintage costume jewelry, including rhinestone brooches (notably holiday/Christmas tree designs), beaded multi-strand necklaces, cabochon pendant, and charm elements, mid-to-late 20th century.</t>
+          <t>Assorted vintage estate costume jewelry lot including rhinestone brooches, Christmas tree pin, beaded necklaces, and gold-tone chains, mid-to-late 20th century</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lot of vintage Edison phonograph cylinder record containers and cylinders, Thomas A. Edison, Inc., circa 1900-1920s</t>
+          <t>Group of Edison phonograph cylinder record containers and cylinders, Thomas A. Edison, early 20th century.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assortment of vintage baseball trading cards including 1950s and 1960s Topps and Bowman issues in protective top loaders</t>
+          <t>Collection of vintage sports trading cards, primarily Topps, c. 1950s-1970s</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="173" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -491,392 +491,392 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT-066</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Collection of vintage electronic handheld LCD games including Radica titles, c. 1990s-2000s</t>
+          <t>Vintage Topps Baseball Cards (1959-69 Golden Era Stars)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$26-$32</t>
+          <t>$250-$500</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5</v>
+        <v>115</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Multi-row cardboard storage box containing large collection of sports trading cards, c. 1980s-2000s</t>
+          <t>Edison rolls (11-12 canisters + bare roll)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$38-$48</t>
+          <t>$100-$160</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>17.25</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assorted vintage non-sport trading card collection in protective sleeves, including MAD Magazine, automotive, and pop culture cards, c. 1970s-1990s</t>
+          <t>Estate Costume Jewelry (Tray 12/14/16: 50-70 pcs)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$38-$48</t>
+          <t>$80-$160</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>advertising / bottles</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1933 Chicago World's Fair Century of Progress embossed clear glass souvenir bottle</t>
+          <t>costume jewelry (Tray Lot 2)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$38-$48</t>
+          <t>$80-$160</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage pink push-button Princess telephone by Western Electric / Bell System in original box, circa 1970s</t>
+          <t>estate costume jewelry (Tray Lot 3)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$52-$62</t>
+          <t>$80-$160</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E.T. The Extra-Terrestrial nightlight figure, molded ceramic or soft plastic, c. 1982.</t>
+          <t>Lionel building set</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$52-$62</t>
+          <t>$50-$120</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assorted estate costume jewelry trays including beaded necklaces, brooches, chains, and pendants, mid to late 20th century.</t>
+          <t>princess phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$40-$100</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction building set in fitted wooden case</t>
+          <t>ET nightlight</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$40-$100</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulk plastic tub containing assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, pins, and fashion accessories, mid-to-late 20th century.</t>
+          <t>Century Progress bottle</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$30-$80</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-016</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assorted vintage estate costume jewelry lot including rhinestone brooches, Christmas tree pin, beaded necklaces, and gold-tone chains, mid-to-late 20th century</t>
+          <t>trading cards</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$30-$80</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-030</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Group of Edison phonograph cylinder record containers and cylinders, Thomas A. Edison, early 20th century.</t>
+          <t>non-sport trading cards</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>$100-$130</t>
+          <t>$30-$80</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>46</v>
+        <v>17.25</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -887,32 +887,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-066</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Collection of vintage sports trading cards, primarily Topps, c. 1950s-1970s</t>
+          <t>hand held video games (5 Radica/LCD units)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>$250-$320</t>
+          <t>$25-$45</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>11.5</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="496" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -491,392 +491,392 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-066</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vintage Topps Baseball Cards (1959-69 Golden Era Stars)</t>
+          <t>Assorted handheld electronic games lot, including Excalibur Casino Calculators, Milton Bradley Electronic Yahtzee, and Radica electronic poker/slot games, c. 1990s-2000s.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$250-$500</t>
+          <t>$26-$32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>11.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edison rolls (11-12 canisters + bare roll)</t>
+          <t>Cardboard multi-row storage box containing bulk sports trading cards including hockey, football, and baseball, produced by various manufacturers such as Score and Fleer Ultra, c. late 1980s to 2000s.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$100-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
-        <v>40</v>
-      </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>17.25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estate Costume Jewelry (Tray 12/14/16: 50-70 pcs)</t>
+          <t>Assortment of non-sport movie and pop culture trading cards in protective acrylic cases, including 1984 Fleer Dune, 1991 Pro Set Fievel Goes West, MAD Magazine, Robin Hood, and automotive sets, c. 1980s-1990s.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>costume jewelry (Tray Lot 2)</t>
+          <t>1833-1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle/flask, circa 1933.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$38-$48</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>estate costume jewelry (Tray Lot 3)</t>
+          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$80-$160</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lionel building set</t>
+          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$50-$120</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>princess phone</t>
+          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$40-$100</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ET nightlight</t>
+          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$40-$100</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>advertising / bottles</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Century Progress bottle</t>
+          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trading cards</t>
+          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>non-sport trading cards</t>
+          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>$30-$80</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>17.25</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -887,32 +887,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BT-066</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hand held video games (5 Radica/LCD units)</t>
+          <t>Collection of vintage Topps sports trading cards (circa 1956-1962), featuring major Hall of Famers and stars including 1956 Topps Sandy Koufax (#79), 1957 Topps Bart Starr Rookie (#119), 1957 Topps Paul Hornung Rookie (#90), 1958 Topps All-Star Willie Mays (#436) and Mickey Mantle (#487), 1959 Topps Yogi Berra (#180, 2 copies), 1960 Topps Roger Maris (#377), 1961 Topps Yogi Berra (#425), Roger Maris (#2), Willie Mays (#150), 1961 NL HR Leaders (#2), and 1962 Topps Roberto Clemente (#300).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>$25-$45</t>
+          <t>$250-$320</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>11.5</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,10 +513,10 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5</v>
+        <v>5.75</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -527,17 +527,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT-016</t>
+          <t>BT-235</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>advertising / bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cardboard multi-row storage box containing bulk sports trading cards including hockey, football, and baseball, produced by various manufacturers such as Score and Fleer Ultra, c. late 1980s to 2000s.</t>
+          <t>1833-1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle/flask, circa 1933.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,10 +549,10 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>17.25</v>
+        <v>11.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -563,22 +563,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-030</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assortment of non-sport movie and pop culture trading cards in protective acrylic cases, including 1984 Fleer Dune, 1991 Pro Set Fievel Goes West, MAD Magazine, Robin Hood, and automotive sets, c. 1980s-1990s.</t>
+          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$38-$48</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -599,22 +599,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-235</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>advertising / bottles</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1833-1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle/flask, circa 1933.</t>
+          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$38-$48</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -635,17 +635,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
+          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>17.25</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -671,32 +671,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
+          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$52-$62</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>17.25</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
+          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -729,10 +729,10 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -743,17 +743,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
+          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,10 +765,10 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>28.75</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -779,22 +779,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
+          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -815,106 +815,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
+          <t>Collection of vintage Topps sports trading cards (circa 1956-1962), featuring major Hall of Famers and stars including 1956 Topps Sandy Koufax (#79), 1957 Topps Bart Starr Rookie (#119), 1957 Topps Paul Hornung Rookie (#90), 1958 Topps All-Star Willie Mays (#436) and Mickey Mantle (#487), 1959 Topps Yogi Berra (#180, 2 copies), 1960 Topps Roger Maris (#377), 1961 Topps Yogi Berra (#425), Roger Maris (#2), Willie Mays (#150), 1961 NL HR Leaders (#2), and 1962 Topps Roberto Clemente (#300).</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$250-$320</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>28.75</v>
+        <v>74.75</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BT-041</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>phonograph / records</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>$100-$130</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G12" t="n">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BT-001</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>vintage cards</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Collection of vintage Topps sports trading cards (circa 1956-1962), featuring major Hall of Famers and stars including 1956 Topps Sandy Koufax (#79), 1957 Topps Bart Starr Rookie (#119), 1957 Topps Paul Hornung Rookie (#90), 1958 Topps All-Star Willie Mays (#436) and Mickey Mantle (#487), 1959 Topps Yogi Berra (#180, 2 copies), 1960 Topps Roger Maris (#377), 1961 Topps Yogi Berra (#425), Roger Maris (#2), Willie Mays (#150), 1961 NL HR Leaders (#2), and 1962 Topps Roberto Clemente (#300).</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>$250-$320</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>35</v>
-      </c>
-      <c r="F13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G13" t="n">
-        <v>115</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -563,22 +563,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
+          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -599,17 +599,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
+          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,22 +635,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
+          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$52-$62</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -671,17 +671,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
+          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -707,32 +707,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
+          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>17.25</v>
+        <v>28.75</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
+          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,10 +765,10 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>28.75</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -779,22 +779,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-181</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
+          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$100-$130</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>74.75</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="496" customWidth="1" min="3" max="3"/>
+    <col width="240" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Assorted handheld electronic games lot, including Excalibur Casino Calculators, Milton Bradley Electronic Yahtzee, and Radica electronic poker/slot games, c. 1990s-2000s.</t>
+          <t>Lot of 6 handheld electronic LCD games, including Excalibur Casino Calculator (2), Milton Bradley Electronic Yahtzee, Radical Video Slot 5000, Solitaire, and Bonus/Draw Poker, c. 1995-2005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1833-1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative bottle/flask, circa 1933.</t>
+          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass souvenir bottle with screw cap</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Western Electric / Bell System pink Touch-Tone 'Princess' telephone in original box, c. 1970s.</t>
+          <t>Western Electric / Bell System Touch-Tone 'Princess' telephone in pink, model 2702 series, with original printed box, c. 1960s-1970s.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight / lamp figurine, c. 1982. Features E.T. with hand raised to forehead and painted blue eyes.</t>
+          <t>E.T. The Extra-Terrestrial ceramic nightlight figure, likely licensed Universal City Studios / Sigma manufacture, c. 1982.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction set in fitted wooden presentation box, circa late 1940s.</t>
+          <t>Vintage metal construction set in wooden case, likely A.C. Gilbert Erector or Lionel Construction Set, circa 1930s-1950s</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Large group of vintage estate costume jewelry and wristwatches across three display trays (numbered 12, 14, and 16), including rhinestone Christmas tree brooches, beaded strands, gold-tone chains, pendants, and ladies' wristwatches, mid-to-late 20th century.</t>
+          <t>Assorted estate costume jewelry trays containing beaded necklaces, rhinestone brooches, gold-tone chains, faux pearls, and wristwatches, mid-to-late 20th century</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Group of Edison phonograph cylinder record containers and cylinders, including Edison Gold Moulded and Blue Amberol issues, early 20th century</t>
+          <t>Lot of vintage Edison phonograph cylinder record tubes including Edison Gold Moulded and Edison Blue Amberol records with cardboard containers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulk assortment of vintage and modern costume jewelry in plastic tub</t>
+          <t>Bulk lot of assorted estate costume jewelry, including faux pearl strands, brooches, novelty pins, and beaded necklaces</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assorted vintage costume jewelry tray lot including Christmas tree brooches, leaf-link and rhinestone necklaces, nautical charm bracelet, and beaded jewelry, mid-to-late 20th century.</t>
+          <t>estate costume jewelry (Tray Lot 3)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Collection of vintage Topps sports trading cards (circa 1956-1962), featuring major Hall of Famers and stars including 1956 Topps Sandy Koufax (#79), 1957 Topps Bart Starr Rookie (#119), 1957 Topps Paul Hornung Rookie (#90), 1958 Topps All-Star Willie Mays (#436) and Mickey Mantle (#487), 1959 Topps Yogi Berra (#180, 2 copies), 1960 Topps Roger Maris (#377), 1961 Topps Yogi Berra (#425), Roger Maris (#2), Willie Mays (#150), 1961 NL HR Leaders (#2), and 1962 Topps Roberto Clemente (#300).</t>
+          <t>Group of vintage Topps baseball and football trading cards (c. 1955-1962), featuring key stars and Hall of Famers including Roberto Clemente, Sandy Koufax, Mickey Mantle, Willie Mays, Yogi Berra, Roger Maris, Bart Starr, and Paul Hornung</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -438,7 +438,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="240" customWidth="1" min="3" max="3"/>
+    <col width="288" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lot of 6 handheld electronic LCD games, including Excalibur Casino Calculator (2), Milton Bradley Electronic Yahtzee, Radical Video Slot 5000, Solitaire, and Bonus/Draw Poker, c. 1995-2005</t>
+          <t>Assorted handheld electronic LCD games group lot, including two Excalibur Casino Calculator handhelds, Milton Bradley Electronic Yahtzee, Bonus Poker/Draw Poker, Solitaire, and Radical Video Slot 5000, c. 1990s-2000s.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass souvenir bottle with screw cap</t>
+          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass souvenir bottle with metal cap</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Western Electric / Bell System Touch-Tone 'Princess' telephone in pink, model 2702 series, with original printed box, c. 1960s-1970s.</t>
+          <t>Vintage Bell System / Western Electric pink push-button Princess telephone with original printed box</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E.T. The Extra-Terrestrial ceramic nightlight figure, likely licensed Universal City Studios / Sigma manufacture, c. 1982.</t>
+          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight/lamp figure, c. 1982</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage metal construction set in wooden case, likely A.C. Gilbert Erector or Lionel Construction Set, circa 1930s-1950s</t>
+          <t>Vintage Lionel metal construction building set in fitted wooden case, circa late 1930s.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assorted estate costume jewelry trays containing beaded necklaces, rhinestone brooches, gold-tone chains, faux pearls, and wristwatches, mid-to-late 20th century</t>
+          <t>Assorted lot of vintage and modern estate costume jewelry including gold-tone and silver-tone necklaces, beaded strands, rhinestone and enamel brooches (including Christmas tree pins), bracelets, and wristwatches across multiple trays marked 12, 14, and 16. Mid-20th century to modern.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lot of vintage Edison phonograph cylinder record tubes including Edison Gold Moulded and Edison Blue Amberol records with cardboard containers</t>
+          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulk lot of assorted estate costume jewelry, including faux pearl strands, brooches, novelty pins, and beaded necklaces</t>
+          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>estate costume jewelry (Tray Lot 3)</t>
+          <t>Assorted estate costume jewelry tray including rhinestone Christmas tree brooches, gold-tone chain and charm bracelets, enamel pendant, and beaded necklaces, mid-to-late 20th century</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Group of vintage Topps baseball and football trading cards (c. 1955-1962), featuring key stars and Hall of Famers including Roberto Clemente, Sandy Koufax, Mickey Mantle, Willie Mays, Yogi Berra, Roger Maris, Bart Starr, and Paul Hornung</t>
+          <t>Collection of 12 vintage Topps sports trading cards (10 baseball, 2 football) dating from 1956 to 1962, featuring major stars and Hall of Famers including Mickey Mantle, Willie Mays, Sandy Koufax, Yogi Berra, Roberto Clemente, Roger Maris, Bart Starr, and Paul Hornung.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -671,22 +671,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assorted lot of vintage and modern estate costume jewelry including gold-tone and silver-tone necklaces, beaded strands, rhinestone and enamel brooches (including Christmas tree pins), bracelets, and wristwatches across multiple trays marked 12, 14, and 16. Mid-20th century to modern.</t>
+          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -707,22 +707,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
+          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$100-$130</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -743,7 +743,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
+          <t>Assorted lot of vintage and modern estate costume jewelry including gold-tone and silver-tone necklaces, beaded strands, rhinestone and enamel brooches (including Christmas tree pins), bracelets, and wristwatches across multiple trays marked 12, 14, and 16. Mid-20th century to modern.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -772,77 +772,41 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>AUTO-SEND</t>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-181</t>
+          <t>BT-001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage cards</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assorted estate costume jewelry tray including rhinestone Christmas tree brooches, gold-tone chain and charm bracelets, enamel pendant, and beaded necklaces, mid-to-late 20th century</t>
+          <t>Collection of 12 vintage Topps sports trading cards (10 baseball, 2 football) dating from 1956 to 1962, featuring major stars and Hall of Famers including Mickey Mantle, Willie Mays, Sandy Koufax, Yogi Berra, Roberto Clemente, Roger Maris, Bart Starr, and Paul Hornung.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$250-$320</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>28.75</v>
+        <v>115</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BT-001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>vintage cards</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Collection of 12 vintage Topps sports trading cards (10 baseball, 2 football) dating from 1956 to 1962, featuring major stars and Hall of Famers including Mickey Mantle, Willie Mays, Sandy Koufax, Yogi Berra, Roberto Clemente, Roger Maris, Bart Starr, and Paul Hornung.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>$250-$320</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>35</v>
-      </c>
-      <c r="F11" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" t="n">
-        <v>115</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,10 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -444,6 +450,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +493,21 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Committed Max ($)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Committed All-In ($)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
@@ -518,7 +542,16 @@
       <c r="G2" t="n">
         <v>5.75</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -554,7 +587,16 @@
       <c r="G3" t="n">
         <v>11.5</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -590,7 +632,16 @@
       <c r="G4" t="n">
         <v>17.25</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -626,7 +677,16 @@
       <c r="G5" t="n">
         <v>17.25</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -662,7 +722,16 @@
       <c r="G6" t="n">
         <v>17.25</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -671,34 +740,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
+          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$100-$130</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+        <v>17.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -707,22 +785,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
+          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -734,7 +812,16 @@
       <c r="G8" t="n">
         <v>28.75</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>AUTO-SEND</t>
         </is>
@@ -770,7 +857,16 @@
       <c r="G9" t="n">
         <v>28.75</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
@@ -806,11 +902,41 @@
       <c r="G10" t="n">
         <v>115</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>115</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aug 22 Bid Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bid Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,12 +439,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="288" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -453,6 +453,8 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +513,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Price Evidence</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Citations</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,7 +537,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Assorted handheld electronic LCD games group lot, including two Excalibur Casino Calculator handhelds, Milton Bradley Electronic Yahtzee, Bonus Poker/Draw Poker, Solitaire, and Radical Video Slot 5000, c. 1990s-2000s.</t>
+          <t>Lot of six (6) vintage electronic handheld LCD games, including Excalibur Casino Calculator (2), Milton Bradley Electronic Yahtzee, Radica Video Slot 5000, Solitaire, and Bonus Poker/Draw Poker, circa 1990s-2000s.: Excalibur Casino Calculator handheld game (qty 2), Milton Bradley Electronic Yahtzee handheld game, Radica Video Slot 5000 handheld game, Handheld Solitaire game with flip cover, Bonus Poker / Draw Poker handheld game</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -556,6 +568,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,7 +588,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass souvenir bottle with metal cap</t>
+          <t>1933 Chicago World's Fair 'A Century of Progress' embossed clear glass commemorative flask bottle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -601,6 +619,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,7 +639,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vintage Bell System / Western Electric pink push-button Princess telephone with original printed box</t>
+          <t>Western Electric / Bell System pink Princess push-button telephone in original box, circa 1970s.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,6 +670,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,7 +690,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E.T. the Extra-Terrestrial glazed ceramic nightlight/lamp figure, c. 1982</t>
+          <t>E.T. The Extra-Terrestrial ceramic nightlight/figure, c. 1982</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -691,6 +721,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -705,7 +741,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage Lionel metal construction building set in fitted wooden case, circa late 1930s.</t>
+          <t>Vintage metal construction set in original fitted wooden case, attributed to Lionel or A.C. Gilbert Erector, c. 1930s-1940s: Perforated steel girders and plates, Red enamel cast wheels and rubber tires, Red cylindrical steel boiler tube, Mounted brackets and fittings on lid display board, Assorted nuts, bolts, and connector plates</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,6 +772,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -750,7 +792,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulk lot of assorted vintage and modern costume jewelry, including faux pearls, beaded necklaces, brooches, and novelty pins in a clear plastic tote</t>
+          <t>Assorted bulk estate costume jewelry lot in plastic bin, mid-to-late 20th century: Faux pearl strands and beaded necklaces, Rhinestone and metal filigree brooches/pins, Novelty plastic and enameling brooches, Assorted chain and charm jewelry pieces</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,6 +823,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -795,7 +843,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lot of Edison phonograph cylinder records and cardboard containers, including Edison Gold Moulded Record and Blue Amberol Record tubes, Thomas A. Edison, Inc., early 20th century.</t>
+          <t>Group of Edison phonograph cylinder records including Blue Amberol and Gold Moulded containers, c. 1902-1929: Edison Blue Amberol cylinder records in original cardboard containers, Edison Gold Moulded cylinder records in original cardboard containers, Unboxed black phonograph cylinder record</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -826,6 +874,12 @@
           <t>AUTO-SEND</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,7 +894,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assorted lot of vintage and modern estate costume jewelry including gold-tone and silver-tone necklaces, beaded strands, rhinestone and enamel brooches (including Christmas tree pins), bracelets, and wristwatches across multiple trays marked 12, 14, and 16. Mid-20th century to modern.</t>
+          <t>Tray lot of vintage estate costume jewelry, including gold-tone chain necklaces, rhinestone brooches (Christmas tree pins, flamingo), beaded necklaces, pendants, and wristwatches, mid-to-late 20th century.: Rhinestone Christmas tree brooches, Flamingo rhinestone brooch, Gold-tone charm bracelet and chain necklaces, Multi-strand beaded necklaces, Large cross pendant on heavy gold-tone chain, Assorted ladies wristwatches</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -871,6 +925,12 @@
           <t>APPROVED</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -885,7 +945,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Collection of 12 vintage Topps sports trading cards (10 baseball, 2 football) dating from 1956 to 1962, featuring major stars and Hall of Famers including Mickey Mantle, Willie Mays, Sandy Koufax, Yogi Berra, Roberto Clemente, Roger Maris, Bart Starr, and Paul Hornung.</t>
+          <t>Lot of 12 vintage Topps sports trading cards (1955–1961) featuring major Hall of Famers including Sandy Koufax, Mickey Mantle, Willie Mays, Roberto Clemente, Yogi Berra, Roger Maris, Bart Starr, and Paul Hornung.: 1955 Topps Sandy Koufax #123, 1956 Topps Yogi Berra #110 (2 copies), 1957 Topps Bart Starr #119, 1957 Topps Paul Hornung #138, 1958 Topps Willie Mays All Star #485, 1958 Topps Mickey Mantle All Star #487, 1960 Topps Roberto Clemente #326, 1961 Topps NL Home Run Leaders #4, 1961 Topps Roger Maris #2 (2 copies), 1961 Topps Willie Mays #150, 1961 Topps Yogi Berra #425</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,27 +976,2660 @@
           <t>APPROVED</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BT-038</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vintage Tinkertoy canisters including a 1950s-1960s Spalding Special Tinkertoy Windlass Drive set and a 1970s Gabriel/CBS Toys Junior Architect set, together with additional games in a tray flat: Spalding Special Tinkertoy Windlass Drive canister, Gabriel/Child Guidance Junior Architect Tinkertoy canister, Aquarius boxed memory game, Bagged soft toy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>$11-$40</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2W_UELP728WmKXnhpLvG53h7E9Sf_7yhppCg4g9MC8l0Qe_LpQc_Q5GUlKUrkc-SJsJq1mFDcgQkU0q6WxN0GV2fgVr9C2XoV5mOebChZ3lZZrrNv_WErBQrN2l3Y45U=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE5MuN-4dJybO-YffXLVZ45M2OBsk01Q36WoCXJuONMifwVg2vUPWAAi1pHjVUkK8szSWOeE7XY2oZ7HrojMf8-ZUPXKTNCeS-bKakLrbe1wo2jmL412YlgXP5xRCxtt6pa5C_92FT1meL_1AK1n1wkWxQ5Ztr_PafaD6-q7cDyVeonNXrxBR5U0BgtZTxovnjUgbCwIt-6RjKcw2T3mmlxkcmw3MKpLG1SYfyc8hP4kyd1kY73GiBTGH6b_EBujbcbky7PZ5y2f5tyGlDCay0QcCuk8KNrN9ZO3-1bqSB2Airj5bbohb2Ji0PIh8L8kGeVW-bS35mVQA-dLzRaPENBbV31ptpAmw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVOqybBoonF4uNDsj7-9i64Kf9w4y9GgKK87gfkBcdtZiRShSSiYr7IPeuE1LolTaJNBfleBFegUuSUazeSGSWx9McK-dzd62bCr_oyxX65EKuRsULz4J5Dy0tO3ICYZ9d11t46ky5bcGkEWazmAKkoduuQ53E08tWluE5KqtEemHSCMIeBp-NJRc9HN4AR7A=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEoIh9d3ichidBU8xvYK4XW0ascFZ_qSdSX2CABRiDuv6tapCvftDov0LypQorbOvLxqN80xr_wgLnomLXlj51jQ50v76AbQbHm3tNmw1H45JLlaSVF02lT1lWsuam7MPkKSIBzkM91r84=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQExYFdGHt6FyXDIpuTGaB7SsZQYhNDTsm6ldZUBWywx0Pw_zzdmyg_y-Y6rMfXeI6PPkWuzjNNi7d_DrhaqcegWPT33kBXXf-gs4dsT_VE9VKXoNFkciVL5fWyi9fuKbvwHqkEMNxgmwn6DQ_NZ6Bw8Q9BKsBhD0j9es6dCQbKAGdP3XOKjshWVHvLppLAr8n2JCkFxyxR5PQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF1WB4e1qPGFk6wJhoMZ3Nf9ieep7ygSgM1vXex-O2Cj4JR2BdZUzeEe3ftk48e1pvhWo0z-62BuPorMDpJIbCoVqhxPncSgqCXw3HEQdzyG8fziq6UwLWS0X303Qx7c5M=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF7DhVdHL5HTOu9dpfwikPPHCd2YF7KyI3YQLYWr1KXEdydOE0pb18p76vXskrOqvK3Pz0bGvgD4qiwSbksaWF9adHZ2WOK22t7BTv8bCdaAxw_CpSjNeknUaVpwWTfIiN7oPdL14aqXCossGEPzZf40VKjE8okmiSbQaqhjyIM0gX1gvKBkhJI8H3mDA_3LRFKTeIw_wAPVdfhiP7Xzom_nO9fv7s0-ExdZJZxqCVDYuq_KnIrk7d_pEjBdRPW84ZgiKHs6A5IXIgAPg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFGV3e-GWmUXc-dos9Jsad2MppHFWXjMTq7QPqTetN_tKnyrVBTXDlgnPODIdbabYAG19fcMxasxKItX-YNJFcY8aOTJRwcZTzPxaWtmhaTTevti3w8lmbpEAoJ0pw94Qz9I144x3XvMlX7gHzmnw6CuN2ukWtg-WdukgxZ9tNSCuE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFRLLIhxzrUFT8qf8i97cp79Tg_LfJfQ59Ad-R1D96LqQ-5JvT_lQNubJKD6XBx1b6PtEljJVmoe_hTOSxbbKQRFVPtgkrUx1Wo3KMzJmZTmf6mKeGDotO-6E926vBxBrP6xY2IIrrO0oZ7GlKZHiv1xTuiOD8_uxalu94o-GJiSVzFZYrOvxUk6LyPd_ASDdQK1coJa_dxykr-jcC8i9TXe6EY1n8pSVwyrGD7SXjM0EV-_igtSSggD8HAJUEo1LEVE8Q5rukXkJZLyQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFRUpKL2g7wnyPBdS0VSxctnGsl_SW6V7xq8Jh8tDvozZQBYY92OsMC77DFFjSduuQmOGVswa69OSxvbQlmntGpJ5IHN3QV70JSmKI1qOBzyjPzujOPpgH2OQkeFbtueOQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFfK81mTMqneNuXfy2LAqEF400inT42lMiG2qIH1vU_OZfbC6sBeFdw8B1TZPZTUJRYsp77IMtPQ6WT1KvK96z7TVKaVRWDOD9Z0-ZW7CrzXlCcyxQ0W23DFRveMXxqAGDr6yF1rKdq5THHlUI7foIYvYb6vjdWh4kzRzyuUclw200ccSxCrDff9zXEpP7tkd4Vxc_Bn4Zu-6c0eg0mhzRZWF3BQv_Q4TnFwtCVMiYsiDqQ4eM1ViVNyoLypsPyQ58H8avSV4pQPeYjiQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFite2ha9CafT2BU03H7j2JrbSdwUhDqtW-GMNLr246tGu9rfPWdgUwdHZi0temnDL6ECT1r9ZjhBDKW18fRbJEgUNBPnPEV3sV42ctCXTTWsaYQEwchZmpQnUczvibn6uPd1i9B4DejA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFyIQWbuUamy_tbHmiKB54DgIJqEh97qJslFBBOJvEJArahPWZkgI0cuXMV5lxSj9bRplhW-CQL84SJMxnvIHwI9x8y-J7d8ZAym1u_JgMjl6eVn0jTfJtjpbDR5HEx8w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1hpMwPYg3QVDJZt2MMW6xeDJxbfoqcKF1XKPIdQX4F1si6CLkk_BWnrvZAqwbPEUkH-C3XDMuiIi-dV0xRpn69f4So5JN2kaxeg7mCdFDhcuLzvPvCereDGgKNZjIWytnZpOHr5BOKg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGOGLa8q9OSdJJcrJOO6WcHA742Ov2iHEUaJZ7jT1vwKjWx7pV0okb_F757DfcaouP0DEZK6YKQk9BE-SpcX-bsUqF22I8Svd-eih5g_hPKiuRlBhqOzaixcGe6gsjFdtL4D4jynFeTgrBR
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGPezQJAsuuw1gVG4fVs5SFjQYp4Wo9vJl8TmjVsV1_t3pSjY83bvQ0IX5tkKltSRjYI9AznrT2I5ig6_DSrQrVl-I1vG_kROHX0S2a1bZXcSUF6GkDpLFl3ToLVgJJMfvrMsRFL1ACB2D3hTm_fQnijhkhoJRCQYjU26LmTADZOi5ZWm6LUYY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGS7FH56YksNCWTGCtfil1s6rS2Axyxtc6hF-KddxenaDJiXJZd7WvBrBoX-Y36Pi6sky2-x5FM3OKAhWgNq1DMppE2Gm9Pc6lIntU7tDxqX9PqM3VxVG90SzHeaTLcMcTmGOoenm9_fvK1szskueJRjoU-k7R8GOT8g67oOJgBauEzTMRGUQM6-9dMUcGECdc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGh9KeQIm51JNMFgSKdReQ-mUXj-6xoma1bPsCReth-n8j9jTrgu_R307sLIDJ4mQxF2R-8JkLr90daR5o7mKdPsC5be_-RJ17ocvMj9LHcgU8T5vOVlgdGy7mBgW3b2hc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6g-gnkFW5xBb2DMDhI2pxmLsCQaa-EUk_AoBhRRJ9Hm-EcPF3WgbJFG_CUwqpJlA9WS_SPX5SZuHefwPQhaxY4U5sRgtq8mnnm6EYdSf1eiHykgeSxFq5sGjpb8RJT_LLDmnFBgB4_nrTtj_XZKyOynHtmurODSgdzZJ7rsxGddTNUThjTnlO0Qji2Z8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHH7SqzYr3V8XwibDPJ-0yi9_Ca8SWq0N_VJFBuhtZX33EIBQ7sZunnss-DR5RdZ8SO4i5Qom_IWyy0LqujOedDBGswiRB0Mac6-OESQOOe_ejtj9eP8I-Qx2AEQX8Iga69rQc2oyr4GEEX7VhNXeX4rF9y4RbavQxcw_H17N7_4PSKXunVtbMKTjYkvIqS
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSOTPiPlaTxjgdViWC549KtBgaLRhzqB-C2Ds1Z08ZD4j_ocg4qCQ4PIxeDAabTx7f8Gjvo5atUBQ7l2q8-yUYu_bT10hv3NjkEyp16nB-zBP8_KKigkgheEIO5LMktAKNpT76lAc1l3pBDidZ1bl0Y5RuNijlrV3y7PQ=</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BT-039</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vintage Tinkertoy construction set in original cardboard canister, The Toy Tinkers / A.G. Spalding &amp; Bros., c. 1930s-1950s</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>$10-$65</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE4sQScBEuasntVyY-qUddHieujetX6CtJ-7KNUTMvsXT_DEqYMmF63I8wvladLYoOQglg5dtmEyohjcXJg7S3--qXA7aOmbExm5n9fV9bqwLtNP2s4sxUo9umtekiGzdJkJpjHMnxiVrAEV3UDNWDam-R6ApOqpFhM-Owm9MrwvR1aEqyxwNtB9FwQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEC4bs5zVrRFodaVRK21hYueq0z4mwhNoDQzfEsi5Kz6fdD1NzOqIopz676OM9d3OpQ4kVKqnj4i6mGFYjWr1WyzovzQryLgka6q82iIy4uFByz1nxi69VXSGKQwCnyIBARzHumxpi6e2vNd-WzbDnm-O_KG3bKOieVkPVK
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEFCDDVlrF5CW4HV0YOuxegAmlO1dJFittjHNfuSdybV0kmJqumhOk8lpgksrziUcoz_PPdApY_1AFU90vxYxFNbggKRb3ccOpl_VMge9BSrZUnUftqWjiWL5ZKmweb4rwb36Pu8xQFNWNO
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQERyOUFyj4KtbkDjhbaF9KPCYWyDvJOP2KeRN_fS5gV5JFTT9rAf6EcNk2Bxy3M5XThhUveD3d3pu8A0X-dNl39HVZl8UsE4QzOEohX3LSf72VCtqHdmL6l5qXjnWDzGUqS-JtlDvoFCOKqyt0-oCPxw0AvkayAPzVTmsj5B-EUDHY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEymaBWQLhucpQloq9oE2Gcfw32qtGCuSgGWOIOOVQcbTA4HwvDkhMo3of8NGCK5EnbrXbNQ1s_d-VU_i-R0YglKL9tik52Btol0HoG27bR2F0_yzfmAKSxMDc1I0p5ARKyzYlTAPFrx95dxKfQf1GgXHywXzTnGynFW-mJb2PUI2XDu0xxFA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFsKKwqedTrEHe0emmNyVOw5WRjZG0nsq4B9hLsyMO1Qn0fFTocJT8OyYdFyA5Ek8vJa71MRLuNqnK5irpU8WrRXLMYhw8UE8qTU8yNLilU8Z97K1IUmEtFFETTOjlP1VTIxyjhUhT7mVnU-uOOUSsnsB_RC2D-y3yNLSAyARyZncbnPiMTJnSDQe551_OAug==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvcA7fHqXSHMXZNjo0Gu9_2jVFHpvsBoR0-LVScYXCkBoKghgx94f8njLZcGVyMd7xPw4kC78aUUZFC01hlanVgdwajazC_fIgqxJxrnWJDDEqLhVBgRYFtjc-NRLEpX4I6Pgm-rHRBb0ROdUUeZuDlMTHt7pt8YWVMNDakpGjkHHMiGn93w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGCTvBaf_6LkDUiDYb1bLvWaPhKFhFYG1N2ygucPEzPqVfqrnnNBPz-8wCvl0V_VeC9O5lvy-UiCWoTfnsFN2if9-aWlO2oq2l9WyjkuQW-D9pIw5AtcUVL8n8hIOTGOWK84-oRYI3U6YmpAdFKhfWslmBZFPRKrkeCHl4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGTpKL8ZsgJHTPC4jMKjtrld02hLS-PbmKqovMP_r2B2DorIE8wZaNk9EerU665CI6bgFlf2tfxDt5Vx2_s1p2wX4rBDQKVjhD8EcyRChGw3tA3VnY2QZkQrEOOhD3U80zlpS_r3C5V6BXnMMx0evwKH4QOp4bezparEE4CQTQSYkCD2HQBy14=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGeTgh_7Q2UnkmwN8fSDGDv-8CMkv0XrraETgNl-YeD9tNp-8eWwO0dH8ZJ0tspU_bknExJ0sd7tLuI99ALXul4KhuUEX9GhSYod14V2ydgEulvC5f-LpOfcFUByUglOLYBUKG0dokAX73OXwdQ_jmJLTOf7Is_r1EG9cuSpEqjKI9i-TAxZiF0lQVD5yytL4sybGIp9m_07w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGnxJg6_ULraYVnlIAplr7tVCwIBxVl8wBW9h_9S68iTJu4f6AZeNiIRhTNCWuZXNTmOKhaVCeUxC7dCPY59mT3Hyshpg-Wjnp8REeEdclCWjZcDp9ToDfdvtkEu-AIu4rgFKi9112UlK1gg0JGsjxEQS_RCUqnqlpnq76oEgy_sPjevNaE1mf_XGIAAP7oQ28lGQeRslvKcqAmPTGQztVROw76kN-BLWarb6MlbFVtsnwVRH9N6zrK_0tWhGTNfQAzR0BJZIJ3xaLNpk6bLs1vFw-MrfBpPsV1VKfI7JgBwdMl
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGvO7syc4_M4MbPFTN3gBrJ3GKG67vgVLizleEmMYkwmLow5tq_mTc0j8JVePbLCYmHGxbXK8eN4IzDEIa2G0p0M8nkhgYqVqTp7sgyAVM4lLWqA9bmsrJTjXfZhVumKPzUU3jj_wIWv6TbioBPUkRavyj2TbSzO1wCkrOG-P6Wh7ltjbWu9Rc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH-J_EwX0VPWR6YDEYhCeXkW_L58lz7C2hDnVkc9yMvVWHHDiWXFrafo4EQa96O__nQb9guWBAWQZRaQ8cQQbuL79vzGbnvaW_-L0LmycUmvQfgf6gbw6zS85ixdZst6r3OA_QwgObuUvCdBUq_vJTo6WrUXiVAqy8uGVGn_pIVHo8UsfeDbjPNZEKaR8WRxV5A_g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHD-CVHnMn2M3zvYn1sx_kr-XvmoE7DJHRD_qq0HIpkwQyJES642r1bLB_zuQM05muSQXrw2JpZPPj75a62_87QeNTsBql7O7Xz-h9iBM4h4ixWDViyxliYnz33oEjTtiaSaT--vlVeAQ0CDarDx4zs_HlAVHDXg6GCHlAwCt0RCaeG
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHQe1hUha9EKg6djmliRGQFr-oW1dhdlUiFypPWCUW7fzzRmK5OuYOqMvihA0e6ROVa_0wSsqt9DwGtNJx2H0qj4bFijaqcdBqKVT8NnPpI4XDUK3EkmDteJQiurv-EeA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHbcyM8w-M89H7Ici5t0V5VCrw27KROqHlKBJKsRXv4G5iV__URrNvU0wFYGyRa-RByTnRE4CIZpO0aFWMq3QmiRq6qKe52m-VdzxPzEPTZuFLFJP3S1OiV8AbVtPNejOgt0-Ca25pxQOm_1iEZArPcDAdZHgufj4hjE8NDBZaVsygzqZuH8hc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwGKaldwUlMUpPTrTUGt5e55O2CCGyep4zP6n50ToxQgY8VDjPb3PWpue232G9sdgGt9tHdLIUoZmcFC0AcnLWS3uZbJQTK2BnwGzRB-qgnwGF3sI_uKIdhhzgBfcgo7z0PsASyYbnwfqThPIYylPMlqmvT_DnAiSontLlvxzIA7ZEpBDksUE=</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BT-043</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Assorted Vintage Dollhouse Furniture Lot, including wooden and plastic pieces (dresser with mirror, carved hutch, upholstered armchairs, kitchen units), circa 1950s-1970s: Wooden dresser with attached mirror, Dark-stained carved wooden hutch, Pair of blue floral upholstered doll armchairs, Green floral upholstered daybed/sofa frame, Plastic mid-century kitchen stove and sink appliances, Assorted wooden chairs, tables, and bed frames</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>$20-$65</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEEE3TPZZluA9JfBFtHUsWdQsv_8VF_5jtGB4lmu1s0jrgMKpTp1I_9KIaMiGUJZUjykljRjiC07rNjIzdgBXW_cty5qjag0aEvdGVEiPPR6a57p6I3IdiwBLqd7TOW9O-I__k7
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEKGBgGcakE-8SoTMbMNoMdWVp9PS1sTvV_w319bYZRoh1yLj55QwSn9HfoMV4zh--12u_Pa46oFnjMrvURBy4n2otZ7Zc3UE7jmHjgV1XRbSyVdn7Em6IRm14VzW1l6n2ga2HoNlV55isQQ1YrrU1ry4IMj1oOc55_
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEL7yeFGu8D4bhg8ZZ5EnY4vcIVBklgKQYnlmMiBSIxhcNjXxn7eHxfBnI5qDAWV9B3wB0gnmnqIUV0deABvSTRtWTbWMmaYtImdNCGW9EQ173S5WP7i2fcIKv8J4w9S1Dlrzxxa3rpBUImDCQ0yH92C5UX5Q6fct4n6a0nr482BgMqF2TsIbDdwqY-oU5K
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQESsQDCEyL_lccND7h8h7zEqhrhcw_U_oIdWOXkhQfjY_uR65CVY_YgIo-hP4JWdGK1rWJX0XDiDS7w1SFdaLbVzU6VgRIAlsjXdwja2bItXFCA3AUOlVot1ivzgxIjUik24-hIl4X5wCN-iBI3uU9ZQiizwpfEMLSwmYEovcghiKVovhuh84zZdRMSC_l4MIKmDw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8QX0FR3egFshtFqSopfp33CmGRL2Zc_SfTG3F_1wz4kiXkYY-Fds6nxmguma5Pk9QafcN1wM9aQ1XWLilGTjITdDeSrhFa_tOZvn7CPZstXJ-8-z8MBZD6X1equrJKBriMrf5EHnbrkC_RA1uJLRetYYz_Bd22lS7agaIpsvnKiLegk4-OgSLBQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBffNYxpOragQi3v3hfsAkjdNuQtFsnQpRFdE6KDdOCHNdfEu1YS9WlzHUAyYcmQHdbDIVOBHA3taavux5wlwl3RJNAZSQoqtoGwb-UkMt3sFdavNKVV343f5iorUOEkcoucXo7fCiph9ftiA-LQ2OxTKKW8LpW_vnSdu1MQN8MCfezQ_nxh-xyQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFERVU7hROfQyyEa11zlyEm6VMtHOletIjSRZfI9yJq5YzmPX2vFkcgjkYIv317XnEmwbFhn05qYeGRKj4Mu-nTfdJe46secw63harN6E3Ft-j5xBRyZ7j62TF3vwx3BDL_GZL6le0dD11a_m0rX5UDd0GIXzSpyeLq_JfwVXE2rVxdWCe1P9aULAtuwPbyNCyM86-uwwngaWYijnFekja7
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFLgpFtgqbHw9oln4_PCK4WGknjnc7HzsfWDdD-K7hIEENB8HmNGkCVEXyH4K35zgbeJBAps5uxMyQu4ITXhic8mmae-zi5Kr4caDZqBooWmA4PXCX_szQU_XPfy44Bms4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFcRox-gqZYClYP-fiTdsd13ylsdtemYliQ5td8cTTIKoyKI6T6FXG4GwW8jh3-m9yhTOYdSphAfJxqK4ociqOxmMfMKgR7GgA1wW5-2d3q8l9H9aGMTMaFQ92K4afegvS7pSsvHkbGj6KNAVIziJ1hsokvTsuYusvUsEJ73BKl6TVgpszQOzbeQg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGXehKDSJ8oCZo2YtHWe0sacpf-tpjMN3aPgtp83BHvWWfRbufCkupLX-x1ecw3nA8chu1nTskB8vq_m8UOLcCE-eLi1bR6npiaNps8ArPnyW_4NpMyghBYz1_9Zi0LAaLlBCA1ja-T2Xrx0MrYYp6u2jrt9Y3Ym_KMppZCvQrb5HHDUl_3uDE5cQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGexGjZVrzS-CKyTfxI0brozE_bSnSDnZ2lMPZgzRy9W8TEt_AYfTOQxxnl9hXs_Ud7RBigkNrjMsaKNXfj1IFLvuuVfTPbiGC8Xb8c9Le25vQq8oGTrpKkQbsl_JI3Odo9XxB6B96SJSUDGgnSi2XbpZef548rlUY6EbJH2Exa
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGgAmpJBi-Hg2nARHkmiZQC_FDWrUsImiWwJa3Q0hO8UIvshB0F6ku66DZrjeajk1BK6l8ysrK2IWjt8uYIef8YNB8yzgNRBGIitfG6eWvN5gH8mZFUbAyabYxTXEl182h9Ra0Taafw9KeRgD3IYfyDE56LLRGP44pCz_HyiJNO5ZpGEseodzjOIQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGiQIQtostwvv1nQsqsjtjglWZo4dt7XHYoRmLjdGVyZAK3qCjGigDyvPJY9w0a7yNm6m0Wea2mu9owFXm3ODP5cJPHC_5qHOHswyJwPnhWfilkxbpIKtwGe8vKbIkGpaSkD6UYCfuWgXMoyebasrE0qmhtiXwzsxNjLg-uNAZfZ7yQBB2ktug1TTL5qNvKMqkY9A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH5e8KpeFGFyfLNdabp0xrIPdwrH-lkSOwdEpxmvROrxl9aqbu5LgMm9gR94DOnhU7NR9Go_5KrP9kj7lob4RPurZvpjq7Cj4gaBuj18CEuVAP1So6XCt2T5wjXIq1Gz1wdC526Jcb-Kw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHun0mJ1_f6ud3DgyYeUnVpMY7lMoPOmMJHDYQlIsrd6NP2eFyhpFcQy9Fb211RYtMYB5cNNO76mXhqrXrSjADVqiZFuA3MjDLpPvdv9w59p0_kh4X6MoitTnWkB2yEE_sRw79yArJHnggL24tMoTZMysgbehmIXjrTEAE5SPiTApSFwKenMT9hxpHCZqJgFw==</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BT-081</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vintage Roi-Tan cigar counter display box filled with an assortment of mid-20th century advertising matchbooks and wooden safety matchboxes.: Roi-Tan cigar cardboard POP display box, The Vulcan safety match box (Tidaholm Sweden), Green Glo matchbox, Assorted vintage local/commercial advertising matchbooks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>$20-$59</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQ7fQxA3DH5q3b8KH7zH8SDv73dNMBPHnz18mJkhmkgHzUEygBnxssiLxLd9kqXDsaPevMFujh_9NVejIMUWAIryN13_sWbjaJsDm8m6K6ETDfcxp5bM7l9F_YwD9veBZD3CrKsmng
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEir0BxdljUafRI12Mul0nVcgQeFhLJKtG5rz9h9sHwbz8mLnR-1EoVivIZ9aR9CLsO8_AGtnrwe4tFnszaCYrCR0iB5sS4tODp-vkRkMvn9xmOAY4LWZZiREHm_TKOQO09uvHJeM-glA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEqoXcjGJXnFC7OrekvUeDs-RE4O7Xg7TSBmiDO5HLNsx6ZbpxoTEwH0qoPoDjbZc_LGKxLHa8Ci3FDKBFxvf1xwxJnosz0rmuAnu6WZgPbaG0aZ1ztTLaeUsYvVaubePg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFJUX_5okY0kjuUwIioLreozXu2En-EGIvqNZbJLKBRXOek-m_4Fv2Y7kHELU6YpApkw7Mc0_WRefxZaSzHl9PHZReljxRRz366ZO8GTPxaBELLkn0JLoAnutYDMQFtYOt6Be-B97tJ99mgO4netiC78jeQHDAGCudRnEOY2n_TbVDeelD8Ft7ji4GXBsKCukjjygSba7iblM9pSuhiURTq2YhOXKjQEG9llSvTuXVndgJU99COVw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNV00yzYrvmKzY6UuerAAL1vJnqPJDz1JwGV5mjnWz24tRzZJFSwk2ElDuGdGQ1QcSjMUqf7ivV3cbODFxrFA2ouo8U3zR2i-VGzz54HqLws8BrNnNvfMch_ZI_1FEduvnFIfMHbsd_fWcFZpITsr02xu3Y5Qx95JtAGwDjJsl1NXJJPfUvQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVNIRu1dC4jLzZsA8Mctp-fdLshi8NfhphVkAfX5E0w6xhNewLsxsCxp090C3JmZzfb-Oq7lH5a1sPqW2h8w6kfLgOjG96YTI6HZiLiSHFu_8l23zR3ZlRvZsEo8BHFsmNpVySGOQPK7arn71kz_BJ8QQ19AdlT2xahcfhnPAniatdT7mz7Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFc_8H4V5L115zOQNoo3Qo0MYQq_7JvzjPTw6iXlKOlF171jhtOE5wOQGj33VbuTKvZFN6J7V3352ckhfVy8CACzvgLjl6VkmQ8mbVA3x3BmkEoGZM1zdPGIXEMEGLfh0Z_fumr-dt7UghnqR7jbKXRutnzN8WlvLirnZa9oUyfFrKPizZ6DB_iW57q-MdfnLWzxs4RRZ0RMWQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFnLhhMaGR2tyFsv0IBWjvcLpsfAwWT3t379o5DBNhbgnAeq9YkGsbyf-GLDGc8XNm0OxbURpPppWjMAZ0DquR-2_eBrDdGhe97thMgKvGVhsKAAwpQ3IkdUZU0IJGesQ3jKgr0ofQ3UdeYLZBjOq4VNFS6GrjrCQVdMJUvdgQ-_8gjywqt64TkiUoO
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFyLvYpYwOrvvm7XEDQ8iM8tr89RhvbC0yiQdnN4xCIQfCx7spS8wsjGL_NlxdPDoat5KB36L_iofy_p4VUPzZfK-4zoOCscBrFwJWyBufZBanBbUga9wEr_dvVnLak9FeRs-5OdGZ-K7Bind2i8FdQu3CbSS43J1yz_3MkSjbxwmzvokuLLrUwW9jJhSkZgfxNUmBJWJzQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG45-0R74pmZ7s_oUXAy7YM3APWBDwVU97waAEddqbgULjEjXCguTzgkVZxyj3qVrdzinq8pMIWetP6y2lGrh8LQpMN51zs4F0vi6Pjp4CpXB3MAyyJEjqn1y9l4k8ebrErnZhg0NkzV1C6yURmppeaQNfD-1qqZcESiQV-7otnZm7HjDmKjC-Rl0at
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGBkl-ROVB7vT0JLPgTGtRwKkoQ-RmQxufC1AHqey8GDGQ5WRsYKMRRGyKuSXhw8fpDAm8aEAt9-tU9HorHV5WW3cvBQtUZoNvMRCOrPB7Ylxbq9ukIoYJJV_LQm-HDpwUH3C6kL9xokOYC3nU6L8JeD_x03oXw3YjCE5BuvTfsvmbFMSol-ZRPscU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGXCqFakYpre-MZ8BzfGYPCkddl0T6liInHsNo7kG8rmff1diZU1cgDnEn-RSXkyPbDcyF5tbJhLGcSEq74X9evO24vflxOLftGm6v3y-_LF8qeYmaHdkv9KkvYbEnGHiMQxagCeJBplFBSSSFBl5EPwtRlJlk3molWeFJYKNFQsRtd8IZ6UJoWRMotOw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH3NefZyLQjX48wkO-tCDzqecWj4PW9N2W6vHBxfsdOJRPNvLOyn3jx_Ak72GISftAHNdLkGFTdiEEj6r5zvA2auPZR14wADYG9Ht3dQNRPFZq9uTaddwPosE9MvVQw3nA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHE4-Yzw8Y7zYYBjg0DywXSqeYm5ShH4t_mwJre4CLhESgMZyIkbhKFZAiHxLeKyZl0Io1D7j6uZ4CDW6hSEl1VsTCZErzacnlN8KdMzhd1CINg8fCr-wburh0szCzGIx6PeEB-Wr2se0VGIvnPABY4zJwkc4r0MCHAqFvDU77btgrQxGfr3dyq6JxNgJEiFbjnVaHs71pe156t
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHJj3IoIGNIvvQVMXN_9zLKyhqotfv3qmoqC2izC5mxzjCZi209xHlnozUYF4gepSzZmP_CccWf_KnhWrMhQ0LpjwpSZI9ur06l1k8ArJe0aaP3R56zagSWz6pc8uy4apMB85OaEymhsG1CXOOBWwUwB9-zrfNz3nk3WEGxQm8qMLyMWwgXw2sCIMEyXMLrSqAJ9fdjvoRxhBsr
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSPmYooFMrrlWDIRLE39QPJV7Gyo6OGeWSyJvZnKmsRVQjUM8TcjFmDW9mnHpMYKVVpDh85nUlwFOhkEK6AV1_pIYSP78MZ8d-kMN-tS9ydM_iwQtBZle1yXUFMpRLl3U=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHwJEOimrtThxOe5yDOJCwtm9Th4stKhkEs21tEMBDSP0HPIpEGlTN9HP7EzZkM_Bkha4exuJL-1LLV3Ut6pYeqrwoEsScr2lLYRbBh-Ocq52oAnDNuRlTTONwzPUF-XvQuI2NxHzC2UE1fXxDigM75ndf6fwWoE8jMgSML1uP_ZwSNa0QSZeBfZCDkaRcVaviBK46FyuYkbDedshXkX9H0onSiersMYP2bcvv0cWqBkLnI0H67xcMH6umP9JwTPHnmv1z0jnH0pwLTqhcbwo-4N4JUbmBCkyx_Zbj2ojD-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BT-082</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Group of vintage miniature green plastic Coca-Cola bottles with yellow plastic bottle crates: Miniature green plastic Coca-Cola bottles, Yellow plastic miniature bottle crates</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>$15-$25</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFAqvK76KVOK7xYyLgNc--z2U6zgxp3ncZhBBHDsbcDGsCLQGvYo4DlpuMLem_OndjyB6eHbj9vWPgacolb0J6wc8rJyX83j5NooLi6dWx08Yq9dlkkcVEwXJrAYMAjAwHTmQ67tpFImv-IN2h40XtqoITutHHn1cfrwdUf8gLehKDt3UnwZSpOJEH-EiI8nJ0y0kiH
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFHVhEa9QNYWyAInGIKpQ9rR12ZA_lYIcNlPfbFG_G1O0yXts9_zY6Xqr1FrR1ILMy4bROj6lx6FZGq_oVY85Up7yVLuv2TrJQf2gR7bJ99MZqzm2QE5QnDKM-_ROE4pV_2J6hrt7j9aA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFS2bx6JvvgoLxuUCXw44d63_bN7CgwrOu97fEfWXuHFJg7a7M4CsYRWHU1dLEJE1vMyEmZLNJSVXrb6x8Te_XE5_wNlFuQXJFF8eFNvxb0tCvULTHwoB5dZl8LYpWUj7_lwRSOdaNDewMAo3zrxXCwqWA0nT8Kgg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFUtLMskSvP-yZGf_FQX9wlkU5WN8b90abjNUKACxFfxiCzbsn2lM-Z81IADnyVC773SU7MBwe4Gry1cod2SsVpAJ70ycA-QUZ-Y1cnNEoMbUxXSbXk3mhUONBt-E4aQxvPNzc_9obepkTavg5-bu4Geqr4ZOdqimUl1fmcSgjhth8PEuOvVLtaZjQ3jRBxFoQ3lS-4
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFaHdxTXUyhWMO9RWx1D4FvozwljQzigExb4V5t7KDSJ59Q9UXVnX9HY5bFByz3AUiPAQXgUkoXIqL2nBRLQ9NnUiVliAgT2WHYb4yU2mrMy9TEUpBOtqEgWifKCqNfFepsxyJawWrgTA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGGhdfFaEjV-7zo1Zhyyo9O04aKJ2Uzkb12dV_pyB7WS92ncmY9rtEIC6LcCJQ6xlAz2T5MxyvNNqq7VDr68C75S-iHTgv6Rp7aNIHAEe5X0aatpgBUw2aQ730fwSO-Bk2miOCDpBVxcpNQ0JUDPWaCKzsKDMLVar_-b0vJhgH_0LNcoAmvEyXmKvg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGHBx1LTC688pn3h_QJ9I_6E8Z3COg2H5hQJZXmm7Glne8w6x_eLpB1vk4uiYJ1C1xgErPVNCB6-aT6wjlmJDTNMaK4HSpDAXUTQosin2_rVb5kcxkICmIklSQDO5TC5_Q=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGRHEBy2FmQp6mihjr7g_2emfkAPHO-wKpeMBebPhx_UgzXuyRIeVWXKv_eu1BMo4JwfiEHdjYoEeI8Of-DxndX1r1UAfnxrGJEU8JHKHB6Vrh_lQXHRAqydO_HfsDIuks=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGXbbqc15B8ZfH7oEehebI974CVdAGCR6UPgMtBUPysBZ6p7tR66XNjGWQybwRXnwOqyQXdBENfkGJy3I7xS-lLUhbyVAzNLxCDqQCw0KxCVwr94x8nOPEbAhYhZexJPRyldl97kOdgItfIQ21dzJbQMYAPBdnJTw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG_5bId4B5SZo3KFZzm3cneRXp2-RHy7npeZw0y3fu-qn6SOWEKbgOBUpptW8lnwLSDhlYz1I_MvAVFXQh80c5kCGX5jMQ4CESB76x2xfMkLVaUqR5bZDfz80WvrOZl5tY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGc5A8HAGzKMpMHnLNInAgd4Kl4vA73MIqrF_9olUU6BJocRKM8l1lH4jtyNOvI2asxC4i1tbxUKIoULVv1gGbboAnQKmKOP2nkq6PI81RQW6XAwphdS7lyRVO-l9QTSTWvKNVTszwLTWFm5x8jqbFK0rY79o879QLjZP06gvTlDTzd6tRw_BRfmrFC92o26SA2W9aGbyKrniR8Kmppkmk=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGz8hPz8daUn2BMxOmD47feWtYT16O-0Yf-5g_vZd1AZHh9UOK3UL3_7hVyub5W8Q5qoCeDhDInpFkgteaY_otUW44hRfaznZu5Dfm8S2gKQlciPFAk8S_Y3onZPEHpkm057V0yZ3yrNgfwu5dibr2pny3czkheZA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHBzjEL14KDo65WTmLipw5DgJGYqxrQax957UVn7O_HAzjd60yda-SxKnmIXbUPeiDWie2mzCgWoIt2L7zPS2UqPGyt8WoKiSxWyrynOMqCImzXNFFGtFxcmIEziRlCtmQYKEkIiNlCM1be0vkxEKV1HeWK7FQKUM5DevDzUJrNrq7v-JKaTVQsx5ky
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHdPG71apYvaZhfzUCOHIhCHGZaBpiH5LFr5zkocEeX-Ko7Kb8ik-50wDjcfo_j_mU6agznkqRkrCYAFMvY1K28btFFEDupaC78qI0J03B1VEVnwldPB9AB9n2T_h7hiSGCe2O8ONWgdrLJDQJIVFNX3VlaSvP9PwTNnKvGP9htK0xnmHjmvsTUWWjfgZk5ig==</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BT-143</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vintage toy lot in red plastic crate featuring a Fisher-Price pull-toy train engine, J.L. Hanson Co. wooden 'Sketch 'n' Scribble' chalkboard, and a cowboy doll with 'Ride 'em Cowboy' felt hat, c. 1950s-1970s.: Fisher-Price vintage pull-toy train engine, J.L. Hanson Co. 'Sketch 'n' Scribble' wooden framed chalkboard, Vintage cowboy doll with red felt 'Ride 'em Cowboy' hat</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>$25-$55</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE-8JJJ2j3nEpbNbp_b4jX-hkxzFt9tMYfZ5k2JJXGX61PcXXLB3eEPwokzq0IvzsklDMiJcXXj11JQwmVoxNe68mBK-2OxAl9YdDpT83DX7NGp1bDEd3LVqj0T0-cmwoRX0AiOk4J9anqstDr9p2gwneW7xwZq6SCQyfoQmDO1IA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2uzokYqpI3TM4X9OmZ_26-ytIQgX17Y5w_0xqXLOX9UJebKxc6_B2o-etik1DCLVW_nS5mz2xOWG5nEXify4EMhXQU8y0NvvC_M1s7BbXQzj3Jf0GPWJpbv9bI4HRP0AasTiUh0LXHBbNcNCYZedNA7cdiNaaQu__LhhMqJToXgk2gw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE6sxh945SzQR_c7xixaaF-XPeebohdcbpy42A9DW9vH0lZndmRZWb_LLCFTaVY2uoO1X4wP1w8psqcWBY8BEPvYRSOht6c7obYoAVOYtrasVz8vicytk-fBbfD-xpEuoxmZqSUgaMIx-dt7OabQuwxExcX10wKJ-uppzE3wuIBzrw330V-blyeTjemHN3syjayDVDFUgIwxTan-SThRgPBhQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbJwJL5LdFQwOlrch5f_I0AOoQZ74dYFcB172CQbNM3GSOUIvDVrI_PWcbnYPwtTfAW7Drowyxn4qxNzETNzBQm2SqJ8BMkKIxoDZBrgRRXMrq-21cBq0cBjGK9kIvDkgjspr0IiTzVD8Uq8aQQTI8nKn4mKukMs7LeZ6WsYEORDnqXAe7x8Sb5G73gT6-NVREv5yIvG3ZZw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFc_mGTUQjRdY1xIXp9l8c3tXpm3sqIAJuAYlyoHP8Cg5q9ZGcCBHE3hjWGVVwUjrSZ2_mWR1KpTQiBUfcRD94T0rbbNdlsu0LaPcZ6oSRB4tloi7DGQEaKW8AK-WTKbhJ3e7YoMPTT2rtp3UT5UCsi8bY5f-xoExWfl7ZahHwt
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFkkAVKY9IwJ8sObjFDOsg0q1NVU_WccXbaMO_2jW3NwUsttuv7OwLpVuz5MRMNSmR321CeyyTvO9_oRZsBIUzJDXRmNRN6LiX_fu5ZDHglJkvAJytIdyMDo-ejD6z6iENxA1xY0ktvKHdtprkvKQIgqfKUniw71YBy1Xz580gnAKAE
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFxVoyVyWj4vpojZ7nq-PSb2G4BDBwjECuhq5s0K4pu1xJqm-ZlakPhDRhUFd6mBFxpRBXmomuHtFvQgMZD4AGk1i3tjIb1FH7Gvdwd7yucYo07Sn-p2bqjYvdfqbyk9eU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGWyIn9U5IlJBTHCw4Qauth0YIesVWwZRaNXzuq2tfbPsdG9BQLKOTEORAywSLTqBWxUOJOrnODzdbZfOuvUaTK1yUtojPo-N_E6cxAVlrUFPQbrHbG4qJz093Dyxm-5DU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHEFTc4gaXlK-m7V08vFVWRDqDZKkrXGJ0XQM3iAv25hdUA5nSvxQX3Kc01vE801kCkSFstIrHFQ0wJwQf7MZFl2rytM6S9e6wxUhK0_VaxWO01zMVaBq56Vz8J35GpY5o=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHQ-6VGv6D_A4gGctJ7yMWtrMiAFanVyVYZ_9WSLbip_9eDpTuVmjnOK7njCA46y1YPV8MvQ2m7NdCnqaYsc3M8dzESoMoU2DSjUCx3BWOx7Fh7KLL8tghA93R4Urab-IRTIls140egzfCQt3amULW5ECH3m36xecdmXjX38WXcyKuDkuToKBxMR-BAEhMry7msz0vFUVOY5-P6OW3wwxM92rE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH_CJRP9BUmr004U8voDd5NIrOfKga_2RqlU4NmlKIs9L-65IK9-fFetcxo9VXxB3UkWCwQmfaemPYb1VRqyXCooPKH4dVI-dMZT37RVA3dui8IHQAl_3NDc7Au_hxcOdDGk0ytbOUDdZMKBNXqc9EKR0ux7i7x
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHlBIEJf_4DiAnB3qo31EeyptDAHiw4ObVDQWsXVVA_Eng2g1uQkHHJxLs6bxhuIAAA0cyFiuYsKhPBniUsvIis2g7ElE0e0rAjLFJ_WpMyCFTCuufbzaglHCeiM1NGyGI=</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BT-159</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Building block playset lot, featuring a Mega Bloks table soccer/foosball arena and partially visible Lego box sets: Mega Bloks soccer/foosball arena set with player figures and rod assemblies, Lego Indiana Jones set box (partially visible underneath)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>$12-$54</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE8uln9YKejJaxvUi6h3kg4xNA5W_6_pE7CzHHVaDuDhjZtsYQpppPA8WwevPXapJY5xldN6is1Sh41RM-rfvJUk4JEfbjRls3ZEnRziSduvp9lDLuyJOi9ftwX_y0bMlj_XNoLg8WeWoihVTazt9S8YIbe7dIZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE9WcaQjKpAxspVEHnF94X-DeG0OvU6IIKvBZ9Y2-d2aNQrGDUXBVRGrr8RjL2zefMslMdIz7R5BXbHzI_ovroC56GD8ffUySlmRC3qRJdD50b3_5Fzrvq3WEbNKRKm-UKWJ0XnK3QnWar6
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEPJ8x242r9ZVJ7m3mjKv4G8beMBPb1cSLRKtBqc-thV3gqrsNc5KB68o6rfT6SXGS_Y_qBYWchzpKYLTopDdRRb9f8Wdb3m8IFL97_4SMYtj5TheYh5iozmftstlLvzY8cd5N8ZUO5DinfyoG1ApBu
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQERS5qubKQJ-PP8FQyDSWKXJ6xXZmqusylaYc73eruQFzUYI96BwADBf8a-jPYz03jSLvYle3xHXEQtPBHNDxBtNUjxT-kOdRicSW6OJeHstniYjhK_cYq04KpqXAq21Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQERpDG1jVcPpUkUuPuAwFQWmIOP9uLifdXRiN3g5JXXN3ZAerSM0Yj1yxYlMAwBstUu8h4vg-b8FZRRdrwlod6PvjgRoT0jV4pLvOnaAysHwvqfCxvL-b0JLdkQ88dpgwB3amMXDZ6wVU9ftdeePs0kSUiNPnI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQERuuviCFAX4Gn3O7VskvUFaB-sS-WkDbw5sfJJEsB41IVaH2F0-naP5iQQRqoUgAixtY9HexDG8INGGmHUf6A4KmEZTlIwNqaxXsXTf2mkbi5L4swtQ1mCKhFso50E8Tgz0CpkxNswgw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEajaw9yXyBCKCGFHFJFvK-mfnLnVD3mJVJ8oN1U_mxilgLq-2C1KJPSSZhtHGZXigC9m4LTyNTItWSl_3iM6IahyPZ1oPLkE8U5LvND7FhvdlJ48lV_-bdxvX28DCoQkHeS3DzvlYO3HTl_wq_WToFwaCauN8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEcxx8XtHcqiYLfUGEyCCn-r0fth0d_vTDmXMY-U0rius6g7pI4dcrPARh9ehy2ei7ddNpKIma2KQKLTsTv7iWIVT8mCgd74--NcFcm9GKqQ5gvOZyyjA7YI5YNl4X40azMC6VvcAWRAzNBPqZ2UWpOrlLY2oOWZSgCNHo7qvvH3mjEY0Ax8ojV
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEhj06p6tIvneQSxR-fVl2Mwljj14otzfdp2r7ywF3KGcw2H2tQ_RVm25KVAbx6Uj-HUS5hi0BDsjC2jplh_IQg3DopNWfuCjMuTjqH9UaW9duDFHyVgiovBGZMkCGY08TU_nE3yrW7j0i_fKY0gCTs
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFV3_8XYGh7UfTJRU-15nTGpGtetRAOF4H92Bc8h3PN9ZmI-xpLrd5myaWpXWgUpsq7gXoqftki5HC9wiRNUa2C_NphF7s4sFjInWW0d3wyjggAYkuPEBLXDV2R1inFYg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVahdBn9AqkYqdsYgFQV8E4IFkA25IaVu3Y4_lFewGU2Z6M5ZqVezEzGHqkPubMI-1WMHnu-_Ud0W7QzvFeZP9a5ADn35cEuASFOkxadzaYJnV9CQW89KD4Uskjidmcg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFiDTkdkPHmoKCiJ-sFuQtai5kS8xK3_jVccvQa5Hn3_sHtR4TNrcAOYOa5t0yi4mP92c2cg4RrlZXI-uY7815aPRqiNY3n9Xv7RXKipX6nKeq9v2QEfvb0_NU_FQHKYDDhaGXk7hJp
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGv-141kmCMjc0bwcxPoA9gJIdnmVWl25MonaAxmm632u3d7-6_CWXtgiCGPQSH_K-phf4NHQ1IFjgDjF3BcwRzgXyoWqPtLCetsoQwlMl6WbDVNUzGW0OI_9PD90mH4ocJ_7Adl1ax8ksSVNLDT6VrW0PVl8qO
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH5pnhnrbe5iff4ozekBA8bR23WqgjjWmOE0sT9fVNBIcPi6H8u5x4BJ5YXcfocFlvO9YvPhkKTOtMJnHSqCUtMtVTBqftXEr1CgHwCGQA_rfFdQk2I8pZgZ4HwM7nd-t6fNnQ7F8flbRTgMu26x3I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHD1xBfeG-bW0byHSG2BsupL-jaR1yGFadkkJyloH0ARsBZMAbYOv59stW_3TcWQZJPw8q2OgI-BHalBeA-rmFZPIRxDt4JSi_vzhR5mDQLCSSMsfTnrf6MY9KD7XXNuD2n5E_D63zou7svGIpzccqJnNueLTr2fB7JlXw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWRacsow2QAI3OPo3lyrwKv39U7UMwKp9O6jiU6G7X57uZUiGiDQReHTsA5lCpav6Qazu1ekqC-PaGH87Xo8F3UJyJU_BTWIfrE0AVWXkWfmEtJkZEKtIWtihrAsBQiWzBo0aDyFhI2hrgvE6maBH8WV58I_qfWRlkcg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHu9nfrNL9h1N7l9wTC92FAypOUD7YBcuEc1U4cnYweKfsD_bv2XSplSNqCk1ytwhD-roGZr3JPENvo5uvy3mgV8rBuKEfW0l9XNPGtoBvNVM6XX4ZbIhDzQayV7pPgKw==</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BT-179</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tray lot of assorted vintage and modern costume jewelry, including gold-tone chains, beaded necklaces, faux pearls, pendants, brooches, and bracelets: Gold-tone chain and rope necklaces, Large gold-tone rhinestone cross pendant necklace, Rhinestone star pendant necklace, Gold-tone medallion pendant necklace, Faux pearl and beaded multi-strand necklaces, Red bead necklace with fluted gold-tone accents, Gold-tone link bracelets and circular pearl brooches, Blue cabochon pendant necklace</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>$10-$79</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE_Ulv4oMLym7jeotfyCixFRY56gVdRlvw5ujlWphZzUmup4p5lWV68tiQXQ2ZH1-6LFTMXq_ND_Ygz_FjVyBBcW6QiKZw2Nu7J3B4CkTfe7dWzg_rceaMhWAkD8u6zzDWqzoGwkgwKVNnd6RRq
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbq0c6WYx0Rh5NXJu00RzAcRjhMlPdT0DTE7soAFZ964MlSLcJjSiQFxFLPeW-ysmnFSHU_vJRP_yA_xdGHWIGyCQXpj6EBPBBZRq7G3h0m8CyR_tFaO-8GI18Hsyvrc0oKpCafAjnqJ6-ugfTvEYtn-lch423HURVNPNcm1kLs3nkFPA9zx_AXQlretN7JbxQypIJi_M=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEn4Na2jH3BsvLNxk5DrThh6BYXrzpuS4IxCACSmmlP-0JL-IE3qqvp9rrMO0gvZV8orYMuwAi760xRlP6dr0x4NE4KoaPlzTW0nDOV6B73iDCJHJfRyJGnas6nhtaHyaLNbkE5yir1MSe4fUXJ-eWf7IsUagBqj1Nfn8DVsMrZE3R5RnDikA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEpw-KC0TjJYD-h7i2Lj7JrkvUQ9i5ioDtfkV0iNhcbPq1AXp4hA2WWU9i2vVBr77fr2ajttW7xoXyW0URzGoHlzwTrDzMQaiIZiip7JnzaUnTZfYrttD5KfIAcdH33pXVYyIHzOBvJhNHQEwa3hQSZONPaslJtQprZ-Di8AfE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF9elT5w8kkMImeYuxwsTGOgWt38zYC5e-cbm1Gk5Xt5fNpxvx8744aI8C37Cel2oZlGUm3wxZ5_jjQj3KAS0MMIIzSCkXrvPXdDAkbFuGuxUwxXOKFTlEGaUkx_CF2AwuVOz3A5L07mLqxwxKTe0X5PLHIx6ggxsXN0tbGFG2slm_wrwjTWQpeVz1MB4BF376zVU50GkJ4
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFClzv36zaY5QJe9Db6arcef5K_5SlkN-PI5t6JqEMwl4NFRUiyuEso0Vum0N_XPe0t0OMzD2Ip-4rrM6jss4wZFGiOQ3fw85M55ebgPB7TxpwHDNgBbtF1MMShf_akJ72CO6E2i8HHvkqsKmp6TmzWsj7EQe5ZOJDAVmvqzrr1-6jKfVys3Z_eUjusVG9inZftSKmqKWLY
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFGF-2ams8B4utsRfsas2_IGShn7XyQuy4ObSK4ZCMokKJ2JKpCKbuI4Y2Huk-TPS7PQ7b0wCNS2uFGmupj8BKteksFlm9YsYwzZAdyVNcCzRT-56_3yj90eRNZeZM9DPJ6AY61AgRI9y7v2OYhts-L1mdFBjdcDTfSf02qe1Apg2uAsROanfxFbKim4r1jH9VMbkBNYddqALq2YjnT4Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFwB20tsECjIiRvF8VirzL17ApX6mG7gvlrfbl-MzZ82wxvpRiyWhBQgSU7V962QeRg1KqYNI0FRYNE-denV1q4Q_sHMIt6aTiaVNPCv2KbMSUSrXuQakWhOrFmqOb5fYm1vkcB9VSPYF_-Q2N33n18-KrBALL88OEa-BADAJxsydHLFMrQkvEArUaKb1mY_1z49AMFIfs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1rAU3bf6JRWbMwS6-Jqn1jx-KIUfLgtXUcqpK-QPd8cIsFFVtMukOwONpM6dD0A-zxjLtZ61pxOteH9OKw96ze6AG6WW-_K-VQ07S9p7xB3nASTTBwIjwlE67kR1ddK6911xJUr1s2bRjJLcm
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9UvkoidEuPxEXXwQ-w00P_CRalNrzN1c6nlcXaGZUVnkcBRmUIswuTk8GyHO1Q3FpL6SBVVfBVCh6tEpBniXgdiuN2AmTDxJ6TgUeaCf7PduGcBH0eOEoJUAYPE6TkNYTo6UDnMY3O-RhDuU1XSi0PlnPfaTB26s=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaiy_8Cq8zwHBP8-VlxKTRirwEhQxK5otEQbHvX175Vluz-WrRx3b9EVI8iTIZTpSN5EubgRZtfbhKZD8RD79yUkUDpRjD_bcOJZOmiwTzNwax9iyrrNStRLKEyYkmmNH1jyyT6bgZSvCS4FFaYxSUtzg8JRZ_Hs2HImYAxw9quIHkDA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH0M4SdtaIUCYHOKEYzF0fVH-bwwj_3W01p5ZwYPujxVCCjwgjMnhV0b6jQN7zezvE3s0B_a09XfLPBkKC9rdOQgpbb3G1vbnZWi8kS-p4bQr6of9HWRp3n20VrzRkVLxb5GoEHnjwC9zimdfY80GDMRcc45kTEGFMLQFlQ0YfKbiSEl7Byyy3AeZ5eAlD4uPC5cwccxM4z
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHGXALsf0CzANihaF5kx7LZZtajKhBiWjBZOZ429RXcDd5JALCg41bP--cEzZsT0jofmnw875HLZ4HlG96rsRNK6RpF7ajAPCQ4JR8puNgK_ojXGEu8Cj2JsUbkc4gVTGqME8qzb4WvLnW7QiR0SyZiS-RftOPZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHMDfXE2xaksn2WQxo08uei5UYE2M9c6ngSABvGC3WWzsLzW025NV_ZbbPcoWqBSIEsD3S1dUdcEcSqu2oO0-y2vF0IqhD33FFV0NlYpArRuqTaTCJWOWtJCAs9hFdr62pia7Gm4Oc6NQRdyXSXHNcsPNPrcdE2n01HCg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHTolFZUosEGF8R-pOHEyGgcjZOlMGhtDtIfS_ZGwWlnTVNInUJUT6rLGLXbP_pnVHd8r6Ow1tNRKqG7TaWRRM_kkU5fAH9A0t4hWKuPM529HIq8Nc6QKrcW1NrLFy3qXLMD3vnEwXUfWwi2swdS-H8jVklpnygZN5C3kZEtuQgyxkxB2vlRuaMe6ebkrZQosFoLzzOQr4iR4FkmrCyTA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHU0i62zFrUAaKzdKkBBsofgBSt7pso6uHSU0tWvz1qqkmZAdjg5dZmxRjG-zAur3-_LNiktwdUhtJX48pSBgKEXmHMpmnqWaMdJ26j6bg84jBnXEhXzrzn5qEf2iU2z0SlIa8JiKTwQ3XV1JEkb0YyARLmcQ7Q1KKZeQBvqPbHltnRC9oxFkbioStNejTisTSx0y6-_p8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHeTsv6SFWKWzQ0ybwlI5W20qKoGxhyaHDPyD34iSEnUdhiwZrr_4mkOia-VPEwv5_Jn4qC_Ot8IK39brTEKQ2DyWG42weYspTVjMpCcqe2kHiHwodZZ2QkK3kO0Rn4m1Hgpvfv055g8b0Q1hDZKfo=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHy4jCZKXxpNIIPUHCF0WFIgELCZcErxghidY9yfsknq9CdO0XS88jpsZCQZtqruILPWvSKrwQ8h-ISJSAD5fjUIfyMT1i6UnR8YrxaJFgQOZpjj8j7osPn1DT149D_LonqNN2dP3rnJW2HJJuFyv6E4bsVo4ptuHDdziI47tDx0295CO8zCFzW9YMOVmQbDQ==</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BT-187</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Group of vintage Chicago sports felt pennants, including Chicago Cubs 1988 Wrigley Field 'Let There Be Lights' first night game pennant and Chicago Bears Fan Club mini pennant</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$20-$55</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE1RTZOuT58zLgHvS5ZyTujcV2TyWp31qNcVgU5c4XkBT1LAjN-TklV8yRzB7W4e19o7JiXH6IGkb1ST7AqEVUV1Pf8peGUHYvXEdcoWuAtSHvjl26F4ZYLE_Ry3DDsBWxDj5yqRIGe0oVsz6sX8law9jVINCQ4SnZYIz4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEg4zJkeyQ3ljA6QYdYc16qNQZRBPnoLneXYIyLmQgJiXlW2q6qlGlIo9w6nkB6yeLG5pENnNdakTrusOV8ahs68rUXPokt04xrNihyohRAAXsCGJaZIlCAc0SuLHf5QlFXxj0Ez9cLvsrVk2RwA5vmIXIvzb9K5DHnrcG2K_WjLnZi28TABqCjAVnDnEmLZmvX3C0SPTOJ28SoLkqe9j5y1TYwrg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEo9XR_dfe4vSJydj4c3Qg77CzcmAN1ioC9zaOkdszFbERermgsuTfSXQS8ESlWuzbnXeGnwIds1Lse7_PbtIsfueyYB17gWOCYWm_HGAuSmldVkFd77BMLgaxmGaZhH8LASXXQA0yXoP1klfTj_bDer4pc_8cmGjmIFERYAih22Id9KgOHVTEB-lKL0mBY8XBzlMqUsDw_NAGDRdDg9DwqC2YcKEviAt40hDdWo8xRV1pLxkSmC3rTNCNDcIZVjo3o8mlnCMMDJkybBJDXZvXO0Zlfni1OtIZOpOpN8C6UdKrjJv7tnc_IuMzHSSamcKv_8PVORpv5BVb12XlGnWFt2_KZCBFjBIOszC7onVJyZOqGpKlKb42vbqfj4I5uGnINDBG22VLzT5yBrFJNcASBpA68yAG-4TEklsrlSWtBYFpaEs0p7B2cHd4C9u8GHecIVIjJZoE_M6OgIkqsANSyjugs10vLtGLAq7BNiItRdlJPK83356vw996QqUB73zE24ASSXE0IMLIRguX_MCzhbasRAmynqXT6wfnbyCDIVQtaJ_GkmwatNvqflzFetzYMfJji68yQQ_ACleDdSsx4oMbS6tVqvdSXPN9C-dpTJ2qPOZJkfSmml-tcaej6FOf-jC-o64ng5W7yiNKmcVJWMqsZqrNJ7nPYWTGCqs1q4ANQuxFXxxaT9LphOe90MkuerY3jFXXB5rS2d08=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEvpzZQW7DRD2T1jEITIJSyRdtbdafmz2BdkhP29jTKzPWFKKlUDTxItQDs6ycN80ko6SuyWBKHQJt-5uNe9jqDBOKcpc3_bfcirkaDL2BBak1IrvvJQ8gW9k6JCZZJZnb1-QNs-IC3maoahQa7KL5l0JXLZ_U=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF-4VflA5ZYltGlgx65-y8eRBVf-Eo8GpAsvrfgxKUfOh_3CaRJAHnVJ5qIkklBNDL3sdTlEySsr0nJvpBPX6MB8U2HMylXENKTgF7WqZZ9ugQkBIaW8OrDs6XIa3H7qNy3fZ_Gl27DAqMdXldJhAnc1j4SzLNuZx0hsALWApBXdXFwoSd_
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF_OUC-m8oBNjQdyYTQAfFQKpnYZDGfu3T6GsCOEtWIWtfaUUixDXygEpaZPJE11isnN4JRFs6R4f9zryh-R3IPgNgNZmjhe6iEypzwh8ab0VuE3xucpvfprTcyJ3y_pvUAR8ymIm6UaNdie9ejWhOPJnDIZAUlUcNnSpdVZwntIrM4Hn1uAuzy_Ru6pbc66ycF8cgK_0QWGnNhUQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFkh0j4E5JQWYQgY4iPlyWXZV6t2PtdroRzCEiHzrm-7vT_k1kHg20mZfTgxT_0L2ymV2h-VeSMjwwASiSJDXA38UNI3FTynHlb1acudeJSlOSACvWdLSDYEQTvVzZcom4Y1ZX1K601wsUjbhu5ewMzwNVm2vRUB0o7_Cl6WK8Sx6TrPN8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFwfmumgJOD9mPQ56xtPdiv9xw6ApVDvCPMBQulXFxOhvrisojYNISjxSGO2mJXznnU5Ovj8REEWxwE0nn1lPwZNvXa0BkuEieIUs5qjmsmqNkq4frmZlAzmA3CYPsd68JR_EMlKilyTW89oHBb57Mn8vUt21DslYmkiPlzYN4MzdZ238DUWuOPrdnpxdZuYAC9wZHSfNJd0V7G
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG4pYGi920lRi8RDEtuO5DQ5ytOL6LrLFZ4uoWWBZqvNnAUVIhsLijtzhpcb5geM28anfBHUnpDpLPyDPe414Dz_aO71MHa_zLyIVrr3Lr3MnUfne-fXcnGxr5Z5WNG8ZYpQgS-p1_RoyqwInNLoHTHu2_w
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH9NHOI1ZUTFsNqa44OMG-Tl44WlDODew9SeXCx3SVanuEkjdkNnj4_QzldKaFGgMVhG-ZwihvF0xDrIWmD03FGXkMyyigL7V_6tbqek63bRADheOCxBDBBQCiKFKmGrD_JS4h9SJYuXNxtoZvSm7Vvi7AXiz6woBHyWcBC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFgswZ8riDiwRa_69aAvdfglaa9mndS_qBpxv3qQFG2n-N7t5dVLefFyj_nBBku5BhuLqF1RMaJ0DEyi4eXKcjhLI9JjSqTVjHmXWiJCUxOHnGLbNpU46zt6qLeidpT3yGOigo6BHe_7HUS4_FGQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHI2vIq0ydj1AKQv18hNaA9aHXuUePGKaygf6oXQIx2atNgDWQNmLxYwXo5-lcjMXidZrx7PHOK8moz2xFMweshk5bSLKEBwvGs-86PWRVdARPVyg8S6ScTXV1fB9DBcVnv-35cKAO6zaMBxsV3MeQFj_LJ0ghWlo5f0A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHIaunPv7Fz9fs7r8_PlawCUGTz-KtmDLu0wSrFkffjC08WChnLA0LadFpgJ7dCrpPJWmaCTb-Xrqp4dHkG1oa0xJCPVETWzbwAnzPBPZwv0gs1RESkUER0j19aIoRHDEw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHKXzb_44u42JeECuR1LLx9GbvohbEkj6b1U-abuppbNtHTit2ktSusdsPrevh2WbqT4FtJKEnuqYJR2DTKW5RoZzNY47_nAB9zOCjUZglbyJeIpbbzhjLpwWQiZC9-jvs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcR2n_Opilkb9zsKItgBWUSJKsxODEBkQPqpEsxVm4zqRMV6_Qkyq5ofQR6LOnfDi_ZIyg6Ojj6JiPsBxCpAoNPnY0HPVg8czKOkIgCe8JJov5-f8vlA4q09q8sy6eoWLrcOPhtNu0dGKV7gZH1oUOXNfb0LmpVNhYYfN_5rkJOAs-oGH6FoBttDer5vOLsti3evVjEvb9wkkiOsFR
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHtkzXIEl4qAD6HgNBeV9v9r_py7EDSPwzZHnQeHLjy_Q0Yg-qAXtl2GVs3qiHmPqVByAbLplYReC88ryFUC58lg5x0LHNZRNkVOkzhy9Kg6Bf5Ljv_Lv1KRP8iCw-Wdw0Tor_Fd5owEAreahnN8AHKCy6LBaLlIKLjBgYOIwlkA3QmtpaRETGCs_GiSqQNhRuyTsA-xiTL5HiXvg9BHg==</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BT-247</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>breweriana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vintage Schlitz Beer Pop Topper woven straw promotional hat, c. 1960s-1970s</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$25-$35</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE3U-ruFdHDgnzd9lA-KX__ysrYchY7diIwcQh9nfRafBUEdm40ektvtdsRLqK_LPoWyw9dY_9lWuN1OkeXP3xbV5i9yAf1HaxawI-5ehXNLCnyoHhFJpxsaa5L7A22h_QilAtu7lzoV0_M81scik99fwQBnlXbSzIhnXloQ-ZlyvtjOhHj
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQENmk8VAhUiz1wcUbN_ZAf3r9MmJl1tbg_HxmSUuCL1iPT1yU1s3LcS_164XlDCNsgo6ATL2BS6X6hOvm1-dB821htLYS5lCE6QnzwYyaAeunkV7F4g0zZzqzDcOFpvry_mXcxecl9W7dPN4w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEZZK1P1YoFlB-AvXn7y8TXelNbC5DxhSgStZv8dygeZIyU3bwU0-1csNZA1m3rVw59ICBA8cY9niQCKkcS5A1AxFx_-7kPuHA575WpxVCdFCHSO9xE33s2TR8GwhMqobXOlgRQQTnHdXQOe7DNAMTH77ffvqCGPO5IUY5Zj5IluRU1bYSy-6Mdf5Jd
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEulbVNTMAGvyRlMDW0IvuTjgBW2XVwg_9IH6qStliLHAeDaZOH8JO7ptEnreYeQ5QctHinZwVoTb_wnBUZSbwCKGTuKgW0-DVmE8yIvOcXraYHrsoKR6aY4AoqFv9BtuYkTJ6udlEW7U5xE-L_eTM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCm9_gffUxwL8BBCMyddD2eOPoK38qyG0ZixdOSf-RKBfH9TrSZeRaIIk1TPuwDxIdMIeUer7ESeRCkeR3ljuQ_c-IojzJlxLXGt_-6A1Y0u71ylzmUAUNWAwysd9Pt9Y=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCxkkADNEVab5x3aFk8FAeZB6nXhR8Q97c6jVGPex9V75-txIMDGpiZmnIbM5HAIDtppYBxZiuVmz-K8RcXFeL1hjfd-oWPmOM_SaPosbAk_Bxy_OANjxy_ZnTnFrqi5fUP0uBG5LjKwKSKbOHSzbAJJuFC550mBgyYQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFGXi-mdyTBfiaLNhZReBx2Ci3Lh6y-o7WDp4bKcq5mOZieTf4gECffFjLBiNIqwm2bqKrS4YZbzCCKq6_yUZ7yi3jjfiKQuk5duqYgr8FB_Ti70Fz-HPlnH40B900N-I3vkG4Cuayfu4XghQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFRkS4FSwS0Qv0TzJBH_zxt4_4Gp0oOy9Sxj73eCCG61Ukgbbtrx_RUS8uzXkWg8DRK0CxaITKwGXUL0YvsQGmttJayg9OiVdBNYpMrBXmArMXOUieloCgPTutU7zakixG7Cgh5C3VI0SwwuX8clivysKfgXkqbY_z3jz6LxBdA8e8ERZZ0DHvtP1x8MYORbxh06l1wMGc_Hb7PLy_gcNPJouPwb8motd2wGz1a9F_jIx0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1idLUojflhTlx1KZAoxGDxzDTB_yeoI0g8CVURHKhWzogS9QJYvf97ZNPx42lN9RboC-L0guyn1YXLFVjXbD6SWuaiBWtu1Cc0OeklIs5FpulEaBN7dcm2rhtzdh1BKwGpia7nIfP1aJovmXW5uZpcM5RyyMd7fIR5TjLeP0F9DdchvOO0TKGdWORRXcHvAPYS778kZgTJluI9bhYP0Spvy0R-AoahOVnJDuQrnbHMFIM
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1rmyZMUwryLemEbX-sIFlmxSMLrGhhO8SBrtUuAKgyRv93ovoTQU_YxVJw_4mV1Y3ht5FL_AC1RpjuT29ZllkZS0ESkIdbJjfWQIO58w689z-OLmRCFpCwcXizPFJjoY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG41Se9Xey9BCNV0vXxV9ApJkKf4uat6Z7eSoGpEfEbyJUUFD_ZvIA8AeRe43BoPw-a3btS9SeCFYP7AW0yl6p0ufZf8jjgzAFyWC46oU4c4LFKtcUV8dLAQN-oEhGCrAbnYhvt_DKQ7K_xnso3tB0FigfRT-W3AN4AlsUoY4EaloyC5auolT0HSRMbHki4WzEekgKqIQ3San5SZSiAYi3ijbsuFEc-34sotKe2Nit-Stg_s9eGogcj
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGUSwXcJZ8m6GrPHu3kPntwN0GoMP_4JwXMacfBGhhQkHVqRdsWopDAfO2Mr9z4WMG0W2mN8NS_jx60CMg0_HMOsN6SsAWId3CpLzGKAH9HMnUW3_X_hL-ZHAg9af7RuKbhsxuuSMEctbOIE2uSF-E9w06mTi3LNXU43xbNGno6TzbR5Mrq1ja2X4Y=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG_pQ9brYdAhx1jYz2J-deBms77oNHnayeIGVVhJTvoBGbTKLMZGBlnyHsN0W1zVfb2Zfk30e8rW250SjAsKMQTbqkXeLMCGaqrSIQ35Fz3x2cANOHovSWwh_363SH_OGgAH3sE9DZJGTnI6RfVKF1RN9B34gO1zsuP_ngSRPQZhkMFUodsxGcq48_M
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH4NRYkHuBQCfkNF_0KjTsFNc9QOuFjiVTU_vEbQaXwC9NuOW4Wolk3GGWYy9MfmALf-p4A_b6ESIgz0Xv7KYBXhnwtBdt9HEz1xbUNjusQmfMRPadNhZ90y6ic68pXc7czbHGdEaCIGn3a-A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHCvhemFuIIfT0RVrFtUYlGWUdILz0thLVReXH5zWPFMnTiBEyiRKne_0Ez9NSal4kepfwpvjWSCcEABQEuuvpMUvu3Zbeda8gNhOaMmdoydus1vsJoUcI6xTKq-NMbvetH_9SI7vnaqx7nVDcNGvM=</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BT-256</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Collector Barbie doll, 'Barbie as Scarlett O'Hara' (Twelve Oaks Barbecue Dress), Mattel Hollywood Legends Collection, c. 1994</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>$20-$60</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE02YPeiCUYFHBByWvNu3e-bMn51ZPX3AkgUywFp3IESfbjLD9eRXxGgc1VqjLIt-z9AJt7-z3YE5lR8Wl_YofRAKA0hsSQNzX-yNjSptZpJZJHn6HNLBYtVNrZTM9o67o_f3oNGSyJFU_mVEtbSDmgmCJZ7asScJzr75yS-vTzJVoDyEuz3iPrNrl8rxmqjisX8ahB98PsndO21hQPk-6DsR2AI4gQ0xsPTgchNLP3Lw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEFbap0X-mdY_kyI1MdH1xSL-U6MfIS6XgjCHgqoVDcRuKI7RhsH53XRtzHWlM0c0KNj5CKNT3Qj9NAbOmp0bqs0i3nqbChN6dCVITCZ6sXcKuhh8Q1T17IU4qw6T1gH5pOejPxGspGO6zz6ETaRYZx25AefqpdwfNcP_yu8yDdu58DtJGXDDsvhtmUVhLPsIyuFcDriVdenMSsWf5pbuEAEqgxdse7hjBngkOMpYwGf_gNI1ip0DWkfkjnwluRAySd-9dbquY5iMSS
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQELQAgKgElkLa8rKAm_-oo0H_thCp9JZeRldirc2yECZzLFtbuFdp17EBSAAkCRmfysIUf6ZKGPxjQqlKmaEKPM6pAPVZb34M-z68TWSe-7axFZtZSXf9D-C_SSv3nUnWzwGdi0_Sv-uA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEksLlcD4I1nBtsgLeYIz3xS-gL0YPRP5NhWDXfcde7OQi6yQ4jo_fX6ehTE9qQ5fu0coeVPa5kyYwAkvEuTjitawdJm_yBxsKHuzRz1-B4yll_KdG-O93pk8ZMsaXjSJCjaU6A6hCDVi_QRlxhE7AsvAptvEsKvfit7Jc6l5KmopWV3_Ns
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFc3c597ZFtJETXsxA6TZ0xnBlYS8e3qjbUrEZGqk7kK_PH0QweMWWGYDyz0ecNnSsm0HucPFlHNpIBaWhAdH8kZndbDy1VZX4rMsmkf0-IUVKD2eerIAeJ5vwdFTd9i-E1OwRNeZRlnXshD42KmfKjHBye6H7VDW9RkutgHnFVDB6O
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFxZ_rpd2UWgU_8vfkiw_RNEpu94fjr-wLR4_NjiJsn7XYTYJVPpzkMA0jNYPGjX3trM5Rqu1jeSuj-3egmb7qrtx2aQ7K0jpbwbBHeM8tLlrP9CGPfYf0kG0afgTCdcqM0VY7kNwHuSItWBVXlydX117OBSgL_Hmyyp9FIX67cR5dIdgCsVSGyk5Al24cO18SadN9-DsqIi66lSrVe4ibO2oZQLQnuVt68yfJiafY7pRH_x_0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG0km35upp-85PDxbFhYNmEZ7vk47WN_29xJLDVRqrV3wYq2MWF5dFYyx3DUbgkDenP2b7XV8HfQ4VjqmWx43dr5cNE5GxsmSjDcNa_tn1lfyuVcIpn4L5pXIBuHltJILTgLVzZhXr1ZnpbrnyEtMoE6m0rz4QULXz5yKXi4rY1dEK029aOIa3PiNyfaalwYXqWNmGFHrkNR9dIVRMyDhdtPTgodqZEGGm1iBt6ipVm8IAhH3I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGEQveZRivAYGSMUD4iqJckblI_hMrYdrbye_viC_pb7WXkMe5qak-_Me0zLUCCPjoY_6YL1ask3XMYZFhbgC5lr70hZnMOjl3j8zh2eDq0LGZ9IU1hB6U0YwtJOeKjXjg-BeCiQ_A84JCurW8v7oVyH4slLpY5UXDk1fT2yReHXPxSbhCHU03aHe0DBfXSLrDYi9r41lSN6y2Mg5StvA-UoCEB1YslTxISGeH1F0tI5z_zUQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGkp4LbVe3uIw5gdE6pe3bchJ5unSUiL7tl9kMcOxXcg_w1yGtl32OloI1-5QnxiUR4AyriSTdGy58EulYWK0uJ0rR3DtU3b5v3auZOZ_6RVXPLFUdaym3eECF_Sqc_eZ4yhrNgZnomZoUc-8cFQTguc-m-mdPEBEB8czwsjhu8WIU3
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGmluoPxfGMkmsx48HMBECf_AYyfjgtF6wvw6o4tBfTx3n94VW10mpj3KpY9pDqq_XMYwbBAzSH6UEEfP3TIFVtzB_BYZ7PEnuIarWOxdu1ZNyQzXLbfiMaB9xA5Ta9hExoTKKrRDJ2g4UcwNIrCpp-3tELSF_NeEgdtLOJAmE2kg388_qbBw5YQPbrbDmoN9jSagJ8D5fDIo_LfXm7G4hX0Ifac3KC03QDoAaQKki1RIArFfL2WIKrQ4pqWS3j40kL-fwH7WEgGg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH723lcoY8LdlAO1wxubzDsb5f7LEGp91ELZthW_OY6k44PvJAGfaamkVVgDP4kEPSJUWjRSPJ3JK-rQYdTrdJDgZ1qSmetKbKFx63VOrb7QiULZfLpjBj0o6AdwLZ2Kf882i7XlXa3JST6ibnUhp12zmBkPIABtQZL_Jx_YcfI7D0FkGsQFhrLe4ogIYAzLIsFl9wMn0ezWDD_g3-vfNUQodA-NVMSpAar9ydY-V55JrhME-OzLutYVAQ5j6MzJuNOWFaY2B7y8w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHoD3YN0DdUIt7YFRD_vGNGf6vnmYmL6RYV3Bb6wtPpsALwTA_hjEGL9P35pmCkJA2kO-30rJEi12WvtFlD9WxaWr3QMdlE6xxmpYkBDOtd4ROqKKooshHVQsZXDBWHN0QnDNIOHufPcjig7rDu5UvWjVPaLTk8X39txhzXh3hb_eGt
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHr8a8OyzUPq0d5oZ-0Q8LfUbfogr1u4h4bQ2O9vlfLvQHSwj3YEpFO0Izzm5uWaHr_QjqJ2rwRoJ-MMFobe4tJq9D0GLUNlXU5IfvzrwEJO_C93zJhTIU2d4XoS3Sv_3oJDudE5YQcu5sIlTqjOVZe7HkJjmaqlU7pgNeLlcfKegMhlM3Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BT-274</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>breweriana</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Group of Budweiser lithographed promotional tin cans featuring baseball graphics and embossed plastic lids, late 20th century.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>$12-$35</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEE_bX-ueRRvJt9bI4CIN6HoinytQ3Is6j04fCTdbksoAgchI8kgavX0G9_kI-XwDDz7096wpBZ9SQ98ECM5F-ouRbJN1q4RVXe3dLAvJ1lR6Cw3M6kNLsgmwxg0XEGfWb9OuIGqA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEPTKigmCriWItB1pzKP9PiIB6k8jIZN3hJBbgY2mPCofhrdeh55VGa7N8UaEOWh5YeZj0GMfPiFDIIIytkYSgq3RqvZu0bkONs3F_lH2OdBPPgdi7BhsnaejdG4z2OOntuOl4F_-wLfg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVxYcPjnns3GRB6WzX27grQXf0dHRNG_97kRzcOcBIlrwZfqKhhPAH4oGbgeGv6DIxcGuf0-w25i46qpZOavBNYmMujPPI1WihMDz9EJgO3AbN42u7s-epXlXJ70gDqQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEf7BOydqT52zuWokxXoAZW2Na7FarTzEZM9tE_LVr859q7M7meedaXg_UXT8CY5DBltOHddpwfv-pN9XqY-PiYfz2exxXQspNx5jbTjhTYwDVggt6WkZ0aixRqMoBcdb5WGJPVSsde9A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEpjb5FfOzFfJKJAGyCT1LurGkW-MsxOLPBXad1svtI3HOScjyay67a0FbgpXatoIypPrt82GTokUigGdi7Br4v2jWB-Ovxq9JkIlOFnnJeqDg5lfi1RKmrOPR7Ab0MQWc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGPGPj7MTGR-KHSvyIZTmP7h1jt0gPbdLMpUxdIHExhXREoxNmvw-BMBeZx0e_6XZIw1JkDwB6x7qMO2xw6Y6nqP0jSg_wdcyS-4y--2KPLJqNodJ-Oh2eMy1sT6rgAqw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHNW0eygsNN7vJcxSGBnpdn_-3C9ezGOP8uu-Udlh4FBQwHZo0mewuLGviyNtRhEC7OvwKlQBlSu53zFCGVKAWLZt7tVszYMGPLTFwaZwgH4wSvKcYLa5k1uuBU4f22a7uiL2sQczEHeTaXCr-s6h8ZhOS5RHRnvtZQuVo6eaGOocm-
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHVasvANE9O96_SjzFyiNaSgZgSnpW7MIHXkFCVMQjQuANiL6Tl37-9ZmoeRMYSaj4Oj-3WBxFkbGTgrRtQgQrGyZ6Zr3rBOY-NU79mmgGA9Hp8gX6iV8VNNmebev_Wgj37zIxKaa3SA6YeknzAP5tSdz4XnQsDCeCETIy6RO_ituQLj_dmAHrf_n7YDgDGKA_bYB823C3hXY2KLtrIVBHyk7_b0StEEPbVlikqvTNE9gs-MYJbQZJXE509JsLHJw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHeRMcCl9lO7gE0zne6Ni-12PDuMl8QeJERSuuRQmbLR3psRUPKVctiuxJHUTO2mzoQ0Ocd0ZmtQkvyB9ORUfxeS7sPUphimZmr73SphfReCo2vv2A87HmFYKtLCqyqiZ0nWI1XcaXJ5GMij7aKnENl5u9VVT24glrrMUcFuOsnkmhWn0PLWlmb1CrQ2ZN2To8UVRtX7El7YuTlIB655rc7BE7IhjQuYv97V_Ca2Xx_nALLdDNxEHFSdIWwWtLIkQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHlEND8EGEM8fohy_ZcERpB8NUAmTGpU--UQu-duRYRjdklaFSegfw4SPjy8m-8sI-Bgp_seuJ-2KV96zqqMV-vyia_SqG_IJA2Yr3cbaJxl-gowoOhsYPYg3yhXz2SlEc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHq3QUvEWgetp5snrnJkW_K_Ym4Hr47FwgGgLWUhlvxNUp91agwUJoV7XGswnaxaOf0bibTjlEQbrEmZQjiBO-ht8P1zAxCPdCqLDV9XTE8ZTQNH_b1bT0ufEJ2fCEyB30=</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BT-337</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lot of six vintage tobacco advertising pocket lighters including Camel, Winston, Salem, and a brushed chrome flip-top lighter in box packaging, c. 1950s-1970s.: Two Camel Cigarettes advertising lighters in original cardboard boxes, Two Winston Filter Tipped Cigarettes advertising lighters, One Salem Menthol Fresh Cigarettes advertising lighter, One brushed chrome Zippo-style flip-top lighter in box case lighter in box</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>$12-$50</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfL8jI4m9zr72KeMiOdx5FPWEUzn09S0KAwwy3DmDWWSbNN5s4NmHlQ6hDH9kCFSXH0WG-U8Hi8ffLrtsmpr08EpPOGW6I0U0APFSWErPrAMOxJN5ZdHaoxZ3MdiOy6fg-WA_FXduLJ6ggA69Lp6O-PUXRUTNb8iFQoX2oWBFCdUPMSIT7-gSmZyJJJaUv3ydnuQxdeZwcCK28yMGc-dlB_55aIw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfm3QPawlhrNRiFV1_bDCFJvVOe7eUcjFSEn1cRW7hJlCTKmvwyqbc6XrmsUIRFbBaPi-bXcobaiwiqEAR9WPlkulYhibJ2DOubAet8GSGigQ_tcXkVYViWjgKjIXOq4s=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQElkyOpXO7jGSGNmcJt8av-lNhNeUO3w1eNC0TFULfMa9is1VyRGWlYWJN3rZlPEgCUUG9Qa9Wu0EeNi_VN-suAO7KrYu5tXMm6TYD-3IzAgET_dFCWQBu1R1MzJupa5dhBHgLPQANVDaFRpabNWIrqHcVwpCBZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEmPr99O6p-d3ek2BZsMHEu2WpnS2G2jKED6rl1AMg3kXsp7M26_79GruEzssmwPL1hUl-9Vh51ZkxWDjiEYm7ATTrBgtp7guv-GWQfKzJGXP7nFWvcFoY8FjHM2MU14gWQuY99WsQxZvutQHfE_z7py2NvcST3J53Y4ZkfGA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFWMeWu3c0YbmWKd83ZCAm799D-3tA-Q2r9uLfqWr-2ZQvG585iIqiN8EdAwHeZK5fYi4GSj9l5Q4jksoCgRyk4aqeAEPSWuqEmNNKexHl2GFNTwqBXaokWExSz3L_N3bylwOmzAMTvw1vhYlQ-GECoJYc5MNWoVFrk2E3v3VkX267brZ4CycRC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFzqbGzsdM0HmHL_NbNWoiZ3kKBE6sLQjckgx29sqjTk2HN9f7D6D_oZBRUISYaQlLBbPLcbhs3UHx8mgqQQbT2ABVQ47y64k3vM4Lkkpm_Dd6dOvDLkFkplrNpSphTS9KdiibhQKqxz20cUXiSyNDURyyR6TVnba5M-Z3GgfBt1pMCYV1Em3wMfrC4QUoH3uBhB0Q_Ld0HchR2z-vE
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG83GH5rPgXWJG-4S5QWzGWYKlPkhYKtzySZA1WwsfZ_sERxgzPIon0LGWrXQMA82ZpADJ-PZsL4eYZaCQoOFu20_zLDGO1DtRrXt4LJKUqKBMX5haQIkB7I0PA59Eqn2Y0iIrNT6XB-wF_rsqRwiI1BG_R1jgGYs1qglZuh6-i1u5X1Kp9elOTGRe__M71d6kIk8AW
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGBx3lLREQ7g2zHvFdpSMOJWScG7q3U25SAwsBt1RegrgvYWqID-7qJdTwiK7cglmLA-Izxkec3lNgEvcOS4uByHiXzVc30I-i9ULgvUEt60lNq9Svl4U4y_iQeTbWaZJa4ElY3AyekQyFboQtOPXT2coqQ42Hq31-0snyponRa5U4EWIcvG-ppDCH3zZRfnxGOApUSSqSwYAjjZgKOChCi0iWP
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGLCmPAT2aDmpw1iwHmo_s17mKONk83nxKvmwxYqSmGFTlMCZf7_NbcYZ2wOiKe5BY5p1dtNo4rrDfQ2UzGjuAJ_kl55heyDJehoyL4HgSv3TGFHv59UGVKAYRd9D1QjpWdnB9uKzaI4eai9hICVzQmBD1KmUa0aQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGlv2VCNs-KJY1wfYEolWFaPiNA3kBoJfq8I5grAmIe8GR1XUxW9aG-ZnOiV8y8hIXjlrvzehhFDwjLqeKjuWEl3P1A8ocCpi_CtBVVTvjSZdDaOdPH9FaPmrNGPxCSeBYNhs-q4xMMiIeLJYknlrIRxQOjWkmRAhXbCo7yP5pZFW0DJK_yEJcBdobIfgB_QVgoUpqs
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH2cB5SVN97_BGl1wf60syoXoqKMRe2kQWQHb4GQJAdMfC90HJlxJUwqimW7nply3wWtrx3m0zeDyI62jl4J64mGrBKtgjBvtStbADYLiLItgHygTz-PlDwRBVj_5OQE9K1x9uXtXYcinNoYg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHBTodpYeFlu21DzygHUzSDd1oj_Tkefv0Kh7xxQTdI2lhVBqhz4009X0Mcbj3K8ZIIknrwwLSw4mwdPs8kGMTLyfh5XJer6n5fWK8uYq6rgV6y9ESqFvHM64fbQl7lHgYb1t6wd0fSNGA1XxSPW-vHHt7MRDQiQsfxsxPqPKCezcGRArzdTRWN4WOl1zANakS10nOGyw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUSvYas7CSAbNmH_Y56QkWiS7JJkSxXAUNQmkuLV52KPwN6htHK6VmdkLugtw72_3FArGTcueRB6qgdk_O_NIU_3lCGcXqpAzcb82SUjdIqQZludJD_EwUSDb5d1IoTt6yWjTPK9qG6zFPCZbRJQZ5CGalHbELsM4Pza7RBkEAQPfcRr0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHjc3NWsc4R8jRNMxxBditO-xrL-goWcAkgKPql4fEpJaFmocxhz7g5p0XEAX_HHhq5sIRN9PYKOdKvz2uwacXXDiI8kk0F_IS7ZXiMsdbIGoj6DfnPeTyYeftYIS8tMXKNlBydTDcDjsWYUFNZx61v0bU=</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BT-362</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1991 Topps Traded Baseball Cards factory-sealed set (132 cards), featuring Team USA, rookies, and traded players</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>$10-$36</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE0k_QwJiNrVYS-Ssj-Zr3N2c1dd1QScDh30zvAzQxGY5fPoe3AuaHfNQ3bY-TRLLbJkKb01JbjvkzppMmCn8ogp9zZ94tsCf4upBcTP3jkHj7XfPxm_JbAbl-fClrpMMlNwCXfwdaXe-zX2ngEOK5NLYe_q-m9eI81nGdjG0QlLiHFQkSQVCeVuE16ffpYrbW86TlnPMKdtkdLcQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQED_lCXktNcEG9Eq_mYdJoYy50WDRTlTb-X31qNjA23S4OB8F4RByTfuVwMKGdUceI_PIENnm7adDjvqldUn9uoYlNcPVFhrgJvO4atQO1kEVu2XVqWtPEMkkR6jTL45Zz-kfpMdfcIwwn8Wfv7Sybk3ORRlZjsabj7Mg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEaG9QRxfejRGlP1TP_NVQZWRHxzDywBpYs8CB7F88ohzJgu4vWGSlyPfuLUpM-rOdQfhNl0mVpnKmtlu8ZumtngEAmUoow_KkGOtKC2ENQStlw0uLyvyhCzE57_iaINjrezBrLigLpkgUSq7mkUyo2UN1hJOI17CYtkwKIDk2c661g
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEhbJISZyVIDHHRWZiVuScLKxkfCZm89kW8ZjqLOG8_qNYDdDzoT3NHELhS9uWpw14CUhYcdw8RPYCRu20ivANPPcYv5g_i5zJdwIX6-RQH-Nng-qa0du-z4Y-fEdP5Ee2RzBgTJ7t16dPaFQhzmSCmoMmSKVvA82XKRGCNbINYDio6LWUCxPPh4w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF2g6YVxKPA91oMfe6tlLdlKozZ7yqTi6pO_3971fomM4T0H9kzPrLKQOSRWCj4f8-nWaUC9KId8rFYKjSIxWcJAnhknW8IzwRcG75LmdQMO-z53rAKDWm2do55DxcrFyxVK7iTlwvJHjrO4Ze_Cv2-3muS90j0FZXHEXc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFAooHV8ivKQa0tZkpBv99-TmxbdZoaxydE-vval19a1f1K2qnwku2m5MDQDqnoeeZP-t_J1k4oy01Lr_QmVyVM3UcD82O5U7M4mxTLhBpSUx7F5mwx3aIplfvw-ZkDUIFmisZMLj5jcVASfZeBJa5mbqpnl9ihF0m2N3GuGDJCqYGow5cs9MUOS0Dw
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFT9b4s8q1R_CcZQa4t7KHFp3_xAVlvOpnXFkCAhtVWSoaZUhCKmxWDCnS2tGcw_j3Mc2AZ88h6uv8a16iGdiQ1zxS7KzqcE7kXl1VY2qw1-qlPT0WBIeNnJiFzMu0Bbvo_Yi7xNwl4_6MNfgfVDWVjo42i1Tx3bHoFs7o=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGGDlm-PI4v5lnt_Lqzu14ojCqiCgV7awTwkLJ3puPo6f2cHgkK0HwGumG3-h1DAJpYLbEp9OEEVuROSeYDyXyptXLwuuWKDnktRUlIP8lF_HOpxZBl2qt1ZkAigE8CU_KWcxXpHkdVc3xWZIM7kwoyQFVEHFXKFv9zuah-Ki4ugwY75bUND2kj4jQUhefBwOaauZ2rzlZv68zA
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGSvXrkl8dmd7N5J5lLiPi0TgGe2dLYU5A7ggy_sXsvPC0TbDfGMIfg9jCZ7CUPNSs9T6TE6xl9alqzSC9Z3jpXdG7DsLwwPwpulTzBNn6oHLayU3RrIJ869rqDDnVvkC-uOs5j-J13cvY85AacYWNNxVvRMFIQ9UXP8_DVGlG3CP1_HoIewYlU-Wqa0A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGhLGgeMXP5aSxqaI0_fse5-k3G_VPWLowkpJ9ZXL0RgLsc_F6KhjwRvbLBeOGH8Sx0HJXiMCNZyVyPv_RuuhQDyobdilYSqtwuos-mdpwgCRatKF9mxyCTcgb-lkQSRkitYVdyNMdErooFfDJpJV_xFl1x2EV33wTSRztPDb3rpG3WcCVmklx0xu_0CA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcCi8Io5jEM4hyz8WYM3xvX4CNyOIhaML1pMR3g7aFvzi2wfuPBMheniqDRYbztTVnk4VePa_rS9bOMT6XtBhgNEIDxaz1p3lVp52JleM6pM9nqGSWQSyjsIU-TDoOF6TYtshtQRNWtcVn9Fu_xTQkUHcg_S0yDeoUrm6ztP1kqOBwkzY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHimKoD539Aezcub8ONKLc8Yi3RyuVZF5DwFKCs2pexE2-kX8_xF_Zdsm8lFRuNy4YG2edgxEsUFmpy9UoRINRC05TgvEvFq-ITcLaG3O0vtHRk3q8Do4E6vziLItP5th-IvLBcbykBM0JBSGZ9D0gp8JP6Pg8E4VN1O7aOZ9cyh3lX5jRrW0bNA5hgtg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpzV7VUnhoZVjruPFAPtM5nuTmDs6KUmlV3i2JEOHHbB2rVvNiFu0u-Pj-3b2Vv1Ct36QuwC22hl_5GQhpYzMuHY1wR5OUBzx3CX4hSnZCMJsR3g0hAhjfgZL-mfdUwHNtuzEZ3W9FXnFWDLNwv8Pn7iiFKayLGSov4J0F0_iwmlcSMJGbtEtZEg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHrOTJs_jFUzG3ykSIx443imSTnAzFhqpt_HPkOQtMwAaTdhSSkMTveUnI-urTM-YkY6tNI45EM_iee9rXPgNjhdXAqVUkBlq2_ywumls3FH9F_0_GGPFlRQpS7Yommm1GNSyK4-cDY9jhc6ulXjJynI2E1FwGfXRS5cg1eDggakyDmxS99</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BT-373</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Box lot of sports trading cards and collectibles, including 1992 Upper Deck All-Star FanFest set, Baseball's All-Time Greats set featuring Babe Ruth, PGA Tour Pro Set, laser-etched glass Joe Mauer card in case, Rockford IceHogs set, and various top-loaded and loose cards.: 1992 Upper Deck All-Star FanFest boxed set, Baseball's All-Time Greats set in green plastic case (Babe Ruth showing), PGA Tour Pro Set card pack/box, Laser-etched crystal card of Joe Mauer in black velvet display case, Rockford IceHogs 2019-2020 card pack, Stack of top-loaded individual sports cards (including Mickey Mantle), Loose and boxed trading cards</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>$20-$55</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2hwRsPIW73ndeZPXwVRzs_a8CUYN9dsw15leIX5rqKhbAxO35mVpwlymNM-xuEgR5URsuPYqW2p4US1pmW4KAS4yLMkseWpR8FA-3baMflK4zwlQ1Jn6PyeYB8cM7qrWyj1ARkqp9T2UQD88-ZQGocAkrQKMTxH842pVI3cqgW1J8sa_PVhzE3ek4sVXyfae6BY0vOcvQXRDtYA9HyXuU9fiLFDDVtzXsRZ6XpAfD0Dm85RLdolw2lygWhKfjE3o0z6Dn-fVuFAcdfeV4UQkTUtoPIIeTR6IF_mMDjM926ebNWQPcqkywkjM9K3ULG9S9jeQ8ForZpDBSm5Ac3QpiZ5PnNRkIM9r5r0kO9XMMHsxkoKSJxtrVmcWFZ2sBhcuBIwkhXrY4PnSz4lMt51YrIKXJ6uFyqLk7w8XfD2B7TydoFCZvkfSinfihfv8nu7nCDLbF8-A7UGK8fr0Y8jYW8HboDwTI5XDZ3VOEwt_SeES5v_E4X56s1UUBNgUv8Y9vdLBJGVUCqRgLCiITGgSX6VzS0BmBSio4D2Mnhj_WgGiy7U_hPOWf-RAT2jMZf9ooOz3P_0mnmh_r2lSDdAC29nRi-hENFM8vQiIK6CHQ2XDLjdHmHR7yMEJm-N9v1ZeuWfAaemhmBdB7
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE9YAICMTKrNT239glHVctESTbybUPuqHeQ3LxsPnvPYCdXiwUxKHtFdQyydzMOQBsBbhq-asBhrK4iFUVpzvY2CowA5MVvqE1pWkz9nEt_Sh32xBmEVlCi-DlhY8uCpKq78HFwif52xSVfIKhbVSEAA9kEg6VCx77CYBkUd6zqMzi5VWa8Twji64YBE__uiNdkEW3_da9h
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEFER7ox0XJzaKwaQA4ZP9PZE9H29uxcsyvdFS4SWQm1zo1k2i_V-Q3R2to7OUkVpVyelRsDLllj1pfXq_QZR3a7Sd0TdKLWGNz2DUgCEqj2AYXM9z22XTgxiWbbnxLXBiBznr5K9naW5aUtFVVcY0df0n681UCksIdLtIKqMN0YQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQESF-0AYcgBQKLpz2uRBIecknN86wtxaCEvricWlEG_dOzjonGL0WysEC9yeIkAgnYFHyuahuUPxO8RjCWghk9rcPDJd9NmFAMQVLwLAMR0sPnAjxF6fJUIActSFgeWU65um7WxaQ_LmBIo03QX5AH_kroYI_EUZmLtE3vwM5YOytNXH_-qv4EHvuTJtpBoqrhZlkNwtjjmVIDZvq48voYi
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVy057XXSq8ATyzM919PggEd3yyocX-_vwfGsy51oYzo3owi6H1gvER0Ri7z23g5SpCaKTxxxkYLqQvtUW1Pakmueu4HjCS3gmgDHxLRj7lEAXb-dKA2798D1eDXO1HcV9TruD_VgYssvRCdSQOOBOnYwFhiJAxDiGChLs7CV366c=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEhxjjF0FwY6ce73iw5gK0D4ebGpNuUZ0kgS2NkGNIIADsUnYY3V7YLLzeBem1hn5k6cL4SAKN6H6n4AJQcxyy2RDipX57gw4AD4TByAFWxb3a8mbSHNNh-taM5FAfPo1lBGNGGdBVMg-ZnnqirlWRgQpU7TRDStxXap6F--CWs6TIgNZhhwo7JmA0BJ_f6NTuztRVTn9Jeb_iC6LkH
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEkmO1jGlNBTn0rRUxahx_DU9GUuJAGIFfT7npcyZACmGLiKTBBhMxZXuvR0ScEDd3YW4RuCeYIfa3dJEHbwzXlZKMtzk3qkB8PcQ0z-5DSlID0garUJ8gOEQGfHMx-Exr8DFPQdNiL2PwnjzPE6G1DRiZ-xzTp0xS2K-Ki6DrBTkPFikMbf3vyzmOeiavVnLo_cIZTzLHmf-OLJyoaJu-8rsLFwQX-ibcnZej6eAs0Jq_IwwA-TG9iEz6z4XhF4WapB5yuNxmIdf2Nmv-X1ySeUJ_h1W9T
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF09Oezc1ysqXd6tIlpKfb6q58J2V0FN_SYqlfhmJGlDVgC3Hy9tgHtSVz6RmgIgm-CWbJ0XKVK6NzfMa4vxXhfMFj2RF7T8rnU5s8EcrtguZmAsEYLv3iOhYoAVYQV5iQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF2XhfngqB_R4YnhdcLfaCYigatrrffkxVCA12WhDYLzRdOIeu90tcmpednaKdlczITg9FJ4rzbhlazGoCcFVs62BdNVYMA_IttBSm9qpI1GRWtPQGx7JbX_0Uiq5WxXXga2C-XMoMo1EzE91VNuT85xI2QoZX0QSSThQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFFU0w4cDSQiUMbiiOmFcmc6TLE7BY-2ryR4M5Crq0qGkkaFRD2koXJR5CTTbZHNfqhaPDB07siPtWu4K4gbp1p0aXSfdlGQVB8bBtYJ7mULzKacvnrMvdOBxyg3rTV8PTx1oEfs6_E6Qx7EafIG0gKn2D_FEbkcuX7lmqhcWqB
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFMkKhPPkvGtP7JcAEHSWg0F4k4vlHk0sUmvz_trMAUlwU2bOmhkbJBgtDxTHytsaDfZO3XvJNZJl9e1ycMW0oYYUGbpvq1cFL7GNis_VEq-I7NXSCWR62RFSCO9mwAJ8mkJ8KI9WMtP5wZjIJ_12h3m-K8JxUJTK6YeScuszaV7Nr9khugkQYsnl72JN_0-zH64PRMyyFZSO_mkAMXRNROCRrirMwF_I3Y
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFPJEwUXcpuYz8oNU3gapk9wqXhoRILkoI0Jj6ecfYb5fK5PwwVrQ3AppAUK4WKUuFHioDZNFtuzTpdXoqCUUeXzTRx0VmacGsI_BnyCf9TzToz_dxm9HJU7tgjH0YFHw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFc-_6ovbz_gKEUyDnmcYcL2m6hiGn1XdQlUAXBIXlSQfzl-_8RG90PeYjMetkQKox92oT92ovhL0dA2IlLouvYnXvEu-kH1npKeV3g-wVZXihOtAziNsq-z8ZyKPx0oFCcS67USC9r8ZYf7ZhEajQB4t6XuXQqbrwi55gle7lFhdTLRA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFh8o_MuW7yffGgKPW4YE1J4mnL06FevGfX62u_Vyo3Y5fXXyPjI0U48HhRaO7-NmwcqEg3DRh8eBDN-N3GXHV3dQzSWMiylD83IS7NkDaRdCGvPHpBot1SUvmGo9o0GCU631M1L1K-dreowKeCQygWkw41S_Iu5DLPZlssT17cVrmQf-I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvvSj1wSHtat0HYhSJvv-wUij-QUjNmrW1t5y2G-94PlC2W2FWq3IS6NqkcVMam1qukenmQM1ZKtOd0cjpo8D9A9g9n1jJyswnrl2quCbREWt3Jq0RaN_Fleu8ON7h_DE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGKzQ6crJhcXzzwcBUI0EgTqAMDUwDtR7ai9FKaMPFUwcJTUg11pnI2GnnoedMOwLpf5G6RQTvI-5wrB48aCGBssLEuQZjklqdUhgFWy7WgK9VZjyLxG_kV-asfFaIsrDtvItB9PPYdGBoxIc6aHEbniSNnUpIqX081gfVBWSvnTwqEeMWw8gP5F8cykbwG8f90Aae3a34=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGP1xHtZqClWqbaHx_WPYS-6R4XRzwwJDD1F9jhFRKFBM5_aVh0y23bDw-_AeGDxaek_UHlBsYLTdltlwta-hhTZKwyuehVy_5PgO-vLu_-wHHM_I0tQBQ-hh6yH4ml8Ehfg1RAQPnWSnnorNwNCtpw7PKhkDpRIkRJYCYn2WNJ28UltN3olzSqat-s
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGYqpgshe7q8VBGrXEoBaOy_36G1w7wWyMRm7sxZIF32-o54pboGqH1iX4Ef090K-ZIv2psY2wzcK_kFDF5iX7rJ79CXi_uTFtH2mGq6Oiim8mz5bz26d0H_1PiMl278LEf9xGsNuO3hqqfSWg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGi-CO7yxHDoR6SR_qt0i2y19125HUxhzEhBVWhQSIRd_FMGm9fZa3qag3LeqS1w5t9FJN6htHa-OQCEF4fZJzcV4XCcKOK7cztyhQCS-znqujrmQZmz-0dmPGFdXHGYBNd_HnaJgp-rs16Vznnx0dSZl1E-DdFegmTUCeACwWc9fi6TNfqKikW8ro=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGnCrQ4WGElV501AV6XH92ZWs0ZboCLjzUtK1-LWAZAHxoqrSctLjEnm4QsPzyjm7EngBwxLSXAOKNWwuUBw1o_w9tGYFwPTn_-T_QvOgZd-XkxC57rNFKt0TM2F5vM-xKIYKx_HpW3cAPAT8S0N_HD5TvXu-pKB8BrL231M8lDI56Chrv2UyLR9rC4LsL-k3Ya1Kp05A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGxtYLuUCEqq4gwClNz0Wriz3S3aRxRu-kzxdQ2YWkoyG6MyQRkYAgibWBIdqC1KYUCJichfwfQoB74Y_txP-pclZ5ZBgmAWFq_5-pqqRYu_8V82IFnzKz4jvNRPjklsDPBeFc4VnZWt2bEi8c0QcnA7dkSjaPCgv21-qoUuiQQi9Bj6VZqnq15pKo9Lj7BoX6p2SZZcw6_IgxmyLxRlwU-KdRfUs50sp2e02WhwvOfyCc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH1L0X3oIRyMqiDkQNeiDuA9tNXhCNICq4H6A1IiTmFamxJ8EifgEBTRjCmqafDGINE77FoZcYzKJatFizjCNW9kDdfYEkNqBk8ddU9haWvCOSxT8uxzgeZ8pA-HMOCfq-6S1iEIBDdlczfyBARP2WKECg3AQNfQD4lsuQsyQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH2OUTyFrSaFrn4KMjGWRvrR61kmvgzMYPjHDWL35WgC_kIAL0N5zHlfLWxBQnNvOG4-mgRqZl52llHdluTmSGeX9pnkJSJs5Bdzc0KrEnBMBDem4s4aCm1-3dnJdqJlF01jRMJ8Rfr6flPNqLuhrEKBCciBaK53QuuKr8sPVJ8sFT0IZSofQGN6-PGCcSWrcOxRetvLOEj
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH63EGejYetvK3Nici_6sZtJfiCwVm7mm27hRF2H4hKywk26Mzw6n7Wgkh9PIu4erohGzdFRbnNvQkvv6PqZHJ_EDW9jzIvd4dBL0itMhxVCD-Ph31XbP0Q6zSGrIRqwYA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH7UXMXNrLexEgbPNkN4zUhVtkGkIxP6coogj1mYlkKqP5zoyo_dlu3hZb3uBrr5uE5c9PrcaH1B9w6ldntxrNXYuan3XcLn1nVyTVlryIImvGFtifYrQBH8Pn_h-wd2nw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH8aRADfCt7T4zhOFmy4RNnUseIbML8isaNv4TRddpcrjrkP6ywWjVCTYmFNDQ059UCLmpTACnM--U3WRMNey2gRyWwSIXItAF_YH4C3X2fCVe3RjfUnmFMpnJKMsrnpmUh4t7QpmgmPdv6F5sVRW7qxKDRYTrDvDKhhsx04IVb7wE_HUU8YjKcmVHOqx_V9CguOw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHRoo4fWmAwK9ha8cKYPK0zqiGMu5YDq63vvfSGT-N3yKFgSIhqguDpiAjiktQSYdw1GG1BUEaySW9oFj_NMx69TucIj-3CAqjKwjU8LHCTJbsBmBs4LHn87Uu8Nd38Ftw5J-zo2BRyEklIQKA1rROmGDPSVcbiROPL3C7PHpzZin4VjZ1DDXfW55HFyws1DVuo
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUOF88n0K4JvRi9mU3hYQwI38ss4rmUH1R4_ri2XzObOo2Gj8EBFRnPpdWMd1pD0g1Ob5-DWdVrxES4_6Owf7ckK7rDxdGSO_rbTMHf8INhAjH51z5YldL74y1o9auhQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHdHU-e2F6_TBrKHy2w4dzDcVGQ5ygf6_plSetsBeV2k-WjRjRhK3jhTDCyd9jppK_xhbGppLdiZZd927GzauLV-vm6QAwwk4UUmIVZyPNi5XMr_JZceOfkPVVt0UCBNETLeZd831WXTdAZ_DtygjFCziEN3LAe
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHvHQQSXTxyGfATmbkCnhTwrVsBn6kqCllUNXYQsbyP-JpLBTJ3LQ0pw_dzePd5eAuBWQgc5OiBmqOp6pOJhiDVEymcGhNbLy63gB0EKJy50nOmGdpTNlga_DTm3-kYCkFg2cmn-XqW_j8WoIVGu3zobczbBzCv-BvhJRXVsiZmqmzS5AcSSO8FT2cwTl9bwHbRzJArlQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHvLSuJWUMpac4rBBQd9QstFUHc62xmCXJxRlzKfSZ7pzACzgTWDhoKeAadEJ71QEMGk5yy25OhyBD29mBVxDIMcJ3cbfa8CVUkS5XmFcFxuZkdWU7kRQIFhRjzTKvgPvSBteugOwx9orFPw7wLfJbiHUHP-QtCa2Nf0B-68j9p3e-UK5m0Ul8=</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BT-384</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Assorted vintage advertising pinback buttons, commemorative medals (including 1962 Rock Island Arsenal Centennial), enameled lapel pins, tokens, and a pocket watch inside an El Producto cigar box, mid-20th century.: 1962 Rock Island Arsenal Centennial medal in 2x2 holder, Vintage pocket watch with aged dial, Advertising pinback buttons (Gold Miller, Safety First, Oakland), Enameled lapel pins and ribbon badges, Local Illinois tokens and tags</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>$15-$65</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEHiSB3t7gsB9ezvS2cJqlB1Y2wY5SLNk0ujudJWjB7auP49Jx5ktw1Eg-GfjCq3Z5oi4Wz9vX37vgZuEtZS4GoCGkmuQ4XuSeDsoBdAvtSwODMQl4xBHV--sRTOGhUVd71ZJbwQs-NHwiorp4Y0y_KEV6UyexGsahp1bfN8UfHVzoGFJaq
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfUr1QTkSzTCrtcyXVD-cqhyCTwmNpBUL0iPnkZok8KIhh-s5bcMaMH34rIZJkP9HuvSZxdOwqMn-X0_GtUaEioaOT1hHaD3io4CnkyJtP2Np6yj8iCpOge6Xv2fglH2dOHz8P2nYjvfoa81oljivHtQk9t0tjfUxt
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEnmh-XFoL6ilyeXhFRQ4dw0y7MhN-4VpthGIIu5eX8oxddAQsX7cEeSX0nCRCcoCcJxk1bKDX16_oVNs9TqREQMY4xk5O1C38LrcoNUD7vanV1sAgxsJfev-qifewy6aU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEshLr0bOv1XSuh0chM8jgLo4NjGwFxf_NYlQrkGyDhJeZ3LQyKPZFyCVkazru3BycC6kzp7uuKej4V9ZMPI9PH5r9FE_6gU1fq_Ubgb4w9Ghh_l35OrKxBvFMT25Z55j8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF2zUpNAj8zZFWDqmSw2EkJJDe7Z8_xEmjR3exIl691bNZEV3_aXgp5VgGB9t7ld6GZczsZ1Zao6fc25g9s97DLHHVsTj126kH53SD9WQmT_ybe9YiTXkKC3nDMwUZV1kCQ9RHwmS0GEp6MhYESYDJG7XmU9opfSMBLt7DYg5m6vqWASeI3w6nR1Ltv5ZaCwLkv7s2PAyELnaK3OOeVli1F
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFQM70DPvYUeNVVlNZnxSS1UXLmR5-xOhtO41wHpdOGKUiy9r6ZwE5BgFH8D82EG2t2FV3AEp2ERjSGBHecTRM9WBN9AsxQP_tW6b6bZYUsUu8eRr4DnJ4-egs5F-u1LsD8nrcqBbQP0auPTzvsQsB-e_hNS6cGV9yjuqr_xYa7ZkaxVdGGLdrP8xjenQFnnn6hOixkAC873qk1IExweInc
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFbSyCgr67c4OHkj_Wu-UoNhXFxJdKWzoLKNkm7ALFcHtZh9Fx3HLHKIF2VeJyPylmCvfDgxWbx9ta4gtnM2J0nIIjRr-0GqC6tW1NeUaI0VlllTb_cTCMm-6T86YmvqCQw32ICghoe
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFs3fI-vxQ_Xg7pWl8D6Nf5WuMj5c9n063KC5owko6dzEqim_V9T5XFPOr5trm84H55XGEsmPuv5RSjtaGAW-6Wt_cgUFCI6rNOvW9s_Q6VpFSNy-y9BjOph1fFcDq2tEY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG-vDaTtBsqSHsIBpj9rYkg8t69KghdwaV8uU6fj-ffIvXlgYBldAvIHY1jAV3lv9iW0u_WIKQ05fzfJZQqcIzXJKpDGa5-a1alTNURL3gHaK-BSEf5lA_RyaCQcHasrSwb8gvYp4m5JvpFxuZamQWTIPxC-c8HPmfuEAFr1YVoSMpDhVOSdmmIHjGJMKWDCWe35rOvZq10APY1Dl01kLAv1lbUDtO9_-9cD_dYTPVXXlA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGDsLY1GG5l4ILelXn_KGpCqT1rI-OoxPrq5M8_9CP7Sar_T6D8u9O2zUAG0dXH2Qsxt2lnLGql6bXfKBU_cfVdqhO2JhPL5rgX6n4VuF0kstQGywZtmW7R7uBilg57_dI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG_clKVFUftPJhid7UPEPqVkSG9Kss9mMVl2kk4Inq4HceozcarK0QFwG6jOf09TXewN_HwYRJU5xyFgepdsTn23sMdLuanHywuurABEv2stB5vKPVfo7hiPmZrTClGIWQVKGOXlmRrykd-65GBYSiCa7ZowC_6gAemP_4wp_xZnfB7vLei
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGsmbHTqPeLmMEWs9ozOf577pK8pYS2tk4DMWWVdvUqipS7b7mTEggDL81frmzPff7qSF4j5v5YWt9J0B5jI-oPAif5hFaAPFTYZp1Drjr4afCzAxXyZw5NZrsm1drkDrZZ4qyMrTQVwE_-ftMRMph9x7OUxNWN6aRixoCj1JtHzbiHGmZTH_z5s90NWccjWT9Nog_ovTBXHPfbiIkToPR7
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHghfUv1BByLZQmsXF25eLT5ylDPQs1yODMLDu-XgblU4JoxFENuVlcjykffkGeKkWGab6bCDlwLQeCfLMrCUUWXNMZ4VDDoat3052OU1H4hN6l24fVii6xCI2h1DHx5WB2xjMDXW7aZUeTmV4dZojsTJrV94oYe82tT2SbguO123lP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BT-388</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cast iron oval relief plaque depicting a striding male figure in top hat and coat, likely an advertising sign or promotional plaque (possibly Johnnie Walker or similar motif), mid-20th century</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>$25-$95</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE32pYrj_NR-mwFZb3apWi_2drpQiGC0ZD5_ZMK4pzCSLvyBg7KjX993z_tT0E473axrR2rV4JT--RU9DuhfxW0NN_ahkKyNaCpbI-5BrWerjGt2QZTCabDrFnuYgoWMcjtOEb3hc3wFrkWc4ciktbVw4i5_o50xW3ZdBm1S5ev-7AKgPQLi9JRECD-FuiiP7Rd-j6gFTj60gcUoRCDzJ5hTXJVzOEfI0q_GuGdVOT3ldhveRw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEEqMCvsB6CAMGedsCMU3OpDWIqLRr-NpAEMlpRs0x291ZugCotzROncqtxhmiyorVBq4ckSRx8n6SUPPEL_vBOXI9FcBC2qQ5rXdc4DXyxTFA6Uq_keZwLgSY9L3qQjVSSVQUzyiV0f1vQVpFb
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEJlnrbE9IpLX_hzk96i5l5dOKFv1tmZJXSy-O46B6JD1Zh6k-8E9GbgGkTR5sak-f2LMBi01T2k9xvx_3LRbrhesimlynuZfgXFFhjHFQWH9xpbOGODmFdmz5hfGfi9OsUsOxVX0AA
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEs9aF1GIGLOBzfCszGB-Jw_Uo-6kRkD-KxZ3lbZrCvmnv3wc_cmT_Op7v_BNj5rK_r1b26MRrGBufYtpZ7v_a6KFMgDIkVWKk9GaeQuXhMU-tgZRK84_8FinJuQNhB6ZP1ueAGCbITgUqZyDiWN7VYLgVccsrhj8dHLZBOU4RmlKoeXcZAj9zjZfMzdvLr5XDwQg4cY_1yHDU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEynRQLQ_CP3k3kWMaztspymnWPtHdmUafXbSaTRnAESRXpQTw5vHFFsCzPiqPi8J7Q9IyhLkgGTI7C2ibVjP0Y2dm1PRCYHgksDzucF6x1MUX_76nrjafWdfVhvAcpOuvZeCkyT-iP-dqKls800bYz2iO_owDHUk7YDsQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8_kKXGKCfAFGmeaesO3oe_Gpx8F-o3eMZQX2kVKzr3tJynNw106qIVZq7zIMsOaaPUiPZQem6UY8_iS2WOPScCdyRu-TwRYwWjWNs1lAj7HZgWpVM3VKlS7Uv2V0m0MiAUpGQtccTBS41II8BH3HriA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFj_wwBnYaxXbD9pnlyE6ceheqielxLOARVrh32ewZ4SA1wVjJEwrMd8UveMomOzbc2Kkci53bB0ic7y1PPZykxpjZMHVV3vkW6xya8XYQ48tebm0T4BmLN-AtffzsSgrlwKrfsT0jHNMlszFq3_5CYDDswQAefxvmQiw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFwcfy7GUpH7yyybiEhCJuzXwibL0pLkBWJ5-tCPwjXLZTZXMJnBtCDRR02D-1gjJQI7XhE-MMmISDK6EeCgGYtDM5gDiUQ4vNG6mBI7iFzcV2c0mcQsx0SdNtt7OSHnvLN9P_34WAkJnkm199YLQEjJHl40tSU2pfXDXAlsLswGPMD0EHiSBmUmQbr3DFRCGp7A0CTg6Oe1C5_l7QKhykhjHBwhq6UxJoJOTQsM-AvOQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGa0Ru0UtRmNGzc2NLNwfb8pOsNVwR1vaGXX8Z6HZSRbmm52cyVNzp2HBUG90zy9nhbCLyw73kcs097ifoF9jyJ73WT6H30AOz1VEfMKEHVf8Hh-f_x4j86uuwyi1oRZBVe
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH2sOdDx-zz1dy56etz9m_oLDOgj5N365eCln1IgjwCjBpNeSl6neBRPhGDKi0L2fZ1bTtVamJCaF7sRtKmYHFkFDDobZIfbG4JMEXNxCCtLaYmOFAf79RIjE8AJHZxyPvTxTDuFd452LtD-A-Fj7rH8xyM3xXL0KR6Ps8qmmh7chJ5F2b3_i_YXj9hdtk1qJYqOwN4nXhYT7o=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHtGjkLC8caiMHBNmtcur0xOxk4rseXmStBRDb142_6dwKsK4ei5Fqa657Jp1N15klpTobpTLV0pJe_41Cs98zWMIoIUWRYnJa9Y-MpG0BnQOc4ysVTMBxU3T7ls770aN3nx6Ymtc3CrJ7VHrvtoHBb_C0q_yAClOTNYtQccJKtMAc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHt_F48RNZxiRhE9SycEMLEuz39b2RGo4ymaJqdX03IZ2onGvH9wMnw7hy-2ALklxogISbX83rQpg0loXNVDIhtRrEu9atLBBPojufAmY8LbSCdTe_vocOgJDQFkaD5p7SLwl7gFUnIcZ3zcvwWwxSU_2HEyC2v8Kh896QBk3WBvIDabJjiPxqYX_077Xwmyyax_g==</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BT-394</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Vintage novelty toy and ephemera box lot including packaged balsa wood plane kit, red plastic rocket/bomb toy, plastic figures, and vintage crayon box: Packaged balsa wood toy kit, Translucent red plastic bomb/rocket toy, Pink molded plastic novelty figure, Molded white plastic figures, Vintage box of wax crayons, Assorted small novelty items and paper novelties</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>$15-$45</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEWSUA0oyTsunRwSsVhROdMbk8BfmLfJDh3L7dGT1IEgfKow_-3R6b1IGVzmMJKxzdW86wYfQ_D3quZHv33XwpFNlnM_zsy5EeHrwI3xfNC9z4tTgbeBrIhS-meP8x08XdtvHMhdqwtYg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEq8O6WRr95ssdi2hzaeWI5PISHHUHFM8F9lDMftXAP-btIIqiSJYD1wn7lZdZdzJWiCuS5tDBshxYgY-7muagul6ao3cWmC4jbbwa3BLwEgdmLDnwQ905pl4IY-gD5rOulTvx4amr2Owp_k5AqrSXaa0Nl5Adum40vOlKiOjnxknULEw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBji8nveUp8r5OSOtFcshvpbqBuLHKvYjb6ScSwfEeIUyhlhBuQBnL1_0oc01pzZIlugRpe5NJFv-9dlFU_0t2LNob5xBAa5UMVFmk7j6OpVVv0godKOD__XTv1lSCdWM--pihgd4gbSasmJfKH78UI0yI1LOzC3lyJIb_xUjRdAM3tBIXznMjDx_5o6PFsBqfJsmCUMYrxJ-pqM23kRpWlLeWhjX0S1UnRx1MEA9GnoTsVpi11x36oBzxqgJ5p_I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFWEQGPUCpUWz372xM9rUJbGoGm-YOMlYlP2L6SfZw3fpyuVyvIPJcKFNDdWJYi3vpoJXQQwNjZgPn6xzyhfTDqf5UeXLYtBAPX0kB3AYK0kEcse17o-GTQMz9SahArNMCpWKL31ECwkBMy3g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFXwhe4K5b-Whz_hJ1_Mr2jUDjE81S_OtKryKfDJrrOkoxPuw78iilIlShh_pssXxt1ycrkyQqdmNp5qoQFAQcOvTdxJFVuX7fqBwJg8G8t5gXCPizcbSu5XjH59pfFfyNfaoep9aosLwfI3oGjK4o119_V_havNkf4mt292EkevxA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFZroNMdhfBNTttW18_IBA7RcRffkrx1czdjzjV3mrWzTyHww7vRmq8MDXaBdorcIXnrGaQUTMBKcsY9M_y7c52V8_Y0-qHDc4tbFYZl4cSifh5L2ioIkGLIHPhJldg7As6PxyxxdP8wPL1OMxz0BgOH-aM8vSq
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFeNwC2gFQ2hccFmpdppdyAULVpC797_c3oCRFdvn5_XiCj0C2eD9WAX4xna5ySiKYgAZvwdyMj_AMGv23gjjAp7SOcIckF0nKJGVv9PB876jSOn8VbbWMrR9v1lZfJDOrr1iTze41JOgk4CuAwzcpdVRa5ZshfValtsw9f_leRyBNdNw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9adWcz_JdOrzb84FqZGXz5QYZ_Hf18Lc-9orpOzvJImcMcdecCpt8TvBmk5HthT9v37CBLv9P1K44tAOgXo4Qte7nje4VKrwxB_LenF5-eCBkQC2jhvyc5UD1Ejdp_UHfgdJjKdt2jkEcWh33Z7x9rAk6TdTBx20DK7I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGBE7Ud7ChszK25c0g7hQjG8FA5ktw1m1uPFiJjjAsVTFJZFZdAwMu_a8DKZDzNM-u0BmCL1zn_qkyNQJRbEKT4eRT3CSLMEFF_varWEh5H7oPHuyQsoy-prEWRLoPPLncMeXXB9cWjBX035BxA5nw4lNDVjj0l-kiyOkRl3GtXRr8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGDV5FF1QLF3kYwNCYDtK6Xf5P6DS4PiZUTyfJ_xpS65QrCK3hv5xImTL9rA9i74tyDdDSBckyweOd4f2NmIDgXyau0sTGnh88QiBrXpS0M4HKPjmj-ytNOmZ2KvY3JEarxQ9xEAPxNF-MLelkyzkF82ak50sM1M3Ox5Os4c_n-dRCdsuqdVwOR0c2313bc
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG_1s_4-3mIrigw1_VcwKd5i10izhQufSGStvEKriPCQdoBPNXfQDQQ3yVl0OF-7mbLW4NnzOmHhcg1H9HEE_XIp_8ojqynmS83I0eWlFfNHEZEk81Rm0I7b-ttVuqDSc8TQSr07V7cpw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGrVszuOnWvlUFt3WLgH11vsRbQstA1THr5IVdgFAs4jQgvSPpFiZJ19WblbL2qOOrJWhFCW5CZTrfXPVynBcDWuFR210IE71C_lRnOF00GwVBrRRRVODxo5Wv4BPymAPnT7e7YRvvt1DnLb-McRs_Jl8WxWnYVhPhVditdk46UVvLiZQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH264JODjm3TG4fThumkn55tQDfJyCktRddXsc2d6YfwZB0px8GdL8bFkX8vt_Za8u3TGcU_9OxGMt2xvscFOohZVAtNzk96yJydmhFk-SasZ-SzWDpJYSj_HcBMaCM-BqHkJZqrTyJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BT-398</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Box lot of mid-20th century paper ephemera including 1950s Profitable Hobbies magazines, Sylvania Electric promotional game booklet, United States Athletic Company baseball scorebook, and vintage greeting cards.: United States Athletic Company Official Baseball Score Book, Sylvania Electric 'Beat the Clock' Party Game booklet, Profitable Hobbies magazines (1950), Vintage die-cut and novelty greeting cards</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>$15-$50</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbJy2cWVo4yreNbuKGa_52zCExpKBpanK1SPUNstLA8hPwTlyRWM3lm_cYULhFwsY1IcQA5IiRXtjUnl-yeBT7Eee_wE1BSgWw75XVns7Bo2erjI5f1lf5ivdU_3U6x7y5h89Fzt4qwioNEM3lVnlZWisRZdJsstaE2NbM-whjeQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEoR94dqQ8ZLxBw0K2YTjqBiHApkEt9OGC9gyDlPy-6OPOSfUtyaRErOLFcqViuTgn4fWJfw8cxGHprRNILiF8h5mdZZcKBi5t8k4-9tK2PBmxC0L30e3q-WuwVBqg1YAvheHeM518ALkKuZo48BzTNLtI7X3NmEAtEiVA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEz6iAN-1gE5ebOhcYJwEfalG3Jo30ellhhgDj31_2Bf036kb9szxHGUCYCrA7DXxFXJbtEOwff7k7LsdrrCjz0rFFJnFhU61cwFm6R5jFpv6paO9iFs5_sb9Rb1Ks5Ggw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF3qhAIXSQlNMhom_0fmOyfSz9mGenxNk4QU4ELuLA9H7EwZ-cjdN5flkoZ5CswNfcstsh0-HbtpVhg9Nswi7vW-WrUIGOmBLw0g6Vg9k0RRP-ZL-Nu2y0oknBb4cNasCLEuDfCzeMszBEzEXp3L9FcC2NI2Q1YeMqZnrpJA__qlRX7DQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCc_aCwNDY-jI5PN4jcRM0Y1JHFPtcqPQEVoNDsKgf8DZTiyI3fFI-K3uex_t18hCjHYpRfeiXjqsKFXOUGc6qgvWcd0PTrCcpcxPYCQ1-shkKKF0BWgSQngkXGzX0uxg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFH77FoS0o1x4Iphne0wAIvskjjCDOOEJtw1C8ZCiPWhUBYSfgE5gbTHwao3NistOVrWd7gRq7izsNLUzaCznuMuuW5sORhaxLleIu2krS8MtxnhzZBxO8JU31WdXhj4zTC1gj5bHMfQg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFK_Z4J0ultM9e7YX0XzCHBfzSBOGUawdxOYihURy35blQ9xQzw5UXqvHjry8J7ig-n2g_1_0JwAg1FlUMKFy4oWevqYlFfFjBgvXXtQP0BeNPypSu9hNHOnr6x1NVANPt4KnQJjnw_hbutPg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNDKzDkAR-JDMU665N5LNDW1akRS-MwXVIe0Hp4_WzNFN-4dLBTd9wHjp8NnpEBACZgTM7ALmQ5Rh78d0-X5BULZHuHYPaa7DwCxWhr6JTqKkZj_6hTWqRV06S1Ntbn1k=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFWmwHCnsuzpMhPw1vtdK5ItWsmuvIeiTzECNhytOxWkvg46Kj9DKcaFQhcacSi7uBcBlrlDdweSC0aufQNTucz_t4Qr4t7ZtdT0-tSeGqZpOtnOLVcOi8aZUiFHDA7VbtHHRKTUWKixTOoYN1wRq7BShcPb5WUyGwqirp1KGc62mMBhdB_4fKP
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFtwdpfTAjL5zJVbVNEDizd242r0_TpbNc3_8Jejg7D2EyjySesxf4xGS_iNMQjpkyfl9b7rnZThVzMtriXkCu-jaNcuJ4ZdWJhqwwDf7Zw2U5lAUYqaYyiYspYCAC2m7A43rvosq1UEuz1cgOpY2WGmsB6Hr8_SsmVaRUc1Lf6JXxbjeP2VqR4j18=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGM_crNWEaDlX8vz1GE3rkUFwIlLSfL_sJMJi-XCe8nLN58ybYV3CAgvZi97_sbgYHhPfSi6nFR0MroomoJ_ePiGMGiL7ksDwiGy72EC4LHEkXwJ0UE-149G8c4Wspqpe2T-iyupj3K7PHCKV2POsVX1dDDF2g=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGuIV9HjYqzmGtydilfTcFzqdFmjefVBSv1s50TjAD9oYVPC2cVpUS8fNGXp-mLi95b2qUCWnmtSvpaL_gtL8sqoYg2RwC45pSn8--EJD9ENsTz8_if1OWMQxnrI5UuMMmqhhELYje3TwA1xpeX5FvP3MCIgnjHrbY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6nw13vMFiwNSJ_r9IQlFDDkRRzQ1rQY1gK_oR3oq_-drwH1FcBYuYQ-T3FntqIZfQ2aVzxoSI4H03HZeQHhQrX-akLWsxS_G0zlWD0CuXElDug-Y1WPkw4qrlgaSIvaA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHmyKSepwkr-miHQGYoVp1wJ3YbNoqZMW6lA1cx3vtT8wLW7SSlfBeHD7B4JPESmMMaqfqiEsXY4qgrDdIZEtUsUgienfaIOqMN0JnSmyx2Wzxskytqi1C7MUzb6zvEtz8L3cjdI6_D_24IV1sBKCGR9JIuFWeiZ5qLJqUwapiYSmlrrU5ob-B2yg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxohuhPI5ZwYryBgGeRX_ZyVyebRceZtmWkH2ZnUqxqiUZiUuqhVfTdKIi_2wjXqSJLHDKbS8oIRNrVQ-HCnrxmmVYTIwpya9aCCGbUmJCuZTU19tVCUVnIBzXKim-K-PnKM6P7V3Fkqaa1JOFXvDXFB3gQPyFUw_6IGwouixoVufbC3NUgpBPqg==</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BT-404</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Flat box of vintage sports memorabilia, ephemera, and trading cards, including a Rod Carew Popsicle cutout, Minnesota North Stars patch, and Miller High Life Braves booklet, c. 1970s-1990s.: Rod Carew Popsicle collection glove cutout, Minnesota North Stars patch, Miller High Life Root 'Em Braves booklet, Wilson Super Bowl booklet, Champion Spark Plugs emblem patch, Sleeved sports trading cards</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>$25-$65</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEHcNBOra7GbtVRc1bT8iE2oZnIXKTcBkL1Klnz9IKDJ1W7bCXOjYrCoVRDr9763UuYairHQQTuaeVKE9dpu6-sM3UwrNpPSUGTOwBZxQfWqGExE2lXL2XcHcSwf9Bu4A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVs5ONHlXtq649RyI0EQuDSmZtfZrKHisxPKy_d36cAit_L90ArxrWXhgXAv55GJl19XXRrH59m6HCEGCRoAu0qTy_Q818cDCRDtSN4n-dG3_iUHW3s4Mty7CA5XUbvZojo3YRKL2LIuWLhASzj2lN3zbSoBHyBR4ifUXOuioAayZ8TCB9hSkT9e15t_1XsjqfpwEU_9cZ4LN7x3QZkg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEa3JnQDEhBY3EnjI2SQa1g8fI1NcDz6-TI0-684d9UjRoloFk8YmiEcNGArYe6r9MxUxxdyDtJchn_weszLLLDEEcsOrBHZFhYKWB-N62VhVI2zLmxfwtwpWZeBguk1FQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF7KRrlUl_O4C-APIT4J0NvlY21hXEN5V-9rfekdWmxXGj-ISTKE4-PSM2vIZRGoJ824xDOP3NIW8XU8Y1IzHv-yTgtRXuXV7zxo5n0Rs8UJwZ4E7obtnUXFh_H4zI5fisnO0IluC84OlYRGOY_Xt0KAXIqQ4N3of3d1JaPFpRUE1SFAqE_ROK6owhCPzA8OfQorjewSgM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG4JlnRyHUvLbueGBm5dPcMEwpBaT3Z77ff6TFJobgRJzvMFEdR8JgiqKrOBr9m862IOccrQowCwAoAeGUAlZ5UuMwp49JEIe-vbcsrEvClG74zqN3nRZn6ryzL54P5Og==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGEup01wAAQUBG81iB41np2h1jc8i2urbY1WhVgaoumGfkUu2HN1TJa9flVhlJBLjr_ACQtsHt0wIAs6cSwG5nENX4m6377R92kbuhy_0EBVy5eZscKS-wQSYMcSaYxq7W0Qx4QTr4q8w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNf68tc4KGBCi_TZ_zHd8V1qWhgBDVOOsw7vAcYFR1lZEyLBdVo_4wIODYRn8R0-hzGKg4rXvEibZqdCAG58OBZ6Y8Bb4o2G9UUtB2fA4xwQyELBPTwuwolIpMhviqiNXlNAbo77l2d1CSyAFgpe-jITqlaSaX5ouLEB052fozaAbyAA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGWo9eHqbhzA2kEDFD6Pw_rw5tWHw4I7ol98Nxl71kkVlkHqZCq8pNZKAae_aDYuJKUjHjGtanhgEwtEbFx7-UQNIK_qAY99Q8mGapFGU4by-rqpHKAzcCsc8OHRZn_ov_kjEHE8OsxLWMAU6U8EpJCK--rSM2_RapQFCZ5_ef0QoGl4tuzXVz-Zyw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG__hSB6xxLvKZ9nhdFOkn5EOD6Kus-v-Smi9mYiQCtshPPGgPydLuFCoY9BCgxMs58Vkzgcn3SRDdTgmVJl-ICkgPnn5tA8_MAOPECEZGhWG9HHVwxBVpnj8AoyT-h1EE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaK0HLAl9Csoq7ZzStcUz0sy4mhkAu5Q-BO30IaqW6ajGySsak18-46Q_dITyQ9pZzYJhhxahumIqZ_xMJOgTw5bhE8-pe-4GDgIjTewSMSEB9uKo_gOuhlIxx_kAQ5Mrp4L-5Sv_cLOJsWCcq2PvugfjeV-nh3DvlIu4iVSvS9TyPcA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGy8KHwUmoHZvwYsP9meDUMjaZg1X1bvGYNv3hiuWmLHv7Lb5hfdD3b5ENbsvjHyNONIbCwKXVv4FZwpS83DKhFIq3SfF6PUUlIx6cV-Yt4uhs2YVJVXRaMC0RlGcHV5uADBx6dI6Vo1XN14fBB1v7AE_Eu31H1kbAL8Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHIe9zc3FnQ3KbtpHF1Zd7wCHbRqPq2v9lbhe9oyRvM2K3Xs_1YUz-_s0G0rA8j_a9eQgBp1sgI5lFYTbMALyzdvlzjb3O2LhUmi8adrQZYDGH7LwCx1nEtSxjNiDOcu0epIxgbAUbtOIFSdRMgJmWOEq-vIjbCr7U=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHMBMZLz4QqfhlJXBZhV2-Vfov7C-dCBxSEUgq9HtJWXTfnhT1cZT4TQ3koKDADBoss4_RSpi6tNUOrx7bIPHXXv1DxnjhT66tDCQ_MaMGoFBW_9yeOOZGvVdiC1DtEIww=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHRhSlk5VlsqKKnmkEImQRvX_8EjSzzph1DOQpCXYO_fHDTxbEek_-ZxYzw4vHVHPJcZdC9q7uw12r0VNwQwC9Pbcy_IF6BgUNPisdvrz6Ssf_aeoghv2fBkJvo_H3gGsexzEcoizMP5Vjt
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWkcYwgat4e52efa_CHpPpJdFsnrhzWXv-AV394wBtfLdNiZ6yR70AA9zC9IbyK-9SRjlf5fhgksXWZ4L7ZLQq60e3UGsfI7uSgGqvfaOSCoSu-dZX_p1x9cGDBviRFQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxcWZk81u0md5K3RAHW7B1YKk2Aj4m4RbxyqUWvCOJsR37fzyylq-mJx-41qFNqcdReeDcWpNGMtmhWYTJOQMuZSg3kFMCjorMZ4VS_I-ax79fqFp62I8gLs0oaK047jg5IQDqRX29hOSgicLPli3HmNtG3tCrCMboIp9CiXuCBpKcLY2iw-2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BT-441</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Barbie doll in winter ensemble (patterned coat with black faux fur trim, red pants, black boots, hat) accompanied by Hallmark Barbie ephemera and a 2001 Hallmark Keepsake Ornaments Dream Book, c. 1990s-2001: Barbie fashion doll in winter outfit, Hallmark Keepsake Ornaments 2001 Dream Book, Hallmark Barbie printed ephemera</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$15-$35</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEZHc-Z59HuEH9ea273BYgPy0cG8-gvWo0AqXUrkaYFD_rysN-GwUmeWyoq-Q4hyzk1s9fJqYpgdUFbZrsTs_OIn6hGs4xFqSiXzRFTKmxFVr7COqGP-Gqz7Lys8pfn-82PJ7Ee6vMMSw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbHQetiGlAVvR6rdK4tz21eXqMv-rAVmPdUJlYf47P-_LDx-_yLVT4HaTC8s8gunORzZhyu6PTIHNPNJ1-3cHZI8IXQASwhtUu039xI3XoYhQQDBFcYbsU-rhrjYDyGbxjjkFslLLjfn21OML4fdUKPpMq-delWw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEwioSu2t5xK5lntNEQNtt_LPxatYy846tiJobRhZ4kZJ8Vm26xrY3IuKGsu13j44qIosd7aNFyD6AXiyW-0eciIvSmEYDp3noezfXDVZPI7exbmYGLC1MQYrTqsphj4Zk=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFKTQGorVryiBkZy23SvtyVWuzSLAiminRScM5wAoAnAVOK42BxnjodbwEmUsgBecQ53ju8djTFWVW9RtXfh90iHZFNXsBIrREff4-ctdI9iaQQL-46Kgz-E4WmypbMa9LJBRi1vgDYVQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9BKfHnQjczBreIdVMXTPkpl7dMOj2hAVY_lX39PEMofhmmgQ2aUmQbIc2MHIoiHoj52CdX0ygxlixxxtlic2IElLw3zzLyUFb0ezVJ1VtkCWy5az6zvzkBk-CFPnao6w40qaupUsNRvQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGU_aiQEG9pOExRakK5q86cn-g9-L7tUQihtViVV10KOS2D42wkRSxOMxwU1kRPNRpIKr1Fn2nhAbv9ebI4_5OS_-6f-tKIQRC5OumgU0QMCxtj0qLttjPthhpwB-Dj2TMLR3InGo7R
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGVbGpMatJMe1aePeqGX7j4VxATxVVt3ww9yk46luGJnwoniOuELy0385FDO6fmU4ZO2ZuqC0dtNvJcjS85LgoFElO9PAoxkhinfRWe_qYfUie8dEO30v7VaiEeXlnl0g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGpprghtWlnfKqchERsgDDiOFMxjmbqWUHoa_Rn1uBIzfChthh2MvM0GdOVYMyrekLXUeBKRMuUyZO6GuNm-oB8nNZFsQXQMCqEPX79ePAa4EJFu0iG8giDPYa1jW9DPPjWAQjAi0oQJlNnOt9E8pwQ7JyfP8JPx_by9ms=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGxC9X9r3l-KuH3ljYx8Zln8kKayUuckE8u5Xlh3BTnLAJTmG-ZtNG_SiSWGybLWk3C-5jLd6nbJW3oharIfG6zRvS9bnRJawjkIIcmSCVTs1uR1OJLHQ9Rr-2H7Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH20luUcPSkEdr1UFs7tihRuBs0wrPtPSb_8frZ8P8E-k3QUeCGxk7xsLEjAXFfcr87hTqRg_UAZaLJ6zPpVHBqVUHdtEjwXPvh4fQegBYasW56QZpxYQDTAY2C-ypkSQQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6lFYKZnv7eV5Fwy5AlCkwRocYD0sNqDoSOiYuQZVwAedLpVWNLsMAX5D76I0ZV09gx8w9Nq_OnzVPc010E2k_d0DJd1VY0cTHaOEBIyScZJSMTWoeoPDH4f7T-bumFxdbXmQGinCy
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6xBaQA7UYAqEIT1l1IHtl5irPlJnCU03kGZ4CNCNevBczujpKfDFxuoCDLpETm3SW_69rxTYFmTdak4p2g_TUa8JDPb0R6x8ZAE0KTeeLHUJrrYqG-vecp_rLcQ1M8yDqW1w4dWDk0VmwVQFIAypFnmxfubc9gFFZNKobKXIi_iig7VenZ5OSWYVQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHNzmJQcE4UUgAdvi1nwFoH4beHTCeXz07RK7iDMwBLxzXhts4NJvOPOiBFU9RvbFkmTiKBrto1oSQ2tWgIdf3zMQQF2-mvd9f1SBS4GlVMtj8xvazczeih9gycj6mYP7cRWNVUV1eEryzk13WnOvCLvvkP
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZ99eNfsbCeW_AOF6ho0pOwelM1y6DS2xF6pptsEVDhlDDW3GLgQNqt0J9wLmsjNCPX9RzxLfAmxlus8mcqH34_j7rZsAVxNPq6v3dWqOQyKdzylKOdX5CjuQOgdI2TQA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHq96lyPiKsR83UASy5r31K5_JALAHV-W2xb_QKYE5PwLnSBYMBRrvNQHZF7FJMKjh3jFBULLh_tlJ7rnGJmsK3msMGcr9hb-REO22IxVBMSr__bVGHj4nht2lBpFLNLaNA1-1I6N-VDA==</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BT-447</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cameras</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Argus C3 'The Brick' 35mm rangefinder camera in brown leather ever-ready case, c. 1940s-1950s</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>$10-$100</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEDHuBp8WvgfiEB3dXm7lpvRxoR0kCUp4PLf8sbPWZkEE7ZJawHV5HkjCCX1rdzHkmHSfXQXi0rgUb9jckTwzxjrrv2TW-qu41hqFo-mysF7VUamLdqtYFSzYMplCJjSsFCMqYrSCGtA7RuM1E6TLnJ1f4qsOWPAAPWDElPlR0Ohz2WGJ4L9iz82a7OuGooDOlfu2bmk21DUrDRS5NhGkiHqgXPkmBx0JLxl4lIBfNp8O0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEMQmzjLSUoPwjWN48k41MEfmxxwqCjG1qCwHu6bQL-ZouTjJeqzBkRVUOP9Jml1RjvjCX7jkQM3SGgVHfZ_xyzJ6cr2Qo01XlZd0d0AW1nTTVWdq3FZOXko7Yu-dQd3iGSdbYZ8G6OSROBmpnyb_QE_1Oznzg49VF6RAIzbiuVwGRLlJ5fbF0jETqtZy2uBXWSgSc4OQQZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEPFPXb2rbv45MFu83iorkohYLMqAY1T89S4n6WqLOsjPMpQKvOEy_N-Hd5GP9YGcaCaDH4PF5ruw5hc-Qu9iA-Pq2jbRBrJvdSTwhH0ReWlDyqy7dAksoqNSI4Ti4SD9UmdQ74vUHHSS0bfUwCv3579VflFrYoPfrTdJhe1qdkN6Rfj6jG0VuIc-I7o9cM5HvwUcyw8dLH
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQERpQ3A_tm7cixv5LE_9tw-DaTE-U5LvSHWNXcc9uvNV8NjvH4j6-y7CD8XdLtbXAUZFpB7lN_ok1yHdlNUcW2hyQ3kdHh9isINyp0I1e9jLD5t7FkF74ESRpKSbX3gLkYTLfG4-xgEVMDdMOKqwmSq9JBmWRiSD121B4c=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVSGFK8FeGkDpxSoBb_KJcqh9Sepr_hwpwqOoDBZ1bA1-Rj8FMOsFjBkj_Zr-AA0uQEXA7F9v4RR6GAAtPZrX3x60HaCo5u-crK6KQxr6s4gmBWKNe35yhrh_VFgYRSfFOoXRytdz292fgJfbjD9bmb2yaumXJSJt7Foc0eOy0DjW4c0f_2ahv2LbV2w-GA5vd5esCwr7R-B26SdPQPgAjaGs1
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEcLuBhms4u4luY5Aa5XJIemTO5HDFgNOFfq1nNgH_KVqDPoCLWUgFdxs6P-kR7vtzdawTnxfCAS6XY95y4LkWljOGyHwdXU6vGpTibmOoFiRH2fDXXNZZfMs7tZe86BmIBme7wRzfBWVBVJ_T8MuI6-JAV0w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQElWgJQwRU3gSRFPMuFDolPGfj6EaeLDtbcAlkNtrG0mlcFeiTiXchWaLMMQ0O6NiaYHyudY3evSySFOSsdwnC1LafFzUGj7CLFfISFTYi2AXWunoKzj_VTWvraKnmRKrZ3ek67j8daX-IXruvtsOumo-P2zaJlm7U34UkCQ7noJxUHIU_hMxHvl1f3I1zWhB7HKgRsRurcVA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF2GhSJ_ZX_fY2Jpqkl05LZSwfZk4g3fG1spcwTDNSgS1pbS4MHZdjeyXqoopzMMP_pEydNUFQRJp-Myr3QtDXbfBem0PUL3jDG4gKIyLtBL2YRK6ZfCzb3GZyM5Q41wLfVPJlC_HJqrErt
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF9dCAz5rExVxwZCLgNIUpkb9smnw9iTyr5n8B0ug7lZ8YwqbyBKnsqj2n1UQ2Ier9_aQGtqAzXdIPArC7oYUgBJ9vbMk_y6uinotLCQfM5VbFjqBRnbjat7RoxFyqfIQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFgZCFHVQ-KmUrnBgG835gWkaO-YbDZlX7Na7m1SaWzHiyQZujdT0pw8ezR_fjxWpSoLTqnWOY9pPLDn51LzCLesRjt_tXPH5CTxsh8nVpTgnF1FNy5vr8xNDGydQ6sb62IIgEO90KOFYYQpjvUUyMO02ZxejdiinbOnw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGjrT6MSYRk-Ejc2BbRTZNZqRmreLtXgYOxu7_b_yQ2IetDiQWYtLGaTPGhxWKiPA3yFfnvBbuHBAlx1ezbSFiy6r9FHVYt-9qfbvUfrNwPpJUHAJ_YnTVn26KwOlBTWC0hs8idh2U0euH2LoqZ6dZUcqc7UuwO5PQhiA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGk1jyGuZmWiRwbdRhmzLqrZJAyBxMoc5E2v8prRLYeAWCgv0Am6da38O9Z2jcK5wmKNdHxcyBSVdRwK09wdHpW0e85fEdEsVg7uoDe_DN-iP0bFEVw-fcMpCm5OyoPOkJjPOBZM5nsth-GeD5aqhzJ59HrkGDLIOFRSiWxU5q0rFAl-gJlCw-tAvfHRSthjja6FOtJKA8e5M9iNQjkhKQBW7xTFbMz6gtgXKA4gA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGlCDvfkfp4mjlTI1ak2p2qZBgdsA0RmYDByqthXu6PcL94ANYgstdJHscflO10j1_oKPsDeq3du6-Dk2OyEtix034ypk8f3VOm6SZR3odCWXI2e0G32Za869cYgtF6uMqbV_1sLYT7VxTpH1rhjuU9q7tu4yt3X4wy05brHh4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGr7132iE9medzprW9FyXX3Bvia7AIYe0XJj1wD6TIxx-cRI-JVmW8xkkv7Qtfps6AuyPR1TwsOmrDzftFcQMMr6S1ODk_sdFjl4I-J20W-_TqAyz4j0KRRJC9fd3uqRSe1zJClkZFc69zQZg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH9PATbClareGmY8wS1jcSKziRXoVlpIfEmDS_7Pv-hiIv2NG19poEMel_Yq9z5i1eGc_GKlsd-E4hJw_GoiOhnUsZurygsNVX6BURQpIJEovDSxIxouFVU9qTNBjKcKsszpS7GlTSsmsrxQQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHe-oevQIYrBJXccfKC-LwF67Cm3VqVq8hX1pFeLYdUXU7m8GTbJi-HUs5yyt4zfNt_w9hU14n6jMHL7X9EmjTXnoRJ9JL3Rnzt1IaE9TPvJmBTg9OExBvhjfI9fZT42Cjx7zbCGkKnbAnelWM=</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BT-450</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Assorted mid-20th-century boxed games, plastic building bricks, dominoes, and miniature iron in cardboard tray: Flinch card game in original worn box, Canasta card game set in green box, Boxed vintage black domino set, Bagged plastic building bricks (Lego/Elgo style), Bagged plastic dominoes with colored dots, Miniature green enamel/painted iron with fabric-wrapped cord</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>$15-$40</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE8QdVPqFtvboZOaSHwHmV_6FuJyV57MxDrCqPQT4kZUDToc8Zt2XGYWp0qJwzfStq1PQepCSslDMHldmREXActGckTlplfUnyNMLrAejVBVWhlgyPvzGK7CrRNG12097G9gL4w70jAeWnZDBBCdlSdHQw-CWiQCbqSGD7PVkNi3fY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEG9HM_kgIp8BHmQEirZ1zzgC_S5jcwuoRIseT6ENvi619rbkswVxxk-A4BoN5FZccbjU4cmVAX7RS--QJM44EuY-2t2IX71ggj9SwhTV7IRWRVK0VHiVhiAkVrD4DQkhiqCmWxfb0ySFXWxOLGw-tBuWoEBlu5p1sQuGgeYaTapd7pQ4s=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEI0djEOLYNCdORVEONjb_SCK_QNlXtTJ4gnIt26ZmVRSV6m8pBYNj9bpP0Dssa8BXIRVmtUB1UXlE_VrsOxyB8B7AaKaAToOjzCeoFDrF2jh-kiVIwKkePAM5-Pf0sHZRnsxAaHZbI0g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEOhery18QhONXohK9CyFXRADtfKkGQAzK7ZU4jDiV3i_8eF9vQxWVhYjxvqdGo8wEg54DdFC-RhgTR6pXz7ECpQIHwGF5bNCwsHcxc_XyBuFAjmgOQ4aFqoPcS7vNj7OkDazXhBgvbv0XHv_WkpO8LFLt0ZVsZCDA3YoEnjmW1JvBi
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEX14qXnPhDemBurZnJ5557XlJR3RU6ivZEZLKq0AOCpuiBi2palvjfE74vZnvoZCnsT_X993oL7U490SpEpPNdOPeem4DAn3GvdFtJucZFFnvG8BZ-8xsIHp5gZGapnSRnw6TuAgsm_acAcYaTzH3YLbFUGVLuLTEaNuNYoK-d0kUk5NJ6lpFzTZc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEeQFackErBhr6WsPMTflERA5uVkLuOSoB99pCcjzSv2CsMBuFAu2ZgNPFu-aUuWDJ-BaWgN7OBiHejTd_udhR3d_Sdr0gU9qCW6NQvf_4_CE5GfNfZTiAwntToD5NHG8J6R0CELO-TIRu8C0dm2HBe9bqBzKAW_xTfP-xKISPmByl7JauPLNp5pCkx44eI
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQErZ9Obq8-1B8yDA1_NWDxtROgf4gU3yBJDzMMX3CeTP0V4qZQbPdDH2Z3S2cimK_Kx9qc-Gvr3JUX5jHLvqdgNJgtUQlpZQrPBvRMVaHubQ0EoxT4VXyrlXR3LbElG1RXiXT9ggHAm9X0KeeZ6jy6dTXm1SjelNBNdoiv7N6BXaKofxO91CPiicNPJQ0gxOVGX
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQExSm_3qrVXFhV_SLFplY0MeKdULl1vdBznXhviGhSrF9HxHbzzeBTpSdzTIkhnEuZx0WZ4ENpDcO-aGqUhTFbKcGPvnnxkB6g23XIGiWgjUz1RjvBEI_WtC3uuDM2uSg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF0C7zGhYTyaxjCvtGWxv5mXhPO3YksE8K2QQTMcLgVTrV-U55EuX-Tlk55LIreE7N1quIlGEV65FOf6VqxncWtbQ_VA40ThD19KqwHsc90_rUxyAnSPsK9cynGD9GAMeyt-h3JLvWYJCfzlXBmX57UQOM_tmbF65j-yblHUadIAA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF3j0fjeUIaYd9VDt4umh96F6xkHMW3qSTOHPVtzmCV8m9NDixa3y0gnLPp9WGONHnXw4UvWZKNfKwq5WD0_NTHY7J_STptBWPJQh1r-t3kkQkSN6GJ5K-5P_QmDMAmerIfVFJeALZCMh4lWQflFVnM_rKGcSNUAnI9vUtBQkBFWyA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF7Hdq_zVLFYoK75xjRyICuSwQH3AJ6BoFxRTgQGx0gIGRuOsoQR-JG5iIWLXQs9bASA0VK1iThjqypTJIaoJrFHTgUJ80kUYqJBDXJMI9WPG7m8xnBOLShNhb5KDkw53Ve6aAQQzvZhQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFEmw016SG0rzFKsVVot2t6oGLeauOmFw41Zm1Tzwq6KJNWVpBnJYBfSBcTJCjFM_dPEQXpjwfT4gvMhM4i8tRRjnz_EyA7yZcEshLsicSn8FmnOxQU2gMaulCVOHPJXQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFKTsxv7crEwaRlvbJ5qPKk7LMgGzBRsUxdz4f48y8O76yyRck8qduwQBDWYPMnQxzJTmue2dtwuUbyCprQPuVUkjUVeeZfM5BYluH4Yy1bNMe8rksb-D40AXdQ_BhP0JXaOStU5Y5avVa8ggLP3IwZn0dcnKE-ijmXs9U6Krnp5Mo8QACBgKS05vR7adOCiQUaU8I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFddYhBQp0lgwCG4mZnerbdxhB13eiUS-ylYM03VPaVRY-UwrZFmDSU97DYDUoQbKsVYi7ZXbfFO3EBYxCDCiQ1F1rYBeZAFMCIgjjCOCALoGHYLoTTpb49eXQ0L65Kk2yBFviA7ZZ_g9q-sRQ7xR7TmQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMCjvozNOkxJ4dJM53MtN1uRwUb7zIpmxxJCqQ9dN4ugPqPNhFQhrVDM7eFsyClnpENzW_DbH5jRlvFK51dVkrxoURzeGYwbddNy644R-T4P00U6W-t5pQ0QemMHcIbfccbQ4ZEmf0NimX9hIzT0SQR1JzwTZPeENLz55Cal9LhNnJH9zE2aPVeOmHhcNpaiPSUr04hjHkkX7pVEtUOtEBwSlkhhLp3FMX8uzgH3nsp8TOFnmeYsiSqYfHLPFCzAIK4dEqyR1Zg0o_6S4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGVYCI0Jd1JUqdUGXfkwRgFWLMeuT5eFIEiIEAk4EkfW6gwcPCFP68moPSx4GQT3ks28WMqGqarfuhu9UVMKKD3qRZ_lZ-t2T1uF60gdLk_awYIU_nz1OI_rxdyMXo40CBv8Xwf
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGc7DUrP_61Vpc4cJwagbKozYaXgwAgkTqKbR_lwtvSan_wCcqfjzGQQN7Wp4Ik5z1DyKhbijCbi2SDn2qgnAcDWavb8evxBFDgRi6k7-2JlF0RRySZgxQ0wkOx2VWfkBmHK_4VlLSoEOZA4VLQQJ4vjpxCFPp7CKfjrF-AjgIk-LwhjqcW8x5vNC-7PgREjpLNCwSST-BIIUhe9r_kqmQp7TPgLU6WD4V2aA6kkUwNFhGFHsP50nm99qw5l6-9eJDKocoanhfVHLpMel4kc66IcaFma9ffzPtsb7QTuC2O7sq6ezEaVJLI
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGcWGAwSDHS5h9cZUdhbIY-AUspNiKlXHQmNx8bQZX_ZCR6UKnHYFFU4he3LvQu3xjEUx3PLjimgahzM-G1ES5Ih9qHY6JO7SgHdzZUCTG319RvVVp2r0YzxCDp4gQBoxxKaI3PNePxKQE43k_gpQ_ZsfkC3bk_KLwU0q9ENWyd
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGdffkoV8_gryQPYCAAdoBDFIwBD74JiMgARXFSgrlTPcOHVgix_iUA-of01QQAz9ULbGINGYiDj5BzwNbD6-LnMj4u3C5FsYSH7OxOHavzBfeH5wDMppX8eOtuq1lmgRpI5vm5xIY2ZVZota2t
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH-GDrOlH_ix8lJK6PpNYV5FE3AWRnnbb43B-dVcvpSXRaPizOK8rmtw5OAnAsvccebGCl4hoAji8dNTml0H5aXZXsqHlppxrOgePBBZ_m4H9aQqE1RtZ6rltT_qXL73ezfZGpScZgVNdkOfJyCn7mDvi3z0zPaZsS6zOQO0QwpAHM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHD46jRDT7PrqlbPDBWq7XEvwJOTc1gEWYLNTqfBwDWnNGc8oZGLlsQubCRs4CE8yHdF1OvF7xCCz6DBN0aTL9GGOVIIymjf_brIMMB4tp8YV1R7UFh1MmhQGwFDGFWrAeREuJ3a43GKTGGvFMtsmnZ2kuERksoPonmZh7PVAN0GEMaYgteHljvOznaQhUScnr80f4VGD7JZT9BNCZ1BwK6ZiHLbpUgecbrLQyqKRQ12JYmIJuTca6_0yhQCa1OJgDfb5wqgGD7liCTUSPCcg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHFBVh1wPEOoTMf8A9Z3Xg_zbzVyz0l5dnWG1wUx6P3_UGr83EdcOVCqFrjBRizRuJHan2HwUDoXpQstf2j0huHiudr_ERA9XpW9qjjGjVQjrbnlPic8IVNnF-Opk4WLdQkrUnVR-VNX4rqmA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHMpZXsjjrkABDKldzRW44xhzrW_H7G7rtb4Yc5JdVEjzWwRWdjVgv_oAsnhKtbViXFeVPIgc3rxF3xH_x6uOxmjMRgH59GKvZTWXkHggi89TXQp_tyejoK5TzOjs7CiatS09u1eVN8Bivsrq9_uVgKqcDrrUd6nzwX</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BT-457</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cameras</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Group of vintage cameras in a leather outfit bag, including a Kodak instant camera with built-in electronic flash and a 35mm SLR camera body missing its lens, c. late 1970s-1980s.: Kodak instant camera with electronic flash, 35mm SLR camera body (lacks lens), Brown leather outfit case</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>$24-$65</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQETp2F_ZpjgOCKL0L56uLJ2ELWOjYJQhiiEpd7Jl0w4YtD6SmzH6c5SQktVyzaL9GjYU9JbfzQPAKeaa7Vqw8sNvXqWCFoD-UYoyUA8xveMIG9xIKUHXkXEoPgfNA2oAjs19VpjxtVdnGefV2_-X-w6lURs1KQ3bbfRSekuYXY7CeeJ4tYDHF6LJGg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEZt7GjCHZzucFbLlYBWgEbn74BY6_DNuM1pwV_nANxEkp_LPG5MUC2_znPbS6m-YnOnPX9AOgLfg7yLHhxqpd2VCrjfW9h6ell0kE1Oz1Gzj4n_8Ew0tXa
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEgk3_bbVlTIcL_3MnGiKi71Td158teyOyYtC7bbYp1CD7bcX3jtIHtcceUDyOyC6LWOXJMG1xITOdlgPTyDC7l3hpcpuz9YE8rKVeYFP_Q_I_VOP2NoqN26H2L4ZrnSblGBW7lcPUi11FwX6SBdNK3qMaA5cRTgyiCDmS2GWfjGiJp4U1x
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEh09bTn3mgCcdS61e4v4hkoJnPKD8B0pG8MAOkwQIsrajBROMal5DkI5j-0LPyuDQLvReK5i16siYxSE-AHO-v6lmh7hHyXbGAm1eJJ2DgecWMXXd1OVF4wtCmWoX3UYIbTi3WfLiVh5cJegFJl67BJXUOmk5HWeB0aNUQ5W2ENYv0
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFKXEfLTLYgUfoDr4n0B9mzYk3rAOjNe5kTfas2l-r32j_FmDsEVOkVxIIwREk91WxZDcBrWnRL0ap50gmGOZL8Qdn0KYP2JDQTaq5fiT5BCa-Mm1hZ9Xv3UnJAcpaS1pA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFM1Sz-JI9QttT1zqBZmD3BY9aEoHdpjWipznEORDXOraT5DNDKGl21pYenhFENqCMr0XYKhwBRyNUDnSdfFwh7q0yiGoyx4d6wvaQAElAMhlkmRg3Fc_vrxVE86SmXOas=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFamdIQWEp_3wBaRTfsvJqn84t_t6tKIjboYa2iHbWCDh5gykAMYpktKScpKDzOPl6qE_pfll_FCjBpKOfzHOgdFDlMEjb3IWTvMpV0T0mOTq8pp6jUUQ-Iu_80ycT7OajV2c-iOAFu4xhHUHph
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFtYnhO_Ff1B-8moK9EKfK1cnkzOrEO3oR1MwTSGvtaEPCepCl93Wm39K2n_8pp5uB5LUNaIV_a4u0s21oC1CjB-_-364FduOR7VAYqBU769vA77PPHobhyiklF1nWZmvjNSu0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG3hcWdJBoaTrDwDkdYBugX9H5GnT2buMwFQaSap_X5ReLmpQHAaDg_aQl1BeUZHMi_OdA7cHhvmJKmukAaKUIMYe_rX7V0GHOzeyJsHNKPW3z9Rmm630OVRC599PVOpeQIfGuiHRQkLG4tHZ1qLR4nKipbXfMATCXbw1RHoTtSuiiEHrMqPhAKBdBLxG5H3sqE
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG8PG1aQ7hzjpZSwGMG2kOegaoZjruiyr3JQnVc2hpa3Mta4gGaBoBRbMDQNxjw67To9X2BP4y5M4bsYf5Tjciin8XttA838TSX-031V9M1tEV4QkzyoU3Orcr1eiX0cf0lO-79mugT3AFWju9a97H8Y9FpoeYy-3qOzHvZeX5hLTRuNN3ampNh6KndCJ5dqyBXMABNPSFUmynzh40GoHkBJlXffPVEvKT0CRunkWZaIo3KU5jkxL8tusgF4T66lQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNkMPZLSsr6CYAJ4ZmFUg-aG-YytZxRAVjN28TvyAs4u0Zk5oTKFD97sWhDai2ZWBdJ5GwfXtWhgwsDn36X456dYAUkUfVmEAaOhr31rGexbHJNA5jXmEhQYyz1IcV9SLd1bJdt_XdamXaAzqsWAhLys5Y4hYrYp3wTQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGpE7jaB8Xy3idbjg-lPKUME9insPtfB7xwCb30c6iK9GKfJo-7U1H4OVhg9blEvELBbgKITMRFYNB0fT5yEcRMIHndwAweXdF_rR6AIDKsPN8u-fwLws5flbhywuAa-jxVPvkguCc3O6kmM83lVv90r4OZzMmqQGO9OLo=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGqI2ddNa8a0McDEok1Gc5NIILmyTuejcf4qUuepHnux2KiMLUNoFEOF190OpRXDmEtMq0VX9ZwYq6EuIRBmHgpbQOFkfU_KE3mWNIbzUqnX-iRYA7e2TwWGlBY10sDxYZZRQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGwZvvK7jKezH60YVXaV1Vww1YCNzOA_IC563RoP0JiOPdAuWnvSFkVi_4mvjgOiKI8mbHQeAfMCDyHBjWM9n98FXLKLpe41cuVAaA7iGoM1x_n6bzFT242UuiIRpV3AOtKSpYRxlsfcNVYmjHxUsIDuba2XBJnpjZzWwwic5Z13g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH7hf2lchkJRYsTUohi2VoTGQaD1QgJwBKz7HmyJetgj9LKwAYOjaDDSA9bw9ypTK6-036WVnm6ZjfutBKMLq1Nk0o1bbiIK6Jgod4AWHY7HanlIpeCtXcLMUlAw0-N-ChnlAUhz47EJ5mcPLohDCxdX1MgLKXhbbBDjglJWpKIux5bvfHxlOx0jCPL5N9qlw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH8ws5q9rqWhx0YkQ-BfAnexI5ClaRbAYsNJik6fBNwQm55iTtwE5lFN3xHG_7TmSARNxOFp2dRQeJJDA_a3TgweI6cfDcANX8tNfKSatmZZMIc80IKNTKnoqQIRTu6pfi3J8bS3LY8RQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHNO7AwH2FS9jgdx4s6km2qUMMlKCtQ4lG4kpI0lwD-2s0PicfJIIHjW8krTNlWBM6aWyDiRNm4QJqk1NsDVna2s3r06CahSr8gh8yIBGvWUUGB5ID03VD0nn_R1ite8Olz2GfuOUctDTyBJ6hlswVydjIQU5-w0x0oU5NIyBsw8W-rL6cksS9W
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcjdsVqkqGhzymyc5A0czDE1FP7l7Wl6cg2fQzex_wqto0n8fyboyW0eto_hV5RAqYRjeZU52M37crYKOZTw0vmJjOp4U_jz2iMVlexkSObskL_gXdHivfjMTahfN7OkemrpP4zsVh5YeERxSrPHUWDfbY7RHG2Q58AR7wR2eSpG1T</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BT-113</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tray lot of vintage Topps sports trading cards in protective holders, including 1968 Topps Willie McCovey, 1970 Topps Rod Carew All-Star, 1970 Topps Johnny Bench All-Star, and others, c. 1968-1980s.: 1968 Topps Willie McCovey #240, 1970 Topps Rod Carew All-Star #453, 1970 Topps Johnny Bench All-Star #464, Wayne Gretzky card in holder, Dan Marino card in holder, Assorted top-loaded vintage baseball and sports cards</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>$35-$125</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE-eI8keyaFQIzRn9egCffr7zQcgCf8Mzno8V3ongZQfoG7GRPK2aA92s0mXam8cYRbzmJLRnkmNeGkIvQfTfBnWc-BeOzt3v8NztzpjMDa3KPygeaVUdgK94DpKZnTGyG5pFVfbGyQ8TVN2XDWw_EFxeVBBIiY70lcmXovvqAzj47LXnChNBi0I9R25r8AxL9G2OMLuLkZSLhxEIBWbIttAxutKw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE3O3_RajRT06R70x3mFLNC4fzI1J2B7qUM-jeK4ppqCwzj4Z31k3S1IXmb92K8rx9q1pFYEg2BnKTJKiDVUMTMfmZ-e8AHBwQIDjq16Mbm45ghq0P_w1EpwzeuSoZCoH2tb5D-1PNQNHQDoifLIrhdnd7CCUNsXdOQ-x5jBmbFK_sZmIyOyST0sTt8
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE42vGQWiXRa7BpKjU-548CMb5o5RHSab68ceoulyKnODGQ-ln8krdmkjL3uomo0P3XBGhLoYnB_27PZSq1WOHNBOsSoTuDupF9Yhvg3waDdFM23rbl7iNNsTe2h7Nv0JAyapN7w-tDWtvWLBdE3BtJ7m62mBsdCqiU27WTkjs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEkX_KkhagF8z_jnB91xcwJIxIoIXlEzJCScn8sy0ejqHYNlRA9uPE89NXdxpt8HR8rusJaMUSFNjUg8zclg7nF4xslPqkNsGSyPLUai803yWxTxKvIcnJUGwTAM3RpSgj_Zb9wwW0Z1qpFaWf-XEwbtrL-RLNEbeTo6o4FTTnjuj9dDPza0aCZ2vswwW5qrgHL9NQIoaBRS9gyD6365teuJavs-GO0FFLx-vvYcV0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEuA98dt5Am-rdC_3wFVAhLVp2MmzTxgzEwAnWEeVc2yoICuj6HgCwRJ_FsXZzA-RKn4HJBmM64mFGw7ipRt96OBdTEt8_4JimantPpGGWSCOdvv0y1gDPgEwXJ5Kk4Mg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFEUOC-bdDu_K7xtyJgTfE9lngJuJVNnIbPzU2hLt_Q80TmuzzEHQgHvAS684q8WHj9yGvuX7NTDztzCbOh6PqGfukHxN3xHwxEICNrRyk15wwZ9PjnVNAq5PQo05IL6zU5-KSpGZ5LsDKbEUpxpCQ94MfvMFCx3rk_1sr6fUCByQY9MlASA1tXAsg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFEYH3Gkt6BwdtzW0fQfSZcxUT-m-YilYyfniA9MJbbhNPexdB9YMfY6t2x1B_AvpD1xeI--RkNIva-EB0BmiW90FrnjH4ZEzLWb4ePh4SKnmL8uKBkBchjUdkrYW2dAgI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFIvzQJ8FjTwq21VXO-jJvys2x6YpTEtxXQLljXYTK5qJ8YE9vA9v6jYgxYSjsBI8UlCQgWpv2y8GzSg8AxXUSWrMzvvTH0BS04r8tcpXuHae6QmAlnWxpQ6wfIAGh-GVXrPzUM0buMgdCkxyreFnPR5jHGW5u6n8xKKhNPqQ7tM9azwzTaRchL_xvF
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFU9xqnVy3iGmXO6MCXRhQAz-hp30xJKs0ddLbHKICr3ZN7UsRgh89pYpl8SkuE2aUVP0d96MdcfRevkkaHLBnoMrhKKOTkJ7i9JrwB-e1jDBGCiiXtHfhL5zDSeZw1ZVA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVzFRm5xWB4VYAJQmL41AxC6RngVV9OcLEds3haUZVD3-01VSU1t3vDu3bKGgMTwdPmPMhhrjdH77PBwzsXi_ZAUfJG_H_6fT47AcRseUssH5bh9p-Fkc9-rAEadgX1w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFXvQPXcPsAXOCSgPsWPR8FbC1cLKPywBaZcW4O1W6dT4dgq1fJAfpa6UXfm8wyCEVmmq8QAHc-cVxp4lco52FUw42MIPozMn1MrAHSW0dqGmhLgPP2aW3sepHmyKNbFA-xYArA2WOHA-lN_w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFbbw7spgnbXwGiGZyPTzsNPGOKiydZRR9DQ0ONAQI8knf6r_odmjrCkAm4k-MskeCaRw2tx3R5Xt5Uyo25-UwzB7T9TZI5gZWO0pWrr8_4iOQxChr5sErkdQupmlp8HuVpcI7njTjwB2JNiqw4lK1HtrO-nV9XG84e3vdjTE6o8Wo=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFrRXE03Ou5vd7FT9rFuESOBPY4GhlRDd1oWp9TiLtTNuyzOEdp22xWc9lQl5F1npvCFVfcsKgjtKbtLBYlQMGzH4MHIeGyuATx0PRgM3rbh8gFap_l1Ym25u89eDygX4dV73O1c7gxvF--Fao9UdBbmM3qEjl_x7xPcwFKi7AeD6d4b2PCzWcUZznpbw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFuizTXsM50x3f674283Hp7w0H-PaAlOsgqO2_TgRhKQOIgusG9BGUz6nJxBTHdNFYsTJK7xOJSCGh56MSlz84djGJe3ElpP0MyUi73d8SpjGbEnW01pwokFHHU6DvZqcI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFxuacLyLytGjAC_xcMCpG5bmMeWxyWz7AP-r18XOHrm4Bj9mDrpnSlPnJENFHdAD1fgBm2VYJaymZG8mb_s2eARAf1JxNU0uE4gOUHcYMfcVCiSIO1fiCPuYe9r6p9hm-_BC3agDZV2XgG3QFHZmppIiyu2-xjT5z_2WhL86Lps5LFNviAosaCU-xJ9HW-3MfxKovslS5IdoRm0mA3ZJevnxYFIGI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG6tduMkTz_o7igA-MhnzCKvEsyVUVolJMkWPGBppq1ypoPgvgVThIJeWLR6brXmcNamqJxa76l3Hzb8-wZllJTWJZGtbiz8t3-IBvro57yb9E35tdVZerKUgoIDOHuK3I8UFyor2YQEnnPu4CBoI3BFONv4BUhIHWY_6Bv9pMK
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGB1xZA5-XLizHXTer_jhYHSULp4uRQfBOOmQ0v_cCE1X7c7AQsnbVq92-w_SAke08rZTVMcwBgRGGbgLqqwj_N9wTayKJA4zatdAh9wcB8p-ADzkQfx1AS_s-CzhpZsmQdjgiNjKaH0gDAvz2oOhoL9-RQwqjcjISk4-HnOXWQqJvCjRfH77CcW6ZoaLGqnY5x2OCMI3hNzPEThj8QM4Rjv1Cs6Y4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMP0rA40em-puqgw4dxbDs5zzaT36UPf7enhUEEL8mC-jnSOM8quXZqXGfRwfyAZy_GwgWRxlaYJbW_V7GVroTRvYdTGWBXc3RNdabExRdQfi0-WF0BPukqzK_f85J-80H8PwMkAJg9_2OOqMflBhzWwJcPXOccNwUCWKo8_jEPXpZLxSKf6l2eg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGkKl6rRy0S3avh2dc_AfcSk8SuBYK28nptBei3pGqjNRRUZX_W1luaS7zEos5Hc1N9Rji7NjrO-77n5-NXj8gH2T_igHxL6WqbyeGZscKNXXogv19ThpWXpXMGNLAL3U_M5_TRoQlqIr74bdDP4Krl1QUjZ4KTW8A5hDRb29aMci_DbOL1W1dVpAqgHuGSsL9Uj-G3eqFHK40cpmp7Wo0J78brcD4-29I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH1CP6hT_xlKIjsoRvcVaAO9C1JOr8AE5B1Dc4JtWO61KA1gTxoi93deHtApysTE6SOfk6HkUOfQloOR4MWoaAQdueNfTmX9pXGflQ4vXQV7KfOhLJsY4SKoS8i7MELQ5XAJpIA328IYqYsltAkTwJUiQ6I7Pv2IUMTEb4-NVxn-MroMbjKf6N47WTIaW_GBqXLo51hWXUVeFMzqLU19_NJM1oy-UBw35m1lf3XOXQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHQ-bPTE9UbjmblzBcKxFlNzF8IWjssqaFS7BYoWAitEJxmsdAOrNzcL4mZUcA8KgtGvabZcH94v_cnYx-I_aAFh-c5WZ3hpaRr4ISxkw8CbRwTFnXaCFphh2zVULSxjjZ3s6jNLE_JlHBuU3quhWJ4fdtNk329scOaLjPZIPkX5xLMjR1b7A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHTo45EvXuMNoOpHwLLkalyCw2i7mtB_aVDgBPp_2lYUNiqEHOIV0v-6nrPKex7GHvMMwdGDSXHulkjfz7orNGjrpFTE-zoY0QXYcHQSStWS0v5-p6XfXVaumwTzMyv-pJB4gzK2PFzcuiFYrFigBSXXrKNJMoegys49n0es3FbhnE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHm7MPc4r8LlULeN5ieCPp-J9pggCxbwVJ_IerxNG2hCl7L0hyoqqw5aedj6_Hhnj_hJ5O8wrfnGUxOGJ5rtdaitBLMn3VeyFMpRZsZbSg8C_WWBHRieiurE0VKKgR81wtokx1yS7H0QWipZEACYxUwivWMkBe6GeiQZxLc6C2vZ0CoFkvhr2w=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxKQDMBmuhjIkXxfJgLk87Gs9TMixWBT4-2mKWM-C_8zc4fA9te2se8m9qXGa7Ota8MAasq_vZaASK2Zk4kG2VKsvAPfQQyDiYcZ0drteZiaZYQZfhBntan0OPO-Qq4fie4Kj-UpanIn_R</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BT-165</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Collection of modern pop culture, sports, and advertising bobbleheads including Walking Dead Daryl Dixon, Star Wars Stormtrooper Wacky Wobbler, Beetlejuice, Miller Lite, and sports mascots, c. 2000s–2020s.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>$20-$100</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQECEYGqu7ZEBsrkti-j8niEzqS1gDBdyvX7FrpDT6LxgoqayEDJ4VZheiXb0fjtvhwPFuQCBMcm3sB64DO4o_QNBJudi7pFLRsDAXpayhHQVgDBezrDN-OahQFhQGKRMnXQrELuzvR1UEdETicEHZftnTeUogJM51L2Ca3YEd9HNWbgXRBqB7S_wqcnSRhFhcCWl0BK_jLdfSFyNnVVTGrW3JcpuYcLeOgC9TykVYumkuxvCOTJQvhC2Bi1fCUI_mCWbzALqawnHbxwoogcSO1V8FNyAM_OREEr
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQELtbjgCXMivwy50zDR0SVUt0aCHp4t3ekVgt8Plk-aeCXAnJj7GXvaFCGLH4qHYNPZxAhAFgLwyjyQI7RZIg2lyd1LTLsiUkm49MmB7fR_vIJBAfsOUX6iP4nGStVW481CORG2-kD488Ci599_-l6QYxVlwpubCN9mV-Q_a1QTEybEGicudNxbRPkstu3v6ON0Ri5Gu15efQDbdDHEllEFB45j
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQNc46CNb81tdmYjzXtBM09ntNgu9qBiUDrxLoJqpIt0q1ZAi7ajU2MfMxnUy3VZzoiYXDBZzMNlrACiGZhlwySLfUDW1kSRyjD6gDeJUyEd9EZhRE9lAW3QMFFlB9EETMWIOrufxQD2p3xwIrYVIbtLg70w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEgtsFYtyqaHy8WpxwDksOgnHF3rZ0pbqSqmEEokP5Ae-2bTaCNPcQix4tpG95ggDVFQGzDAjuR78fvFi-U4eClOaAVJqdax2FgtsWA7LWvA4nekU7k3kNMpYnHRCgcnpaEr_HqallVQ8ST-ligiITYzEhv9GSW1e0og7ixkH6B74ofT1eElIigXbUlySDQNnJbBOv2wk7-9NszFipeQsQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQErcrWUqJh1i1ZwMgz2hlBVrXFfuaKnUayDx5LccyqMjVcUhk-Apzy0uoIlY2vYH58LkPg_4xFKzspgycFywE6fCkMc2XJWeVr7DUd4mzYNFNq8yZhwUXcd_7PITIlTGH2SErlW7AXjJVBwaFR8z-PlxMI8VI2QVSE3YKtztKeAeJKow9T56uIV91q28YkIIdYGiJ3W7DV93By5tzcMnedRAONP
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF6oWBqrVb1RT7Rp8E_puLqeZqEZB99smbGN2xx4Kf0qWLaJVde9IYZQYXjBjzXhv5aMjJQWGnc7xErhe72B_j3EKD456NIOG1PSwUdWA5ObGZ7jg96Navn3wHKpkV93Jd1-2X26RX9
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8hcnpFEqh661sxpVlnPPxs5oEbgBszLH89wUjJqPB4Vaur09qizNE4LpzgiPTK3vkSA8wxIW5VhQMu6xlYUE3NH-uv678lCCdJO53smxWzXzxYchJaz11bVzzUsfYqxapKyq-l42Ac9iG-Wezv_spgXDaxcq_2mbkFwgeuBW6vcbpDQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8qVBDqvQfu2KBOINlzk1r3hlceJA8xGok0xHUulMsrIHZ7D70V5CjUyYw6XVItPtBwuqthq5Kd4_Xy_PrnpEAU6wkFa7vXwbmHwXjKiH7LMwwRinohvR18xxj_URoyya0xDyyhhI_sZrurItReHSnzN2RRmjkR6I5K73rHVp3w-GJH_bj_w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCkQGFQF_xEJaNSWG6bjrrNYbiyYoLSuaaJE8Cp6sbriFK5UsVyKKJUis0bdJ1P_WeDwY0JXfCkS2bDkSs2nRsZOWB7zQcAhWjZYlIOwM6ARybuSaOuWU47yaJMsjMJwvsG-t2rpj9fmJ9N-qPRCTtNHNGjsKC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFaQFMNoSVmNrwgw9WAbpxYziKSv6WLr4UXqMlC3YtImlOGSjC_VyKSjMJvskstyCewaAxuq4GJ4ANsZTH_RGl1BQuZJ5rYZq5aOjmIhORC64oMthcQVASjQmYPU6js1Q00
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG5bTQvTuUkaFMfLguUr_t5RcoK-kc8GaLWq2ai9PJIer-Di8FlADU9oYGIUGp-TWAWH5ezQBIb0B1i-tV-xAkTJwfN1SEXVpDOhGIrKooSd1V4VYMdDqicpvxuTnoWajoJ_9UYqt69yZyflLaA1QIRBcM7XWJFC4oTAcQr0Pm27WlvD74ln7Pde8x8FlqSStiKU6WDTodcIHoSAdRduh2oZGiSIvapNS_wDXdkIPX8JnSD2oKQVwbdKBE8S58DJMZZrS5g-NpW45mLzymTK362w7rwTPXKSYhrEuo=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9Tc26O1LDiCKWCZz2D6SiuFm2sMggIJ50rQ390QrVoym1Gxhu3VAQyjFkB8-p0ncPyc3wjCO-P3_UiJQCS3cRK2jWDoZ3xy3ktPOENqrPzMFR3X4WQ08A-oU9U00ASfRuTP5ZO3PlumXXHwLuD3msWfVOEsQUC_i4FG9DmF7f2lsfwYcrb05GMwURw2GO3IQ5x8CqKvAzuRCBC6C4cGA_SvuW7g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGFEMdHwgY8KphvRD5fkj5DFWIdXuD0_pF0ozY8qjebFbJ6TDzQhauk-imr0cRVmgfvBvcv6n_QaD1cjq6Jww25hTcH4NEB4ciDULCBYgU5u07pBy8M7ROdJo5tRTeVrGvy1DhPoUQs7uPvkNqYYdfCvccr6nBYz7jZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGGWK0_pr_5hUpsqKHQS1bQwDssaDTOx4WtdQBpr9T8ascqqj2tJLpwgxqERn_DXZx_4O9ozilGmTtbJiH1TqwILmcjP3zP5_UQn1IY4uWh4lrYrL1jsEpI24f7VdPHkU0=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGQKL-HYF4jP57NnTxrqFV5VS4Afn2o_PBaPKoilwQg1UNIQjVpOIbCCs2YE4SHBpfa8ea1gXSEeus94ytv0Tz2DsHed8iHtZn6GZOfLE3ltH5n49f8BI6uWcU9zAl4JsK1w3bvB709HCejSxUu1esAg0E-comwgvrj4rYIcwBOhA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGScdCS_C6sy1Tk3qgR61lVo2pR7Vgul3T7r2f_CMw9Ll0vH_SAYFcTbsmeo8WhiAH6rZbliTvUZI7c0I1-v5-RLf_RvNszIhMD--0NGXCgETdMCm26KO-4jc_CNEzVUN3fxa2kNLH_UtW1j29EsSLaqNJi03_bTh3F
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZ8QPllu9Eeqh_Ir0mM9x2uvZPRKXA2a8yqpvlSDfiTwTcaB1sWqQkePze4VETVD9bBl6gULWiZavCsSCRdenAzY1-abTNo5zlLiEf82UKoQcFPsN-ZqeV98nYJoNfO7uDHu3sSZ5s
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaQovEoOnzvTSteaIh47MX4kRHUnsQnorwVj9lStdG-qCNf2ODjaxqJ9q8hYgPAQRvpBiFE9saep4Ci-1QHoopY9Kqe62bmcJqNUH4aHXJSZZ3GhrWX3Xj6tr8CMry0LgAIZPQrpTaTvq2EMI0CDdSVgE-XR5wEeSlKQMOb69F-20=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGbZ5o3cmvRHmjrP6g85pEJ9iePhGe2-ztKhKFGPmBcogl8Y-DNnAvOpdf7KzDD6avlY8ZnPaqNyE3mc3pJYsqsVZ3g-5wVITqMKe8UdVeymKrpTbtc2nX7mgDYNPRZdZXERy68bDhvJueAiVXWjaJqjayjuZtsektO
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGc3c4DdBUuNu5BV_S04yC3lmCEi15HD33N4u9DFdSvhRJR6cL0UpkOyY25TrY5YBW3olhp5mITpEAgJWBqgbt0JxPQxMKJ-9a9pNJV1cw_zR7jr08RScmEJ_CZjFWGAr425lL9L7oT7nJJQw-h1fd9W8rNSnXyHT3WPUg5Cujjzb4h_9TVa2AGJ8y4N1SCBYBUjdi_
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGkLwopwDetTQrsegifWh9UuV_yswZWwA3k08-dix9ihwtwEYvSs0sv9FDcGTxufBMS5OiJos7IqmV_D7_WutK5SPmipi05T4F0pIYFjKrVvztptH80tjD-1t-PAsvwHQO9yTNi7oZmRm8Wmh-eZ5opX5_UefsRX-P0
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGn27gmMamH2FZaRjtEGLPF_M5yQbncsukAS4PfFc4ntLSpb1PVb1xwkMJBNbKeHPK0GNgpJHfznEnLG-VlWZ8za2wFFDZBgH2LPhlhyqUYvLI1ULYZWcc8GvZvpRL6Sje_8HF2rnwtEW6DRdYs7Hm18lNIaeQe2vT3zZ_IZpDs7MwpLTWG-XmTzCrrcM81sjTpNA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGxzsoA4F7gX6qkGcuZI_EplzseqgzPYEe3s7HyTJsfkC1K--MLZ5Ackis3zyLk8Gky1KW5bJbba9TEtR1rYFOI1EHhkroCoaQUPcUAkeVeI_-OpyyABHai4mGW-BToM4EuaSL7FnAqGHuAv-tA5g75P43LgM5MXOgqZnKqlBIri-kN9MC7xbXd_86NUiz5cRRACG3URu9KZEPVtn94-MQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH5CSXklT_EA3iI2NLCxQoHQsB77NAy-UnRj5_uhzeDmQChVRcSXKwbv9SaX4BWcVQgShNbCDH-ZGUgHVF9_UCTd8_a-A03Q13sMlLLggP15eInFz7bV7mAM_ZtQArFiGwYM0xzOg0SsKNpN68jRFr6yzpgGVM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHJT-Yh-f8K6jinJtNq0CwMPWimgqb8W0yczGkNN21HNttK7FSUTbwN1MbNRTVLpxgbR1bnsddvtkouaFveMqfgCl4hUulmFcLYPmvYfXvGqXueS7GFWGL6Y5Nn-rzPCDdJhijnfqPVBnkJisgc2gmvkOcd8jdIvpdaiN67szBVvkv12kRnclkWrFdmE83rSZL4jXFfIvSKyAip0Cc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZN2P8-APWVKJ5BhgcJttT055BI6C0Rv5EN3HL0S_-7w5tUCHl6kXuJ4P7yQZXhQtY1T7qy1vgTHqVyXRSarzYO8ppZnrh-CaD3x6mL20OQRwwuz4aqVfAMxBGtHEIgAu75WZAKGIJ5tPft_CvP08pPb3Pq3pyib4aZmshTdbMCJT_SOtc
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHb_FUfWszeuk6TJVDBnTqVx_PrLb6Dp79-mp3cmOy91f56Ia1YrTvtYnJ4xTe46w0fJFZlYyKr3zbe3NoGxnryyuv0kjdRiNfTwe0Z-pzN-WjxRFd1McSZx0CU1f5rEJSP4cPHZvGiyZOcQtgDh8M-Dfu_VnoetY2ueb3PPTTPopVrKwgl7XOnwobc4jN--ij2RhhMfjDHSWLYqzIC6kZnM40iB_kCCQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHgHZHSe2KSKZo_cvkIsv9JBI2mqi4q_AozATKtaraFc8sPaqAwcwiQSGq3dYCS0xHI2BbgobKxWa_xpgc70710QkbSIcgnoM8xGWnC_arhDpIOFhQDfn2n9wEmuDHAAbQg1XwvWnv8kpvwX4waMLkLeIkY9PP4nCtX7MbT4-YodQEbkIHrATZD6JxmfQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHgeIK7OLpzcKRydh5eZoRWlUAVUlXyUteFo5zwhrFO2yhaxENvB9v6FCSAj3_7EQgXI3RbfCUhzAMif8GhaEyYvLftZJsyRWv88YoGG9FD8fqjjdlRazI8lOX1uEaVeuyIGlGOaxDttk2Ej8XYm1bfm7NmeCoRW1j_PJ10EOFXaY4fpaVW9cyFwaoCDJHgzCYRihx-9cevYsAIvwA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHhhOiiu8gwkDQ7XrHViGCHIYo857FkItWOoKC7G7VZMZMaODpe4Z77ykixzadeU8RjQFQo6c8Z71KVDlUIYicMp8Hws0c5WHneC1xDV0b9pONH0LfALhyEVT7atWMx0qwtKDHwdy1fPjUF6Xq6xWoCaQV7C2UMSw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHi_Rd2pzmYsbVpaPfcWY5T3CJkLqbx8Oo_ZrvHIZ569V1EthSM1y5AztjxIpDYzBKH6-gOAAZxSh53nGs4K9hhFeUFd69yuWnsE57UMMI6iflKnEMACSodZ7OCdlZAmoiY-iMCP5UYz8VO8InCTpjU1zytpuRySObggWcQDAjTqJhisw2qkwY=</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BT-203</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Planters Peanuts commercial advertising display sign or rack header featuring Mr. Peanut, late 20th century.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>$25-$99</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEXnHCqNepRpBu6GFxO05HHzc8ZWSyoDGMa85E5o5K9CsveNEIFhR5BBE-svELLPl54b_78Yo-Ng5Rji5ptusqgk7wfFRcB0xlvhPfCb7Oo-j-YzFLHhbI7LQV-r3CkUmaFpS3ftk3Rmq0E-XD6WBedA8rLU-Nsyl9xjfc1g4_9u-cW0g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEimKgUw4MC5IZWSAJuYgRPbeTQ2Zu0WUPgHAJo7XQa8am2nkGTWfGr2Qshun7fac815FqPAIZwE9-oZ1XsL3P3MLjVUYIq2xr6YRxtm9otqQk0SHaayFOlLqtHhb2j_8g=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEm6w1vxeg5vd31hF5cFYw6wg0go2Mq3IPZRt-AB5k9FGHqcDHZLpGlyVv3gIKzqRC4f4qVyYEe5H-cr-SkMB9UNN3OfqNlkta5A73il083PdS7-cscsugu4U3zaZ2FjDUUIHtwAFJWTalrHP2WTRjSsosFLFK8DtS6d7jHSz0M3COhvQitEMglE3CoZXDQgdgXjw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFR5ml7cYCYQtSs3wjMiwgDoSbCiTV7rX-afINZcrc3e5Vdkm7tv35ItRsiIp7mJAYIIyhBNyPIr_XvcwkVXephMMiu_ByHzNMWqoZXmzOYaqy3F7JGxwuPO8LaQAiTGic=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF_KEyblnfmnW_YuDXuZrnGboyAxVaqb3zypuSThq0l6Zy5mT6AJ8nI0N5LPZakJV2Utvm8WoLoGvnnMP9qfQQcBhG4jWYfvrrvlWimo919MZBrwhoUgZtZH61abWREx4mRe_PnriXVRB_syegqPHESVcxaH4dg
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFj8hVThOrLT4TJUQW-VIzehlHTXPgeO0FjkJsVGY6nBGu_SFesthMtY0CPO5Dogo4L4u3tsDblj9ymeC6Ge2oaWNurMnC9ZS8kwKwNUDW4a40EVRrhoZlUOMFX5DCv-IsNHh5-eDPK-5PCoNbz0ohNSlxU6REqAMeicu3wOD0scm7wtfwxhso65FrEmzz26Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGfR2ksgdO6TEp4ZuJPMTn4hyeDWL02RbwPawhnXVZ8pxwhXhcDfd0JzmwYUKELjKnCk893IJeY083wXy7gWfBOqWClaqLAMdX_Adh9i-uWgTR4w4eap0NIJHDsuojsayx2aOg6hcsimXR2bhDcGTW3Qu_sRsPrkA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH-fU2Q1qMzb2HDL_rejYR7iy2p9J4QsxowIDhDbE6xYogasv2ZMXg7KDg8oZgzFPdgkesjqmTxM7Of-F__UrYi5wS0FC_J1oER321zfjNNF0wjwWVtAV8T9g9iRG3kmR8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHEW2qQODSrsvo4jF8DRQheUsmuiMShcYJv2RRF1rX85tYQMSMJUK1cEFEhvu5RfhPT3DAnXNabBIV9FvcoXtJkRsvdoqoRervSyumKCPAEIHK_9ZtOCR6rAoFMl5GoUg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHO52P3hwPDawgwPAm088RpK5h9qBjX15FKi4EGtrD3lIn_uMsVd9L49cw2IHYS2IWjhHr6JbvCRIxxJs7ZRr18T9lBUMRLdVEoZ75yqUYXIam8BNVUBIE9s56tsfTSH3AnqPT50Q3Jl1n3sF1lmYzMm0hIXAP1n3nLjybJ49m6AYfX
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH_ra1zQUfANkzp8mMMk82ZoKZ_MvE4Wncte3-lYket36BenS0C6v9OuLD1I_awHrai8IhwKODcD0nsWqjxWlJmegqaXZkQZkih-xs1OTDqlUqlprFStyAWskuJhGjq8cUUG9oN3gUQfZTmTGB5q6RIGUi8anrrAqnwNFaIfz_NKpM8tcKRQUdkCoPIn6FS6lgEBQqUNqLSLsikupeg
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHej79QcbiGUiOPWnvTNEcWtG51YvFcCW6TFZ8hIFdvrUjshwjzmhrMxX2mwaqS29RCm_DWmXcGQYDyLr4D5ZXtPy3l4l8xW_yuSmS1r8GsOt-OmmWFPPg2n9k4w5g0bojzvjei-FU__kxHjFsl5f3GgFR0yPTKrg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHm772TbgLig1EqP83xPx79cqe9FpH3e9qTi0SKgQhY5RaQUN-wvfg7mwIuyJW0ahM_92sNxQ_oxlqB5M_QRF3X23rU2y8te-e5weTAbbuxJPfLbhW2yX-6yDYMvUWztk_rCd_o-_0h_yFe5efWStAXAJEEdd-D9b5H5i2ROAsxSSP_Qg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpGN7kSSjBcHZj50UaSmhgwscGhUnn8vpIZVZWbBb52NIxnBtiA2WvVVyNOsnIwssZOHVboGc3Xu2b10MQjoY0wGXmsv-8Pd5-31V1H1vIhDxq8c12E8eT8B4Y7-p978l3K8HzHTFBWrF1Jj3IhaPoFryuJVyp5BK092qnKOMECduN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BT-242</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lot of vintage glass Christmas tree ornaments, including Shiny Brite boxed sets, a Silvestri box, and clip-on feathered birds, mid-20th century.: Shiny Brite boxed glass ornament sets, Silvestri boxed ornament, Clip-on feathered bird ornaments, Loose mercury glass baubles and indented ornaments</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>$25-$85</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEE7FQ1vk5rcvOKyY73GV-_U0efwIp6P9jVJ5BTJDWGvM_Xj6xB6981w4zqFzf-xTcp8b3lWdPa73nGJbzu1NmGNygYQBWXOqWxwFX15LTcWM6CFRLyrCp8yvS8Ki07C8AqjyniPopQ8F2aXeHkpL1IDg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEKBQI9thiEDG8dOg2YhSPn-3VnecN1zy1YYuEz7byutpoH7OOJ8FRpnUbzW1nF97ztqqcelH_RrlON9IduWJw5HVq8rWpQ3han-egJ1FeV8VOdWXNvEAAoWemVqamlxxtl3v24UR7S-s9b
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVnlH_v5CNNRggTH6rNOEaQUiSyoMD-FBI9uh9vcKlaiDZdJwFur0BTLrBGzY6A_4i9SfBPXXuOjEGa06mgJK1P5nHrrxLPFBOsmDPY2D2LKDKj7mr3PjUR_4Hh9CMPtDNPCsec3tZ1pxJof8Or5Wr2_MgEtUlpHzP89E76R5geZVplyrhbWcql5KkcqrpnBrGm0A1yjdoFJ6XCFvemynNwpYXUzdHIQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQElxLWENRdiYdBrmvcib9ox6iCuH5AtnpNglc8O0pqJ1sxLnwkdp9cr48mDUtEFy9slFlR-pcmg32GwRJzEvmGznMO6oxAjUwPk-FXzT8CdYM66yPb3ELYEQaakkCD398ALoFKtk2ZejsalMvCVsqZ3IwCgrVKmQnmkWaH-QgcZmZ5zYm0IOyaGU9f4-zU9wrACZTGVANm0wBOwTAg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEwMUYAjt-XesS5qKomCFRNDUuLFS__7buJiKU3eFsTmLOzsAVCEkCUt-VgZbrqCOm75M2bpKoS2caywQPDsES43XZCXuo5Aji_J8lJ93FaOe7ud7JQ3vQA2XoPdjvhYNqLAvXi-PnZZ3uPKP6VsY3o3y73uPnReHlN6ghQ3QosnsUDw3BI94i5TkSJug==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF3rsBpfVLdtPSlW71KsdTZUjHf-JtZgHa5A6oQ3IOGaHVGnBRBNtaXcg3XmZzDoRGJduNVR9LSxXi3UaFmenomaGHttUQLGXXq_9H4_rmhy1vvi7d5YT8bvLOblHdqkLojyAFlTrT1HwdoWbPqY4Q16Kp59hhADn2WIui0yL1XfFI8LA3Uus3OSHdxNw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF4uPer5bREiaEZwbI5w8OZI3a2--vsigchEOeN7XC4L7J7HswF-Qxt1YYSMA_rzn3vjBUV2cvCvwE-T5WACaZrKZxGTVBX_oaqbJz5ZF1IiNtwnkLhIPJAhgBHcaSr9g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFS0-4AGfsDpfzQsg0IRdq4tX3Zk4GTWg6TFns_GHMpe5PJtJe_Zu7ssPvc_YCNmqn0QvefBw2nQ9-F3FxNMDheYlYdRNK7jPzG__oodm46-5ePI32MTxlzA8S4ybE5dTQwSh_2RUc3
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFVklm1_v_IZHIfj_YNC_of9YVVlBi8qZgopwls_zJ116A68rXUV2Xmp6fvL-QCkOy-xU2nZqKfRwrzew6KUAgsW6NNhum2jgTEk7SgXh9CTgCwoGTs9--7MALWpD1C0yNqmq0csfarNedSboANknBZy-ftIbqv9jgsMr_iDfsRCikPY1A6dp_buUf-3geiBcQzSuJGIr8fL5Jk2aucdImqLHDmuRODm5NeFrRVBcOmF9lMj1-Vmv4I99pAMDm2_A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFsiFDG9tzShNZo3pmNxcLit7iqYFr-q4JkgflGFWqXSZJggRVHQi9VcEn1S5yt30DTkeL7gL6stTafYziUGzDy2YnmRD8ziRSdKwyY2WRUk2WZoMGFVQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG35o23WFCJ--8Jqa1jPyTQUxGG7QlEgRpHL8hy8kzVowBvAERc2AR3wXsMvwJIfDxqas4R70-SJtUsL5SFq4NSVqE17KXKVH5ufcNWIguxoxkaLzfAhDZdJ8vshSK1HimyBusp3Wrq8bF4ksu8nn9RyoMPhA9LSthkEvRks7I8TRoO4NV8m373IJKcS-1n0sG86b68qXfoSFNAuEjM3HNaopIn9sNfqdOq
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGHYoqZJk4N3HAFNwtWL6famubek-SjuChvoToNKoY4F9-Fdig_v0ppt3NO7eNu_HD4t-qLEir5ANWrVmZ2d1ymmk3NqyhLsc38luWXTshjTM8mDxJnl5AxLy4U_DepAd6W7PQOgQS39HmX7VGwqnZZ36IwCX6tyuf-4WYJq7OS6X8IaeA8DLB-RmKnWv4DEH131KJd1GQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGQ-Rgm2czT9SpRI_aQN3Dl3x4nowWDz-lOMe5w4UyuLmWm7mZXl054BlsO9_dkOSI5M6Acr58yEC6JcOfxyMLquLTnGSOlYC0yp5gvZR2s78RZpZXCmEt5Wiy97j-FMbCTdvU0xU_LHwZGrCpnktFLQwSS
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGRYgDdlARexQRlJfB8Y_Crpli52dwHDgnF0oKU-yLnuIg90KvYAZmHMOwVCEyt9jCrZXDAw5SJWAEKOSeb_vE02GTSvFcNCRRJ9pedR1KwNhP3g6D08dY_3Y6vh-a75utiRX3zlw70U2q10Dxqlyf_wC5eMRJaZGlD
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGyHE03znlZbCMgiSKZ5qnLj6qYN12k0pbeBBkoy9KvMnUcydO6ZJuyHpoHb6ztV_lVb2WJfS7vlphxn86Ob4anYuZD9m0QEISZYwN_flIFBR7CqcE_WcuKrhUGX53Dd0CIYYn4bOQXsaJ-pZASwwIlXeLif-UlLrs_yAy8BQ6t8ke3MIMi
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGzK4js5yXkoakjlRtx6UsmupcW-_dRla0ubm-lOJYB4E6JSgbzmMnSX6Y6i41ZREB7TBhRf-OmY2rAC5LVVt9Baa90JfASYmtK6gWY7SZ7J1MXa7pQtpXJqnAvXofB6rOwl4jhLpdVNRX0K4pUUFpdtc_rUbA9fz-bqpEoY2f-W3b21_a7x7TlAYwWbEJTHjxVFusp3ryovJaselU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH79R4oo0O9BJe0mQhC1bfRhEJMsxNsSQ5OCHMweRlPJQhwd5mcmKqDAkMYy9s6WwXKvP1iARFotUkdREMjA0PNS9LzmxahpcGMXIUbNwhUpFxtiJn6ZmS1DbFYCcaxK_0ymC0nwh7VrX4k9lYfSVpxuMtTqvm9z9u1NB2GiwdiH8UjjGdJgA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHhwCFCrMh7KIOVfZnMMPP4Mg3oNeL6QwXfr7ciRO60xhSU12W5PYl9-62mbBA9_E78dNCGiMBw0IO05AYsiDWCAWxgUNnpL9cYgyn8IY1pYnoSTHtD-3L3i24Wv-gSiQ70Cinoqd_LBMENNJwTGLds2oDlLsAYEo4UqveuIc6OumWn6g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHlbmug4KDbtlnERI9XoUeHwBCT3WomKsmQkVpBrr6IN37hi9cNjAVBP9ceaSLWJYKGi9_m4U2Ofqz108hTjotLYpOKADoIrK4EQvsZOutyJDZBmFImApLZermPoasp_PkkZIm9wxUuks09J8LaZXoyZk_1DmI5m4PFoek_RwAP0bg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHs36-sODVVdbss5BOjrq2YRZomMA46F-ek7KxEa3Tq-3XLlYIyKo8TQKMgTgQewaXyJnRl5gJ5i1OTHqZ3Eiv5kpn1DXAXKwvjFcWjDWsx1NV5Nv254ge9ma4luSeKWUJkiSV1x7i_WNSNZDKt3RfVqWiiAD87VJlR
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHvu7BPnBo-dSgcRMvnwAr-Iz0NzzwhnBGOvbvrFnXN9Il1wzczrm8OLJ9MaK2HvdCzJ2tTPRrDo2fSC_uUXVH63kIabZIW0kSctR_xTMmelfQW03wS4JVaQSpQlYv_nCiyKsOP1XvRHEjmDm55fWlO9YTkMk5XWSVGtaoY8Gu9Y9agyN_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BT-329</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>The Tiny Golden Library 12-book miniature set in original cardboard display box, authored by Dorothy Kunhardt and illustrated by Garth Williams, Golden Press, c. 1950s-1960s.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>$35-$77</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEKxu1pAzPucc4Eg2oAhHfNCUSJAI-U9ej9S4LmKs9k_QcL0ZAFTQWetL7-sPgSJBj4Txtc37toCV5jkkrb-W7w3OVnvh3BBIxB5XCS83cP07YgyTkSw0ExJeG8Vo1WoquiUdaV0UNPdpRqu0Hv7_CEFe4DUucgBfJk20CiaB8q1E510sMNsMM4GNyQDfjL2ENMMZmrlrq08WRmOu4A8tCIUD-VLDzE1oC7GxnE
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEWqOwFXGQr9XmMe9t6bsr2lbjhpvXMPd7aC-bhGl2L5QBgPLIpG5WUFHabKcf0kpvOZcFqgfHUNj3onXgX9aIyT7Q323xQIAH-x8qGKsSOAcm5e0TIvH8O7e2niDYJdNyEnoSCkVx2zFWD7Cnr6RLkza3A3vtVA1TLMUctq6uZVt-8YyVSMSiznp1XPvDtGUUttCTbffpqfC1Tvh4U_Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFMtiktM1QTSvIw2dDDOhw04aecQb9_G_sLOgiv1QYxLipExbbiPJgdHWWgd6o6MMmEO2Ywht8-40WS7YBea3ZiJy8qlMMg2NsI1QBmHKECeqyeL2U7rjgfw_6BoQVffk4_IC_lH9dhKG1GBYcTECwXVstdsS9khC-lxZkDTVgtijPTmoCI6AUYwOM0oI6cL-6_sEPzIvxiXXP5KU28zpOd2_7jXY8_yioXwogJ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFXT5d-EHGxafXn2hgRCFfQbN6-v-4r1wysK7nucctX5o1assbKgCTNCtpV92EFu-tjmHuykKq9ObviF1y-rAdIq2KcnXJEAUhQEAq_IzQaORhzLa2I250MdYxUijdsKCOMDL33tT8WzfKJ9c_pCKhO8pF1kMy2VP4I8yU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9TR40SVEre1oD40-90PrUT2if-QkrMKtzKRqCWm4xag_zmfk8VpjFAdyJJsPLTdIKshc2AudZ9d4HcQkJ__cLhIl8LM9uaCiszLsQNwFOvDInuqY-ranJOr_ngKneTW7OcBtTp_gkjSZnKCG3Z0mC5lWleUlFSbbSfHYNUtChOib29eOKMvuenEmDV2-zPjACJYGCtoMZ-p-HCq7mSg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGDDxUgSqtHvhQmje1Kkj--e45t7P12yiXL1cSpG8YUMEy2MQYwDMRpdSCzmFA_q7yF12NnV-cGVhgeBtutr69NQPEzWuL5sMlxWJkwBOjOxox2opttSKAN74Cl_aq4ysk_vZJGdHpiyvEYikh4QJpLsO8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGFP6Cb9rw520FU2LIMbI_RinsQEK4R0qvEWzid8yD3ILc8I5VO4e3WQdjgYm3xt_jvIHR32fBEgnNq6FPzF19yprW7yyXhDPxv3FiabkPuHI0OVtyxCJ94WKPzNByofj95uJhqyoHicFutqHVpT3p7-3-1ov22riqlAS07H_rzANWl4dDbwto_RFljh6F958u6ajqNvKfoDvdOocXIdX_EYUU0CMtIaU75f9yr
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGyCd2HfH5IJh0Wb6efkRCeWl9rqwgfvuPJ75g_zc2D9mWCHUiPk7WlU6gWr4Bgk1L4tvsPIni1JBbxHXmShlo7YVZVvNcIYQLMt1Xhc4KaIVl87Cd_tgBF09LAYUVw3ZxIOUBINRLb74ASZJ8NUAg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH8V3cyFAAtp2p4OM2FZwmZNNaBhLCJTH-ng_YCzjJLog4aF_gK-necZTqAohiDk2b4drAmv5X1taQaSop0RpzgARv_vK6NimG354k5khrtrG-MZsLtsEpU664QGTurJAQ_6g0G-5juwZWzEeH9PwZq3aT5pIRnQEMKTUdEm_CSuzIqibwOqseJeuB4jQTviZRRKQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHOncsoqGq-zOSSlFWJpDHV6HgevNnSyXUskcjE7zZkip3HkPLof4FTjeaSPT-7X0iW5hB9Qn2FCWlArgQKBD1u_8cLqGk6evqOk0mFBy40Y2icoSoqX_ilFNpN4JheuMLk4IzSVJn4aw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHnASK0OeCLJI-2rSdfOWfrsFCsddPjt1KjLwMivYA6DyHH1YeSiVzYqwCLBmyzLx2xKQqmNG9Vx-dcGAvLe7o82Lt9cXKjGyqyHsrv64pkjRaM2coAXrVReCe2SH0rZkI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHnJNDZxvc0VchwtU-YvPWpXd3Z8bnNx8KcFSpwT8Gtsn2hHNzjhqAAmEvrwEMjsBafCxoU5ocbKDUy4YGPUX8W_EtceYxtWVOwdsYmVo2gigLgFQn9oIGIK2Afyh5fouTi7ug31pgtWrL_k1c97uyRjKvIMaqmBUuJCLBxU_MLngQGTptn8KZpjteA1aqZiA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHvlNw7NNlD39BTrLH6yRGBk_vS57SK5rjpcN6qUErDB74b8Ka_En24VfrAfWrKIJ9vU_xBSciwC9T0n-0BKdJhbYC-Wmz5kC-hlKW509tuyVHG6ZlBP-jNBSNIR2ADU2M=</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BT-332</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>railroad</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dietz railroad or utility lantern with wire globe guard and clear glass globe, early to mid-20th century</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>$25-$78</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEkiKr0emnB5EFZ5lGLdXy8M3bFyVmXwOaI53ufHj8-PYaHfyzZXwSRZIvkihSj37QnOd6t5XhIiED8fNYoNNQ4YhD_Uu45-g880ACsPc9-vYdfuzu-L00hhmNBdbUUkvalLxV6fDAr3IP3F4TxcnrzbfQnCOYV5ONMy_5uAlrlLMvUe34aRg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEltAoNkKDukEkPMW-W88Vyib4iW5AOEu_CovO0ExACQLDSTuM9QOicH7d4R7KyM5xYETuDuzSBgIctFlDdNbAsy_EvboP3k9lHUahFLrOON4-Bgijbjotc6mOUnM9LEc8wPbjcxMxvGtEHudV4v0fyz8hSLThDdMp96S4wVgagVVes7_lJ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEuDrq2d5UHbLNYXstU9RhvJrU6UMDZVTIPh0RRk_pZYgkRkYV-M8yy9-YZptc7XPRVWf5tu_vUPFiATmpNQRk4-Ez32Lpj6sMC7DU8t647g2M11mmmxJz2tkcf0UzYy8qZ-3vBDyl3cWPvA5NiklWYYQNC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEyFpqtJYyGpJ4OeQgCF_HMsXnIAY3e1ab6m42b_Go0fMAGdd8DixtzHDeu2cBlJYIVFm98Qpmf-aNPne6yACAzPbfdketFzjq_HoDsjdx9xDdQtP5pFvQzAC9jSg1XcOv2I16vWB_Drqqv_bnFJUcQry5BrQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFv9HsPy7UEq0H4992R58WiqT4mZvdxnvbSBFBVRV2JPWh2uL-p5JeXILsTDw1IEY10XVKQy0h1a5nCnoiwzklzC6stfd5ALhOQ655kY5QeIUSfGD7RenYB6m3Dwvly2FGSn1-rvOXszzLd1JNuR10X7TPxsbWPzJ-ncPsmikMcLkIMww==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGHQzxT2JLMi6tx_r_Ae0c52f_jQsjtncf_NPUJi0_F9QC-Ug7EWuyKqX8BPOxDsy5ZvdPyEyFm6ldAtDIN-9pE-aRdkkDvpDciIPBMw_hMnEmw8HGPY80U3RFytWdAZ8DNUHOvSnJpBxOF3E_RZKfR56P4L0ueQAn-ViO3r1T_r8Ht9o8iy3ahJMmc5socm8Q=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGlM1jaeQLEvUFnS5-jjKM7BpAmTlc-eEgRMvw7nNfW1yz0O7fR5xlOmkNrWzfX1QxdfSxl10Qd7NVKxE3c2SyQ_hm1hTtlokTjQxPauoToaWRGd1mxbbTPBx8WxhDqXtGYujq9a9Sfvs8EvJSwXgtmClgZXE2U1SZMoIuXye1S8eZI89tery7W2cOvSg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGzlnlHwZg24jTEzDnVo-pyfRatk_BdT8KM6ddNuHrXELDpK3XgmXdo1GHSfd_ihZ6ps7x774iij1J-J3FY2NTnaNfG-1W1dY0FZYPJt0GumJ_HfmbMBkdoga7_WiOxKXcXx_aQ48RcS1FYQo_O3GCJtExtS40KLLZLMWf77olTiO4ke8c-QOc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH8b9ObljspZvGgraet1thW-d0UJ-wZse1staOMfcCXgdTwyN2u1WCj3zIt9js65yHuGQkalPQNRRGz05rNk-FycuYVqsCxKn-NhnzGV4C3PMMvdrSPo2vx8i_TkYG0kZQ0P1soNyYTMiZvNZVQXCsROEO_g-I_4qV7Xu9alaJddzfaSyugHPZd28PrXATm0N4Bc1rf_fDtDNx8FCTHwj3-taS4GQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHMRj56LSc5lpc5IyaHhe_5G13yi6Inut9k3597YQrKu0siCCclKQlghrGIsCs8iALLtlGQFf77Y8etbQhYqmVl7fxg8d9JmVRyNYUNUm_bAQG9_oV-NpusndxXJsqzAWf7bXQFvYGD2RPSoRVhk5y609L7kbHLYeFyL3Px
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHQeLdcT-SZmZnecE-Jj4rFhUjd7T8968z1AXIrP3RnEf6js4XV47C2esS0nO0WRW9FuuCIWJkepiI5aKbiVW2fv1POknO-yMJznuGE6h2ZnnMianR1ZEPtJVlSnoKu3BVyDke9SfRYUQJWAHpJWkZWswilSyOZ4d2ex8bbmt9bt6c=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHaqVZEEtVJwCHme0qFhx12_By9SDhmtwozYzIAOjGDYJpW1EgYvxN2YA7TP_NBhITyPIM_MbpBGlotfRcYZgbkq8r_aj2OBq9KrFjCgpBywe_rCEDdZ2l3yCXWRPQQxkgbbeNUvOz-jZioEQuMXMcI2mp9du_FKyRHcY10
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHrC1c_gNkNu5rLw8ltMzpKCRvD7XC6T990A4MkwAUl6VxmWml9j-VT6sqvXqSGeOh51rgc60yoh2rIxvvL4ExcigN23D2RN8vqel34ZFUPJAwN6fhr8kD1qys0Gdg-8nUTIW4OBt8YMEcUqD-SETn33r7IGeULEyhhj-r9uPIaBfgyYkiPRTNZ9PeA0OOxHm1j</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BT-348</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>advertising</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Assorted advertising novelties and collectibles including miniature gas pump pocket knives (Sunoco), Budweiser Clydesdale 8-horse hitch wagon figurine, gargoyle orb figurine, and boxed belt buckles, late 20th century.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>$30-$85</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEH7uPR6jLoU1HyRQdbq3ChOH5qAXlCDJo6giKy12RrSJjXLytzHTBeEUxH-_WvCdN6IhHvy7-XRCKwOQmJxidyCdjLxGVuw-ID3s04mmBVi_0WllpatZUt5-qi2s2h19Iwyg8WVqZQTzTM4rwVbO6lVM_DprcoRPm-X0gWJYeVS3LDMFMQlPks8c2Cw5DjeqKE9GQn7JbdbnBETg8spzwlywH_ZO8XvxFt0eHeY4RQuswc6w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEeGodGT44khWyPiYbdtWUlpYwSgzYuB6oCrdpY6SAFqpZWzmmd7oyAC7XguZXb3YBkj9F1l1id5uIRwdXCjfcRvboVFvLSgBLasXYQGZFvNkwMVnrCYFnUAOpOWJf5A-GHJmSZYiyeKIVcJrib3Z2avE6Lwh9O-vQnsWJ8wm2KVjXkoquXxv4ZWaFz
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEhHNu-1YfVgjIsyMjfKLxuUKWoYrqZjD0KN2ZZWS43jGyWfiXUStz2CH5CVRP3UdUyMSqwxvu1p2m7xL9LlKUI2jRDwH35_uwP-Mn9qCzYMf32UbQk1k9y6AyctmO80lnDBiz_-k0VLywOKAP-m02We7MeB4kN8-YQjfXOwAp9uizlBmthwZFZXB6GWyzcVXfMGEPlSZlJzY_nlAWOl1oZWy3HHZ3q7A1Xithpc4YHHOmrswJBjAs7EA8e8ZOyjA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEq8b-UEKlepklvvRbdDNlMXAcW7sMML3cSm3LZuauRMDUogcb2Cf91sC6x3IadXXfdzCosUBUqK44hFwBUb_lkyo9BqFOZ71WovfDyDfLZ-_Za-5NLSkg5cQ5G53yJc01ouGkk2JGuYtQVHR5hxcr9TutABurfdYgCObPOmk0txij5Qcs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEqDF0nBlPVPD5x3-mlz5mGglGc37bN8AO0oJa7BW_h9t5P4ASYVv9y-7WjOkOP5K5ms6b__sZs1js2V6pW_5oQp16Spfc7Pb5qKS61OrXrHtcvIAGLGzkpIx6PbaENEJLVDsibol94rQEjbOuGsmv1M7MDCfk-w2x7rrwL8_StzYUhNMvc8u56oKzBNcud6Kys_uBfQH1MHLhlefeo5IzTiX3a6omDhd7sQo5dg-lACFNgpQxoO4Umdi5ZM7R9AvVr6lKH
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEuFMV_Wl0ankFJhtgpPFKBx542Pfm1qojMQXzUfE0rLb8iSHhL7fwE96_kh2VlxnS-JHyvNr9OciskwgrwoObzRSvJNWemwI9JTdhflHD06ITyQKfxtILSxe6b8yawXWG6AS5Gm_NYN1qfnzl7_tf6uvMSQii-1t0oHq45_DbxG67VRN5mvEMqxOx-z1tPhHFSmaYRB2Ybow==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF5PE5Lx4qDAHwHL7mIRSkbM0y-d31mGfNA-A0QDU_a2qKoleqkR_e5Ks1oP9-ptDcEFihdtvFXRU4fZbMaRo2ysdCAQq9CVZYiO4fIfe3UsbNsBJzEAtLNxCPNrij1fXFq-hs6YIdxCFOuUzN4bv-lmhQr3v1tBeQc9Lid7n0suIlWGtx2h5jzKeVL1CvOYLYmt6kcx01s2CMkyzRarOU-
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFSM_qXvqO7g2VKUPo4vbofHEnK5JGB27QInciRlBHZnGpugSHDd5qjVexui3b-jIm_TzRR7LaA7gF0AqLK_sgQwuqcqoX_FCzK_qwk0Y94OLgGlir9FA4fYH0DuSwJ4AIWJ_GsbviIbkeR0BX5y0ocCFIQiobUcUpdyxAtExSo
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFTt-X73QylJDjQXTaSHNSsXkkBjglFiTbG-Ok2IrdoMUZKzj2EFZKCIWUbF9Yah7NK80HQChomS2Zt7TXXTh91ANHmft5HLS2rvWPOB8H9CiH7nE9fx7emdaPm14_vDVz0sk-p_S74Uol6tW9ty3evIhRi0-BkLrwPhmT7HJVifykzxN-b1ZmamkcC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFWPpLw179Fq46SM7QGZVEFBEG9VuXgplhuLX4DtWqi_x5e8CBbEZcSS1XNoTZTS-RU_Q-y4SYqcmcT-S66K0RXqpsZxFoJzCOrS9qx3yK3dFWV-MxphHmU6MM3jCGr45hN0BeUm_Tc917bPEAMfcXcyrcMB0pRShuw6g-z5V_d1jbEA9vCNSn73wtoEZZqxmOnwLxO2bzK
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFojnZ_aG4zkiKcM_THumRMPgNzGqWs-eG_0aNhCPXV4otDEjAnt9mUQWT3VGL1OaMFGp5YqEBfBCDaUmha5I5ERNKirXgH7SKbQhKB00jI8YZIZgrQ1J70ldjBov-zcDbPqK8zG0uRJhyA2lv6jYwvoROL02unjxLbDbomtCmH-j3MVBzy2NO3WDIJY-mn2HyiCYcd2PP-8bWKsqm5mFQWS00HGaaZpgQM9LO89GJROzls7QtTA_xIpnBh0XVNpIjSbmF4
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFv5ezciVkfhHRpglEtVJ6YHrBrHocwMzZ7ViyxXwQDw4-MflGsoL_R370CfhqLcU4jPe3kDEolEs37PRsXBCjLMITk39BB-ALnBQAgs9mYjMYLLC4TDZhA7e5FZtS_HZ5gH_RXBAAQ6zKSRFXZSB8DE851E0XaTIoxJWmCf4Oz6nwxfmA_NzwS569dgIjWc35WICXL
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9se6aBjCmHdUfaBoDxyKyGmT8Seo0lmrGtqCTKRciCOCWX6wSToVYaZU5xdeLuj3VM25BuUr32T1vUlMOLpo51iFwh4oaoAdDSmRN9cf5G-jGUAIEUyBwoW9kSTpbx9PbQAQThhTE
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGF5CJfQ3CwmbrCD2GCNb6wW1qjYL4AClu5WgNlNsEBSx03p1w_qCvZLsgGLjOOb4ru77Rw7FhtR_j2q0gCaIM3Yc6SbZZXTlQTZTLW7E2zWMP4v_To83TNWxcy2ofcR3ICVQz5hyalQnGjcF1gAhV-u_7ntvhpSx_lXIK0aEtjVlFRm9BCI19fwbq26-c4GRwgZZ1370Ltz3qos3MZFkl9c9YoodX2bN2pAfEARO4EV4ITw6fWU4HgyMYXEEsYnQMcBR9XjGVarg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGmy6AU_BT7yEr9oGj7caaDlM5BoJjECGvIuRHv4CQezJ9F7OGRVEd2x__qM0XxBe_e4XpGA3kSgt6bsM_Rvy2Kx3369V3D7unjjVl5PNrFzIXAMBE3nUXavhae6s8Wnjcz3NKRTegaeyH4sgMkMXN3uWfcQebAmovN3C1I8Q2-WhrgPr83W3ZZfdYlSbIWVnxIQYeOdZYPjvoBUvsy1g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGxKX78PzSH2SU_qOxGkvEonPq4aO3zcrtN2kuzrTC5AAvS9wrbdRAhP7u9WfltKsP_xhY6cOvozaYs5uyeCpE_6ybpKFIQN2VFFmb8W_QOXhFuqdLQeen21_7PJRwExaJFgIQtim9J1B5DeH7AEQ8z_gIZmohw_pOEjXq_3IerV9EjiIle_m9Bkx2wTh8d5lJKLhI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHHV-k_GkrbY7jtB5K1ClXqILr8OoK8mXwcpRruRGM4vAarur6DmZZ9Zc6LXE5t-1Z_li__hrhATk-5sn9qHOls7eHSTW1rtLx1u5VI3PhYCrOBIqZ5P-h_yQ7laMwIFnc5J6RGMl8duEEH3M57z910qr7Z6Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZUEujmt-BcP3DYK9SJySfXBu0naUcIp5X40LeGi3fwEB_qWKHTENPMfJsHtBfMDgNhQAn3Jc75_4nw3jNdcL2Rt9CXoyN34FEMfulpt185523b7oieTDmDtCJ5PbMcD25PTxVExo0cuDNYfAoJWM9PRqC27ckDPNwesFu0XqwldUDzzOB7kth7Wbg
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHeHIY-6lUhQXZNRcZYoiUJnaKGOZ3NtdfISkYSqzwkEzC--iAZrQ0z8r73NdQl7bC7WVYFg7seaRmKqU9acinqmoxrMMulcp6vfbF38ZKuGH2CdddEgKnzJ2Vgq0kyZl0aUvvKFK71WWbRk9D_jch9xA9wVH9I_0Xdz_FrWqvYiGm9cc7KxLulHcq6tJ4OjMniMLYY540b4A==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxW9zeROBRSDWtwkp04MFfdmgwSqeRbQ0R0AgpO6ldaXR1CJ_6uYE7bkMkDXdUfSiV7NJduJyIZ3mTWvXcdhkMFmoEsS3RoUbaM6YFKUFgr9QwMknLBPYzyjy1w8GVbUhUYJxgDL80qJN3xQ==</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BT-372</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Cardboard two-row card storage box filled with trading cards, featuring 1990s Ty Beanie Babies Official Club collector cards in protective sleeves, alongside a tray of 1/6 scale military action figure gear and accessories (G.I. Joe style), circa late 1990s.: 1990s Ty Beanie Babies Official Club collector trading cards in top loaders, Bulk double-row cardboard storage box of assorted trading cards, Assorted 1/6 scale military action figure uniforms, helmets, and gear accessories</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>$30-$70</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfK5jCCCJIguEQOn-h-lZMwFdpwDxFno5e6uiqiRrFV1KOIe7H3RoY7hRqoqcmXKRmtJuklq3XA78AIVsxXx4MJwiXsPmkjVKNU9syIQCYuAH9EyNlf3DfonXPZJ8Dew==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEw16646sy0_Ad3nxxY8ReCBjgUpsynf0OLG0K2T0HbwFHx21kZPOXHA0LCHCoNq7YVOxJ9B0ayLdNyDzXdTuK8mCiOWBdcnTNZlc9SqO2EJ_6kOubbnJ2nEA8k9TGKuxg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFDPupw8ifuSFljlSUkZloPXigNFa9zM5pyNNtlzWyzK0D91-0kcosLmrUtPevP9P8ZSI3_eDtqpPnRXTMFfrTR6T0Col-4ZBIO0sOaL95SgESX4t4x5xm2K4BHhpWhAf6SiK4PGNbgiAaLzrIhg9I337LbV2D6KBe9PEW5NBE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFIAhnBg3oc2JIgIUJqmx3AgH7DjJxZF6VR4_iPSOOBkf_2s2ax_9Lm-Gb6rId-FWpgXclIcAFOIVf0DHn1k3ZTeEiY0si-NZVMPLxOBGq1yW0f2YYIrJgnb9ofD5VevFX8ljwi9Lgqo-Mi7vXYH7fMQsTU8keoFsXofv3FgyO2sUiXIdEJ0bmw8jDGZ1eKYT0JTbLN
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFMlFalS318IvOtdI5nkds5D-zjPN7GtLWMWP628sLqvwVnnqbdSMr9q0l2yAN4Q-tlAFgwdxWC40qmgFGRIF3uMasobsS5c8fzbf2qyV-rLRQQfmNaP-GBHWrBtJbgcfdPbB1AhHxMfFfgrjro8HZa7Iq7FDqVYxL0
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFQ1PnCHw-gwVlNgLB1m2Uome3wMsgc6pOM7yEa7leaVwMX_fQtjs9DDkZhfdbcvIvFhrOf2UFC_Eg8com35eM8CjPskjnk6VI618GApPOLr64Qu9wwd4NXfMhNbt1L3w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFTxfEQQTgiqlAql9GKiUtsFc60LStybqZZoIx6jWSBzCHpb1xjfg-iTHlrMtjIPKP1oVHS7B4YkWViIbAxV7fP-C0Jpm2B5B82h1h3rwHEZPQVXPiziIB4fV5-XFq7mDo1cxUHpHVcOysohLBubWM8N6RekKDeOQhiL7tK9P0rcpyOJKQukg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFujoA_zNUQrk0n1XKJLIgC2b8IRPegl3-WdKWbGeeitqH64CAaHT9SQMJ-9YUdwhnn-0zX13hwfd0I0kpiHZxWGNIfwsZvMEMVxw5vZlLpKSte1sDBE2vooaZvBHwCDwMGUOUEJoI2jKBS9nLPVPP6Xw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFwo8m9FpJnzrzrKG0Xq_buCweB7a_8e4MxFJ3Zqqoyi3EvXkmpW7FeoQUlTIClGvTd_Ko_pKUAc6oX--4esECAAv-aCNULrNrzv5TQK-mByHsNHwYLuy2ERv19ZuzwdKM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG8eoiVhfywfw9PWQZ5SABL4GmXEattmpZB9KRAGVBWW3BRfv0kLDsHw61tlwrbAOdk8z63ArzUM8DDdsfsf9kluU2HWRBtTlgdL-8vDcHr-iYVhqJBHV0-Zq92Zbp8qVLJRTr0qH0xlychG3wQpgsiI8A1tiIvoMqhp6I3VepKC_YkF1xZ9jGSqR0SaS_P
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9dPkr4z8P-7-NIpTSy01dyFbn013w-um03CiPuplXeCZ-ZLBt7hFsTwXL_Cg43BN-i6uRcEMpfxM2KGimlvI-7becanbs-fe4J29mzeBcDowRVO56MUphLixGNiUnM5MCsZVM-WtI07wRou8sSugHG2nfFZUjjsmWl7E=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGMzO8HP6S-01kb8GL3IhGXFC7dzj7l-npNscGqCbksBGwN6-XpyrPK30yx3bVotKMiRSn_SgH6sn6hXx0G7l-sPMRDz6M-_UWie2eClqbeiAH3-VN1nDlA-zFXtFvM8wwwgw445X7hzPwIqRO0crtjmjNf98Pd_QWZByJX0nn27uK3DkMFZKF-mZVCYBdMTYfinuNQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaHZj2uRKde901g4YeXftTctWgU4JlXyZxUS116Er29oOgjrkiySiA9FRIYAIamuvpP1BzaRX9x8BDn24UkRkuXXaVc-ziVjTuZMm_COLNxJxkDsfbSJIa9HK_-08lh-v-yPNG1LIo6cv0-yJ4gB1IWtpN5CWhAAoTnie5Imf3nbw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGeVnG48BjVFhoQK7I_KIPW8amz_KfReTGgwYLVKB6nJePYZfqEJ3czpEDx7JMlzkxg6AV3lmqMQS8C7ujj81CqWnbjuul2QqZiquVmYtvY3JnuI12tA8E-rmqNA7Yu6dTaK8fesYTuK4vM5aZzUyRNzH1R35TZqpw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGySaWMPHwcDZvWBWhNN4CpzoS_VYnPuT4-NhSbGzWJOykDRa15Cjom3nmo3QvzhxsdWqhNsp909ewQXS15UpY__oKUjWXS1m6zlJMDxn-lBNgvOErZydQHTiI6-TOKrIganYivDm51UVxP02mN7CU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHUMZ_Qpj9IpnVScaqe3Do6TA9qDIzyXqn_p38ziZ6ZYCLmZVSDb1p5MIdUVUYQdxHpOfC1pQbn7TxTTqdKnTp8MKf-FiNKnVop-DYZYgVP12who8LwwiDdY48-PEO4RWSAVXrkVeNVkKAJZ8KFlu2Ki9ySfSx40A-9p_J-BVuer9Y=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHVtT3iulN2BfrwQqOR1H9lIAhdteWIUfSWkFWfKd5N0x5ibyql2leOv6lzG06WVDwgOd0WT8Y4UCBlJFcioJSvFaChIQw9F5xhhDJtg25jeJUmlVj6kluDH2zF5V9YT28jIHNy_8GBgKkmvbGeS7m2Q3Q=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHXNQv79b16a9IUXxzxu4LGN9t1AAf7eKgWS8ARGB8uy28kBazmdzHkCFk5QM9nB_3QgySqgB6d7V7UyyBvuO0qvqInIuG8_KMQrrkA4ttHv8V6uuO7-FUC5iMWoSK_Kw0mXYnzlsUtKQ3n-zRyi84OuRTc9wc_OZsSBKIpB1-oNIWsg-FGV5T8
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHklRsCDik2vCKQXjCkh5RfCCQbocaQgZeM4KeWzxsYzqWgfl5SB2a_12Yi6P5rM2PvsiuVDEg9laZAltaGoJF_nAPklHdEiOV1oRQ7vxiULoNJ734W3VeTsE0eZYCCMQEjQOnSE2z-IsCkfWA=</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BT-385</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vintage Mattel Hot Wheels vinyl carrying case / Gear Box, circa 1968-1970.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>$22-$110</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEBC28GiFuIjBhEqMtdbOAY13KF1hOAW8vYGgE_uP1hgOEzyOJc3WKoVrJaEcXib9a0roHZgK7aJfKh7F27tF8HsTnkPHg-8iOUvBXCs7kXaDjyMS2u3uf02BAzfxXf_G9LKoL6phB6l3onUQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQI629CsvNkqVn4MxEDlZQ2xM1qgReHsH-FJv7XyzHoGG7g2BPeoXDG2brHo_j4U4wsPVum_ba0njRsVumcuZSjPOlWgvAOi4PqnA1vfSpCI7raAkLJSd-8-v_gFMqygbuPIfXu9qxgnXiurZOJj0hrio6f0YcqJxLbR1p8CgbYFWowpvvuA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUPFPapoZVvTjiWUeifB6sYmqdqW_We3fzOhaQxdp9T8iv3m9p6F9jiORjahUD3YANbmUd2wZ6wQJ4_I6-m44H58spZnW8rJik2wc-WX_ZE0PnkngCXsMl-ueegnEWFWrJHUrZhmaX6jwV6qL1gD0K61F2cS4bSzZqbeAvgye0Qjzgv1ZNGL6-ByLV11OGozYNdKy_e01RseI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEv4u1O5XEZPPwaG1c2F8qXChlt0MemN-ESSpTFwinzGhKA46yXWpwzGRH-FEbab2Wx7tLFHSaj9DbjRhCO-sIixTsu8aNWjmxd-iQtmp5V7jGtcnmB77dXRzFHoKR93FKIVzK5BiFWnojsvHoeVrwyOcWgQIdrJdWXTYVtj5ql9nZaSdK5HT76i1G78RBI_EOxXWdg3TQT3i50
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFDj8hQ9FM8mtYnejjaRlYVTV5U20tA9-MGF8KL6D6N6I7IYz0gQc6O9EvlgLvN4inEZdvUpCFqknSh_wcj_O0fOp1Raiz0XjlAX5-V6JXFraWi0ZVICd-rzw7kHc6Hv8uxNMin7Et_2ZfRiCO8PXUKbdMwYddcl3jIWiHYVwtl6P2XSAc2VhODco7MSDugdsS51ZT7LeRmZXLONYUtSDrqRVrOwns9ZXUirES1cWHqSmm5IXmnBcNYDXaWiTF_
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFhDc79bLlL1Pk0n8tbzlq1olyfrCFnjmCvG-Ltikuh4YPMznI7FKOxH7yRuOpPmWhcnUqQsiS0KKkX1E22Z2setNkG6gpim_O2tKtuyu7WB2SxwtTuvdywPZOlRX9-sG9KMHCLea124Ea819TE7UkV_6Eiq-6HqmIOmP6J
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFuNxCKNHiomRNU7GBBRd2OMv4wjHPag6J78UBXS1oJv6s8GMUFdljNLO8UcEMTlLngrkc_Qrw4F3VMexwnzar9VzhliCCCtngnZUX_aJIc_0pfDuw1GB0cf2lfSm8wxsXV6C_ZBf6YPz8f8-SQno-C5DkbyG6NkzWvWoimn9r-fOKOH1Nbzp8aZeFSqjXk0D9gaa9fLh66Ef9Cm5j4KnP-uRHzJPI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvPS-sMdOdHhaqdfewWUelnAj-Fas3NeYDM30WsdRsVqWZXr1XlaSs3Pf54dtq63PXJTl0l3l_PQ9Rzdud2eNdXAFiYsLwvnxZ_4JZ6-pVGfmYMXi26ZeI6NqFiffOal9Gdaaezzyc7T9VXpQN
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG8AzFS0Du_su7pt-SNpud1s01BxRdoipBkEl3qSdSMhkTVfjp7yfJLr6U_y_AeOfelKPBOUG4oLKf2Ms-1ODDYIWLN9lVVq5AMqbQw5IkJ8tnyFesOGAACOj1-NAwMPHPHfSir65wMlWx0KeVsLTKO2l2xsTTjip3zL5I5FzHHo0X0o8mPCvQR449xi-6fw3p8FmobZgFBJw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGLywuanXVzW5RKzhp2PUV9Irpd53t1CYIfd_jHmVU30WDhFs0NtIzhFe-uaSxxzbGOqy46AR3NNuE6c7BYCCmu4hEFtJsvoMgUeA_VbxTkoNPIhcAQ55WhZEinHMjjVqsv6ENBwDnuEB-ucNf_WlGOzi4KsBHnk4i2m1e4PdC8M3k0
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH04Vu3ok_hf2O4w0MxLUyjLAMZ67lq16i9eJZhkaZNn3J2avdvFlGr_nMYWUYwOexQ73cJgEBAny8oHbvUbMihKIgDcVaZldPWNM2Gd6t0CofaGebQF5Z6G5vYJ48jm-evogAi1EOy6sTLrB_dFeRp26tE9hkliqlbRJY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH0ZxjYGOR5GY4xmwpyuHrO5vrGX-OlzrGOYyOTcTiN59UoA7Pf4SyShr_WlFooppbwDB226WX0ZtZIsr4pOEzL9smIIUHzAfD5qDS1eDUvXYfDSR3_zMCtugqpFTdR2vd7amYFe7rRZg3wdEzS7Dv1yInbntYzTVM_wVlFJRP3gUgpuHpkRxpQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHShgLg7mBg0GBWpZvcdAw-iWFHxU-nTREk22D5_qAY8arOXscixl9kGV56Uxh5SN01sTaXJwgOGReMSF5WZJaxqoxK9SIsil77Y3_NxIgjgUptJaLB4EiMTtXHBq4OfAb7tb4lR7784P84UZzTJWdRzncRyRgJWSw7zhatlZ5C9kVdcypwgXYdiQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWgv7kumoMP73ft8t6unWR0ITedBkFOftviZpdmG3bUFl9pIBR2FwfhqP5QnHxV4UlWwyppMfLzyIR12m907PvAu4M9Pg_BGfqG_5d0rNWiyS6Epte0yHM_E97S2Z2ms06d43UOpZ8Ss_Xb_dbBABcfv9s5To=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcZqQDAmo6sPBXMG4Na0vC4cpzY0NapmQ40eiI1upiyIrdUswP39USR8KE5cUogzavNxOsECKjhTmiIOUCX1lMAaKf5eme5SC8Rp2LOhtdHRTKoZglgBnTYcmTGSMvOqu86WGcp1028mrIL7KB3YMLChG7o1_tAvdYBFXU</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BT-432</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Assorted vintage Pokémon plastic collectibles and electronics, including Pikachu figures/banks and a pair of Tiger Electronics Pokémon Walkie Talkies (Meowth and Pikachu), c. 1998–2000.: Tiger Electronics Pokémon Walkie Talkies pair (Meowth and Pikachu), Large waving Pikachu molded plastic figure/bank, Large sitting Pikachu molded plastic figure/bank, Small Pokéball toy, Small Pikachu figure</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>$35-$75</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEM3LlU-ITCjjuuvZFz1Y4FL9Bqu7AOg7IgwNwWefPddCIHGCrYb8TfFL1dsAlz2jXtRiu0ZPV5NxYuSdEAy4zLuN6uwAyzohnKZTnKaYoxmgBpcvGkorcgAds4EU4c-S8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEYiP44r87-AYHD6AxrkNlcdZfzJJ0vcixEh15xLPyhwhT0aPKf02um9VoJN2pOluufQMQenNjCQnlmM22UY2g7i9fgosKS0ZiDnDxJcBxXvsW3LfD5u7toGm_-8n6qwtU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE_Zv7KlrGPNMA1aK8vw8uR98BoftelliJoUc4ITZ06L841qehasZRl4aeg-CIWSQTe4aOkqeB6Io2UXXGLvJ0pDHPYmpffDkDIys0TMuwv7ECxJ7zXZnEYeGpYuXIozWuapT9nPNoG8sz_14Ye1ghZsFjRWMYtMN4cXkQlw0-KqHT9nAfNeHbjZc98Nt5Y_4bdWgJKB3hZzO40RKwO
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEl1L7DZxGWioelGbiGQrC9yWUgTUXNbGPvV53yJXCR-ZmyOQG3kkmZThXX2rzFgZoslqhcUn_qvtwlVmdo6maeGI9SgLYrHgtEcDZDyXhaHuuzYE6d_oe7VTChSDWLET4srls0hxXy
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEod-IZDj54M4omEFxKXZTXEvbh9DZVZolTmFRhEv6wOpBqvqcq9wCRpiv2Jv7XqdHuVBk-jrfBbL2Bo4tWdkiYEweO4u7HunEbYmwmJYx5Z9g9w4sgNR50CA8tdViv2BiJpIO2aTKOQUfmbX0iS5thQ2euME64brX9ehTGQ9YSs_lOn1zFKginMpTmv-ri8pisvgeDfrKP3ZwUZw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEyqI6YxwRe9-BHVatxr39_3UIhYLXEpoUo-telDVIhO-YZ49vxLfw7DWdtmM4lHtttWOJcp82NUGCOMcyw0WhsNkpxSs6qSwsb3aCkeSFOUAfhL-1AHCUeyQroSApZNgg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFC9LmH4qDuxB47J7dMUNTeAKkzhU6oI3Pt4-mrIDabxaj36-VFfv_QAsJWCa6t00E9oBemhABHC5LJw1y7CPC0Pbsve7KYqdZRkGIqsGBeGo5k14qQ76nkSVGtHZSGm5mTlOIPPEfgRn_8eF-wSkuCEkfvEcFhz_lHr3xALWfWYTicjweF0JUY-7mF4EX6GqnTO04HNTVJLYAbPg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFEhJAwnkJDQ-TBPVk9s-ThDENs-mVcvAwlGECDkXHLglOY9aiuB67WSpYgyCgB3rS889-xIbwze7Myeh7K_ll86cH1CCDq_veQ4e3bvFTkNy1lYmYnvj10hB7KqJl_0tA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFFMOmcp4GquMET2xXkWNNRlQFAot8qZ-Kp9AUmQYqFKXU-REp2gTiMismBNABjSXpxz9aMJO1Ybx5EBUcZGg1FkIlShyhoFFMpSKtiID8EZZaFYbd_lnuBzuTC6avHWMs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFGM0ViGnAFZBCPmlvnXI8GeY0UJRn72h06QOJ7bKuxv8Ovvq-N9Pw75ucyR_c72AERUz8i9DV1XpKpCyijGITKskDu9eqtOTqPjZWS1CJYS4RZ23D4n4WMv9mC9fmIZb1zgzRxSYBKU1KHRz9wUj0AxRAVZFPRfifj5XeXPA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFI26Z3LkR3EVkI3qKdF7MwQjB-p-8r463ly2k9V0R1dXcKKCuRD3zh4p9XxgPCj8ZWluK2osyprvTM2q_aWQDkFWGZxNKtUFRdBNLwqO8EgvfU5BTnnGKPoQ28T8WIzHoHVx-2Lh4q_81ojE9ZNAZ6nGXDN5XL79UzqCHSie2V_eGz3cOZgftmggcl_TcQwTOKoQGY
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFUHqxvfki-Y3f-ocZjyLM2oZihdZS6x4bF1MjP_i6oP73Q80InpXYKhZq5-Ex7M2bLLJfyJLJRUSM011kjxTVEkHt2rcqrP0ZTTMqztPHncHiludSN6naRjibV-T4zkY-8RfCMPtWmeL5gnhQTWsXOuxVp3_hiqWyhaJg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFoUPltToVzQUae_sAgjlYy2Ln0C590t9JeOSI-7pfY_BWCduZCfNozwxNRqKl1KrfOrImNXHu40wKi-xlIMGYYP-p3uij4KGtXF2KXj5bGaeeErbsjwdmv5HRofObAUhk=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFuoMaIIcvuDL3BefgZvuE2wcFJMygdAuztAY_ZLwuQcQShsPZ7-LVEoLNiP69G70D2UJEW26cnGqFXNbiErFJ00-C12VpEDIlQVE2mHgZE-qeskSFHxOkW5mqizLTYjjYObfMs-qaryp1mBfJ9rHlLalzV9tcF_x7Pa629-qVWOJQmWRXbmShzuhDGpGEvkC5VdVm92aPd6fXg
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNQOs5yoFqtkggnUK9u5_1oKKrgpZKmctbnkdJYTNP2q67xl-94Vm1eYHiNXvaxceo3uS8PkezgJCgVMxxpIc7JwsM_T3rPmXXpre78jLvfOv1VDYhtmjMJwyGd1Rm3O8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGRU8FpWSWlf7vyw2G3V4EAAaPDEkvHReDf73cEyaNCEitpf5-b_NQIO7DaK8BXnpkV8g8vswmCw4CSuVB2y1KtzGpROdQU4FW7AIlIDPN4g6Vb1-JEqsazwX6KRE10XX4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGTHn6G7r3dJO8SbfNvttvEiZyfd-WrmWY5SQs3eVqsArgl9m0uKbBX-Dx0MC_C-slDOkuk2jgd6bKuibLy3KpwB_ApIB4nPzKC5g47Eq42MzyDRjsOFLxSMolc7GEPF-O9WqJFh09cxZ8diw5H0hFgehrPaEWwfNSc2mEKtmvSww-vGVsbbaUP6COU
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGWZUfgUZv72QAXwKB9zF--T1UfJ7pyILJO3_7hMfVdy_00-oOD5w0_DvIubVvicLrBQyWTzvQdamlz3oWl_R8M7H-WAANx90BG4kOtHRI5fVUdlt5qy6iewnsY1PHEcpSNgaC3dpn_civCjPZYQmjj242FhJYMZMgUKmvb3_hREuFoLXRpeuWQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaqpFI7i2i2H65uCknyPCRR2gdN-PXGJ2t1S8C-tW8bJjj2tAn2_y3Zn293gXAuIjJ7B50Dmg_oFzzUEfP3-AfrpHvbkaXSKSH9XxZ4YXPClyr4PgUk89D0hosZLDtD7PS36u4K1a5cjkhBEKE8YRS1Vu8ebo17GcnEvShZiiVXQlI4CFxmeUA2R9FRZydb0WN2G7j
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH8PFz8t43e-mEXqxBsUF7Fp5QCzbCE3URwG2KU0HlxxsxBZ79BiE3S-otAXwGKpRwLQyAAPNEGDRVIV95VQD3_QSCh37n1b-GFkzcrGSlcFg6a4G27dYpeLI75Kg11HPyg7zDywSEQBjbVYC1QdHB4oI1FBRAIwbohpURFfM-5
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHBTFQZQHdmqxG6A66MwwRpxQV7oyYgL9MCNcf9h-GMGaSOHNbSVCXFYBmVC8BsZCMVWGz0xcPxgGhxkt7aEdFIcGTWvfQQ9wNRgQ85FrIaHjpNUeS8CyG6BqlI8uzvybbOUouEnE3z4nRxLWehJpOm4z1PEkLAGYtl9v0hPFnpNByk9LGVNDMn1CTReQYc7F097EU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHC0RDrYAqNTHNKMP1uNJwVbrKje_Iv4CPWegkF80cTG38jyDaGuo-hW2WoPbQkyAnlh1hqj040CCbZhzzvst0OAK2ScXcDA6BGwBSYqqe29Ije6QIlAuGYKhk07_mk-RGB69JWEGVCungJM0W3uyZQDHM6wz2VHnh3U351ZHK_-8fg4iG0NeR3rA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH_kXH5XsGtRkBTLZM24_iEkpL_GoM2U-gicE4cPVape5JaZmDhiOjKxBR1nkjqlDHa1aAEuX4bcb2VVpXTEo4FswKL3vUFmjSpvZTD2AdYxvOdn_YERCAFUEjd0FowVKoER4gOSiUqdPBhknnH7pF47l2OscoXYbvBA4bJw9W9MFf8lIaHK6oTV6Ff
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHhouKUN4hhZbspqlzr8t8H8jnh9QQysYSo5XTa6g5sfjFRchMNVe0HnjtDAwcMqFtytlmLKZIGLT1bCqz1cbDAB0tMrNYbd9FganH643IOsmHiP_febqcgnPleF6IJ7s9ZGzvqQ3IkE7TcxrUFWugbzkdL4GUC2YL-hPQLc6-KUpgV
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHn4NP8W9uMJgqKbmzecsBkV-9w6MaNdsg1iMrpo-RQvUYKcW1hesyyzcPUv0d3PmRv4SbrEE6vmipSUm41SjhC5L_d1CmcpYLo-3NqGxXCJ8axvH6dNVuWR26kywp-5deY8-Yqi6W7IM1ga_kGmA7Wx2Jezf2i8YW96nsyE4Gsow30M6ceVnrIs3RNebyY09hVcQT4dBO4Wq5oSg==</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BT-434</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Vintage Lincoln Logs canister set (Playskool No. 891, 125 pcs) and Original Tinkertoy canister set (No. 116), c. 1970s</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>$33-$73</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE6YUHM4T3pE704OHI-p4Q8a-GMbmhtQpu-3nvrSUJG4sD_JwUx2NXW4EQAjFf9PjqTDgIP9OLZswe57OBhhF1AoieBNRV7MG7bwmtxpLEguspIGleJ-LkELK_l3Lq3-BI-8hJLMXgdSJ12QTQuQY8M4ToigwUyqsCgk2xf01uR37XZpuH2BwFr5zuQ4C3vP-k=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfkXaL0UlcCej1_QcOMc_ALOTjkfos6yUlGR_6gZVoF8IEC9Ruwy3XZrqQq7F0I1odsdPN5Ynh0Vx2iBcXmv4ZNPv_eWzZbEDEMv7n5N_eef8Hyf5snSe8pmPeTqak5Q==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEixny4OENhReZxk6L-7-_oETo-pp0mvi90ackfoZvJiTIU5QysBO1Kuq7kVqX8E50WMsMfw4DZ0ry7YVKFcZM1fmq0HUw1M71ncNQv-CTpAIxEQAv44uWKRTtHwdW_CA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEytgcCLYYWKpHYYg0FCQS3TBwpcEZBW9qlywt7vejH7iS0GVJ4Gqgy806s9McovFy602NJdETGWRqdYYMj6RFpuysMiMWsVnFLoE3KvaCKneaZWtLTwg2fKHmzq6ILdJC3goN64MvBi7y2hincCOTKQ_w44dJxwH5ZVY4NBEvge1IbyGV148Q=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF3Sk6P4QeeDOGS5pycCl7ngNdDaiG9sV36RjYfERy3NpOJhNwKwxsE3ucYob89u2CIZTMPA8JtaPn8KwqYtGt2xIF6OxkX60DaY_D3RfImDJUYPPh676Pok8EqjPNNOM3G-dcgHwBVw3G1M7dPHwpQb-9_nK6rtQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF7uYQhT2ebyXRNJTbnp8LYC4Z4s6mS6hNIVUDJN1U2U04GCWNNw_RwY03kObjPxdemVWzKmIdgrSZuUtzYpR9gHtfiqD7gTugp1P1v-92kanudxR_ocpsy8Mo3lfQh6B30tyLSOrFIJVGF42RsVHwxn7ECYjcZ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFBMYAy325gv0KqE2-Ff_9k4feGwhIRERfnIVJ6Q7aKNj4XR28yaxsHZtvCM5eVcnfQ5GJGdXPKXFmt8a7bDFUz31ZbNqSYb3Nibj8vSXzJYTLh3AqdeZBa5mkfxZpXOyaKT3mpXc4Pv9Zrnjvrfvq2l5GJllpeKQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCd-Cm099QKg7LUoHY9nCnN0YG1iukmPkP_xHT5qUfP67V25UB4wgIjLjShozY98lPf7eL5bV3O_4kR1ngt0V7F97PLBrKeE2NjtNdw2CT2q2EWSIBM_OLZKkcZJdLUA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFFJMVdmfUykmpHIkCgjciwX0pOrH8pz9TRcWK7nwwmFDJupOuzCB5xqUBBrYkmEyM2fggHnus8oWeAYbEDvZzYl_rUWZNzoaduRY7H6uLJ28BmkExuOjCw9Aw4o-8R5ElWkhrGjmVU1M7AQwfkMCN-QuN6v-B-b16ORgVOYHUlsAreIh885jjD
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFFNnYcH8OFe-QfGDje8Fd9Qhy7qBNrVRiTBpoWYG1aQP5voVw0ibER3FN5vHKCPJZKisnG4jqj5vSOhn0YYehxGNS5P41XMnt4th5eSN8FSTSTJb0W2JsroEbOCc0PIFi8viFudNUjHf2wwB5YMfg0uxQ9u3eiUg1dYiXkDTpIcb2PwztyynGNTekHX9fLdACL2fcrV3zncDdB1u844w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFKmZx6XCnLxuwWTuEV_2VHy2PgMUzXmDGixtVBPNMNwjG44b4Qt4mPHV06iTsLFSbEWwcpqZa5kia1cQ_P0g41lQP3jFaaA8DyH5LEL5w1EoKBJTA3yiUK_EM-05CPa8E=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFN_SFowWeg1yzblmbxAObwh-LQSDle3WP6u5i3G5OVo7XIAa9k_2i2Jq_J8BE1OJlV3rdn5SjC6jrSaX0RI7agqUzKzL2LV2Zx0PhcnciApEySuR_az86KfFpDnU-Q
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFTxNHKbHhlwAwkDBIsP28O5m-wE5VY8RKVa-6InR_-sruYgOVkqogg8ug_S7ztHetGygNs68hUax-8ddtSXU_VUji5GRPIBfCiFntNOGLAfOkOJEwrLD_LAydtUZfZOyAFD1YVd3rnZGljRr9HQbQr9_TPlL3J7uRzXg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFXxqSgClQWLHG6oBeH8FOCDbTXqSEvwkqOtrAEoFRl_R1P_a92VRGa7LsG-b8R616U2Xy2OQMflSVdZ5YVfrvBZsJiYX-BWE8dNnhm0ACwqT6iNoY2DWFPPAWgOS_lG1kZjJZE78cJuOlOG8mh2TJnLm0uJOHU9-Xgqog577Pi1hCNpQGPUeYGSgTAOE9uYxS6Tf9hRg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG2dXrJVrTaQg8zRbtifw5I15E2BGCSZUeCoueR33uOj39apwVFkRak8q5l7uAbgRWm9ZOmD9W3IbO1LPWvslKqzcnfpHrPxV-2ZUhUx1H-mFOw02FG6bkpwWuP6Ed8QGqUqBdLxxXatAylsZ_Fw6-KM7wpc1UPBKeOi_B7mH4Pyv11wMg0fL_TAxM_Qnog
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9EYd9C-oUTBaHwAkXedsKkGH4X-V_UhRot3IdlQtMLICzhcL3uBtlI3Hp92hRn6iVibXQm7wALdrTfSaevKuEOgey8coXnoS9B3YefOmrlKpOZ49oaCpubv_aP0EFAGSbGQwrZmEq8yvFP5GhKTS8PK-Ec_3Po_Rk312Dimypi4Cn
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGL-FsM8SVOhF0zQQ8vvd0Vjlq_PsSYicpl_Ga0cfdNuHmL7cCnCx3ZEVl3ffHR_4lvGrOeSkeYms_W-juExSifYq033UEEFwBX--QQHmk2dSrl-4qzF8zeaq0Y1vaGoTE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGQ8kZqqBPfNeHPWOlTS_HnVNOErsnllZpjmRW7oLplrdIpYlIC6Mt4ZvgcYLNnaCnYIkmI7uc2vVuyybWzFoDRz71W6iq6ctBcckNuJX8YMS2iyldavAJpmsPJPZAR13WXMDyiP8UmGJK_wwgqCIN4j05vMpmBbp1Dzg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGWplZMJgkzOxuE7Vtpsqfgswz3SU55AkUGRNWcFBu9-zK3MwaZJIJkd27bYZBJJVxnBGlmyDQLx0RVJr6ZyFckqMJwRU80Ddh0m3d91hCVkYbBefFDZKQ0L2cTOdZJay1IIpxMPPqmMPb0yMaypHHpuv7Umj_2spFc2BBPLcs7CTRYHwnUzvTuzAfaFntHlXdVngAIz93hfce_4qs8cWPVbto=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGjdJAjqatp4oUe9_lASRidIYgjjXE3tKAF3yF3HYcqr6NBWXjECoMh2GThFgJgLfou1eR2SJglJpGyfD62SJq1hfs8YE5N9M6f2IT5ockGPFiEAzfoeXIdMpbk_JIc_gcSfB73d3Gca9FIFvqJjOVgHjEhrAPeqbSjppcSc4egz2dXsWfIEvk=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGzuE8yxjRanmuA8Ikv97hQXCMK2LCBtygWYH7kAgja3mXdxf_g66G8ZepEe9ETZErRSKR9beA5zfRoDvtm2tKghmveGV9MhPyp4lHGRkE4ZGCezHUuAUF-baRWCMvqfSXojDso-3sJTgCMQlyJ0pJCmRD_V9yDlm8wYWTA3-DPJfTCrc9jA01M91Gcu2KWkk8q7BRpdEwOgbyRDXE-WaonFhzhoQ42C6Rfcg_y
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHKsRgzxYhvlcVG1YtXHkkXJnifgJkZXb5BLAUAhln6kv75IhsbPwE0MdM8bz8atg0BpnzJT5bIx6KQP96vr9yaiJ5Rq_z7Kg3dqFChV8jNTangJbSQ0Dz6LfxHqebd1dh2iYo6SE01VLp0ERwNDqlbgOJC9E_paAOkc4bK4YE6-j_D2XbZjV59Py8rYJ6V
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZvTSNWLL9Dg7Owbz_MTsAgxigYEkV71cFktqMJUR08TcfmEykLjL_pK2ra-bp_3HsiW2Aj2icC6Z1CpsEs7h_5HFn1Z6Wuk8gQvaFL9kNV5yMq7JqnKdHCu22qE8dPAteg6Pem_awwZ_ZPq0nCwVYXAXEea2GnYBKLEDRs2ptaUeEH9aUgz40ITSBte0l9w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHamaRRK3TarFM2N4_AYwRxsLSPRWEgafFQnMxSuJpVTe5-dHE0PJXSTuQy2KiOC5t7UHIDuuO5bve8BWvP_jSJYHmvpVgSmQlhOXhyYvFKeCjKPgOweglI-Z1dGmujNg==</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BT-436</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>breweriana</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Vintage Hamm's Beer 'Tapper' aluminum draft mini keg dispenser, manufactured by Reynolds Metals Co. for Theodore Hamm Brewing Co., c. 1960s</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>$20-$82</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFfyS_AjMdJ7apj_qaM_MCW6CRJ2mwcr-8HD4oU5wNlEoYIdOEjorw7NBTzGibQswWSwXfaoXk8XsOA-Fl1Y6FUgPfarK6Us5jC0BRi7Z9QXB1tB3fK-U0c7NoEPSBiadp5jsaiqket31ATuZw-CnqkAjwY_-QHh0s1BSnJSQSAzVoh4jz4TsFS_T7KYL0UrUBtcg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1CRtbhmjEgqPhm2GWUyKb_u_vlAU2BqxHbgaRRBAVahaHKZ2oY-2HfApY1u-djHrnTnxeg5txQCW4WuH5c2E-p7lFitpbeB_vyRPU5G7S1eyTZi5oCzQmoAA4AUEEJVXz56gTRnpUQuaY0QU2xGQLdlhQdA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG5t0akY4E8yKLBR7uETc28lcfBpW7P_Vn2o0GJqYBz-3uji_VyppLpjVgG7fP8WHC_vevgA68AsplYsxRufbgS0j3KibJ-T4IEVVf762DpcdIfYHNcGzaGBp6r3_RE3QYEa_xfOePwdntxVkFN_4JKIP4w3G7K
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGODNX1j-vO2FXNDTpQV5UXgvmw9xZRV5jSv_QoSoW4laerUKYzfuAhdsNczABJx6ZasQijQsE5sFhp1OAn-ofvNBN_npjhdfh8kyNFXGjKsUtu5z5lrKIkDBr7dHfeapRCBYU5XrHNwPRhNFkyKY8qr0Vprh-ieY8_Eu6lOgnkYQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGYcYSq5WDuZqyzIqcg_uvYiF_VoVABRwcCF-Lgk8r4_jAHCNB_B9cD8trIYUyGcoVlMV3ZH9of5Lw8B_xcfAIxhX4FFn5arTGszP1UdsApunvcf6Lu0jNtIXlAZ6WO--AzBJXGvNF6Y6vX5aY5Paeva8N9RsO0mQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGiWvp0mmWjqzV7JXXiqevb5fJJoGUvkmZ0UDY_JImJ6LN_2HNEgUCdmUk1tkg-ApUVBH9_FKZ26ClbueQrZ-kAPl-Ln1TOke9O45-2vTAiRqPlfcXIASd3tay_1f73KYQtyhquu_cHrd-qpf8fDdKD9hvWTM2K0paUnbp2h0VIlDot4yQgJVawwnfyZwNQPhVNUg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH1mEVkG4okTFoe3RmZtvwBE964DwfJNLkwJ5OsdoSRqME8thwnRXhcmA9MMqMy79l1LZk7eP5FSFInuW8wqO2PY2n32a-Otaeqjt5EY1J36VJu-A50tdNcPVRbTYf9CV6usqlVvw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpCaZhp3ls8M5Bv-IOkXyTPLfYrUP0JhOzLi7rjKGr4Ikh3OcpCw7im1yzVC6GClcYIwsSpVN7b2MSWr5fgNYEUFd_mjRcVA_ih8Ud3XpuBPOakJrbxqMWC2ETPlXcgNv3o71BdDxW
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHr1PdQaW_MFHkn9Vn9WYZn6AdoCZkzkVBxgHsSsqkNHWi_4bEg2752Hcttmh1j3z5xOJDKkKhZ25kYdpNwjCLHpuuthwl8Q6oOolP2p3TwWkZ__azOHTpwGNR-r61kRElXDe5oK9TFe8onXt_nC6nimg0cglXVMQvAJ_MS14kKch8_N9f3_KNWIFLR6bQw-cXa-g==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxC4Ng0wFeMVcEPXl3Zyk3ZSd4_g3IC-WnYLaYaFRlA6rkyqh8hkEoteffKsljPlPRI1rOeN5g0QAb6waf0Gg4jt1PFTN7ANMELDh1UWG1PE3Ae77_e3ddZxwvP9XgwB8qEtEQeT64pgx8QRaK6h8H0z5Livka8Pwktu3MULez_C3qhg17GNZgl7GVv9nTKQ==</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BT-213</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Star Wars commercial art posters featuring X-wing space battle, modern or late 20th century printings in plastic sleeves</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>$10-$42</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEWQ3KozMXGkFyjrLE3htvM_W2QuZWfjrOHz5p63ksCgs4hcaLWp0F_SjhUfNzwrIxh9boSCroHPMZb90pnpjPdn7nfC8WAwp5VEJoL5gIzkc5uiT72clLIQ9RzFfj3PvvjVrfRoorcdDM9dKUyEGWEMNs1rIMoWO8zxUekaHFoXqqTU8-0BL_D4w==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEtVEkBfsnZYRK9v_MllgjhyaMqJ24wxBWvqfRELek02M7VPcYSKGHhb8B5gObCbLgsYgJG6F1OeLhg1BWAikiYsh4ci9UWbCouJf1so89Vuc7b_t67yefUE0Hn-atYEWU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEyPBWDS5Pl6fxzejLgR5kb0qqs6Cj3GiIirBb1v-2da2K8QEiAHE1C-RY7miBJxtYj6cPSBl2nr01HllZaFszm5_rMlwO2sMRn_m9bvkGzhp5MJCk6WtQkUdmvY3JYfS4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFAqA8Nf4EuAi0Bjl44Lz0oIxVYn5U6SGAXcJ3O5YQYSvGyqliSG-Hfn_QMIuGK885q-Kd1RD7XQsIIr5ig9k3uQ-b-WHkTFBwJl3pQ2gWw4TV_0FNvp7u6cWvi2zZT0XY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFm824qkylnsSnHlrl2hYgSZ_YnfK1g1z3WKvpiw6GIURaNywbzAccvuqqt5bIvKfhQSke27iZA0hn2kKU0aDHfLnWEQqjZbf8BiNEiOB0qUIE-uNhWIyqZKw_a5wBhceXeEusLVFHiGseO6lyWih74w4FONR8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGAwlH0GQtbivuWJMgbGeTf_ekEBqKSkARFMRDZdVFQNfAFy-nDd-OvD9J8_h7Tg6kUgjbMHC27WQqAOPnqoxxYdfEPAzfUav6iaApjBtlBjRsgin6QN7dQSllyFxKqyKI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGhfg2uf5P0ecQRfkMukqEhHIhbHsXC0psfnLmmMJOEhFsYBfk86yM_TM36FkjbUB7uzVBQKzsM887slOk-5eQToelGJxux4S3seRWKGO7VyyjVYVawMt78rchUlQrQr8JMM6fkLLH0rd2rdgtzK4oglKKRs4E=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGvfhUxm6BPCNH6fj87P38TJFxhF-MJ7oD5MYKX_2VTTOURqX4-F0scGbctXQP6uowUQql7u4BPy58S6vckid-GEndO8KgPZCcCVmxxGnLODdUeDX7IfcNczNmhlJpgtQY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH0XPKYFT8T4sDWGCixX3eS-jjht0R2NHe7TOdlKnDgiwErY1fVrma8yZL-8gf06Rjfz0i2_XjUVlEhayh9cXfU3B2eLNKKP1shHNh91jCJJkrmTGMNSaEjlyRVTGbFPZg=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHSFSkoCbBDsKBsoH8kJ_vnrMH20AiJzFD7MyyaWoGjGdMmS6hWAmF_YNP5663TqAvMdRV10F9fFaqRyUlGEB17EJuDrKCQelTL4lpvOExrwK0syfXkZZHXRkPXM5cnd2CiySShSZjtS2RNQsweLiFHzLzCdg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZPi7ni-gi8ijfmdxjDS5d5OMPHgGKsbd7vzrVxCkCgi5T4LO8bfsA2v-kMOWfyTcVjPEtALSVXJjeiVuCEbj9u1SIZBVa4xe2Esj6aWkRIrYMOHrM9qajOFcI4LK_6Um5mnDS5Wit-L6ijCYaASYrLBrWM8twnTDpPDDsdy1AVJY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHd80I7oa1dEUWH_PIya2lmemtf2mowzcuWwH-K0DgkyKSyfZbAT4Eub4svXw3-MQH4ja5-byD2oxaQ_R5Eqfar6mATXG5v5Th4vqGIQUhjxIzux0Pys9XzHRX2k6FG3i0=</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>316.25</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="I48" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>598</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BlueToad_2026-08-22_BidSheet.xlsx
+++ b/data/BlueToad_2026-08-22_BidSheet.xlsx
@@ -629,41 +629,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT-021</t>
+          <t>BT-385</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vintage electronics</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Western Electric / Bell System pink Princess push-button telephone in original box, circa 1970s.</t>
+          <t>Vintage Mattel Hot Wheels vinyl carrying case / Gear Box, circa 1968-1970.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$52-$62</t>
+          <t>$22-$110</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>17.25</v>
+        <v>11.5</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>17.25</v>
+        <v>11.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -672,25 +672,43 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>operator_reference</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEBC28GiFuIjBhEqMtdbOAY13KF1hOAW8vYGgE_uP1hgOEzyOJc3WKoVrJaEcXib9a0roHZgK7aJfKh7F27tF8HsTnkPHg-8iOUvBXCs7kXaDjyMS2u3uf02BAzfxXf_G9LKoL6phB6l3onUQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQI629CsvNkqVn4MxEDlZQ2xM1qgReHsH-FJv7XyzHoGG7g2BPeoXDG2brHo_j4U4wsPVum_ba0njRsVumcuZSjPOlWgvAOi4PqnA1vfSpCI7raAkLJSd-8-v_gFMqygbuPIfXu9qxgnXiurZOJj0hrio6f0YcqJxLbR1p8CgbYFWowpvvuA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUPFPapoZVvTjiWUeifB6sYmqdqW_We3fzOhaQxdp9T8iv3m9p6F9jiORjahUD3YANbmUd2wZ6wQJ4_I6-m44H58spZnW8rJik2wc-WX_ZE0PnkngCXsMl-ueegnEWFWrJHUrZhmaX6jwV6qL1gD0K61F2cS4bSzZqbeAvgye0Qjzgv1ZNGL6-ByLV11OGozYNdKy_e01RseI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEv4u1O5XEZPPwaG1c2F8qXChlt0MemN-ESSpTFwinzGhKA46yXWpwzGRH-FEbab2Wx7tLFHSaj9DbjRhCO-sIixTsu8aNWjmxd-iQtmp5V7jGtcnmB77dXRzFHoKR93FKIVzK5BiFWnojsvHoeVrwyOcWgQIdrJdWXTYVtj5ql9nZaSdK5HT76i1G78RBI_EOxXWdg3TQT3i50
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFDj8hQ9FM8mtYnejjaRlYVTV5U20tA9-MGF8KL6D6N6I7IYz0gQc6O9EvlgLvN4inEZdvUpCFqknSh_wcj_O0fOp1Raiz0XjlAX5-V6JXFraWi0ZVICd-rzw7kHc6Hv8uxNMin7Et_2ZfRiCO8PXUKbdMwYddcl3jIWiHYVwtl6P2XSAc2VhODco7MSDugdsS51ZT7LeRmZXLONYUtSDrqRVrOwns9ZXUirES1cWHqSmm5IXmnBcNYDXaWiTF_
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFhDc79bLlL1Pk0n8tbzlq1olyfrCFnjmCvG-Ltikuh4YPMznI7FKOxH7yRuOpPmWhcnUqQsiS0KKkX1E22Z2setNkG6gpim_O2tKtuyu7WB2SxwtTuvdywPZOlRX9-sG9KMHCLea124Ea819TE7UkV_6Eiq-6HqmIOmP6J
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFuNxCKNHiomRNU7GBBRd2OMv4wjHPag6J78UBXS1oJv6s8GMUFdljNLO8UcEMTlLngrkc_Qrw4F3VMexwnzar9VzhliCCCtngnZUX_aJIc_0pfDuw1GB0cf2lfSm8wxsXV6C_ZBf6YPz8f8-SQno-C5DkbyG6NkzWvWoimn9r-fOKOH1Nbzp8aZeFSqjXk0D9gaa9fLh66Ef9Cm5j4KnP-uRHzJPI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvPS-sMdOdHhaqdfewWUelnAj-Fas3NeYDM30WsdRsVqWZXr1XlaSs3Pf54dtq63PXJTl0l3l_PQ9Rzdud2eNdXAFiYsLwvnxZ_4JZ6-pVGfmYMXi26ZeI6NqFiffOal9Gdaaezzyc7T9VXpQN
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG8AzFS0Du_su7pt-SNpud1s01BxRdoipBkEl3qSdSMhkTVfjp7yfJLr6U_y_AeOfelKPBOUG4oLKf2Ms-1ODDYIWLN9lVVq5AMqbQw5IkJ8tnyFesOGAACOj1-NAwMPHPHfSir65wMlWx0KeVsLTKO2l2xsTTjip3zL5I5FzHHo0X0o8mPCvQR449xi-6fw3p8FmobZgFBJw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGLywuanXVzW5RKzhp2PUV9Irpd53t1CYIfd_jHmVU30WDhFs0NtIzhFe-uaSxxzbGOqy46AR3NNuE6c7BYCCmu4hEFtJsvoMgUeA_VbxTkoNPIhcAQ55WhZEinHMjjVqsv6ENBwDnuEB-ucNf_WlGOzi4KsBHnk4i2m1e4PdC8M3k0
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH04Vu3ok_hf2O4w0MxLUyjLAMZ67lq16i9eJZhkaZNn3J2avdvFlGr_nMYWUYwOexQ73cJgEBAny8oHbvUbMihKIgDcVaZldPWNM2Gd6t0CofaGebQF5Z6G5vYJ48jm-evogAi1EOy6sTLrB_dFeRp26tE9hkliqlbRJY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH0ZxjYGOR5GY4xmwpyuHrO5vrGX-OlzrGOYyOTcTiN59UoA7Pf4SyShr_WlFooppbwDB226WX0ZtZIsr4pOEzL9smIIUHzAfD5qDS1eDUvXYfDSR3_zMCtugqpFTdR2vd7amYFe7rRZg3wdEzS7Dv1yInbntYzTVM_wVlFJRP3gUgpuHpkRxpQ
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHShgLg7mBg0GBWpZvcdAw-iWFHxU-nTREk22D5_qAY8arOXscixl9kGV56Uxh5SN01sTaXJwgOGReMSF5WZJaxqoxK9SIsil77Y3_NxIgjgUptJaLB4EiMTtXHBq4OfAb7tb4lR7784P84UZzTJWdRzncRyRgJWSw7zhatlZ5C9kVdcypwgXYdiQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWgv7kumoMP73ft8t6unWR0ITedBkFOftviZpdmG3bUFl9pIBR2FwfhqP5QnHxV4UlWwyppMfLzyIR12m907PvAu4M9Pg_BGfqG_5d0rNWiyS6Epte0yHM_E97S2Z2ms06d43UOpZ8Ss_Xb_dbBABcfv9s5To=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcZqQDAmo6sPBXMG4Na0vC4cpzY0NapmQ40eiI1upiyIrdUswP39USR8KE5cUogzavNxOsECKjhTmiIOUCX1lMAaKf5eme5SC8Rp2LOhtdHRTKoZglgBnTYcmTGSMvOqu86WGcp1028mrIL7KB3YMLChG7o1_tAvdYBFXU</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BT-048</t>
+          <t>BT-021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vintage smalls</t>
+          <t>vintage electronics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E.T. The Extra-Terrestrial ceramic nightlight/figure, c. 1982</t>
+          <t>Western Electric / Bell System pink Princess push-button telephone in original box, circa 1970s.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -731,22 +749,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BT-050</t>
+          <t>BT-048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vintage toys</t>
+          <t>vintage smalls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vintage metal construction set in original fitted wooden case, attributed to Lionel or A.C. Gilbert Erector, c. 1930s-1940s: Perforated steel girders and plates, Red enamel cast wheels and rubber tires, Red cylindrical steel boiler tube, Mounted brackets and fittings on lid display board, Assorted nuts, bolts, and connector plates</t>
+          <t>E.T. The Extra-Terrestrial ceramic nightlight/figure, c. 1982</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$52-$62</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -782,17 +800,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT-087</t>
+          <t>BT-050</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>vintage toys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assorted bulk estate costume jewelry lot in plastic bin, mid-to-late 20th century: Faux pearl strands and beaded necklaces, Rhinestone and metal filigree brooches/pins, Novelty plastic and enameling brooches, Assorted chain and charm jewelry pieces</t>
+          <t>Vintage metal construction set in original fitted wooden case, attributed to Lionel or A.C. Gilbert Erector, c. 1930s-1940s: Perforated steel girders and plates, Red enamel cast wheels and rubber tires, Red cylindrical steel boiler tube, Mounted brackets and fittings on lid display board, Assorted nuts, bolts, and connector plates</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -833,41 +851,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT-041</t>
+          <t>BT-087</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phonograph / records</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Group of Edison phonograph cylinder records including Blue Amberol and Gold Moulded containers, c. 1902-1929: Edison Blue Amberol cylinder records in original cardboard containers, Edison Gold Moulded cylinder records in original cardboard containers, Unboxed black phonograph cylinder record</t>
+          <t>Assorted bulk estate costume jewelry lot in plastic bin, mid-to-late 20th century: Faux pearl strands and beaded necklaces, Rhinestone and metal filigree brooches/pins, Novelty plastic and enameling brooches, Assorted chain and charm jewelry pieces</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$100-$130</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>28.75</v>
+        <v>17.25</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -884,22 +902,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT-002</t>
+          <t>BT-041</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jewelry</t>
+          <t>phonograph / records</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tray lot of vintage estate costume jewelry, including gold-tone chain necklaces, rhinestone brooches (Christmas tree pins, flamingo), beaded necklaces, pendants, and wristwatches, mid-to-late 20th century.: Rhinestone Christmas tree brooches, Flamingo rhinestone brooch, Gold-tone charm bracelet and chain necklaces, Multi-strand beaded necklaces, Large cross pendant on heavy gold-tone chain, Assorted ladies wristwatches</t>
+          <t>Group of Edison phonograph cylinder records including Blue Amberol and Gold Moulded containers, c. 1902-1929: Edison Blue Amberol cylinder records in original cardboard containers, Edison Gold Moulded cylinder records in original cardboard containers, Unboxed black phonograph cylinder record</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$65-$75</t>
+          <t>$100-$130</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -912,17 +930,17 @@
         <v>28.75</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>86.25</v>
+        <v>28.75</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>AUTO-SEND</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -935,41 +953,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BT-001</t>
+          <t>BT-002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vintage cards</t>
+          <t>jewelry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lot of 12 vintage Topps sports trading cards (1955–1961) featuring major Hall of Famers including Sandy Koufax, Mickey Mantle, Willie Mays, Roberto Clemente, Yogi Berra, Roger Maris, Bart Starr, and Paul Hornung.: 1955 Topps Sandy Koufax #123, 1956 Topps Yogi Berra #110 (2 copies), 1957 Topps Bart Starr #119, 1957 Topps Paul Hornung #138, 1958 Topps Willie Mays All Star #485, 1958 Topps Mickey Mantle All Star #487, 1960 Topps Roberto Clemente #326, 1961 Topps NL Home Run Leaders #4, 1961 Topps Roger Maris #2 (2 copies), 1961 Topps Willie Mays #150, 1961 Topps Yogi Berra #425</t>
+          <t>Tray lot of vintage estate costume jewelry, including gold-tone chain necklaces, rhinestone brooches (Christmas tree pins, flamingo), beaded necklaces, pendants, and wristwatches, mid-to-late 20th century.: Rhinestone Christmas tree brooches, Flamingo rhinestone brooch, Gold-tone charm bracelet and chain necklaces, Multi-strand beaded necklaces, Large cross pendant on heavy gold-tone chain, Assorted ladies wristwatches</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$250-$320</t>
+          <t>$65-$75</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>115</v>
+        <v>28.75</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J10" t="n">
-        <v>115</v>
+        <v>86.25</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -986,53 +1004,104 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>BT-001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>vintage cards</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lot of 12 vintage Topps sports trading cards (1955–1961) featuring major Hall of Famers including Sandy Koufax, Mickey Mantle, Willie Mays, Roberto Clemente, Yogi Berra, Roger Maris, Bart Starr, and Paul Hornung.: 1955 Topps Sandy Koufax #123, 1956 Topps Yogi Berra #110 (2 copies), 1957 Topps Bart Starr #119, 1957 Topps Paul Hornung #138, 1958 Topps Willie Mays All Star #485, 1958 Topps Mickey Mantle All Star #487, 1960 Topps Roberto Clemente #326, 1961 Topps NL Home Run Leaders #4, 1961 Topps Roger Maris #2 (2 copies), 1961 Topps Willie Mays #150, 1961 Topps Yogi Berra #425</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>$250-$320</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>115</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>115</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>operator_reference</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>BT-038</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Vintage Tinkertoy canisters including a 1950s-1960s Spalding Special Tinkertoy Windlass Drive set and a 1970s Gabriel/CBS Toys Junior Architect set, together with additional games in a tray flat: Spalding Special Tinkertoy Windlass Drive canister, Gabriel/Child Guidance Junior Architect Tinkertoy canister, Aquarius boxed memory game, Bagged soft toy</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>$11-$40</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2W_UELP728WmKXnhpLvG53h7E9Sf_7yhppCg4g9MC8l0Qe_LpQc_Q5GUlKUrkc-SJsJq1mFDcgQkU0q6WxN0GV2fgVr9C2XoV5mOebChZ3lZZrrNv_WErBQrN2l3Y45U=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE5MuN-4dJybO-YffXLVZ45M2OBsk01Q36WoCXJuONMifwVg2vUPWAAi1pHjVUkK8szSWOeE7XY2oZ7HrojMf8-ZUPXKTNCeS-bKakLrbe1wo2jmL412YlgXP5xRCxtt6pa5C_92FT1meL_1AK1n1wkWxQ5Ztr_PafaD6-q7cDyVeonNXrxBR5U0BgtZTxovnjUgbCwIt-6RjKcw2T3mmlxkcmw3MKpLG1SYfyc8hP4kyd1kY73GiBTGH6b_EBujbcbky7PZ5y2f5tyGlDCay0QcCuk8KNrN9ZO3-1bqSB2Airj5bbohb2Ji0PIh8L8kGeVW-bS35mVQA-dLzRaPENBbV31ptpAmw==
@@ -1058,56 +1127,56 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>BT-039</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Vintage Tinkertoy construction set in original cardboard canister, The Toy Tinkers / A.G. Spalding &amp; Bros., c. 1930s-1950s</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>$10-$65</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE4sQScBEuasntVyY-qUddHieujetX6CtJ-7KNUTMvsXT_DEqYMmF63I8wvladLYoOQglg5dtmEyohjcXJg7S3--qXA7aOmbExm5n9fV9bqwLtNP2s4sxUo9umtekiGzdJkJpjHMnxiVrAEV3UDNWDam-R6ApOqpFhM-Owm9MrwvR1aEqyxwNtB9FwQ
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEC4bs5zVrRFodaVRK21hYueq0z4mwhNoDQzfEsi5Kz6fdD1NzOqIopz676OM9d3OpQ4kVKqnj4i6mGFYjWr1WyzovzQryLgka6q82iIy4uFByz1nxi69VXSGKQwCnyIBARzHumxpi6e2vNd-WzbDnm-O_KG3bKOieVkPVK
@@ -1129,56 +1198,56 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>BT-043</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Assorted Vintage Dollhouse Furniture Lot, including wooden and plastic pieces (dresser with mirror, carved hutch, upholstered armchairs, kitchen units), circa 1950s-1970s: Wooden dresser with attached mirror, Dark-stained carved wooden hutch, Pair of blue floral upholstered doll armchairs, Green floral upholstered daybed/sofa frame, Plastic mid-century kitchen stove and sink appliances, Assorted wooden chairs, tables, and bed frames</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>$20-$65</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEEE3TPZZluA9JfBFtHUsWdQsv_8VF_5jtGB4lmu1s0jrgMKpTp1I_9KIaMiGUJZUjykljRjiC07rNjIzdgBXW_cty5qjag0aEvdGVEiPPR6a57p6I3IdiwBLqd7TOW9O-I__k7
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEKGBgGcakE-8SoTMbMNoMdWVp9PS1sTvV_w319bYZRoh1yLj55QwSn9HfoMV4zh--12u_Pa46oFnjMrvURBy4n2otZ7Zc3UE7jmHjgV1XRbSyVdn7Em6IRm14VzW1l6n2ga2HoNlV55isQQ1YrrU1ry4IMj1oOc55_
@@ -1198,56 +1267,56 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>BT-081</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Vintage Roi-Tan cigar counter display box filled with an assortment of mid-20th century advertising matchbooks and wooden safety matchboxes.: Roi-Tan cigar cardboard POP display box, The Vulcan safety match box (Tidaholm Sweden), Green Glo matchbox, Assorted vintage local/commercial advertising matchbooks</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>$20-$59</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQ7fQxA3DH5q3b8KH7zH8SDv73dNMBPHnz18mJkhmkgHzUEygBnxssiLxLd9kqXDsaPevMFujh_9NVejIMUWAIryN13_sWbjaJsDm8m6K6ETDfcxp5bM7l9F_YwD9veBZD3CrKsmng
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEir0BxdljUafRI12Mul0nVcgQeFhLJKtG5rz9h9sHwbz8mLnR-1EoVivIZ9aR9CLsO8_AGtnrwe4tFnszaCYrCR0iB5sS4tODp-vkRkMvn9xmOAY4LWZZiREHm_TKOQO09uvHJeM-glA==
@@ -1269,56 +1338,56 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>BT-082</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Group of vintage miniature green plastic Coca-Cola bottles with yellow plastic bottle crates: Miniature green plastic Coca-Cola bottles, Yellow plastic miniature bottle crates</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>$15-$25</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFAqvK76KVOK7xYyLgNc--z2U6zgxp3ncZhBBHDsbcDGsCLQGvYo4DlpuMLem_OndjyB6eHbj9vWPgacolb0J6wc8rJyX83j5NooLi6dWx08Yq9dlkkcVEwXJrAYMAjAwHTmQ67tpFImv-IN2h40XtqoITutHHn1cfrwdUf8gLehKDt3UnwZSpOJEH-EiI8nJ0y0kiH
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFHVhEa9QNYWyAInGIKpQ9rR12ZA_lYIcNlPfbFG_G1O0yXts9_zY6Xqr1FrR1ILMy4bROj6lx6FZGq_oVY85Up7yVLuv2TrJQf2gR7bJ99MZqzm2QE5QnDKM-_ROE4pV_2J6hrt7j9aA==
@@ -1337,56 +1406,56 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>BT-143</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Vintage toy lot in red plastic crate featuring a Fisher-Price pull-toy train engine, J.L. Hanson Co. wooden 'Sketch 'n' Scribble' chalkboard, and a cowboy doll with 'Ride 'em Cowboy' felt hat, c. 1950s-1970s.: Fisher-Price vintage pull-toy train engine, J.L. Hanson Co. 'Sketch 'n' Scribble' wooden framed chalkboard, Vintage cowboy doll with red felt 'Ride 'em Cowboy' hat</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>$25-$55</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE-8JJJ2j3nEpbNbp_b4jX-hkxzFt9tMYfZ5k2JJXGX61PcXXLB3eEPwokzq0IvzsklDMiJcXXj11JQwmVoxNe68mBK-2OxAl9YdDpT83DX7NGp1bDEd3LVqj0T0-cmwoRX0AiOk4J9anqstDr9p2gwneW7xwZq6SCQyfoQmDO1IA==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2uzokYqpI3TM4X9OmZ_26-ytIQgX17Y5w_0xqXLOX9UJebKxc6_B2o-etik1DCLVW_nS5mz2xOWG5nEXify4EMhXQU8y0NvvC_M1s7BbXQzj3Jf0GPWJpbv9bI4HRP0AasTiUh0LXHBbNcNCYZedNA7cdiNaaQu__LhhMqJToXgk2gw==
@@ -1403,56 +1472,56 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>BT-159</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Building block playset lot, featuring a Mega Bloks table soccer/foosball arena and partially visible Lego box sets: Mega Bloks soccer/foosball arena set with player figures and rod assemblies, Lego Indiana Jones set box (partially visible underneath)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>$12-$54</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE8uln9YKejJaxvUi6h3kg4xNA5W_6_pE7CzHHVaDuDhjZtsYQpppPA8WwevPXapJY5xldN6is1Sh41RM-rfvJUk4JEfbjRls3ZEnRziSduvp9lDLuyJOi9ftwX_y0bMlj_XNoLg8WeWoihVTazt9S8YIbe7dIZ
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE9WcaQjKpAxspVEHnF94X-DeG0OvU6IIKvBZ9Y2-d2aNQrGDUXBVRGrr8RjL2zefMslMdIz7R5BXbHzI_ovroC56GD8ffUySlmRC3qRJdD50b3_5Fzrvq3WEbNKRKm-UKWJ0XnK3QnWar6
@@ -1474,56 +1543,56 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>BT-179</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Tray lot of assorted vintage and modern costume jewelry, including gold-tone chains, beaded necklaces, faux pearls, pendants, brooches, and bracelets: Gold-tone chain and rope necklaces, Large gold-tone rhinestone cross pendant necklace, Rhinestone star pendant necklace, Gold-tone medallion pendant necklace, Faux pearl and beaded multi-strand necklaces, Red bead necklace with fluted gold-tone accents, Gold-tone link bracelets and circular pearl brooches, Blue cabochon pendant necklace</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>$10-$79</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE_Ulv4oMLym7jeotfyCixFRY56gVdRlvw5ujlWphZzUmup4p5lWV68tiQXQ2ZH1-6LFTMXq_ND_Ygz_FjVyBBcW6QiKZw2Nu7J3B4CkTfe7dWzg_rceaMhWAkD8u6zzDWqzoGwkgwKVNnd6RRq
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbq0c6WYx0Rh5NXJu00RzAcRjhMlPdT0DTE7soAFZ964MlSLcJjSiQFxFLPeW-ysmnFSHU_vJRP_yA_xdGHWIGyCQXpj6EBPBBZRq7G3h0m8CyR_tFaO-8GI18Hsyvrc0oKpCafAjnqJ6-ugfTvEYtn-lch423HURVNPNcm1kLs3nkFPA9zx_AXQlretN7JbxQypIJi_M=
@@ -1546,56 +1615,56 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>BT-187</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Group of vintage Chicago sports felt pennants, including Chicago Cubs 1988 Wrigley Field 'Let There Be Lights' first night game pennant and Chicago Bears Fan Club mini pennant</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>$20-$55</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE1RTZOuT58zLgHvS5ZyTujcV2TyWp31qNcVgU5c4XkBT1LAjN-TklV8yRzB7W4e19o7JiXH6IGkb1ST7AqEVUV1Pf8peGUHYvXEdcoWuAtSHvjl26F4ZYLE_Ry3DDsBWxDj5yqRIGe0oVsz6sX8law9jVINCQ4SnZYIz4=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEg4zJkeyQ3ljA6QYdYc16qNQZRBPnoLneXYIyLmQgJiXlW2q6qlGlIo9w6nkB6yeLG5pENnNdakTrusOV8ahs68rUXPokt04xrNihyohRAAXsCGJaZIlCAc0SuLHf5QlFXxj0Ez9cLvsrVk2RwA5vmIXIvzb9K5DHnrcG2K_WjLnZi28TABqCjAVnDnEmLZmvX3C0SPTOJ28SoLkqe9j5y1TYwrg==
@@ -1616,56 +1685,56 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>BT-247</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>breweriana</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Vintage Schlitz Beer Pop Topper woven straw promotional hat, c. 1960s-1970s</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>$25-$35</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE3U-ruFdHDgnzd9lA-KX__ysrYchY7diIwcQh9nfRafBUEdm40ektvtdsRLqK_LPoWyw9dY_9lWuN1OkeXP3xbV5i9yAf1HaxawI-5ehXNLCnyoHhFJpxsaa5L7A22h_QilAtu7lzoV0_M81scik99fwQBnlXbSzIhnXloQ-ZlyvtjOhHj
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQENmk8VAhUiz1wcUbN_ZAf3r9MmJl1tbg_HxmSUuCL1iPT1yU1s3LcS_164XlDCNsgo6ATL2BS6X6hOvm1-dB821htLYS5lCE6QnzwYyaAeunkV7F4g0zZzqzDcOFpvry_mXcxecl9W7dPN4w==
@@ -1685,56 +1754,56 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>BT-256</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Collector Barbie doll, 'Barbie as Scarlett O'Hara' (Twelve Oaks Barbecue Dress), Mattel Hollywood Legends Collection, c. 1994</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>$20-$60</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE02YPeiCUYFHBByWvNu3e-bMn51ZPX3AkgUywFp3IESfbjLD9eRXxGgc1VqjLIt-z9AJt7-z3YE5lR8Wl_YofRAKA0hsSQNzX-yNjSptZpJZJHn6HNLBYtVNrZTM9o67o_f3oNGSyJFU_mVEtbSDmgmCJZ7asScJzr75yS-vTzJVoDyEuz3iPrNrl8rxmqjisX8ahB98PsndO21hQPk-6DsR2AI4gQ0xsPTgchNLP3Lw==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEFbap0X-mdY_kyI1MdH1xSL-U6MfIS6XgjCHgqoVDcRuKI7RhsH53XRtzHWlM0c0KNj5CKNT3Qj9NAbOmp0bqs0i3nqbChN6dCVITCZ6sXcKuhh8Q1T17IU4qw6T1gH5pOejPxGspGO6zz6ETaRYZx25AefqpdwfNcP_yu8yDdu58DtJGXDDsvhtmUVhLPsIyuFcDriVdenMSsWf5pbuEAEqgxdse7hjBngkOMpYwGf_gNI1ip0DWkfkjnwluRAySd-9dbquY5iMSS
@@ -1752,56 +1821,56 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>BT-274</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>breweriana</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Group of Budweiser lithographed promotional tin cans featuring baseball graphics and embossed plastic lids, late 20th century.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>$12-$35</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEE_bX-ueRRvJt9bI4CIN6HoinytQ3Is6j04fCTdbksoAgchI8kgavX0G9_kI-XwDDz7096wpBZ9SQ98ECM5F-ouRbJN1q4RVXe3dLAvJ1lR6Cw3M6kNLsgmwxg0XEGfWb9OuIGqA==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEPTKigmCriWItB1pzKP9PiIB6k8jIZN3hJBbgY2mPCofhrdeh55VGa7N8UaEOWh5YeZj0GMfPiFDIIIytkYSgq3RqvZu0bkONs3F_lH2OdBPPgdi7BhsnaejdG4z2OOntuOl4F_-wLfg==
@@ -1817,56 +1886,56 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>BT-337</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Lot of six vintage tobacco advertising pocket lighters including Camel, Winston, Salem, and a brushed chrome flip-top lighter in box packaging, c. 1950s-1970s.: Two Camel Cigarettes advertising lighters in original cardboard boxes, Two Winston Filter Tipped Cigarettes advertising lighters, One Salem Menthol Fresh Cigarettes advertising lighter, One brushed chrome Zippo-style flip-top lighter in box case lighter in box</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>$12-$50</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfL8jI4m9zr72KeMiOdx5FPWEUzn09S0KAwwy3DmDWWSbNN5s4NmHlQ6hDH9kCFSXH0WG-U8Hi8ffLrtsmpr08EpPOGW6I0U0APFSWErPrAMOxJN5ZdHaoxZ3MdiOy6fg-WA_FXduLJ6ggA69Lp6O-PUXRUTNb8iFQoX2oWBFCdUPMSIT7-gSmZyJJJaUv3ydnuQxdeZwcCK28yMGc-dlB_55aIw==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfm3QPawlhrNRiFV1_bDCFJvVOe7eUcjFSEn1cRW7hJlCTKmvwyqbc6XrmsUIRFbBaPi-bXcobaiwiqEAR9WPlkulYhibJ2DOubAet8GSGigQ_tcXkVYViWjgKjIXOq4s=
@@ -1885,56 +1954,56 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>BT-362</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>1991 Topps Traded Baseball Cards factory-sealed set (132 cards), featuring Team USA, rookies, and traded players</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>$10-$36</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE0k_QwJiNrVYS-Ssj-Zr3N2c1dd1QScDh30zvAzQxGY5fPoe3AuaHfNQ3bY-TRLLbJkKb01JbjvkzppMmCn8ogp9zZ94tsCf4upBcTP3jkHj7XfPxm_JbAbl-fClrpMMlNwCXfwdaXe-zX2ngEOK5NLYe_q-m9eI81nGdjG0QlLiHFQkSQVCeVuE16ffpYrbW86TlnPMKdtkdLcQ==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQED_lCXktNcEG9Eq_mYdJoYy50WDRTlTb-X31qNjA23S4OB8F4RByTfuVwMKGdUceI_PIENnm7adDjvqldUn9uoYlNcPVFhrgJvO4atQO1kEVu2XVqWtPEMkkR6jTL45Zz-kfpMdfcIwwn8Wfv7Sybk3ORRlZjsabj7Mg==
@@ -1953,56 +2022,56 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>BT-373</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Box lot of sports trading cards and collectibles, including 1992 Upper Deck All-Star FanFest set, Baseball's All-Time Greats set featuring Babe Ruth, PGA Tour Pro Set, laser-etched glass Joe Mauer card in case, Rockford IceHogs set, and various top-loaded and loose cards.: 1992 Upper Deck All-Star FanFest boxed set, Baseball's All-Time Greats set in green plastic case (Babe Ruth showing), PGA Tour Pro Set card pack/box, Laser-etched crystal card of Joe Mauer in black velvet display case, Rockford IceHogs 2019-2020 card pack, Stack of top-loaded individual sports cards (including Mickey Mantle), Loose and boxed trading cards</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>$20-$55</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE2hwRsPIW73ndeZPXwVRzs_a8CUYN9dsw15leIX5rqKhbAxO35mVpwlymNM-xuEgR5URsuPYqW2p4US1pmW4KAS4yLMkseWpR8FA-3baMflK4zwlQ1Jn6PyeYB8cM7qrWyj1ARkqp9T2UQD88-ZQGocAkrQKMTxH842pVI3cqgW1J8sa_PVhzE3ek4sVXyfae6BY0vOcvQXRDtYA9HyXuU9fiLFDDVtzXsRZ6XpAfD0Dm85RLdolw2lygWhKfjE3o0z6Dn-fVuFAcdfeV4UQkTUtoPIIeTR6IF_mMDjM926ebNWQPcqkywkjM9K3ULG9S9jeQ8ForZpDBSm5Ac3QpiZ5PnNRkIM9r5r0kO9XMMHsxkoKSJxtrVmcWFZ2sBhcuBIwkhXrY4PnSz4lMt51YrIKXJ6uFyqLk7w8XfD2B7TydoFCZvkfSinfihfv8nu7nCDLbF8-A7UGK8fr0Y8jYW8HboDwTI5XDZ3VOEwt_SeES5v_E4X56s1UUBNgUv8Y9vdLBJGVUCqRgLCiITGgSX6VzS0BmBSio4D2Mnhj_WgGiy7U_hPOWf-RAT2jMZf9ooOz3P_0mnmh_r2lSDdAC29nRi-hENFM8vQiIK6CHQ2XDLjdHmHR7yMEJm-N9v1ZeuWfAaemhmBdB7
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE9YAICMTKrNT239glHVctESTbybUPuqHeQ3LxsPnvPYCdXiwUxKHtFdQyydzMOQBsBbhq-asBhrK4iFUVpzvY2CowA5MVvqE1pWkz9nEt_Sh32xBmEVlCi-DlhY8uCpKq78HFwif52xSVfIKhbVSEAA9kEg6VCx77CYBkUd6zqMzi5VWa8Twji64YBE__uiNdkEW3_da9h
@@ -2038,56 +2107,56 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>BT-384</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Assorted vintage advertising pinback buttons, commemorative medals (including 1962 Rock Island Arsenal Centennial), enameled lapel pins, tokens, and a pocket watch inside an El Producto cigar box, mid-20th century.: 1962 Rock Island Arsenal Centennial medal in 2x2 holder, Vintage pocket watch with aged dial, Advertising pinback buttons (Gold Miller, Safety First, Oakland), Enameled lapel pins and ribbon badges, Local Illinois tokens and tags</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>$15-$65</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEHiSB3t7gsB9ezvS2cJqlB1Y2wY5SLNk0ujudJWjB7auP49Jx5ktw1Eg-GfjCq3Z5oi4Wz9vX37vgZuEtZS4GoCGkmuQ4XuSeDsoBdAvtSwODMQl4xBHV--sRTOGhUVd71ZJbwQs-NHwiorp4Y0y_KEV6UyexGsahp1bfN8UfHVzoGFJaq
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfUr1QTkSzTCrtcyXVD-cqhyCTwmNpBUL0iPnkZok8KIhh-s5bcMaMH34rIZJkP9HuvSZxdOwqMn-X0_GtUaEioaOT1hHaD3io4CnkyJtP2Np6yj8iCpOge6Xv2fglH2dOHz8P2nYjvfoa81oljivHtQk9t0tjfUxt
@@ -2105,56 +2174,56 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>BT-388</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Cast iron oval relief plaque depicting a striding male figure in top hat and coat, likely an advertising sign or promotional plaque (possibly Johnnie Walker or similar motif), mid-20th century</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>$25-$95</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE32pYrj_NR-mwFZb3apWi_2drpQiGC0ZD5_ZMK4pzCSLvyBg7KjX993z_tT0E473axrR2rV4JT--RU9DuhfxW0NN_ahkKyNaCpbI-5BrWerjGt2QZTCabDrFnuYgoWMcjtOEb3hc3wFrkWc4ciktbVw4i5_o50xW3ZdBm1S5ev-7AKgPQLi9JRECD-FuiiP7Rd-j6gFTj60gcUoRCDzJ5hTXJVzOEfI0q_GuGdVOT3ldhveRw=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEEqMCvsB6CAMGedsCMU3OpDWIqLRr-NpAEMlpRs0x291ZugCotzROncqtxhmiyorVBq4ckSRx8n6SUPPEL_vBOXI9FcBC2qQ5rXdc4DXyxTFA6Uq_keZwLgSY9L3qQjVSSVQUzyiV0f1vQVpFb
@@ -2171,56 +2240,56 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>BT-394</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Vintage novelty toy and ephemera box lot including packaged balsa wood plane kit, red plastic rocket/bomb toy, plastic figures, and vintage crayon box: Packaged balsa wood toy kit, Translucent red plastic bomb/rocket toy, Pink molded plastic novelty figure, Molded white plastic figures, Vintage box of wax crayons, Assorted small novelty items and paper novelties</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>$15-$45</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEWSUA0oyTsunRwSsVhROdMbk8BfmLfJDh3L7dGT1IEgfKow_-3R6b1IGVzmMJKxzdW86wYfQ_D3quZHv33XwpFNlnM_zsy5EeHrwI3xfNC9z4tTgbeBrIhS-meP8x08XdtvHMhdqwtYg==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEq8O6WRr95ssdi2hzaeWI5PISHHUHFM8F9lDMftXAP-btIIqiSJYD1wn7lZdZdzJWiCuS5tDBshxYgY-7muagul6ao3cWmC4jbbwa3BLwEgdmLDnwQ905pl4IY-gD5rOulTvx4amr2Owp_k5AqrSXaa0Nl5Adum40vOlKiOjnxknULEw==
@@ -2238,56 +2307,56 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>BT-398</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>advertising</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Box lot of mid-20th century paper ephemera including 1950s Profitable Hobbies magazines, Sylvania Electric promotional game booklet, United States Athletic Company baseball scorebook, and vintage greeting cards.: United States Athletic Company Official Baseball Score Book, Sylvania Electric 'Beat the Clock' Party Game booklet, Profitable Hobbies magazines (1950), Vintage die-cut and novelty greeting cards</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>$15-$50</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbJy2cWVo4yreNbuKGa_52zCExpKBpanK1SPUNstLA8hPwTlyRWM3lm_cYULhFwsY1IcQA5IiRXtjUnl-yeBT7Eee_wE1BSgWw75XVns7Bo2erjI5f1lf5ivdU_3U6x7y5h89Fzt4qwioNEM3lVnlZWisRZdJsstaE2NbM-whjeQ==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEoR94dqQ8ZLxBw0K2YTjqBiHApkEt9OGC9gyDlPy-6OPOSfUtyaRErOLFcqViuTgn4fWJfw8cxGHprRNILiF8h5mdZZcKBi5t8k4-9tK2PBmxC0L30e3q-WuwVBqg1YAvheHeM518ALkKuZo48BzTNLtI7X3NmEAtEiVA=
@@ -2307,56 +2376,56 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>BT-404</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Flat box of vintage sports memorabilia, ephemera, and trading cards, including a Rod Carew Popsicle cutout, Minnesota North Stars patch, and Miller High Life Braves booklet, c. 1970s-1990s.: Rod Carew Popsicle collection glove cutout, Minnesota North Stars patch, Miller High Life Root 'Em Braves booklet, Wilson Super Bowl booklet, Champion Spark Plugs emblem patch, Sleeved sports trading cards</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>$25-$65</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEHcNBOra7GbtVRc1bT8iE2oZnIXKTcBkL1Klnz9IKDJ1W7bCXOjYrCoVRDr9763UuYairHQQTuaeVKE9dpu6-sM3UwrNpPSUGTOwBZxQfWqGExE2lXL2XcHcSwf9Bu4A==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEVs5ONHlXtq649RyI0EQuDSmZtfZrKHisxPKy_d36cAit_L90ArxrWXhgXAv55GJl19XXRrH59m6HCEGCRoAu0qTy_Q818cDCRDtSN4n-dG3_iUHW3s4Mty7CA5XUbvZojo3YRKL2LIuWLhASzj2lN3zbSoBHyBR4ifUXOuioAayZ8TCB9hSkT9e15t_1XsjqfpwEU_9cZ4LN7x3QZkg==
@@ -2377,56 +2446,56 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>BT-441</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Barbie doll in winter ensemble (patterned coat with black faux fur trim, red pants, black boots, hat) accompanied by Hallmark Barbie ephemera and a 2001 Hallmark Keepsake Ornaments Dream Book, c. 1990s-2001: Barbie fashion doll in winter outfit, Hallmark Keepsake Ornaments 2001 Dream Book, Hallmark Barbie printed ephemera</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>$15-$35</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEZHc-Z59HuEH9ea273BYgPy0cG8-gvWo0AqXUrkaYFD_rysN-GwUmeWyoq-Q4hyzk1s9fJqYpgdUFbZrsTs_OIn6hGs4xFqSiXzRFTKmxFVr7COqGP-Gqz7Lys8pfn-82PJ7Ee6vMMSw==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEbHQetiGlAVvR6rdK4tz21eXqMv-rAVmPdUJlYf47P-_LDx-_yLVT4HaTC8s8gunORzZhyu6PTIHNPNJ1-3cHZI8IXQASwhtUu039xI3XoYhQQDBFcYbsU-rhrjYDyGbxjjkFslLLjfn21OML4fdUKPpMq-delWw==
@@ -2446,56 +2515,56 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>BT-447</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>cameras</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Argus C3 'The Brick' 35mm rangefinder camera in brown leather ever-ready case, c. 1940s-1950s</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>$10-$100</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEDHuBp8WvgfiEB3dXm7lpvRxoR0kCUp4PLf8sbPWZkEE7ZJawHV5HkjCCX1rdzHkmHSfXQXi0rgUb9jckTwzxjrrv2TW-qu41hqFo-mysF7VUamLdqtYFSzYMplCJjSsFCMqYrSCGtA7RuM1E6TLnJ1f4qsOWPAAPWDElPlR0Ohz2WGJ4L9iz82a7OuGooDOlfu2bmk21DUrDRS5NhGkiHqgXPkmBx0JLxl4lIBfNp8O0=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEMQmzjLSUoPwjWN48k41MEfmxxwqCjG1qCwHu6bQL-ZouTjJeqzBkRVUOP9Jml1RjvjCX7jkQM3SGgVHfZ_xyzJ6cr2Qo01XlZd0d0AW1nTTVWdq3FZOXko7Yu-dQd3iGSdbYZ8G6OSROBmpnyb_QE_1Oznzg49VF6RAIzbiuVwGRLlJ5fbF0jETqtZy2uBXWSgSc4OQQZ
@@ -2516,56 +2585,56 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>BT-450</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Assorted mid-20th-century boxed games, plastic building bricks, dominoes, and miniature iron in cardboard tray: Flinch card game in original worn box, Canasta card game set in green box, Boxed vintage black domino set, Bagged plastic building bricks (Lego/Elgo style), Bagged plastic dominoes with colored dots, Miniature green enamel/painted iron with fabric-wrapped cord</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>$15-$40</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE8QdVPqFtvboZOaSHwHmV_6FuJyV57MxDrCqPQT4kZUDToc8Zt2XGYWp0qJwzfStq1PQepCSslDMHldmREXActGckTlplfUnyNMLrAejVBVWhlgyPvzGK7CrRNG12097G9gL4w70jAeWnZDBBCdlSdHQw-CWiQCbqSGD7PVkNi3fY=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEG9HM_kgIp8BHmQEirZ1zzgC_S5jcwuoRIseT6ENvi619rbkswVxxk-A4BoN5FZccbjU4cmVAX7RS--QJM44EuY-2t2IX71ggj9SwhTV7IRWRVK0VHiVhiAkVrD4DQkhiqCmWxfb0ySFXWxOLGw-tBuWoEBlu5p1sQuGgeYaTapd7pQ4s=
@@ -2593,56 +2662,56 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>BT-457</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>cameras</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Group of vintage cameras in a leather outfit bag, including a Kodak instant camera with built-in electronic flash and a 35mm SLR camera body missing its lens, c. late 1970s-1980s.: Kodak instant camera with electronic flash, 35mm SLR camera body (lacks lens), Brown leather outfit case</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>$24-$65</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQETp2F_ZpjgOCKL0L56uLJ2ELWOjYJQhiiEpd7Jl0w4YtD6SmzH6c5SQktVyzaL9GjYU9JbfzQPAKeaa7Vqw8sNvXqWCFoD-UYoyUA8xveMIG9xIKUHXkXEoPgfNA2oAjs19VpjxtVdnGefV2_-X-w6lURs1KQ3bbfRSekuYXY7CeeJ4tYDHF6LJGg=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEZt7GjCHZzucFbLlYBWgEbn74BY6_DNuM1pwV_nANxEkp_LPG5MUC2_znPbS6m-YnOnPX9AOgLfg7yLHhxqpd2VCrjfW9h6ell0kE1Oz1Gzj4n_8Ew0tXa
@@ -2665,56 +2734,56 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>BT-113</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Tray lot of vintage Topps sports trading cards in protective holders, including 1968 Topps Willie McCovey, 1970 Topps Rod Carew All-Star, 1970 Topps Johnny Bench All-Star, and others, c. 1968-1980s.: 1968 Topps Willie McCovey #240, 1970 Topps Rod Carew All-Star #453, 1970 Topps Johnny Bench All-Star #464, Wayne Gretzky card in holder, Dan Marino card in holder, Assorted top-loaded vintage baseball and sports cards</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>$35-$125</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
         <v>10</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G36" t="n">
         <v>11.5</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>11.5</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE-eI8keyaFQIzRn9egCffr7zQcgCf8Mzno8V3ongZQfoG7GRPK2aA92s0mXam8cYRbzmJLRnkmNeGkIvQfTfBnWc-BeOzt3v8NztzpjMDa3KPygeaVUdgK94DpKZnTGyG5pFVfbGyQ8TVN2XDWw_EFxeVBBIiY70lcmXovvqAzj47LXnChNBi0I9R25r8AxL9G2OMLuLkZSLhxEIBWbIttAxutKw==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE3O3_RajRT06R70x3mFLNC4fzI1J2B7qUM-jeK4ppqCwzj4Z31k3S1IXmb92K8rx9q1pFYEg2BnKTJKiDVUMTMfmZ-e8AHBwQIDjq16Mbm45ghq0P_w1EpwzeuSoZCoH2tb5D-1PNQNHQDoifLIrhdnd7CCUNsXdOQ-x5jBmbFK_sZmIyOyST0sTt8
@@ -2743,91 +2812,6 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BT-165</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>vintage toys</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Collection of modern pop culture, sports, and advertising bobbleheads including Walking Dead Daryl Dixon, Star Wars Stormtrooper Wacky Wobbler, Beetlejuice, Miller Lite, and sports mascots, c. 2000s–2020s.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>$20-$100</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>10</v>
-      </c>
-      <c r="G36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>grounded_search</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQECEYGqu7ZEBsrkti-j8niEzqS1gDBdyvX7FrpDT6LxgoqayEDJ4VZheiXb0fjtvhwPFuQCBMcm3sB64DO4o_QNBJudi7pFLRsDAXpayhHQVgDBezrDN-OahQFhQGKRMnXQrELuzvR1UEdETicEHZftnTeUogJM51L2Ca3YEd9HNWbgXRBqB7S_wqcnSRhFhcCWl0BK_jLdfSFyNnVVTGrW3JcpuYcLeOgC9TykVYumkuxvCOTJQvhC2Bi1fCUI_mCWbzALqawnHbxwoogcSO1V8FNyAM_OREEr
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQELtbjgCXMivwy50zDR0SVUt0aCHp4t3ekVgt8Plk-aeCXAnJj7GXvaFCGLH4qHYNPZxAhAFgLwyjyQI7RZIg2lyd1LTLsiUkm49MmB7fR_vIJBAfsOUX6iP4nGStVW481CORG2-kD488Ci599_-l6QYxVlwpubCN9mV-Q_a1QTEybEGicudNxbRPkstu3v6ON0Ri5Gu15efQDbdDHEllEFB45j
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQNc46CNb81tdmYjzXtBM09ntNgu9qBiUDrxLoJqpIt0q1ZAi7ajU2MfMxnUy3VZzoiYXDBZzMNlrACiGZhlwySLfUDW1kSRyjD6gDeJUyEd9EZhRE9lAW3QMFFlB9EETMWIOrufxQD2p3xwIrYVIbtLg70w==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEgtsFYtyqaHy8WpxwDksOgnHF3rZ0pbqSqmEEokP5Ae-2bTaCNPcQix4tpG95ggDVFQGzDAjuR78fvFi-U4eClOaAVJqdax2FgtsWA7LWvA4nekU7k3kNMpYnHRCgcnpaEr_HqallVQ8ST-ligiITYzEhv9GSW1e0og7ixkH6B74ofT1eElIigXbUlySDQNnJbBOv2wk7-9NszFipeQsQ=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQErcrWUqJh1i1ZwMgz2hlBVrXFfuaKnUayDx5LccyqMjVcUhk-Apzy0uoIlY2vYH58LkPg_4xFKzspgycFywE6fCkMc2XJWeVr7DUd4mzYNFNq8yZhwUXcd_7PITIlTGH2SErlW7AXjJVBwaFR8z-PlxMI8VI2QVSE3YKtztKeAeJKow9T56uIV91q28YkIIdYGiJ3W7DV93By5tzcMnedRAONP
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF6oWBqrVb1RT7Rp8E_puLqeZqEZB99smbGN2xx4Kf0qWLaJVde9IYZQYXjBjzXhv5aMjJQWGnc7xErhe72B_j3EKD456NIOG1PSwUdWA5ObGZ7jg96Navn3wHKpkV93Jd1-2X26RX9
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8hcnpFEqh661sxpVlnPPxs5oEbgBszLH89wUjJqPB4Vaur09qizNE4LpzgiPTK3vkSA8wxIW5VhQMu6xlYUE3NH-uv678lCCdJO53smxWzXzxYchJaz11bVzzUsfYqxapKyq-l42Ac9iG-Wezv_spgXDaxcq_2mbkFwgeuBW6vcbpDQ==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF8qVBDqvQfu2KBOINlzk1r3hlceJA8xGok0xHUulMsrIHZ7D70V5CjUyYw6XVItPtBwuqthq5Kd4_Xy_PrnpEAU6wkFa7vXwbmHwXjKiH7LMwwRinohvR18xxj_URoyya0xDyyhhI_sZrurItReHSnzN2RRmjkR6I5K73rHVp3w-GJH_bj_w==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFCkQGFQF_xEJaNSWG6bjrrNYbiyYoLSuaaJE8Cp6sbriFK5UsVyKKJUis0bdJ1P_WeDwY0JXfCkS2bDkSs2nRsZOWB7zQcAhWjZYlIOwM6ARybuSaOuWU47yaJMsjMJwvsG-t2rpj9fmJ9N-qPRCTtNHNGjsKC
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFaQFMNoSVmNrwgw9WAbpxYziKSv6WLr4UXqMlC3YtImlOGSjC_VyKSjMJvskstyCewaAxuq4GJ4ANsZTH_RGl1BQuZJ5rYZq5aOjmIhORC64oMthcQVASjQmYPU6js1Q00
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG5bTQvTuUkaFMfLguUr_t5RcoK-kc8GaLWq2ai9PJIer-Di8FlADU9oYGIUGp-TWAWH5ezQBIb0B1i-tV-xAkTJwfN1SEXVpDOhGIrKooSd1V4VYMdDqicpvxuTnoWajoJ_9UYqt69yZyflLaA1QIRBcM7XWJFC4oTAcQr0Pm27WlvD74ln7Pde8x8FlqSStiKU6WDTodcIHoSAdRduh2oZGiSIvapNS_wDXdkIPX8JnSD2oKQVwbdKBE8S58DJMZZrS5g-NpW45mLzymTK362w7rwTPXKSYhrEuo=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG9Tc26O1LDiCKWCZz2D6SiuFm2sMggIJ50rQ390QrVoym1Gxhu3VAQyjFkB8-p0ncPyc3wjCO-P3_UiJQCS3cRK2jWDoZ3xy3ktPOENqrPzMFR3X4WQ08A-oU9U00ASfRuTP5ZO3PlumXXHwLuD3msWfVOEsQUC_i4FG9DmF7f2lsfwYcrb05GMwURw2GO3IQ5x8CqKvAzuRCBC6C4cGA_SvuW7g==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGFEMdHwgY8KphvRD5fkj5DFWIdXuD0_pF0ozY8qjebFbJ6TDzQhauk-imr0cRVmgfvBvcv6n_QaD1cjq6Jww25hTcH4NEB4ciDULCBYgU5u07pBy8M7ROdJo5tRTeVrGvy1DhPoUQs7uPvkNqYYdfCvccr6nBYz7jZ
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGGWK0_pr_5hUpsqKHQS1bQwDssaDTOx4WtdQBpr9T8ascqqj2tJLpwgxqERn_DXZx_4O9ozilGmTtbJiH1TqwILmcjP3zP5_UQn1IY4uWh4lrYrL1jsEpI24f7VdPHkU0=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGQKL-HYF4jP57NnTxrqFV5VS4Afn2o_PBaPKoilwQg1UNIQjVpOIbCCs2YE4SHBpfa8ea1gXSEeus94ytv0Tz2DsHed8iHtZn6GZOfLE3ltH5n49f8BI6uWcU9zAl4JsK1w3bvB709HCejSxUu1esAg0E-comwgvrj4rYIcwBOhA==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGScdCS_C6sy1Tk3qgR61lVo2pR7Vgul3T7r2f_CMw9Ll0vH_SAYFcTbsmeo8WhiAH6rZbliTvUZI7c0I1-v5-RLf_RvNszIhMD--0NGXCgETdMCm26KO-4jc_CNEzVUN3fxa2kNLH_UtW1j29EsSLaqNJi03_bTh3F
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGZ8QPllu9Eeqh_Ir0mM9x2uvZPRKXA2a8yqpvlSDfiTwTcaB1sWqQkePze4VETVD9bBl6gULWiZavCsSCRdenAzY1-abTNo5zlLiEf82UKoQcFPsN-ZqeV98nYJoNfO7uDHu3sSZ5s
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGaQovEoOnzvTSteaIh47MX4kRHUnsQnorwVj9lStdG-qCNf2ODjaxqJ9q8hYgPAQRvpBiFE9saep4Ci-1QHoopY9Kqe62bmcJqNUH4aHXJSZZ3GhrWX3Xj6tr8CMry0LgAIZPQrpTaTvq2EMI0CDdSVgE-XR5wEeSlKQMOb69F-20=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGbZ5o3cmvRHmjrP6g85pEJ9iePhGe2-ztKhKFGPmBcogl8Y-DNnAvOpdf7KzDD6avlY8ZnPaqNyE3mc3pJYsqsVZ3g-5wVITqMKe8UdVeymKrpTbtc2nX7mgDYNPRZdZXERy68bDhvJueAiVXWjaJqjayjuZtsektO
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGc3c4DdBUuNu5BV_S04yC3lmCEi15HD33N4u9DFdSvhRJR6cL0UpkOyY25TrY5YBW3olhp5mITpEAgJWBqgbt0JxPQxMKJ-9a9pNJV1cw_zR7jr08RScmEJ_CZjFWGAr425lL9L7oT7nJJQw-h1fd9W8rNSnXyHT3WPUg5Cujjzb4h_9TVa2AGJ8y4N1SCBYBUjdi_
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGkLwopwDetTQrsegifWh9UuV_yswZWwA3k08-dix9ihwtwEYvSs0sv9FDcGTxufBMS5OiJos7IqmV_D7_WutK5SPmipi05T4F0pIYFjKrVvztptH80tjD-1t-PAsvwHQO9yTNi7oZmRm8Wmh-eZ5opX5_UefsRX-P0
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGn27gmMamH2FZaRjtEGLPF_M5yQbncsukAS4PfFc4ntLSpb1PVb1xwkMJBNbKeHPK0GNgpJHfznEnLG-VlWZ8za2wFFDZBgH2LPhlhyqUYvLI1ULYZWcc8GvZvpRL6Sje_8HF2rnwtEW6DRdYs7Hm18lNIaeQe2vT3zZ_IZpDs7MwpLTWG-XmTzCrrcM81sjTpNA==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGxzsoA4F7gX6qkGcuZI_EplzseqgzPYEe3s7HyTJsfkC1K--MLZ5Ackis3zyLk8Gky1KW5bJbba9TEtR1rYFOI1EHhkroCoaQUPcUAkeVeI_-OpyyABHai4mGW-BToM4EuaSL7FnAqGHuAv-tA5g75P43LgM5MXOgqZnKqlBIri-kN9MC7xbXd_86NUiz5cRRACG3URu9KZEPVtn94-MQ=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH5CSXklT_EA3iI2NLCxQoHQsB77NAy-UnRj5_uhzeDmQChVRcSXKwbv9SaX4BWcVQgShNbCDH-ZGUgHVF9_UCTd8_a-A03Q13sMlLLggP15eInFz7bV7mAM_ZtQArFiGwYM0xzOg0SsKNpN68jRFr6yzpgGVM=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHJT-Yh-f8K6jinJtNq0CwMPWimgqb8W0yczGkNN21HNttK7FSUTbwN1MbNRTVLpxgbR1bnsddvtkouaFveMqfgCl4hUulmFcLYPmvYfXvGqXueS7GFWGL6Y5Nn-rzPCDdJhijnfqPVBnkJisgc2gmvkOcd8jdIvpdaiN67szBVvkv12kRnclkWrFdmE83rSZL4jXFfIvSKyAip0Cc=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHZN2P8-APWVKJ5BhgcJttT055BI6C0Rv5EN3HL0S_-7w5tUCHl6kXuJ4P7yQZXhQtY1T7qy1vgTHqVyXRSarzYO8ppZnrh-CaD3x6mL20OQRwwuz4aqVfAMxBGtHEIgAu75WZAKGIJ5tPft_CvP08pPb3Pq3pyib4aZmshTdbMCJT_SOtc
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHb_FUfWszeuk6TJVDBnTqVx_PrLb6Dp79-mp3cmOy91f56Ia1YrTvtYnJ4xTe46w0fJFZlYyKr3zbe3NoGxnryyuv0kjdRiNfTwe0Z-pzN-WjxRFd1McSZx0CU1f5rEJSP4cPHZvGiyZOcQtgDh8M-Dfu_VnoetY2ueb3PPTTPopVrKwgl7XOnwobc4jN--ij2RhhMfjDHSWLYqzIC6kZnM40iB_kCCQ==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHgHZHSe2KSKZo_cvkIsv9JBI2mqi4q_AozATKtaraFc8sPaqAwcwiQSGq3dYCS0xHI2BbgobKxWa_xpgc70710QkbSIcgnoM8xGWnC_arhDpIOFhQDfn2n9wEmuDHAAbQg1XwvWnv8kpvwX4waMLkLeIkY9PP4nCtX7MbT4-YodQEbkIHrATZD6JxmfQ==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHgeIK7OLpzcKRydh5eZoRWlUAVUlXyUteFo5zwhrFO2yhaxENvB9v6FCSAj3_7EQgXI3RbfCUhzAMif8GhaEyYvLftZJsyRWv88YoGG9FD8fqjjdlRazI8lOX1uEaVeuyIGlGOaxDttk2Ej8XYm1bfm7NmeCoRW1j_PJ10EOFXaY4fpaVW9cyFwaoCDJHgzCYRihx-9cevYsAIvwA=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHhhOiiu8gwkDQ7XrHViGCHIYo857FkItWOoKC7G7VZMZMaODpe4Z77ykixzadeU8RjQFQo6c8Z71KVDlUIYicMp8Hws0c5WHneC1xDV0b9pONH0LfALhyEVT7atWMx0qwtKDHwdy1fPjUF6Xq6xWoCaQV7C2UMSw==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHi_Rd2pzmYsbVpaPfcWY5T3CJkLqbx8Oo_ZrvHIZ569V1EthSM1y5AztjxIpDYzBKH6-gOAAZxSh53nGs4K9hhFeUFd69yuWnsE57UMMI6iflKnEMACSodZ7OCdlZAmoiY-iMCP5UYz8VO8InCTpjU1zytpuRySObggWcQDAjTqJhisw2qkwY=</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -3255,7 +3239,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT-385</t>
+          <t>BT-432</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3265,12 +3249,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vintage Mattel Hot Wheels vinyl carrying case / Gear Box, circa 1968-1970.</t>
+          <t>Assorted vintage Pokémon plastic collectibles and electronics, including Pikachu figures/banks and a pair of Tiger Electronics Pokémon Walkie Talkies (Meowth and Pikachu), c. 1998–2000.: Tiger Electronics Pokémon Walkie Talkies pair (Meowth and Pikachu), Large waving Pikachu molded plastic figure/bank, Large sitting Pikachu molded plastic figure/bank, Small Pokéball toy, Small Pikachu figure</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>$22-$110</t>
+          <t>$35-$75</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3302,75 +3286,6 @@
         </is>
       </c>
       <c r="M43" t="inlineStr">
-        <is>
-          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEBC28GiFuIjBhEqMtdbOAY13KF1hOAW8vYGgE_uP1hgOEzyOJc3WKoVrJaEcXib9a0roHZgK7aJfKh7F27tF8HsTnkPHg-8iOUvBXCs7kXaDjyMS2u3uf02BAzfxXf_G9LKoL6phB6l3onUQ==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQI629CsvNkqVn4MxEDlZQ2xM1qgReHsH-FJv7XyzHoGG7g2BPeoXDG2brHo_j4U4wsPVum_ba0njRsVumcuZSjPOlWgvAOi4PqnA1vfSpCI7raAkLJSd-8-v_gFMqygbuPIfXu9qxgnXiurZOJj0hrio6f0YcqJxLbR1p8CgbYFWowpvvuA==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEUPFPapoZVvTjiWUeifB6sYmqdqW_We3fzOhaQxdp9T8iv3m9p6F9jiORjahUD3YANbmUd2wZ6wQJ4_I6-m44H58spZnW8rJik2wc-WX_ZE0PnkngCXsMl-ueegnEWFWrJHUrZhmaX6jwV6qL1gD0K61F2cS4bSzZqbeAvgye0Qjzgv1ZNGL6-ByLV11OGozYNdKy_e01RseI=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEv4u1O5XEZPPwaG1c2F8qXChlt0MemN-ESSpTFwinzGhKA46yXWpwzGRH-FEbab2Wx7tLFHSaj9DbjRhCO-sIixTsu8aNWjmxd-iQtmp5V7jGtcnmB77dXRzFHoKR93FKIVzK5BiFWnojsvHoeVrwyOcWgQIdrJdWXTYVtj5ql9nZaSdK5HT76i1G78RBI_EOxXWdg3TQT3i50
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFDj8hQ9FM8mtYnejjaRlYVTV5U20tA9-MGF8KL6D6N6I7IYz0gQc6O9EvlgLvN4inEZdvUpCFqknSh_wcj_O0fOp1Raiz0XjlAX5-V6JXFraWi0ZVICd-rzw7kHc6Hv8uxNMin7Et_2ZfRiCO8PXUKbdMwYddcl3jIWiHYVwtl6P2XSAc2VhODco7MSDugdsS51ZT7LeRmZXLONYUtSDrqRVrOwns9ZXUirES1cWHqSmm5IXmnBcNYDXaWiTF_
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFhDc79bLlL1Pk0n8tbzlq1olyfrCFnjmCvG-Ltikuh4YPMznI7FKOxH7yRuOpPmWhcnUqQsiS0KKkX1E22Z2setNkG6gpim_O2tKtuyu7WB2SxwtTuvdywPZOlRX9-sG9KMHCLea124Ea819TE7UkV_6Eiq-6HqmIOmP6J
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFuNxCKNHiomRNU7GBBRd2OMv4wjHPag6J78UBXS1oJv6s8GMUFdljNLO8UcEMTlLngrkc_Qrw4F3VMexwnzar9VzhliCCCtngnZUX_aJIc_0pfDuw1GB0cf2lfSm8wxsXV6C_ZBf6YPz8f8-SQno-C5DkbyG6NkzWvWoimn9r-fOKOH1Nbzp8aZeFSqjXk0D9gaa9fLh66Ef9Cm5j4KnP-uRHzJPI=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFvPS-sMdOdHhaqdfewWUelnAj-Fas3NeYDM30WsdRsVqWZXr1XlaSs3Pf54dtq63PXJTl0l3l_PQ9Rzdud2eNdXAFiYsLwvnxZ_4JZ6-pVGfmYMXi26ZeI6NqFiffOal9Gdaaezzyc7T9VXpQN
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG8AzFS0Du_su7pt-SNpud1s01BxRdoipBkEl3qSdSMhkTVfjp7yfJLr6U_y_AeOfelKPBOUG4oLKf2Ms-1ODDYIWLN9lVVq5AMqbQw5IkJ8tnyFesOGAACOj1-NAwMPHPHfSir65wMlWx0KeVsLTKO2l2xsTTjip3zL5I5FzHHo0X0o8mPCvQR449xi-6fw3p8FmobZgFBJw==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGLywuanXVzW5RKzhp2PUV9Irpd53t1CYIfd_jHmVU30WDhFs0NtIzhFe-uaSxxzbGOqy46AR3NNuE6c7BYCCmu4hEFtJsvoMgUeA_VbxTkoNPIhcAQ55WhZEinHMjjVqsv6ENBwDnuEB-ucNf_WlGOzi4KsBHnk4i2m1e4PdC8M3k0
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH04Vu3ok_hf2O4w0MxLUyjLAMZ67lq16i9eJZhkaZNn3J2avdvFlGr_nMYWUYwOexQ73cJgEBAny8oHbvUbMihKIgDcVaZldPWNM2Gd6t0CofaGebQF5Z6G5vYJ48jm-evogAi1EOy6sTLrB_dFeRp26tE9hkliqlbRJY=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH0ZxjYGOR5GY4xmwpyuHrO5vrGX-OlzrGOYyOTcTiN59UoA7Pf4SyShr_WlFooppbwDB226WX0ZtZIsr4pOEzL9smIIUHzAfD5qDS1eDUvXYfDSR3_zMCtugqpFTdR2vd7amYFe7rRZg3wdEzS7Dv1yInbntYzTVM_wVlFJRP3gUgpuHpkRxpQ
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHShgLg7mBg0GBWpZvcdAw-iWFHxU-nTREk22D5_qAY8arOXscixl9kGV56Uxh5SN01sTaXJwgOGReMSF5WZJaxqoxK9SIsil77Y3_NxIgjgUptJaLB4EiMTtXHBq4OfAb7tb4lR7784P84UZzTJWdRzncRyRgJWSw7zhatlZ5C9kVdcypwgXYdiQ==
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWgv7kumoMP73ft8t6unWR0ITedBkFOftviZpdmG3bUFl9pIBR2FwfhqP5QnHxV4UlWwyppMfLzyIR12m907PvAu4M9Pg_BGfqG_5d0rNWiyS6Epte0yHM_E97S2Z2ms06d43UOpZ8Ss_Xb_dbBABcfv9s5To=
-https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHcZqQDAmo6sPBXMG4Na0vC4cpzY0NapmQ40eiI1upiyIrdUswP39USR8KE5cUogzavNxOsECKjhTmiIOUCX1lMAaKf5eme5SC8Rp2LOhtdHRTKoZglgBnTYcmTGSMvOqu86WGcp1028mrIL7KB3YMLChG7o1_tAvdYBFXU</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BT-432</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>vintage toys</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Assorted vintage Pokémon plastic collectibles and electronics, including Pikachu figures/banks and a pair of Tiger Electronics Pokémon Walkie Talkies (Meowth and Pikachu), c. 1998–2000.: Tiger Electronics Pokémon Walkie Talkies pair (Meowth and Pikachu), Large waving Pikachu molded plastic figure/bank, Large sitting Pikachu molded plastic figure/bank, Small Pokéball toy, Small Pikachu figure</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>$35-$75</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>grounded_search</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEM3LlU-ITCjjuuvZFz1Y4FL9Bqu7AOg7IgwNwWefPddCIHGCrYb8TfFL1dsAlz2jXtRiu0ZPV5NxYuSdEAy4zLuN6uwAyzohnKZTnKaYoxmgBpcvGkorcgAds4EU4c-S8=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEYiP44r87-AYHD6AxrkNlcdZfzJJ0vcixEh15xLPyhwhT0aPKf02um9VoJN2pOluufQMQenNjCQnlmM22UY2g7i9fgosKS0ZiDnDxJcBxXvsW3LfD5u7toGm_-8n6qwtU=
@@ -3400,56 +3315,56 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>BT-434</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>vintage toys</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Vintage Lincoln Logs canister set (Playskool No. 891, 125 pcs) and Original Tinkertoy canister set (No. 116), c. 1970s</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>$33-$73</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F45" t="n">
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
         <v>10</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G44" t="n">
         <v>11.5</v>
       </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J44" t="n">
         <v>11.5</v>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE6YUHM4T3pE704OHI-p4Q8a-GMbmhtQpu-3nvrSUJG4sD_JwUx2NXW4EQAjFf9PjqTDgIP9OLZswe57OBhhF1AoieBNRV7MG7bwmtxpLEguspIGleJ-LkELK_l3Lq3-BI-8hJLMXgdSJ12QTQuQY8M4ToigwUyqsCgk2xf01uR37XZpuH2BwFr5zuQ4C3vP-k=
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEfkXaL0UlcCej1_QcOMc_ALOTjkfos6yUlGR_6gZVoF8IEC9Ruwy3XZrqQq7F0I1odsdPN5Ynh0Vx2iBcXmv4ZNPv_eWzZbEDEMv7n5N_eef8Hyf5snSe8pmPeTqak5Q==
@@ -3478,56 +3393,56 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>BT-436</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>breweriana</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Vintage Hamm's Beer 'Tapper' aluminum draft mini keg dispenser, manufactured by Reynolds Metals Co. for Theodore Hamm Brewing Co., c. 1960s</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>$20-$82</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
         <v>10</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G45" t="n">
         <v>11.5</v>
       </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J45" t="n">
         <v>11.5</v>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>AUTO-SEND</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>grounded_search</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFfyS_AjMdJ7apj_qaM_MCW6CRJ2mwcr-8HD4oU5wNlEoYIdOEjorw7NBTzGibQswWSwXfaoXk8XsOA-Fl1Y6FUgPfarK6Us5jC0BRi7Z9QXB1tB3fK-U0c7NoEPSBiadp5jsaiqket31ATuZw-CnqkAjwY_-QHh0s1BSnJSQSAzVoh4jz4TsFS_T7KYL0UrUBtcg==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG1CRtbhmjEgqPhm2GWUyKb_u_vlAU2BqxHbgaRRBAVahaHKZ2oY-2HfApY1u-djHrnTnxeg5txQCW4WuH5c2E-p7lFitpbeB_vyRPU5G7S1eyTZi5oCzQmoAA4AUEEJVXz56gTRnpUQuaY0QU2xGQLdlhQdA==
@@ -3539,6 +3454,105 @@
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHpCaZhp3ls8M5Bv-IOkXyTPLfYrUP0JhOzLi7rjKGr4Ikh3OcpCw7im1yzVC6GClcYIwsSpVN7b2MSWr5fgNYEUFd_mjRcVA_ih8Ud3XpuBPOakJrbxqMWC2ETPlXcgNv3o71BdDxW
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHr1PdQaW_MFHkn9Vn9WYZn6AdoCZkzkVBxgHsSsqkNHWi_4bEg2752Hcttmh1j3z5xOJDKkKhZ25kYdpNwjCLHpuuthwl8Q6oOolP2p3TwWkZ__azOHTpwGNR-r61kRElXDe5oK9TFe8onXt_nC6nimg0cglXVMQvAJ_MS14kKch8_N9f3_KNWIFLR6bQw-cXa-g==
 https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHxC4Ng0wFeMVcEPXl3Zyk3ZSd4_g3IC-WnYLaYaFRlA6rkyqh8hkEoteffKsljPlPRI1rOeN5g0QAb6waf0Gg4jt1PFTN7ANMELDh1UWG1PE3Ae77_e3ddZxwvP9XgwB8qEtEQeT64pgx8QRaK6h8H0z5Livka8Pwktu3MULez_C3qhg17GNZgl7GVv9nTKQ==</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BT-443</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>vintage toys</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stack of vintage board games and activity sets, including Gabriel Take 5, Milton Bradley Skill-it Frying Pan Maze, Hankie Embroidery Set, Selchow &amp; Righter Parcheesi, Milton Bradley Battleship, and Skip-A-Cross, c. 1960s-1970s.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>$35-$85</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-SEND</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>grounded_search</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQE1Yv7duOZFqRGk70uhdteLjr9mZ3S8NmJxmrh47RATFyrJjnGqzL8yneQzzb4jTVsa1-GJBc3XjiahskkWBMokbmJNhL-z9VSYjsxLdweo1bImhSNeeJzmZ62Sv_L39UA=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEFn6EQx3Ww0qQUUsLdetQy4pWA65EWp68tZQRn3rTtgMp2jblmNQ8yee-qbBiTl_EjySQu-JclqZWFx92Km1XRB-T13nkfPBjuZtB0qTwjRYplw7NZkdNQqUFhjx_VuAc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEHeiROUhyCRcv6_XA6_qohU-HcfZQ5zMGBaBnjcN4_PEW0LHisym5Vuo7kwVhzi8cXp4A2pCfaxqw8P61Q7xCrha1oXRqRrOBcr9_k_B1Qy7g4SEP_LfbMj_Q1iv5ZzsOUwbVJwVBcQ9vcLmQbBoFwBuULNxOcvjxaAnM5dz3xgXvMYDae-q0zdQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEKK_HZgQf3WmAen6CTAJyAKZMVJBa8dPrJSbZIoUKGVR5aQNT6kwxa1EPHdF1RYamv_p3uMj0yi-LapnU5THn8Pt3tXg6K9l3SsETnot8kkl8Uu5ezySdgIVxArnZEwkqpEMLOLYpVceibYnHoRpsXHMsNksRUYhBcbg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEQKgE9POltPheUo8vXbZ3n-bNEVvuP4Hen7b3iIjzsxbE12INZQ_99KEnDEN9W_I8PbSWaTAzT8TN21giPoIqGAiXr9OX4ytQVqjcR7Hc32QaBMnpz6BNz1gktiCN7_oQwZEgLe8e7LBre4ouO7dBDUg0-
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQESCVZoSvBZHJhzqPFdSthD2CHxq5dVckVYY3Io4XeE8tL2APOnu1r_kQwnU83m9zoC9oVMtWXGXXt3Jjs2atverbxY58NSNYA333TTNfCFKGpkzUDe8mhfK_iUVV34EzgYrJBIP-2VAhyILXzBDJi-M4S9aMDn5IC2hTP56CQRvgj8EhWARcfW2zkEhFNMnG6xXF4VqYs8aNSVBnLLwA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEeJuf7DSgKvZZZX0bKd6YpxZUn3tDbDUz2MmE2OLu51ho1J8N2dllxe_Jji-V8_1kDfiqWbHdcNGt_fUm8Pdm3dppchYuZlDT_scAN0vAB_xFQdpUMkv-KQ8V43RrA8wU=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEg1CRSmtkHIH95oZduuT-fRISL4EhzQ-kIJiDDxXmik46gI131PvBusTsy58B9Mmdh5HyiJwfF0H3nerlzhNZk4SNuRYE-RAGsNdINXR5Cn_2wdLW_-VKDdM5hwCO_X5F9dRMSZQIRlA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEgpSUfpNcqYx3tGzUmLNBa88ywI8E2juGBa2a8LgR-KlCs6vD2JGQAjZHWTRtbSWv-UYOqncglpheIfVBNcSYQvZEIh2y2AId0AUP7a0xIksSuxQ4GqEZMBuTN-oOWSj0tU6oIpjXxLqbo_luyq_ZOsp2OuAVBJstXu-5dkH2-dOYBEVztaB8=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEizWRCx7ptwNdutdCRKCzp-dtf_ZSgZ-u9LPX483_6X9CMIp5bS47GPq0BNMt6TOjSTFD-m3WVpdHZKShkxZT2epOTwc02iPUIrXlIpAznTsm6qofvNpljx0--B0UFVqpYWZmAUfz7GjK7jiuVzVA5M6-E2f-5kBonONP0VYIPKZ1akuN1i-7VoeusG8M=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEltGIfY5_UxX3MC1fRsRg82_RogL1Hldq5ArYa5wL1p6ZduLXeaHcWIbStVwA_45Wm9I_XLEUMyZhzEuB0Bnp5VKRBNWr9vqDqqNb2PQvcy4aCmA61i3H5ZzXhTs-YdUg86IM9C2Xx2qH71-NdwEOzFDhHSKsAjzlNIA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQEvrQjv3Kte182Mf55G-74kngjwSb41PSw1dpvRe-6Rf9Fah6KkqdT8bErjwB16_aaCRLVnlcg5IlyU0UZXmXQ9A8kniQSH5y_xmIR-kfV2ef1NZuNPDZdlqFrYP9S1MX5UBteTqFgMvyxPcTm1ina_fP41m-MzIbQdJR1djBPJsK14ldEVsw1goJbup4O9XYnZXw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF0SAjjv1X-n7nNVHn_RytxE8r5cjPbksJgYD_QpVblbnkQbe1rUMJAR42n11aIwOIYW8hupSX6z_l0fC7xjVjuGpd8_8nii-mpJ9AMpzyO8UFg4mj9RkZ_JgNatQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQF6BUr8HUOm0FxYdO_xIwXSD26rJfgWZAsCwWKZWhQMNj9BvaYznOdzNXKEZ17TtZhfen2RL8Vx6HM5pjlUjHD1Qs6MT0qalwJG1RLMYfpz3DECCTyqPnffUq0RsDLTRfc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFE1Kida7DzVApXejtjfutDY85OIgQYFcrkbGODR3pEi663nn01s8EprgyHpPVldgO5oN0u7jJm9jE5WaDgizqmtCrjw_4uR7BYCffE-W7w53EKJ3H4E21m5EEWkjhShZw5byE6YldybLkzNgabkLENxNY3sTBUF0Q44XmpYOrm3y_IPVA7X0VhdzI=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFMSXVEbJV8VH46PVKjE2jiDjyXXfAjCiSmlmC6UYOBkAssTkat1TJ45xoSPeYNV1PQxU2rjbHuF-ROk2iNu7WZcETaGmw8YjvakIGRQZmmPlFK9s78qGxq3NnPZqk41QBRFb9cghILV4vl3pmLIHnq0YNbLZbytaiZMiYC10XHFFfUtG_eHj4bUkI8bke8I-PJtQJ5GZoAHU3OvQkKdOiDEgSPWJuwDrrCijo=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFMv2bQzeQWesd0yypFFlYIqDlb1XZLUPxV5yJq7QwwkRfDVBKnhbkwgveU6PXDYRWBh_TKEKrS8N9eCz-Y0yiKYLQrTmP59Z9LXMlynsAJyejUJukv4LmC0Sdo4B2hAQOHwZMnn-07BRe9WqJNE2MgjcaOdgVdRF3Fb4r-DKr0pT4UJ7vs8syoUw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFNmpI2OwXyA_B722tzgJ4rt1dQxCzkjlwmK5foSkKbyBPygGiJQ_r7oK8Fc7SIe4gVpRl8cfy7r-peRMo65rJ8nHfdPG2z8F_Jtgz_HilodnyZsvi9bSHuZc4pjw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFajfzFL-ZwXiuj_7WkCgQ5R-CvPwCcEEl7Si1pKsvyVjlTia3tokncTuSY5mZsGH4YXXzOuZtx4A9e8GaS3hlLKf7CmZZXNBX3mLN1MOK2tnl3a1Ouju_p1lRM1sIoJcbaQ0y1pKKAmPGw-CwkxKuVkvsvjC2rmOLAD80ltsy5_B2cdfdrUjsHlnordfrdXtx60ibTFqNkjhAuDL18jz0ttrPDePY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFqUkV26pOqi9hTIKHJCI4SWkomsAC3eFf0cjnGIA_BQy7PZzUCNM6MENaqfeZkmVnFXg8qVpOcB4uF_CFoV5dhXl6VbQm8WzZQHQfp5RXP2HxSNlu5xI7gmBjWV_nAYbZKmvW2ZoOGipFRTtnOaWRGRaOj
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFritX0Ykf-VBzZubzlTy3EA7YiwzzGskYISve0XWJua-qA0iMakkfqWi68cED-uDGkKVIBOZA7gfOQ2thRfmMaXPS07tJ8MGt5KTYkajdviLcfGkiWj_HCcppw47SXmKOJy8SjBZBh4hsGfNfipuyOoX8pZAvsKcDKZNpmbNEuLEYAk7b6mGaVg2v8
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFtKoRsDE6iqgakv0sB_JsSzwQrzxajN6VoKppeBs_Veg1R4KoBpVaZ3rYU6lLLlZd5YAHFy1bqYGx9fvxpqcVRARM-ev3k-F2lUBRf4H4TsNwelEUeHyFnQO0-pZRtMD4=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQFzb-IiG5WIL9r6UmTEswghMTjExycMBUjNCdkIybq4F6wGeLSfAdpNP9yaJijrKo13P3gF3jtSOdDF-WGqu4pSECiWjbhcR6V-spY7uY8PD8PAFGJEpfH7ppWC-qv7B4hm_XBv0vcfqfDkIJS7ipwD-7RAOTs=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG-XyO55bDXX9df2TGQurJI8PSnPBoT1cwPf7Hm7U-fYokG4YKLgokht5PQwwMjJ1-RDO0YnzTwWv_GDNVChNdV_bi3diDUI0MHJ3wQ-ippDfKk1YX-wpp08ZK8Y9twh8RLXFab4wXEou9q-p7CuzM7DIkC5rM9mA5bIrEy8kLfn5GlHKwmciDZGg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQG3SAKPjfZbk3IMe8d2xHzVjiI4iu-6FOsWHZ8ip55NcsDvpVkjX8GZ_yXg4l6Wva3sjkwyKTKG1rh9T0qHj1maKl61jcQ1saJq5sJuVeeQPMbyh1rG-ibgi7N5ixXRO7twPo_jdTGHL-nWRiC9dOmzXPyFVXp88EU3r8hMxp-xVnV62zCJAg==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGAc53-i07w6zf-tfjx5DgptLlmpBhdD4ZsgViojKLDZbUDpB16eEYVKHkbQ_LT12mdDSgxbK-2rkG2D4EelQ_MaeUcYQW9R8yx_6fgFWqsLUDyE92LtOyqoBHpSZXTfAc=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGEiNOEoNC356KCrtPRMOPfB0ZYurI15ycjVJHxIEB8YzjirGRFATyBVHMBbTtw2N6oAMob51ANeNqnAsDZ9ZkOYxMrytx6JZ3k_SlMlV1UJsfX1aWGyLgSAp1EWeYAdFNaczMQd-KAUwTOHl9A_Db6L2yAjJAW9y_3i1l1hNEHYaLeSrVD3kLMRHzfwCPksPZ1SeA4Tas7LwMWg_pTbw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGGRyqefZWUQlXRHy5fQewkx7f3_fgxDzFa3FYNrYd-O2iFMAFhZLF3vSg2UJg-hIwGcqD91vG0y9GyBqCtHxKf61ZklN8yEowcqfEKEIwMuoL6r_SfeKfXIo-Uf8kv1PE=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGIjkrK-In7vKrX3i4eelH5IsU4F37lFFDfXv_tH2s70avTsxAGwILdpih7XnFVmT9MyDkt6jSEwvWSP5SCs-Kd9Mr0JjPCC5Pgp2bBEvmAUvQvxKejXLnv7X7ZQQ-UCpQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGKXSGM61TPcr6JE9u95U4BrZwi7jcwyUBUOQ61GNm-TBz7qW1ikC_e04WrrucbynbX10Dyo1sbfNAa7ZSGRYJ78s9Y8CDifG9lPcmxbl8fgDEOxmeOYUvXjWvLCJKUjTAWXGAJUKXcB1hyPtuoOj-9NS3VpYCaerinHQb6qA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGNcn6tStB-7JooKW3xbHZjhONFexhmrdOWBIBb5Hpi65XzmoFGHkZGROxaUKREz9dggzaVB_c4D0Pfzxu7-lgJev50FOermoXpQkQ_yKzocYw2v3f05sglxxMOVWO8AW0197yzubwEElh19-3ZKgmA6crM61LWoYaFn3drP9J_RQwQXLDj77RpGtIC
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGXN90ukyXoxLLo3dwGiw6BjdC7JCibhhWH5rkKm3mRZH6RCtryUD-HS3ce0T_h3dU_8gvPn-S_bxqUcNRkuJnKBaELFrR-E8TjRr4ib5IRwx7HB_9D41cBZzevENb4GmNIi23iwGkGmK7jfpz1rs73GpMCx6jzKRB7qVFjUQganNqNNmlY_2KLKaDW3U_KnytAaiQ=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGXv0ZBL7VepNgFZJajUMsSWJWN3O8zc1DhRc5djtEO-PBmNeluJkWFAzEYPW0s2lscos3qTUczbvIxDWL2QxMwNiKA-TOPkkgT5I0vbZ5J4hOOL_zRRdbkIUXwAb6kCDw=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGY4z-b2hA3Oj5KA6eZ6JflfnX_nVCSXKxjEeNgvgbRL2O8Z49pDEMfNzolfF5QAErw11_6hAA4k25ROs2MDVLrftyjd9tZcAUBW0R7t-Lo1r8fY9H0dcNAF8MGF4t7q2KwQXQLEk0vW9EgT85uC1HC51hAwziyv__oQDUZ_Snj5ALEpic30FB4PZ8ICTb2gr_vDg7VSxvzvl4fu-GRQtYJ1gybqsxdbl7jUTaaM_qaifGN
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGnICVL2LiXe2u1A1_ybAls9GAApmqKOx-KSi1n6WpbbQequZIDEOW9p-j9Um9XjqzHhNwtuLpcdOspQFPuBTwFYEGGeyV_mraHFEOxdRRAJsYY56JeF3aiyUNV_9HNeVH6f1FRlTjD0EBtU_HveXV_gKhyEwBD7bRjVNLPRw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGpFZsy_Y2Kyve0SxAgp8lGoIumpN1YCsmIzfvFf7SdfAPdCwrsqhn_CxPaLyD6nZS2x5OTbiKfTuDWh4hextoUbY3smvW-W1i8eZZRFUHq_i6oDZ9d7FrD4C-K1px2cNY=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQGsovdghgrfYS0Fi8eoYZUgOJxHF4DVPzJ6bW64ViDJbijotbtjcz_zs5TjnI2uCk8U6K5y92NcUeMTwMV5wwimvAlomh_IylpIE_8fCAneNB-sCR4hrDrhdE9198_K65I=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQH6KDj2WXxeL_cnK-3YJfwb9UFVm-MOpOWIbJ85MErLtgFnrVHL1b4k1_xosbDoHpkruL2IO-MuGIzA68xdwZVYbOUigf7g_SzP1QltvfvO-HzmTN2JufHZNaOGcY2cmmFHGUVYDXFgqR40-ef1hyTLcz0xrVMZLfMU1MDk2Z39YLDm04JF
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHM4puQtzFf7j9TDpTEc6us0T_UPo4eQcl8lxsgROTpjEWFZfrgIINBgWcPSitJB-vDVb5tdiWe_bycpkp7DNrhSEcVgc9vtYjcwx0px2Q_BpKXlm1L76YxwmVFgp8m_pM=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHPzDiRlsehpfioEkkcL_1TvHfupZwJbOPkPr5DFBYBM71nff_8P07uTkHKvoyfljeegl4LpdmzLEWMomoYUdZPRaGfXTIV3n1VtG7DxJM5fgHJrdMtFqRdlNPnNeZ71Q7jc5CS-5pWz0eSXOOfQwUXkUOzRmvM2r5Xuw==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHWWiPSxIbCaliRcXZC7hbd5fSnqxeREx58X3pl3EBHltMD87PdRJuIYEc34JQegoP_I02nOq9kr2auXNIJFdeaMGrtj7R3F2oIPd3Cp4tYpGu6YHEXZMEMFQiuYAQ7Pts=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHaZXnb315CIC2sVo_HK_O6PA0WYQVhRz61gMNmBZd1e_B2k0U-2MqI0Get4t0OB3066JFn3gijMCjfNZRxn15ftZKVALtrt8BmqtILYIA3muzZN_ARdHtWm5TWh7XH3fLhnpOxRlykJqryIr9DkxLUbW6fcoVuOL-aEnlmW4b1pFv5DpMAaAr3Cl3AjUEys_IA2md8Gcbtbg14H7f5yFcn32eysVQ_RyyIxIeOSwjwbQ==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHhqciieTAEfSMjpK3MM9aSr6_djzMU5DY7mv7TSq6t3BZNn0YyQxoM4d5KTXE6gaXe3n8KJcW5qs53eeDQ5UBlMDptQZAfVw-Fx5wJJqB5n5Kck_QEMhTvbVLqtZUMfew=
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHiiNzeOgiuNVs521PlySuvRULV5bOl81hwL69yYp6SJW5g4B7m3lyVfAae_omq4sNhUf7W3iBpmzVPxLHtnqyxtlPNh4xiUIaiKXLiXCbnDrFywdCToLacUP2Ox2QuTU5zVCPKyczQqVejX4Uq_OIOOlV3Iy-4aKFhaIY7rA==
+https://vertexaisearch.cloud.google.com/grounding-api-redirect/AUZIYQHnLd5fYssV92-cEvT3LbTlwluy7Vj5dsBWBL-FppssZRQSfhVtQfMQ97EmRP1VdUvVI22eLdejjungn5NjYhGz9BsCZHGYrJlObu-FdOIpuHVvUkA5f3bfJTyQ3nFq3ilYMjA8lf_t_8nlwVx7VYkNlGuQuQs2e-352FUBUKw3PBtfAQKlAagiYCrdo7vC1P-4RQAGtkR4AE-gCfUiMqXyoUFx48xJQA==</t>
         </is>
       </c>
     </row>
